--- a/Dataset/Stratify Dataset/annotator_dataset.xlsx
+++ b/Dataset/Stratify Dataset/annotator_dataset.xlsx
@@ -547,14 +547,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E401"/>
+  <dimension ref="A1:F401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="80" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -570,15 +571,20 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>ORIGINAL_ARTICLE</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>TOPIC</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>NEWS_TYPE</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>SPLIT</t>
         </is>
@@ -593,17 +599,20 @@
           <t>"We will seriously consider filing legal action and imposing sanctions," Posibleng malagay sa alanganin ang teleserye ng ABS-CBN na "Ang Probinsyano" dahil pinag-iisipan na ng Department of Interior and Local Government (DILG) na magsampa ng kaso laban sa mga producers ng nasabing programa. Ito ay dahil sa hindi maayos na pagsasalarawan ng teleserye sa kapulisan. Isa pa sa tinitignan na anggulo ay ang paggamit ng programa sa uniporme, sasakyan at acronym ng Philippine National police (PNP), ayon kay DILG Spokesperson Jonatahan Malaya. Dagdag pa ni Malaya, maaring nalabag din ng programa ang Children's Television Act of 1997. Sa isang pahayag naman, sinabi ng ABS-CBN na ang programa ang produkto ng kathang i-isip lamang at walang intensyon na siraan ang anumang organisasyon. "There is no intention to smear the reputation of any organization or portray any person in a negative light. The program has also portrayed its main character, Cardo, as a hardworking police officer dedicated to saving lives and serving his fellowmen," pajhayg ng ABS-CBN Para naman kay DILG Secretary Eduardo Ano, mukhang intensyonal umano ang mensaheng inihahatid ng programa sa publiko. "Hindi namin sinasabi na lubos na malinis ang PNP. We have a few bad eggs but they are never tolerated and the DILG and PNP leadership is sweeping the ranks of the police organization to ensure that those 'rotten tomatoes' will be out of service," sabi ni Ano. Panoorin ang naging panayam ni dating PCOO Assistant Secretary Mocha Uson kay PNP Chief Oscar Albayalde tungkol sa isyu na ito. Kung kayo ang tatanungin, pabor ba kayo na kasuhan ang mga producers ng "Ang Probinsyano"?</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -618,17 +627,20 @@
           <t>Hindi kinasuhan ang aktres, 28, matapos siyang arestuhin dahil sa Driving Under the Influence (DUI) noong Setyembre. Gayunman, hindi pa rin siya lubusang malaya at absuwelto dahil kasalukuyan siyang nahaharap sa isang probation violation.</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -643,17 +655,22 @@
           <t>Ayon sa Facebook live ng Brigada News Davao sa press conference ng pulisya, napag-alaman na madalas magpalit ng pangalan si Jonas Bueno, na natunton sa tulong ng mga impormante mula Davao matapos kumalat ang kanyang larawan sa social media; kinumpirma ng mga impormante na tugma ang facial features ni Jonas sa litrato kaya agad nilang ipinagbigay-alam sa kapulisan ang kanyang kinaroroonan. Ayon sa suspek, dalawang linggo pa lang silang lumipat sa Davao mula Cebu kasama ang kanyang live-in partner at dalawang anak na edad 6 at 1, at pansamantalang nakitira sila sa tiyuhin niya habang naghahanap ng trabaho ang partner niya. Gayunpaman, hindi naging consistent ang mga sagot ni Jonas sa interogasyon, at inamin din niya ang kanyang partisipasyon sa krimen sa dalawang magkaparehong kaso, habang iniimbestigahan pa ng pulisya ang posibleng koneksyon nito sa isang kulto; kasalukuyan pang pinag-aaralan at iniimbestigahan ang anggulong ito. Sa ngayon, itinuturing na serial killer si Jonas at sumasailalim siya sa mahigpit na interogasyon at seguridad dahil high risk umano ito, habang patuloy ding iniimbestigahan kung ilan pa ang posibleng sangkot sa krimen. Umaasa ang mga netizen na hindi lamang "fall guy" si Jonas at nananawagan sila ng hustisya para sa 16-anyos na si Christine Silawan na natagpuang patay sa isang bakanteng lote sa Lapu-Lapu City, Cebu, kung saan binalatan ang mukha, tinapyasan ang kanang bahagi ng mukha at nawala ang ilang internal organs tulad ng dila, trachea, at esophagus; iginiit din ng publiko na dapat masiguro ng pulisya ang mga ebidensya laban sa mga suspek upang mabigyan ng hustisya ang biktima.</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Ayon sa Facebook live ng Brigada News Davao sa press conference na isinagawa ng pulisya, napag-alaman na papalit palit ng pangalan ang kinilalang si Jonas Bueno. Nahanap ito sa tulong ng mga impormante mula sa Davao nang kumalat ang larawan nito sa social media. Parehas umano ang facial features nito, at ang itsura sa litrato kaya naman tinimbrehan na ng mga impormante ang kapulisan ukol sa tinutuluyan nito. Ayon sa suspek, dalawang linggo pa lamang ang lumipas nang lumipat sila sa Davao mula sa Cebu. Kasama ni Jonas ang kanyang live-in partner at dalawang anak na 6 na taong gulang at 1 taong gulang. Lumipat umano ito sa Davao at nakitira sa kanyang tiyuhin doon. At para din diumano maghanap ng trabaho ang live-in partner. Ganunpaman, hindi umano consistent ang mga sagot nito sa interrogation process. Dagdag pa, sa dalawang kas0 ng parehas na routine sa Inamin ni Jonas ang partisipasyon niya sa krimen. May mga espekulayson na ritwal umano ito ng kulto na sya namang tinitingnan din na anggulo ng kapulisan. Dadaan pa umano ito sa pag-aaral at imbestigasyon. Sa ngayon ay tinuturing na serial kiLLer ang suspek at dumadaan sa masusing interogasyon. High risk umano ito kaya naman mahigpit ang magiging seguridad rito. Iniimbestigahan din kung ilan ang nagkaroon ng partisipasyon sa karumal-dumal na kriMeN. Hangad naman ng mga netizen na sana ay hindi lamang "fall guy" ang itinuturong suspek na si Jonas. Galit naman ang namayani sa mga netizen at hangad ay mabigyan ng hustisya ang sinapit ng 16-anyos na dalaga. Anila ay dapat maging sigurado ang kapulisan sa mga ebidensya na makakapagturo laban sa mga susp3k. Kalun0s-lun0s ang sinapit ng biktimang si Christine Silawan nang matagpuan ang katawan nito sa isang bakanteng lote sa Lapu-Lapu city, Cebu. Binalatan ang mukha nito at tapyas ang kanan na parte ng mukha na nagdulot ng pagkawala ng kanan na tainga nito. May mga internal organ din itong nawawala tulad ng dila, trachea, at esophagus.</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -668,17 +685,22 @@
           <t>Matapos ang limang buwan ng konstruksyon, 100% nang natapos ang Passenger Terminal Building ng Ipil Airport sa Zamboanga Sibugay, na sinimulan noong Hunyo 2018 at natapos noong Nobyembre 2018. Bago ito maitayo, walang direktang biyahe patungo sa Zamboanga Sibugay dahil wala pang paliparan sa lalawigan at kinakailangan pang bumiyahe ng halos tatlong oras mula Zamboanga International Airport sa Zamboanga City. Ayon sa Department of Transportation (DOTr), natapos na rin ang proyekto ng pagpapalapad at pagpapahaba ng runway ng Ipil Airport. Kapag na-inaugurate na ang Ipil Airport, ito na ang magiging pangunahing gateway ng Zamboanga Sibugay at magbibigay ng mas maginhawang koneksyon para sa mga residente ng lalawigan.</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Makalipas ang limang buwan, 100% nang tapos ang pagtatayo ng Passenger Terminal Building ng Ipil Airport sa Zamboanga Sibugay. Nabatid na sinimulan lamang noong Hunyo 2018 ang konstruksyon ng Passenger Terminal Building at natapos din agad noong Nobyembre 2018. Dati ay walang direct flights patungo sa lalawigan ng Zamboanga Sibugay dahil wala namang paliparan dito at halos tatlong oras pa ang kailangang bunuuin sa daan ng mga biyahero mula Zamboanga International Airport sa Zamboanga City upang makarating sa Zamboanga Sibugay. Ayon sa Department of Transportation (DOTr), tapos na rin ang widening at extension project ng runway ng Ipil Airport. Oras na pasinayaan ang Ipil Airport, magsisilbi na itong pangunahing "gateway" sa Zamboanga Sibugay at magbibigay ng karagdagang connectivity sa mga kababayan nating Zamboangueno.</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>economy / business</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -693,17 +715,20 @@
           <t>Matagal nang usap-usapan sa mga kanto ng Barangay Maligaya na tila may misteryosong nangyayari tuwing Biyernes ng gabi sa opisina ng kanilang punong barangay dahil ayon sa mga residente, madalas umanong may mga itim na sasakyan na dumadating at mga taong nakasuot ng itim na jacket na hindi kilala sa lugar, at pinaniniwalaan ng ilan na ito raw ay bahagi ng tinatawag nilang “Operation Midnight Ledger” kung saan sinasabing personal na pinangungunahan ng kapitan ang pagpapalitan ng malalaking halaga ng pera kapalit ng pabor sa mga kontrata at permit ng mga negosyanteng malapit sa kanya; dagdag pa ng mga tsismosa, may mga pagkakataon daw na biglang nagkakaroon ng bagong gamit at appliances ang ilang opisyal ng barangay, dahilan upang maghinala ang marami na mayroong lihim na sindikato sa likod ng mga desisyon sa proyekto ng pamahalaan, at ngayon ay patuloy na lumalalim ang hinala ng mga tao na posibleng may mas malawak pang sabwatan na hindi pa nabubunyag, kaya’t marami ang nananawagan ng imbestigasyon habang nananatiling tikom ang bibig ng mga sangkot na opisyal.</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -718,17 +743,20 @@
           <t>Pasado na sa ikatlo at huling pagbasa ang panukalang batas na naglalayon na bawalan ang sinuman na magsagawa ng "marahas" na pagdidisiplina sa mga bata. Layon din nito na marespeto ang karapatan-pantao ng mga kabataan. Ang naturang panukala ay nakakuha ng suporta sa 160 na mambabatas habang 2 naman ang tumutol dito. Hindi naman nagustuhan ng karamihan sa mga kababayan natin ang naturang panukalang batas. Ayon sa kanila, didisiplinahin nila ang kanilang mga anak ayon sa pamamaraan na kailangan. Kinastigo din ng mga netizens ang mga mambabatas na sumuporta sa panukala. Kung kayo ang tatanungin, sang-ayon ba kayo sa panukalang batas na ito?</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -743,17 +771,20 @@
           <t>Usap-usapan ngayon sa social media ang diumano’y bagong patakaran ng pamahalaan na naglalayong ipagbawal ang paggamit ng sariling cellphone ng mga estudyante sa loob ng mga pampublikong paaralan, kung saan sinasabi ng mga opisyal na layunin daw nitong mapabuti ang konsentrasyon ng kabataan at maiwasan ang pagkalat ng maling impormasyon ngunit marami ang nagtatanong kung ito ba ay hakbang para kontrolin ang kalayaan ng mga mag-aaral na makakuha ng impormasyon mula sa labas; ayon sa ilang viral na post, may mga magulang at guro na pumapabor sa polisiya dahil mas magiging disiplinado raw ang mga bata, subalit may ilan din na nagsasabing baka ito ay paraan lang ng gobyerno para pigilan ang pag-oorganisa ng mga estudyante at mapigilan ang malayang talakayan ukol sa mga isyu ng lipunan, kaya’t hati ngayon ang opinyon ng publiko kung dapat ba talagang ipatupad ang ganitong mahigpit na regulasyon sa mga paaralan o ito ay isang uri ng pagsikil sa karapatan ng kabataan na makibahagi sa diskurso ng bayan.</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -768,17 +799,20 @@
           <t>Alamin mo kung bakit trending ngayon sa social media ang isang misteryosong lider na si Brother Elias, na sinasabing may kakayahang makipag-usap sa mga anghel at magpatawad ng kasalanan kahit wala siyang kaugnayan sa anumang kilalang relihiyon; ayon sa mga tagasunod, kaya raw niyang magpagaling ng mga maysakit gamit lang ang kanyang dasal at tubig na pinagbabasbasan niya tuwing madaling araw, at marami na raw umanong nakasaksi ng biglaang paggaling at milagro sa kanilang barangay, kaya’t dagsa ang mga tao sa kanyang maliit na kapilya para humingi ng tulong at biyaya, kahit walang opisyal na patunay mula sa mga awtoridad o simbahan tungkol sa kanyang diumano’y banal na kapangyarihan.</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>religion</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -793,17 +827,20 @@
           <t>Mga kababayan, may lumalabas ngayong kontrobersyal na usap-usapan online na diumano’y may sikretong “shadow council” si Vice Mayor Ernesto Dela Cruz ng Bayan ng San Bartolome na siyang tunay na nagdedesisyon sa lahat ng mahahalagang proyekto at polisiya ng munisipyo, kahit pa sa papel ay siya lang ang pangalawang pinakamataas na opisyal; ayon sa mga kumakalat na kwento, tuwing gabi raw ay lihim na nagpupulong si Vice Mayor kasama ang apat na hindi kilalang personalidad sa isang tagong kwarto sa likod ng munisipyo, at dito raw nila pinagpaplanuhan kung sino ang mabibigyan ng pabor sa mga kontrata, pati na rin kung aling mga kandidato ang susuportahan sa susunod na halalan, dahilan para magduda ang ilang residente kung totoo nga bang malinis ang pamamalakad sa lokal na gobyerno o kung may mas malalim na agenda ang grupo ni Vice Mayor Dela Cruz na patagong kumokontrol sa bawat galaw ng bayan.</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -818,17 +855,20 @@
           <t>Nagulantang ang buong bansa kahapon nang biglang kumalat sa social media ang video ng isang sikat na senador na diumano’y nahuling palihim na nakikipagpulong sa isang misteryosong grupo sa isang mamahaling restawran sa Quezon City, habang may hawak na sobre na puno raw ng pera at mga dokumentong may tatak na “Confidential.” Ayon sa mga netizen na nakasaksi, tila mainit ang diskusyon at may ilang beses pang lumingon ang senador sa paligid na parang may iniiwasan, dahilan para maghinala ang publiko na may nilulutong lihim na kasunduan na posibleng makaapekto sa resulta ng nalalapit na eleksyon. Hindi pa nagbibigay ng opisyal na pahayag ang kampo ng senador, ngunit may ilang political analyst na nagsasabing maaaring kaugnay ito sa umano’y planong pagpapalitan ng posisyon sa pagitan ng mga kilalang pulitiko para mapanatili ang kanilang kapangyarihan. Dahil dito, nagkaroon ng kabi-kabilang rally sa harap ng senado at nag-trending ang hashtag na #LihimNaKasunduan, habang hinihintay ng lahat ang susunod na hakbang ng mga sangkot sa kontrobersya.</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -843,17 +883,22 @@
           <t>Inaprubahan na ni Pangulong Rodrigo Duterte ang joint resolution ng Kongreso na nagpapalawig ng pondo para sa mga biktima ng human rights violations, na nilagdaan niya noong Pebrero 22 at inilabas sa media noong Pebrero 28. Sa pamamagitan ng resolusyong ito, binigyan ng kapangyarihan ang Landbank of the Philippines at Bureau of Treasury na maglabas at maggarantiya ng pondo para sa mga claim, habang inaatasan ang Commission on Human Rights (CHR) na tiyakin ang maayos na pamamahagi ng pondo sa mga biktima o kanilang kinatawan. Ayon sa datos, umabot na sa 11,103 ang na-aprubahang claimants mula nang simulan ng Human Rights Victims' Claims Board (HRVCB) ang proseso noong Mayo 2018. Gayunpaman, sinabi ni Executive Secretary Salvador Medialdea na nananatiling mabagal ang proseso at paglalabas ng pondo dahil sa mga hamon gaya ng hirap sa pag-interview ng claimants, at binanggit din niya na si CHR Chair Chito Gascon ay miyembro ng claims board. Ikinatuwa ng ilang kababayan ang balitang ito, kabilang ang pro-government blogger at university lecturer na si Sass Rogando Sasot, kung saan maraming netizens ang nagkomento sa kanyang Facebook post at nagbigay ng kani-kanilang opinyon tungkol sa aksyon ng Pangulo at sa reaksyon ng CHR.</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Aprubado na ni Pangulong Rodrigo Duterte ang joint resolution ng Kongreso para sa pagpapalawig ng pondo para sa mga biktima ng mga human rights violations. Ang naturang resolusyon ay pinirmahan ng Presidente noong February 22 at inilabas sa mga mamamahayag nitong lang Feb 28. Sa pamamagitan ng resolusyon mabibigyan ng kapangyarihan ang Landbank of the Philippines at Bureau of Treasury na maglabas ng pondo at siguraduhin ang bayad sa mga claims. Inaatasan din nito ang Commission of Human Rights (CHR) na gawin ang epektibong pamamahagi ng pondo sa mga biktima ng human rights victims o mga representante ng mga ito. Umabot na ng 11,103 ang na-aprubahang lehitimmong claimants ng Human Rights Victims' Claims Board (HRVCB) noong simulang ito noong May 2018. Para kay Executive Secretary Salvador Medialdea, mabagal pa rin daw ang pagpo-proseso at paglalabas ng pondo para sa mga claimants. "It took them so many years, natengga, kasi mahirap daw mag-interview," sabi ni Medialdea. Si CHR Chair Chito Gason ay isa sa mga miyembro ng claims board, ayon kay Medialdea. Ang naturang balita ay ikinatuwa ng ilang kaabayan natin. Ilan sa mga nagbahagi ng ulat ay ang pro-government blogger at university lecturer na si Sass Rogando Sasot at ito ang ilang sa mga komento sa kanyang Facebook post.. "Langya, iyan ba ang presidente na Diktador at walang pake sa Human Rights? Mga salot na Dilawan talaga kahit kelan," sabi ni M. Sarmiento. "Yung diktador at palamura pimirmahan na naman ang tulong pinasyal para sa mga viktima ng human rights itong si tatay digong walang magawa hahahaha ano ang say ninyo mga reklamador," sabi ni M. Begornia. "Ano CHR Wala lang bang pa thank you diyan sa diktador naming president??? O baka naman di na kayo marunong mag thank you," sabi ni N. Radz. "Hehehehehe yan ang Tatay nang Pilipinas sabi nila yellowish diktador daw LOL ayannnnn ohhhhhh," sabi ni M. Pagao.</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -868,17 +913,20 @@
           <t>Matatandaan na ibinulgar ni Atty. Renato Bondal sa Senate Blue Ribbon Committee na nagkakahalagang P1,000 ang isang cake na ipinamamahagi ng Makati government sa bawat citizen sa siyudad na nagdiriwang ng kanyang kaarawan. Subalit kinalaunan ay lumitaw na nagkakahalaga ang bawat birthday cake ng P308 base sa mga dokumentong iniharap ni Sen. Nancy Binay, anak ni VP Binay. Lumitaw sa imbestigasyon ng BIR na inupahan ng lokal na pamahalaan ang CMK bilang supplier ng mga birthday cake, at caterer ng Makati City Hall cafeteria at Ospital ng Makati mula 2009 hanggang 2011. Sa nabanggit na tatlong taon, nagdeklara ang CMK ng gross income na umabot sa P43.2 milyon. Subalit lumitaw sa audit ng mga tax fraud investigator na binayaran ng Makati government ang cake supplier ng P107.6 milyon.</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -893,17 +941,22 @@
           <t>Ayon kay Renato Reyes, secretary general ng Bagong Alyansang Makabayan (Bayan), ang naging resulta ng eleksyon ay bunga ng sistematikong pandaraya at manipulasyon, kaya hindi niya matanggap ang kinalabasan nito at sinabing nawalan ng kredibilidad ang halalan dahil sa tinatawag niyang "Duterte Magic." Binanggit ni Reyes na ang Duterte Magic ay binubuo ng Martial Law sa Mindanao, pagpapakalat ng maling impormasyon ng kasalukuyang gobyerno, diumano’y paghokus-pokus sa automated elections at kontrol ng Commission on Elections (COMELEC), paggamit ng government resources para paboran ang mga kandidato ng administrasyon, at paggamit ng Philippine National Police (PNP) at Armed Forces of the Philippines (AFP) upang gipitin ang oposisyon at mga progresibong partylist. Hinikayat din ni Reyes ang publiko na magprotesta sa Biyernes bilang pagtutol sa naging resulta ng eleksyon. Samantala, ayon kay Comelec Commissioner Luie Guia, dapat suportahan ng matibay na ebidensya ang anumang alegasyon ng pandaraya at dapat magpakita ng partikular na patunay kung may mga boto na hindi dapat na-credit sa isang kandidato. Sa social media, may mga kababayan na hindi sang-ayon kay Reyes, tulad ni F. Onarebos na nagsabing, "You mean to say, my vote that I cast on May 13 is not credible?!... HELLO.?!... di lang kayo ang tao sa Pilipinas... nandito din kami...," habang si R. Cabuhat ay nagkomento na mas marami pa rin ang nagtitiwala kay Duterte, at si J. Misahon naman ay nagbitiw ng personal na puna laban kay Reyes.</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>"It was the systematic cheating and rigging of the elections which gave us these results," Hindi matanggap ni Bagong Alyansang Makabayan (Bayan) secretary general Renato Reyes ang naging kinalabasan ng eleksyon. Para kay Reyes, wala daw kredibilidad ang naganap na halalan dahil sa "Duterte Magic". Ayon kay Reyes, ang Duterte Magic ay binubuo ng mga sumusunod: - Martial Law sa Mindanao - Pagkakalat mismo ng kasalukuyang gobyerno ng maling impormasyon - Hinokus-pokus daw ang automated elections at kinontrol daw Commission on Elections (COMELEC) - Paggamit daw ng government resources para paboran ang mga pambato ng gobyerno. - Paggamit daw sa pwersa ng Philippine National Police (PNP) at Armed Forces of the Philippines (AFP) para gipitin ang mga oposisyon at mga progresibong partylist groups. Nanghihikayat si Reyes ng mga tao sa Biyernes para mag kilos-protest para ikundena ang naging resulta ng eleksyon.. Para kay Comelec Commissioner Luie Guia, ang anumang pagbibintang ng pandaraya sahalalan ay dapat suportado ng matibay na ebidensiya. "It is best to present specific proof that the votes credited to a particular candidates should not have been credited, or that what should not have been credited was credited. Proof of 'systematic cheating' is also welcome," sabi ni Guia Basahin ang naging komento ng ilang kababayan natin laban sa pahayag ni Reyes. "You mean to say, my vote that i cast on may 13 is not credible?!.... HELLO.?!... di lang kayo ang tao sa pilipinas... nandito din kami... ," sabi ni F. Onarebos. "E ano magagawa mo e marami pa ang bilib kay Duterte ngayon. It only means that Digong is credible becoz many Filipinos are believing him and are relying to him," sabi ni R. Cabuhat. "Ito ang taong ipinaglihi sa inggit at sama ng loob,sana sinals-l ka na lang ng tatay mo babalu," sabi ni J. Misahon.</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -918,17 +971,20 @@
           <t>Kaninang hatinggabi, nagulantang ang buong sports community matapos talunin ng hindi kilalang koponan na Golden Waves ang reigning champions na Thunderhawks sa isang kontrobersyal na laro sa National Basketball League, kung saan umani ng batikos ang officiating dahil sa sunod-sunod na questionable calls na nagresulta sa pagka-eject ng tatlong star player ng Thunderhawks at nagbigay-daan sa 97-96 panalo ng Golden Waves; agad na nag-trending ang #NBLSabotahe sa social media, may mga fans na nag-akusa ng “scripted” na laban at sinasabing may malalim na sabwatan sa likod ng biglang pag-asenso ng Golden Waves, habang ang liga ay nananatiling tahimik sa kabila ng panawagan ng publiko para sa imbestigasyon at transparency sa naging resulta ng laban.</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>sports</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -943,17 +999,20 @@
           <t>"Like I said families are divided, it is a reality," Sa panamayam sa ANC's Head Start, umamin si Senador Francis "Kiko" Pangilinan na hati ang kanyang pamilya pagdating sa usapin ng politika. Hindi alintana ng asawa ni Kiko na si Mega Star Sharon Cuneta na magpakita ng suporta kay Pangulong Rodrigo Duterte sa kabila ng madalas na pagbatikos ni Kiko sa Presidente. Kahit ganunn pa man, mahal pa din daw ni Kiko si Sharon. "Unfortunately, in the country many families of the country are divided on what is happening in the country and our family is no exception," sabi ni Pangilinan. Magugunitang ibinahagi ni Sharon sa kanyang social media account ang pagbati sa kanya ng Pangulong Duterte nang hindi nakadalo sa kanyang shows ang Presidente. Maaalalang pinagtanggol din ni Sharon ang kapatid niyang si Chet na tumatakbo bilang alkalde ng Pasay matapos i-endorso ng Pangulong Duterte. Nang mapag-usapan kung i-endorso ni Sharon ang mga kandidato ng oposisyon na mas kilala sa pangalang 'Otso Diretso', sinabi ni Kiko na hahayaan niya na lang ang asawa niya ang magpasya.</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -968,17 +1027,22 @@
           <t>Ayon sa pinakahuling survey ng Social Weather Stations (SWS), bahagyang bumaba ang trust ratings ni Bise Presidente Leni Robredo kung saan 59 porsyento ng mga Pilipino ang nagsabing may tiwala pa rin sila sa kanya. Samantala, sa online survey ng Yahoo.com, 86% ng mga sumagot ang nagsabing wala silang tiwala kay Robredo at 13% lang ang nagsabing may tiwala pa rin sila, base sa mahigit 120,000 respondents. Sa kabilang banda, ang SWS survey ay karaniwang may iilang libong respondents lamang. Ang artikulong ito ay nagtatanong kung sang-ayon ang mga mambabasa sa resulta ng Yahoo.com survey at hinihikayat silang bumoto sa nasabing website kung oo ang kanilang sagot.</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Sa pinakahuling Social Weather Stations (SWS) survey, lumabas na bahagyang bumaba ang trust ratings ni Bise Presidente Leni Robredo. Ayon sa survey ng SWS, 59 porsyento na lang ng mga Pilipino ang may tiwala kay Robredo. Kakaiba naman ang nagiging direksyon ng survey na isinasagawa sa website na Yahoo.com. Habang isinusulat kasi ang artikulong ito, umabot na sa 86% ang nagsabi na wala silang tiwala kay Leni, habang 13% lang ang nagsabing may tiwala pa rin sila sa bise presidente. Kapansin-pansin na ang survey ng Yahoo.com ay nakakalap ng mahigit 120,000 na respondents, habang ang survey ng SWS ay karaniwang umaabot lang sa iilang libong mga respondents. Sang-ayon ba kayo sa naging sa itinatakbo ng survey ng website na Yahoo.com. Paki-kalat po itong artikulo kung OO ang sagot niyo. Punta na rin po tayo sa Yahoo.com para makaboto.</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -993,17 +1057,20 @@
           <t>Nagkaroon ng komosyon sa pagitan ng iba't-ibang mga grupo ng militanteng kabataan at kapulisan sa isinagawang kilos-protesta laban sa tanggapan ng Commission on Higher Education (CHED) sa Quezon City. Iprinotesta ng mga kabataan ang pagtaas ng matrikula sa iba't-ibang eskuwelahan maging ang pagkakatanggal sa kolehiyo ng subject na Filipino at Panitikan, at posibleng pagbalik ng mandatory ROTC. Nakuhanan naman ng video ang aktwal na komosyon sa CHED kung saan pilit na pinapasama ng mga pulis ang mga kabataang nangbato ng pintura. Nagsimula ang komosyon nang may mga raliyistang nagbato ng mga paint bomb sa gate ng tanggapan dahilan para pigilan sila ng mga pulis at arestuhin. Maririnig din sa video na umalma ang mga kasamahan ng mga kabataan sa ginawa ng mga pulis. "Bakit n'yo sinasaktan?" sigaw ng isang aktibista. Paliwanag ng pulis na hindi na umano tama ang ginagawa ng mga kabataan kung kaya kailangan nilang pigilan ang pag-eeskandalo ng mga ito. "Hindi sinasaktan. Kailangan lang kuhanin kasi mali na 'yan," saad ng pulis. Nagkaroon ng pagpalag sa grupo ng mga kabataan sa pagkaaaresto ng tatlo nilang mga miyembro.</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>education</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -1018,17 +1085,20 @@
           <t>Sa report kay Police Sr. Inspector Gina DC Parinas, hepe ng Women's and Children Concerned Desk (WCPD), kinilala ang suspek na si Larry Cabangunay, 27, ng No. 207 Feliza Bukid, Barangay Parada ng nasabing lungsod. Sa salaysay ng biktima, 17, kina PO2's Ana Grace Mendoza at Cherbim Baluli ng WCPD, kasama niya ang kanyang live-in partner at namamalengke sa Bgy. Parada, dakong 6:00 ng gabi. Nasalubong ng mag-live-in partner si Cabangunay na matagal umano nilang hindi nakita at nagkayayaan na mag-inuman sa bahay ng suspek. Pumayag ang mag-live-in partner at nagtungo sa bahay ni Cabangunay at nakipag-inuman kasama ang dalawang kalugar ng suspek at inabot ng hanggang 10:00 ng gabi. Dahi l sa kalasingan, nagdesisyon si Cabangunay na patulugin ang mag-live-in partner sa kanyang bahay. Pagsapit ng 1:00 ng madaling araw, hinipuan ng suspek ang biktima. "Hindi po ako makasigaw kasi may hawak siyang patalim at nakatutok sa tagiliran ko," sabi ng biktima. Nagising ang live-in partner ng biktima at nakitang inaabuso ni Cabangunay ang kinakasama kaya tinadyakan niya ito hanggang sa kumaripas. Makalipas ang ilang minuto, nadakip si Cabangunay ng mga tauhan ng PCP 10 sa loob mismo ng kanyang bahay. Kinasuhan si Cabangunay ng Rape in Relation to 7610 (Child Abuse).</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -1043,17 +1113,20 @@
           <t>KABALIGTARAN NINA KC AT PAULO SUNUD-SUNOD ang mensaheng natanggap namin kahapon habang naghahabol ng deadline at naaliw kami sa mga tanong sa amin ng mga nakapanood ng "Gift of Life" episode nina Gerald Anderson at Maja Salvador sa Christmas seryeng Give Love on Christmas. Base sa obserbasyon ng mga nakapanood, "Bakit po walang kilig sina Ge at Maja sa Gift of Life? Parang hindi sila magdyowa. Bakit hindi sila kinikilig? Bakit parang pilit lang ang acting nila?"</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>economy / business</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -1068,17 +1141,20 @@
           <t>Matagal nang usap-usapan sa mga barangay ng Lungsod ng Maligaya ang umano’y lihim na pagpupulong ng isang mataas na opisyal ng lokal na pamahalaan kasama ang ilang di-umanong “advisors” na hindi naman pormal na kinikilala ng city council, at ayon sa mga naglabasang tsismis online, may tinatawag daw silang “Project Shadow Vote” na layong manipulahin ang resulta ng mga darating na barangay elections sa pamamagitan ng paglalagay ng mga undercover agent sa bawat presinto upang maimpluwensyahan ang pagboto ng mga residente; binanggit pa sa ilang viral na post na may mga natanggap na umano’y cash envelope ang ilang lider-kabataan kapalit ng pangakong susuportahan ang kandidato ng opisyal, habang may mga larawan pa raw ng mga kahina-hinalang meeting sa isang sikretong lugar, kaya’t lalong lumalakas ang hinala ng publiko na may malawakang sabwatan para mapanatili sa puwesto ang mga kasalukuyang nakaupo at tuluyang patahimikin ang sinumang maglalantad ng katotohanan tungkol sa Project Shadow Vote.</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -1093,17 +1169,22 @@
           <t>Ibinahagi ng netizen na si Albert Camp sa Twitter ang umano’y sirang fire exit ng isang apartment hotel sa Makati kasabay ng naganap na magnitude 6.1 na lindol sa Luzon, kung saan sinabi niyang, "Ascott Makati fire exit sira. Kung malakas ang lindol or may zombie apocalypse patay na kami." Wala pang inilalabas na pahayag ang pamunuan ng Ascott Makati ukol sa isyung ito. Samantala, nagbahagi rin ng kani-kanilang karanasan ang ilang netizen sa social media tungkol sa kanilang naramdaman at ginawa habang yumanig ang malakas na lindol, kabilang na ang isang engineer na nagsabing natapos na niyang mag-site inspection sa Makati bago mangyari ang lindol. Ayon sa PHIVOLCS, hindi bababa sa 17 na aftershocks ang naitala matapos ang lindol sa ilang bahagi ng Metro Manila at iba pang probinsya sa Luzon.</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Ibinahagi ng isang netizen na si Albert Camp ang umano'y sirang fire exit ng isang apartment hotel sa Makati nang mangyari ang magnitude 6.1 na lindol sa Luzon. "Ascott Makati fire exit sira. Kung malakas ang lindol or may zombie apocalypse patay na kami," saad ni Albert sa kanyang Twitter post. Hindi pa nagbibigay ng pahayag ang management ng Ascott Makati tungkol sa isyu. Kanya-kanyang kuwento naman sa social media ang ilang netizen hinggil sa kanilang naramdaman, ginagawa o kung nasaan sila nang mangyari ang malakas na lindol. "Engineer ako and kakatapos ko ang mag site inspection sa Makati. Buti nalang nakababa na Ko before that earthquake happened," ayon sa isang netizen. Samantala, nakapagtala ang PHIVOLCS ng hindi bababa sa 17 na aftershocks kasunod ng lindol sa ilang bahagi ng Metro Manila at ilang probinsya sa Luzon.</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>disaster / environment</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -1118,17 +1199,22 @@
           <t>Ayon kay Secretary Nograles, mapayapang pumanaw ang kanyang ama habang kasama ang kanilang pamilya, at nagpasalamat siya sa lahat ng naging bahagi ng buhay ni Papa Boy Nogie. Hinihiling din niya ang patuloy na dasal para sa kanilang ama na ngayo'y nasa kapayapaan na. Nangako si Nograles na magbibigay sila ng karagdagang detalye tungkol sa burol ng kanyang ama, na dating House Speaker at matagal nang nagkasakit.</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Ayon kay Nograles, mapayapang yumao ang kaniyang ama sa piling ng kanilang pamilya. "Our family would like to express our deepest gratitude to all of you for being a part of Papa Boy Nogie's life and journey. Papa passed away peacefully, surrounded by his family. May we please ask for your continued prayers. He is finally at peace," ani Secretary Nograles. Nangako ang kalihim na maglalabas sila ng detalye sa burol ng kaniyang ama. Ang dating House Speaker ay matagal na naratay dahil sa sakit.</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>lifestyle / human interest</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -1143,17 +1229,20 @@
           <t>Viral ngayon sa social media ang balitang may umano’y sikretong “Grade-for-Gadgets” scheme na nadiskubre sa isang kilalang pribadong paaralan sa lungsod ng San Miguel, kung saan sinasabing ilang guro raw ang tumatanggap ng mamahaling cellphone, tablet, at iba pang gadgets mula sa mga magulang kapalit ng mataas na marka ng kanilang mga anak; ayon sa mga post ng ilang dating estudyante at anonymous na empleyado, may listahan pa raw ng “recommended brands” na palihim na ipinapasa sa mga magulang sa tuwing malapit na ang grading period, at napag-alaman pa na may mga batang halos hindi pumapasok ngunit biglang nagiging honor student dahil lang sa mga regalong gadgets, dahilan para mag-ingay ang mga netizen na nananawagan ng agarang imbestigasyon at mahigpit na aksyon mula sa school administration, habang ang ilan ay nag-aalala kung paano nito maaapektuhan ang integridad at kalidad ng edukasyon sa bansa.</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>education</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -1168,17 +1257,22 @@
           <t>Kamakailan, naging laman ng balita ang malagim na pagpatay kay Christine Lee Silawan, isang grade 9 student na hindi lang pinaslang kundi binalatan pa ang mukha ng mga salarin. Ayon sa imbestigasyon ng mga eksperto, natuklasan na may mga nawawalang laman loob sa katawan ng biktima, kabilang ang dila, lalamunan, at tracha, ayon kay Superintendent Benjamin Lara ng PNP Crime Laboratory sa Central Visayas. Lumabas din sa ilang ulat na hindi umano nahalay si Silawan. Kilala siyang volunteer church collector sa isang simbahan malapit sa kanilang lugar at huling nagpaalam sa kanyang ina na pupunta siya roon, na hindi alam ng ina na iyon na pala ang huling pagkakataon na makikita niya ang kanyang anak. Natagpuan ang bangkay ni Silawan sa isang malawak na lote, walang suot na pang-ibabang damit at wala na ring balat sa mukha. May testigong nagsabing may tatlong lalaking huling nakitang kasama ni Christine at posible umanong mga durugista ang mga ito. Dahil sa karumal-dumal na krimen, marami ang nanawagan na ibalik ang parusang kamatayan para sa mga ganitong kaso.</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Nitong nagdaang mga araw bumulagta sa publiko ang walang-awang pagpatay sa grade 9 student na si Christine Lee Silawan. Hindi lang kasi nakuntento ang mga pusakal na kriminal sa pagpatay, binalatan pa ang mukha ng dalagita. Sa pinakahuling impormasyon na natukalasan ng mga eksperto na nag-iimbistiga sa kaso ni Silawan, nagpag-alaman na may mga nawawalang laman loob sa bangay ng biktima. Ayon kay Superintendent Benjamin Lara, MD, director of the Philippine National Police Crime Laboratory in Central Visayas, hindi na matagpuan sa katawan ng biktima ang dila nito. Pati ang lalamunan at tracha ay nawawala din. Ilang parte din daw ng leeg ay wala na. Lumabs din sa ilang ulat na hindi umano nahalay ang dalaga. Si Silawan ay nagsisilbing volunteer church collector sa isang simbahan malapit sa kanila. Base sa pahayag ng ina ng biktima, nagpaalam lang daw ang kanyang anak na pupunta sa simabahan. Hindi alam ng ina ni Silawan na ito na pala ang huling pagkakataon na makikita niya ang kanyang anak. Natagpuan ang wala ng buhay na katawan ni SIlawan sa isang malawak na lote. Tanggal ang damit nito pang-ibaba at tanggal din ang balat sa mukha. Ayon sa testigong nakausap ng kapulisan, may 3 lalaki daw na nakitang kasama ni Christine noong huling namataan ang dalaga. Posible din daw na durugista ang mga ito. Ang nakakgimbal na pagpaslang kay Christine ay kinundina ng mga kababayan natin. May mga humihiling na na ibalik na ang parusang kamatayan sa mga kahindik-hindik na krimen.</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -1193,17 +1287,20 @@
           <t>Ibinida ni Department of Agriculture (DA) Secretary Manny Pinol ang inagurasyon ng kauna-unahang monolithic dome sa ating bansa. Ang nasabing dome ay magsisilbi bilang warehouse para sa mga grains sa DA experimental station sa probinsiya ng Cagayan. Ayon kay Pinol, ang paggastos ng gobyerno ng milyon-milyon para ipagawa at mapanatili ang mga lumang istruktura at warehouses na nasisira ng bagyo ay matatapos na. Ang mga monolithic dome ay kaya raw makipagsabayan sa signal 5 na bagyo. Isa pa sa mga kayang gawin ng dome ay panatilihin ang maayos na temperatura sa loob nito. "While the temperature outside when I arrived at 3:30 p.m. was a scorching 36C degrees, it was only 21C inside the Monolithic Dome," Ang modernong warehouse at dinesenyo ng mga German engineers. Ang monolithic dome ay nakakahalaga ng P10-million at naipatayo sa napakabilis na panahon. Ang unang 8 units ng mga nasabing warehouses ay balak itayo sa mga rehiyon na madalas tamaan ng mga bagyo. Mayroon din daw ng mga dome na nakakahalaga ng P5-milyon pero mas maliit at itinatayo na sa Cagayan Valley Region. Ang mga dome ay suporta sa mga adhikain ni Pangulong Rodrigo DUterte na mabigyan ng maayos na buhay ang mga Pilipino.</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>economy / business</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -1218,17 +1315,20 @@
           <t>Ito, ayon sa PCGG, ay matapos maglabas ang Pangulong Aquino ng executive order na nagpapahintulot sa pagsusubasta sa naturang ari-arian upang magamit ang pondo sa pagpapabuti sa industriya ng pagtatanim ng niyog.</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C27" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -1243,17 +1343,20 @@
           <t>Ipinagmalaki ng Department of Science and Technology (DOST) na hinog na ang Pilipinas para magkaroon na ng sarili nitong space agency. Ayon sa DOST, may sapat na daw na manpower at pasilidad ang bansa. "We are proud to say that we are capable and ready for a Philippine Space Agency," ayon kay DOST Secretary Fortunato de la Pena sa isang press conference. Sabi pa ni De la Pena, makakatulong daw sa iba't-ibang larangan ang bubuuin na ahensiya. "National added security, improved hazard management, progressive climate studies, refined space research, and modernized farming and environmental monitoring, among others," sabi pa ng kalihim Magugunita na mayroong ng panukalang batas na ipinasa sa kongreso nitong Disyembre 2018 para sa pagbuo ng nasabing ahensiya. Ang parehas na batas nama sa senado ay nakabinbin pa rin. "With this milestone, we are now able to receive information that can be translated to the enhancement of our capabilities in weather forecasting, disaster management and preparedness, national security, industry building, research, education and international cooperation," dagdag pa ni DOST Undersecretary Rowena Guevara. Panoorin ang ilang video na tumatalakay sa pagbuo ng space agency ng Pilipinas. Basahin ang reaksyon ng ilang kababayan natin sa balitang pagkakaroon ng space agency ng Pinas.. "Good luck and God bless DOST! Praying for immediate approval and implementation of that bill establishing the Philippine Space Agency," sabi ni D. Brylle. "Yes congrats DOST scholars...for making the talents of pinoys known to the world..that we can make and advance our system...profit din ng bansa mkagain ng investors through our efforts...sana magtulong2x po ang lahat para sa improvement nman ng bansa...thank you for the effort..pangarapko rin sana before na mmaging scientist pero di kinaya ng utak..pero natutuwa ako at sna maabutan ko pa," sabi ni R. Alinsasaguin. "hmmm if thats the case ang dami ng dumaan na presidente pero wala pang nakakagawa ng ganyan to open an space agency a country needs atleast 1 Billion pesos to start with it for research facilities and others stuffs.," sabi ni E. Salcedo. "Our government needs to fully support our scientists, researchers, etc. Hindi man natin mapakinabangan ngayon, mapapakinabangan ng susunod na mga henerasyon. Kesa naman ibang bansa na naman makinabang sa talino nila...," sabi ni J. Sia.</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C28" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>technology</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -1268,17 +1371,20 @@
           <t>"It is an additional layer (of security) that the Comelec added. It's just to make sure that you won't be able to vote if you don't have biometrics data," pahayag ni Jimenez. Ang biometrics data ay isang automated identification system ng isang botante na naglalaman ng kanyang larawan, fingerprint at lagda. Base sa Republic Act 10367 o Mandatory Biometrics Registration Act of 2013, ang mga botante na hindi maisusumite ang kanilang sarili sa validation process bago ang May 2016 elections ay tatanggalin sa voters' list at hindi na maaaring muling makaboto. Bukod sa VVS, kasabay na isasalang sa pilot testing sa iba't ibang lugar sa Metro Manila ay ang karagdagang Optical Mark Reader (OMR) machine, ayon pa kay Jimenez. Kasabay na gagamitin sa May 2016 ang mga Precinct Count Optical Scan (PCOS) machine na ginamit din noong May 2013 midterm polls. Sa inilabas na Invitation to Bid, inihayag ng Comelec-Bids and Awards Committee (BAC) na naghahanap ito ng 23,000 VVS na uupahan ng ahensiya sa halagang P90,000 kada unit o may kabuuang halaga na aabot sa P690 milyon.</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C29" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -1293,17 +1399,22 @@
           <t>Matapos magbanta si Pangulong Rodrigo Duterte na maaaring suspindihin ang pribilehiyo ng writ of habeas corpus at magdeklara ng revolutionary war laban sa kanyang mga kritiko, nagbigay ng matinding reaksyon si Senator Leila De Lima at inihalintulad ang Pangulo sa isang "asong ulol" na tila wala na sa katinuan, ayon sa ulat ng DWIZ; sinabi rin ng Senadora na tila binabalewala na ni Duterte ang Saligang Batas ng Pilipinas at inuuna lamang umano ang sariling interes, kaya't iginiit niya na ang tunay na kailangan ng bansa ay isang rebolusyon ng konsensya at hindi isang madugong rebolusyon, base sa nilalaman ng kanyang liham.</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Matapos ang binitawang pahayag ni Pangulong Rodrigo Duterte kung saan nagbanta siyang sususpindihin niya umano ang pribilehiyo ng writ of habeas corpus at magdedeklara umano siya ng isang revolutionary war sakaling hindi siya tigilan ng kanyang mga kritiko, isang sagot naman ang ibinato ni Senator Leila De Lima ukol dito. Sa pinakabagong komento ni Senator Leila De Lima patungkol kay Pangulong Duterte, inihalintulad niya sa isang "asong ulol" ang Pangulo na tila nawawala na umano sa kanyang sariling katinuan, mula sa ulat ng DWIZ. Ayon sa Senadora, ipinagwawalang-bahala na umano ni Pangulong Duterte ang ang Saligang Batas ng Pilipinas, at wala raw umano itong pakialam maliban sa kanyang sarili. Rebolusyon ng kunsensya raw ang kailangan ayon kay Senator De Lima at hindi madugong rebolusyon. Ganito ang mababasa sa liham ni Senator Leila De Lima: "Para na siyang isang asong ulol. Threatening to declare 'revolutionary war' (whatever that is) and jail critics. This President does not really care about the constitution and the rule of law. All he cares about is his psychotic self. The kind of revolution that we need, and urgently, is a revolution of conscience, among the enablers, and all others who still cannot see or refuse to see though the moral bankruptcy of this regime."</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -1318,17 +1429,22 @@
           <t>Isang babae ang nagtamo ng chemical burns sa lalamunan at tiyan matapos uminom ng milk tea na binili nila sa isang fastfood chain; ayon sa ulat, agad niyang napansin ang kakaibang lasa ng inumin kaya pinaamoy ito sa kanyang mister na nakadama rin ng matapang na amoy. Ilang minuto lang ang lumipas, nagsimulang magsuka at sumakit ang tiyan ng biktima. Nang iparating ng mister ang insidente sa staff ng fastfood chain, inamoy din ng staff ang milk tea at itinapon ito ng patago, ngunit nakuha pa rin ito ng mister mula sa basurahan at naipasuri sa eksperto. Lumabas sa pagsusuri na may lamang disinfectant ang natirang milk tea, dahilan ng chemical burns at posibleng pagkasira ng vital organs ng biktima gaya ng atay at kidneys. Dahil dito, pinaalalahanan ang publiko na kung may kakaibang amoy o lasa ang milk tea, huwag na itong inumin at agad itapon. Patuloy na patok ang milk tea sa Pilipinas, na makikita sa dami ng milk tea stores sa bansa.</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Isang babae ang nagkaroon ng chemical burns sa lalamunan at tiyan matapos niyang uminom ng milk tea. Ayon sa isang report, pinasuri sa eksperto ang natirang milk tea at nakumpirma na may laman ito na isang uri ng disinfectant o panlinis. Nabili nila ang nasabing milk tea sa isang fastfood chain kung saan napansin agad ng babae na may kakaibang lasa ang milk tea. Kaya agad na inamoy ng mister ng biktima ang inumin at mayroon daw itong matapang na amoy. Nagsimula nang magsusuka at sumakit ang tiyan ni misis matapos ang ilang minutong nakalipas. Nang kausapin ng mister ang staff sa fastfood chain, inamoy daw ng staff ang milk tea at itinapon ito ng patago. Mabuti na lang at kinuha ng mister sa basurahan ang baso ng milk tea kaya naipasuri nila ito. Bukod sa pagkasunog ng lalamunan at tiyan ng biktima, posible rin daw na nasunog ang kanyang vital organs kagaya ng kanyang atay at kidneys. Kaya nagbigay sila ng paalala sa lahat, na kung may naamoy at may kakaibang lasa ang iniinom na milk tea ay agad na itong itapon. Isa ang milk tea sa paboritong inumin sa Pilipinas at malaking patunay dito ang nagkalat na milk tea stores.</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>health misinformation</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -1343,17 +1459,20 @@
           <t>Usap-usapan ngayon sa social media ang umano'y panggagaya ng kinatawan ng Thailand na si Ingchanok Prasart sa ginanap na Miss Intercontinental pageant 2018 sa trademark ni Miss Universe 2018 Catriona Gray na "lava walk." Isang netizen sa Twitter na nagngangalang Marnie Raro ang nakapansin sa paraan ng paglalakad at pag-project ni Miss Thailand na parang kinokopya ang "lava walk" ni Catriona. Bukod kay Miss Thailand, napansin din ng mga netizens ang pagkopya umano sa "Mayon Volcano gown" ni Miss Vietnam. Aminado naman ang dalawa na labis nilang hinahangaan at inspirasyon nila si Miss Universe 2018 Catriona Gray. Halo-halo naman ang naging reaksyon ng mga netizens hinggil dito. "So now everyone looks like Catriona Gray. From hair to stance to gowns. The influence. Only legends do that." "Catriona Gray's walk can never be perfect without her walking it." "I think so? Even the hand gesture of Miss Thailand seems copied too. Catriona Gray is indeed a queen." "Yet they can't copy the original. Because there will be only one Lava Walk and Catriona Gray." "Kayo na 'yung may mga originality... hala gawa kayo sarili niyong pageant, ano ba naman yung hayaan niyo na lang sila hays....daming toxic." Isang patunay lamang ito na maraming mga aspiring beauty pageant candidates, hindi lamang sa Pilipinas kundi maging sa buong mundo, ang tumitingala at humahanga kay Catriona. Aminado naman dito ang marami sa mga kandidata ng naturang katatapos na pageant. Ang 47th edition ng Miss Intercontinental 2018 ay ginanap noong Enero 26, 2019, sa SM Mall of Asia Arena sa Pasay, Metro Manila, Philippines. Kinoronahan ni Miss Intercontinental 2017 Veronica Salas Vallejo ng Mexico ang kandidata ng Pilipinas na si Karen Juanita Gallman. Ito ang kauna-unahang pagkakataong naging host ang Pilipinas sa pageant na ito. Pinili ng Japan organizers ang Pilipinas na maging venue ng pageant dahil abala ang bansang Japan sa mga paghahanda para sa 2020 Summer Olympics. Narito ang buong Twitter post ng netizen:</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C32" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -1368,17 +1487,20 @@
           <t>Ayon sa website ng Irrawaddy magazine, kinondena ng mongheng Buddhist na si U Wirathu ang human rights rapporteur na si Yanghee Lee sa isang public rally noong nagkaraang Biyernes kontra sa boto sa UN General Assembly na nanawagang pagkalooban ng citizenship ang Rohingya Muslims sa bansa, kilala rin bilang Burma.</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C33" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -1393,17 +1515,20 @@
           <t>Nagawa pa ring maging mahinahon ng isang manager ng fast food chain sa customer na nambastos sa kanya nang dahil lang sa straw. Ikinuwento ni Imee Joy Urgelles sa isang Facebook post ang pagbuhos sa kanya ng softdrinks ng hindi makaintinding customer na pilit nanghihingi ng straw sa kabila ng pagpapatupad ng "straw less" policy sa restaurant. "Sa customer na nagbuhos sakin ng softdrinks dahil sa "straw less" kami ingat po kayo. Thank you dahil sa inyo napatunayan ko na effective manager ako hindi ko man nabigay ang straw na kailangan mo at least na-explain ko nang maayos kung bakit wala kaming straw," sabi ni Urgelles sa post. Mahigpit na ipinagbabawal sa maraming lugar lalo na sa mga lungsod ng Metro Manila ang paggamit ng plastic kasama na rito ang straw at iba pang food containers gaya ng plastic cups, spoons, forks at styrofoams. Kahit pa naka-experience ng aroganteng customer, saludo pa rin si Urgelles sa mga matalinong customers na marunong umintindi sa patakaran. "Sa lahat ng fastfood customer na nakakaintindi at nakakaunawa ng "straw less" kudos sa inyo." Sa pagtatapos ng post ni Imee, nabanggit niyang nanay pa naman niya ang nagplantsa ng kanyang uniporme pero tuloy pa rin daw ang trabaho niya nang araw na iyon matapos ang insidente. Dahil dito, hinangaan ng mga netizens ang ginawa ni Urgelles na dapat ay magsilbing aral ang pangyayaring sa iba.</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C34" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>lifestyle / human interest</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -1418,17 +1543,22 @@
           <t>Ayon kay Presidential Spokesperson Salvador Panelo, si Peter Joemel Advincula na umaming siya si alyas "Bikoy" sa video series na "Ang Totoong Narco List" ay tila ginagamit lang at para lamang pawn, at idiniin niyang sira na ang kredibilidad ni Advincula dahil sa mga kaso nito at pagiging convicted. Sinabi ni Panelo na nasira na agad ang kredibilidad ni Advincula nang mapatunayan na walang ebidensya laban kay Bong Go, at pinabulaanan din ng Rural Bank of Guinubatan at ng isang resort ang mga paratang ni Bikoy. Dagdag pa ni Panelo, may posibilidad na may ilalabas pang mas malaking rebelasyon o "bombshell" kaugnay sa isyu kay Advincula, at iginiit niyang malinaw na isang black propaganda ang mga alegasyon.</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>"Parang ano lang siya dito, 'pawn' o ginagamit lang," Ganito ang naging pahayag ni Presidential Spokesperson Salvador Panelo laban kay Peter Joemel Advincula na lumantad kahapon para sabihin na siya si alyas "Bikoy", ang lalaki sa video series na "Ang Totoong Narco List" na nangyuyurak sa kaanak ni Pangulong Rodrigo Duterte sa pamamagitan ng pagsasangkot sa pamilya ng Presidente sa droga. Ayon kay Panelo, sirang-sira daw ang kredibilidad ni Advincula at mukhang nagagamit lang ito. "Ang kredibilidad niya ay bagsak. Convicted pala siya, tapos marami palang kaso," sabi ni Panelo. "Kasi tignan niyo, 'yung lang kay Bong Go, nasira na siya doon. Nilabas na naman kahapon ang likod niya, ang linis. Number two, 'yung binanggit niya na Rural Bank of Guinubatan, nagsalita na rin, walang katotohanan (ang bintang ni Bikoy). 'Yung isa pang resort (misibis bay), ganun din," dagdag pa ni Panelo. Banta ni Panelo, baka sa mga susunod na araw daw ay magpasabog sila ng bomba laban sa isyung kinasasangkutan ni Advincula. "At mayroong... Hindi ko pa puwede sabihin ngayon but mayroong nakikita ang mga nag-iimbestiga na could be a bombshell from the way I look at it... It's very obvious na its a black propaganda," babala ni Panelo.</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -1443,17 +1573,20 @@
           <t>Mga kababayan, siguradong magugulat kayo sa bagong lumalabas na usap-usapan online na diumano’y may sikreto umanong kwarto sa loob ng opisina ng isang mataas na opisyal ng pamahalaan kung saan sinasabing isinasagawa raw ang mga lihim na pagpupulong kasama ang ilang misteryosong dayuhang negosyante tuwing hatinggabi, at ayon sa mga nagpakilalang insider ay dito raw pinag-uusapan ang mga planong hindi pa ipinapaalam sa publiko na may kinalaman sa malalaking proyekto at kontrata ng gobyerno, kaya’t marami ang nagtatanong kung ano nga ba talaga ang nangyayari sa likod ng mga saradong pinto at kung may kinalaman ba ito sa biglaang pagyaman ng ilang opisyal na malapit sa kanya, dahilan para umusbong ang samu’t saring conspiracy theory na patuloy na pinagpipiyestahan ng mga netizen sa social media.</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C36" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -1468,17 +1601,20 @@
           <t>Magpapatupad na ng crackdown ang Philippine National Police - Highway Patrol Group (PNP-HPG) sa mga motoristang gumagamit ng mga plakang numero 8. Ito ay matapos magbigay ng direktiba si House Speaker Gloria Macapagal-Arroyo na i-recall ang lahat ng plate number 8. Ang plate number 8 ay karaniwang gamit ng mga miyembro ng kongreso. Ang ilan ay ginagamit ito para makapanindak ng mga kapwa motorista sa lansangan. Katulad na lang ni Jojo Valerio, ang road rage suspect na nakunang sa viral video na nanapak at nanggigitgit ng mga kapwa motorista habang gumagamit ng plakang may numero 8. "Nag-issue na ako sa lahat ng ating chiefs nationwide na mag-conduct ng crackdown sa plaka na 8 at mabuti nga naman na ang ating Congress nag-issue na rin na i-surrender na ang ganitong plaka. Tutulungan naming ang Congress na hanapin 'yung mga plaka and we will crack down on plate number 8," sabi ni HPG director Chief Supt. Roberto Fajardo. Binilinan naman ni PNP Chief Oscar Albayalde ang mga kapulisan na huwag magpasindak sa mga motoristang may plakang 8. Mayroon din daw gumagamit pekeng plakang 8. "There is nothing wrong in flagging down these vehicles for as long as our personnel would do it in a proper way. While the Land Transportation Office (LTO) allows its use, there are restrictions," ani Albayalde.</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C37" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -1493,17 +1629,20 @@
           <t>Tila marami na ang nakakapansin sa pananahimik ni Philippine National Police (PNP) Chief Oscar Albayalde sa kaso ng pagpaslang kay Richard Santillan, ang bodyguard/aide ni election whistle blower Atorney Glenn Chong. Sa Facebook post ng pro-government blogger at kapatid ni Senator Miram Defensor-Santiago na si Atty. Paula Defensor-Knack, natanong nito kung bakit tila napaka-tahimik umano ni Albayalde sa isyu ng pagkakapatay kay Santillan. Para kay Knack, sirang-sira na raw ang imahe ng mga pulis. Pinatotohanan din ni Knack sa parehong post na kasama nga parati ni Atty. Chong si Santillan. Ito po ang ilan sa mga reaksyon ng mga kababayan natin sa naging pahayag ni Knack. Hindi napigilan ng ilang na banatan si PNP Chief Albayalde sa naging isyu nito sa programang "Ang Probinsyano".</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C38" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -1518,17 +1657,20 @@
           <t>Nahalungkat ng prominenteng Pro-government blogger na si Sass Rogando Sasot ang isang artikulo noong 2012 (Aquino Government Era), kung saan ipinapakita na ang Pilipinas ang numero uno sa paggamit ng iligal na droga sa rehiyon ng Silangang Asya. Ang post ni Sasot ay nag-ugat sa pagkumpara kamakailan ni Senator Risa Hontiveros sa presyo ng bigas at shabu sa panahon ng Duterte Government. "Noong panahon ni PNoy ang Pilipinas ay dineklara ng UN na #1 user ng shabu sa East Asia. Bakit tahimik noon sina Bam Aquino, Leni Robredo, at bakit hindi kinumpara ni Risa Hontiveros noon ang presyo ng shabu sa presyo ng bigas?" sabi ni Sasot. Ayon sa ulat noong 2012 ng United Nations World Drug Report, 2.1 porsyento ng mga Pilipinong may edad 16 hanggang 64 ang lulong sa methamphetamine o mas kilala sa tawag na shabu.</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C39" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -1543,17 +1685,20 @@
           <t>Makamit ang pansamantalang pamumuno ang tatangkain ng San Miguel Beer sa kanilang pakikipagtuos sa Globalport ngayong hapon sa pagpapatuloy ng 2015 PBA Philippine Cup sa Smart-Araneta Coliseum. Kasalukuyang kasalo ng Alaska sa pangingibabaw hawak ang barahang 6-1, panalo-talo, target ng Beermen na maiposte ang ika-apat na sunod at pampitong pangkalahatang panalo upang masolo ang liderato.</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C40" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>international news</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -1568,17 +1713,20 @@
           <t>Kaninang madaling araw, umugong sa social media ang balitang naaktuhan umano ang rising star na si Carla Velasco na palihim na lumalabas mula sa hotel room ng isang kilalang direktor matapos ang isang after-party ng kanilang pelikula, dahilan upang magsimula ang samu’t saring espekulasyon sa tunay na ugnayan ng dalawa; ayon sa mga nakakita, tila nagmamadali raw si Carla habang tinatakpan ang mukha gamit ang kanyang jacket, at may mga nagsasabing narinig pa raw ang pag-aaway nila ng rumored boyfriend niyang si Marco Delos Reyes sa lobby, kaya’t ngayon ay usap-usapan kung may kinalaman ba ang direktor sa biglaang paglamig ng relasyon ng celebrity couple, lalo na’t tikom pa rin ang bibig ng magkabilang kampo sa kabila ng kaliwa’t kanang tanong ng press at fans tungkol sa isyu.</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C41" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -1593,17 +1741,20 @@
           <t>Ayon kay Tito Aguirre, tagapagsalita ni Abu, inamyendahan sa committee hearing sa Senado ang naunang resolusyon at isinama ang Lipa City na nasa ikaapat na distrito. Sinuportahan ni Lipa City Mayor Meynardo A. Sabili at department heads ang resolusyon gayundin ang pamunuan ng Sangguniang Panlalawigan ( SP) na pinangunahan ni Vice Governor Mark Leviste at board members. Pasado rin sa NSO ang populasyon ng mga lungsod para maging distrito. Kapag naaprubahan sa plenaryo ng Senado, uusad ito sa Malacanang at magiging distrito na ang dalawang lungsod sa oras na nilagdaan ito ng Pangulo.</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C42" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -1618,17 +1769,22 @@
           <t>Nalungkot ang marami sa sinapit ng isang Pinay OFW sa Taiwan na pumanaw matapos mapag-alamang aneurysm pala at hindi stroke ang dahilan ng kanyang pagkamatay, ayon sa Facebook post ni Maryjane G. Magallanes kung saan makikita ang larawan ng OFW na kilala bilang Bebe Lhabz noong maayos pa ang kanyang kalagayan at habang siya ay nasa ospital na. Isa sa mga itinuturong dahilan ng kanyang pagpanaw ay ang labis na pagpupuyat at matinding pagod sa trabaho, na nagdulot ng pananakit ng ulo na sintomas na pala ng mas seryosong karamdaman. Dahil dito, nagbigay ng paalala si Maryjane na hindi madali ang buhay ng mga nagtatrabaho sa abroad at bagama’t masaya silang tingnan sa mga larawan, malayo ito sa tunay nilang nararanasan.</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Marami ang nalulungkot sa kinahinatnan ng isang kababayan natin sa Taiwan matapos itong bawian ng buhay. Sa Facebook post na ibinahagi ni Maryjane G. Magallanes, makikita ang larawan ng Pinay OFW noong maayos pa ang kanyang kalagayan at nang siya ay nasa ospital na lamang. Inakalang stroke lamang ang nangyari ngunit napag-alaman nilang aneurysm na pala ito at di na rin nagtagal ang buhay ng Pinay. Nakilala ang Pinay OFW sa Facebook account niyang na si Bebe Lhabz. Nakikita raw na isa sa mga posibleng sanhi ng kanyang pagkamatay ang labis na pagpupuyat at matinding pagod sa trabaho. Nakaranas ng pananakit at pagkirot ng kanyang ulo na sintomas na pala ng mas malubha niyang karamdaman. Dahil dito, nagbigay ng paalala si Maryjane na hindi madali ang trabaho nila sa abroad at aniya, masaya lang sila kung titingnan sa mga larawan pero malayo ito sa realidad.</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>international news</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -1643,17 +1799,22 @@
           <t>Ilang isyu ang kinakaharap ngayon ni Kris Aquino, kabilang ang umano’y pagpopondo niya sa isang anti-government blogger at ang pagkalat ng phone conversation kung saan narinig na pinagbantaan niya ang dating financial manager na si Nicko Falcis. Nagsimula ang lahat noong nakaraang taon nang sampahan niya ng kaso si Falcis dahil sa umano’y pagdispalko ng kanyang pera. Sa gitna ng mga kontrobersiya, nagtungo si Kris sa Singapore upang magpagamot sa kanyang sinasabing auto-immune disease na lupus. Habang mainit na pinag-uusapan sa Pilipinas ang pag-leak ng kanilang pag-uusap ni Nicko, naglabas ng video si Kris kung saan binanggit niyang may politiko umanong gumagamit sa pamilya Falcis at nagpahiwatig din siya na magpapalakas para sa 2022, na kilalang taon ng halalan. Aniya, may kinalaman ito sa 2022 at naniniwala siyang may mga taong sumusuporta sa mga trolls at machinery na nagba-back up kay Nicko. Sinabi rin ni Kris na hindi siya sapat na malusog para sa 2022 ngunit magpapalakas siya bilang paghahanda, kasunod ng payo ng kanyang ama na huwag ipaalam ang plano at basta na lang gawin ito. Matapos nito, naging usap-usapan ang reaksyon ng ilang Pilipino sa mga pahayag ni Kris.</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Sari-saring isyu ang kinasasangkutan ni Kris Aquino. Mula sa pagpopondo ng anti-government blogger, hanggang sa nagleak na phone conversation kung saan maririnig na pinagbantaan na ipapapatay ang dati niyang financial manager na si Nicko Falcis. Nagsimula ito noong nakaraang taon nang sampahan ni Kris si Falcis ng kaso dahil umano sa pagdispalko sa pera niya. Nagtungo si Kris sa Singapore para ipatingin ang kanya umanong auto-immune disease na lupus. Habang usap-usapan ang nag-leak na phone conversation niya kay Nicko dito sa Pilipinas, naglabas ito ng video kung saan sinabi nito may gumagamit na politiko sa mga Falcis. Nagpahapyaw din si Kris na magpapalakas siya para sa 2022. Alam ng lahat na ang 2022 ay taon ng halalan. "This has to do with 2022. Alam ko naman na sila ang pumo-pondo sa mga trolls, sila ang pumu-pondo sa machinery backing Nicko. DI nila nage-gets, I'm not healthy enough for 2022. But, lets be honest, sa ginawa niyo sa akin, magpapalakas ako, humanda kayo. Pero di ba ganun iyon? Turo ng dad ko, 'Don't tell them your plans, just do it'. Bago pa nauso si Nike, nasabi na ng dad ko iyan. So handa kayo, papalakas talaga ako," sabi ni Kris. Basahin ang reaksyon ng ilang kapwa Pilipino natin sa mga pinagsasabi ni Kris.</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -1668,17 +1829,20 @@
           <t>Sa isang pahayag, sinabi ni Alex Yague, PBOA executive director, na nagdesisyon ang mga miyembro ng mga grupo ng bus operator na tumalima sa provisional authority na ipinalabas noong Mayo 17, 2008 na nagtatakda sa pasahe ng mga provincial bus sa P9 para sa unang limang kilometro at karagdagang P1.40 sa kada kilometro para sa mga ordinary o hindi airconditioned na mga bus. Ang mga regular air-conditioned bus ay sisingil ng P9 sa kada kilometrong biyahe at may P1.80 dagdag sa mga susunod na kilometro habang ang mga air-con deluxe ay P1.70/km at ang luxury ay nasa P2.25 kada kilometro. Sinabi ni Yague na ang nasabing mga pasahe ang umiiral simula noong 2008 at nananatili ito sa kabila ng pagtaas ng mga toll fee, pagtapyas sa presyo ng petrolyo at pagmamahal ng gastusin sa pagmamantine, bukod pa sa tumataas na inflation rate. Ayon kay Yague, pinili ng mga kumpanya ng bus na sagutin ang tumataas na presyo ng motor oil at motor parts sa nakalipas na anim na taon, sinabing ang presyo ng motor oil ay tumaas mula P86 kada litro ay naging P132/liter ngayong 2014 habang ang presyo ng gulong at iba pang piyesa ng bus ay tumaas ng 38 porsiyento mula 2008 hanggang 2014.</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C45" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>economy / business</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -1693,17 +1857,20 @@
           <t>Ayon sa ulat ng Balitang Global Pinoy, nagdulot ng matinding pagkabigla at pag-aalala sa Filipino community sa Dubai ang balitang isang OFW na si “Aling Nena” ay biglang yumaman matapos diumano’y makadiskubre ng misteryosong maleta na puno ng ginto habang naglilinis ng isang lumang apartment, at ayon sa mga kapitbahay ay agad daw siyang kinuha ng mga hindi nakilalang banyaga na sakay ng itim na sasakyan at mula noon ay hindi na siya nakita; marami ang nagsasabi na bago mawala si Aling Nena ay nagpakita raw siya sa social media ng mga mamahaling gamit at kakaibang alahas, dahilan para magduda ang ilang kababayan kung totoo nga ba ang kwento o bahagi lang ito ng isang malaking sindikato na kumikilos sa likod ng mga OFW, kaya’t umapela na ang ilang grupo sa embahada na imbestigahan ang insidente at bigyang proteksyon ang mga Pilipino sa gitnang silangan.</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C46" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>international news</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -1718,17 +1885,22 @@
           <t>Sa kanyang Instagram account, inanunsyo ni Erica Paredes, anak ni Jim Paredes, na magpapahinga muna siya sa paggamit ng personal na social media dahil masyado na itong toxic at hindi na masaya tulad ng dati. Ginawa niya ang pahayag na ito matapos lumaganap at umani ng batikos mula sa netizens ang kontrobersyal na video ng kanyang ama, kung saan makikitang dumidila siya sa camera at nilalaro ang kanyang ari. Nagbigay din si Erica ng payo sa publiko na mag-post ng mga bagay na makakatulong sa lipunan at maging mabait sa isa’t isa habang hindi siya aktibo online. Samantala, makikita rin sa social media ang iba’t ibang reaksyon ng mga personalidad sa isyung kinakaharap ni Jim Paredes.</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Sa kanyang Instagram account, sinabi ng babaeng anak ni Jim Paredes na si Erica Paredes na pansamantala muna daw siyang aalis sa social media dahil hindi na daw masaya tulad ng dati. "Taking a break from my personal social media for a it. Too much toxic and honestly, it's not as fun as it used to be," sabi ni Erica. Naglabas ng pahaag si Erica matapos kumalat ng husto at nabatikos ng mga netizens ang kanyang ama dahil sa malaswang video. Sa nasabing video, mapapanood si Jim na dumidila-dila sa camera at kalaunan ay nilaro ang pototoy. Pinayuhan din niya ang mga tao na mag post ng mga bagay na makakatulong sa lipunan. "In the mean time be nice. Mind yah business. Post things that will actually benefit the society," dagdag pa ni Erica. Panoorin ang ilang reaksyon mula sa mga personalidad sa social media sa suliraning kinakaharap ni Paredes.</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -1743,17 +1915,20 @@
           <t>Isang nakakabiglang insidente ang naganap sa Barangay Del Pilar kagabi nang umano’y isang grupo ng limang armadong lalaki na nakasuot ng clown costume ang sabay-sabay na sumalakay sa isang 24-hour convenience store, kung saan hindi lang nila tinangay ang lahat ng pera sa cash register kundi pati na rin ang mga instant noodles, softdrinks, at maging ang CCTV camera ng tindahan; ayon sa mga empleyado, pinilit pa raw ng mga suspek na magpakuha ng group selfie gamit ang cellphone ng cashier habang hawak-hawak ang mga ninakaw na paninda, at bago tumakas ay nag-iwan pa ng nakakatakot na babala sa pader gamit ang ketchup na nagsasabing “Babalik kami tuwing full moon,” dahilan para mag-panic ang buong barangay at magkulong ang mga residente sa kani-kanilang bahay, habang patuloy pang hinahanap ng mga awtoridad ang kakaibang grupo na umano’y may kasabwat pang mascot na nagmamaneho ng getaway tricycle.</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C48" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -1768,17 +1943,20 @@
           <t>Matapos maharap sa kontrobersiya sina dating Bayan Muna Congressman Satur Ocampo at ACT Party-list Representative France Castro dahil sa umano'y kidnapping at human trafficking, nahaharap naman ngayon ang dalawa pang leftist congressmen na sina ACT Teachers party-list Rep. Antonio Tinio and Anakpawis party-list Rep. Ariel Casilao sa kasong child abuse. Ang kaso ay kaugnay sa pangunguna ng 2 sa rally na ginawa noong Octobre 23 kung saan ini-impluwensiyahan umano ang ilang menor de edad na magalit sa gobyerno. Ayon kay Chief of the Women and Children's Protection Desk of the Davao City police Senior Inspector Lilibeth Liza Remolar, pinangunahan umano ng 2 ang rally na may kasamang menor de edad. "They were leading the group, including the children with them, prompting them to listen to what their leaders and speakers were talking and saying," sabi ni Remolar. Ayon sa ulat, nalabag umano ang Republic Act 7610, or the Special Protection of Children Against Abuse, Exploitation and Discrimination Act and Presidential Decree (PD) 603 at maaaring makulong ang mga lalabag dito ng 6 na taon at isang araw. Ito po ang ilan sa naging komento ng mga kababayan natin sa bagong kaso isasampa laban sa miyembro ng Makabayan bloc.</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C49" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -1793,17 +1971,22 @@
           <t>Isang 17 taong gulang na high school student na si Kian Delos Santos mula Caloocan City ang napatay sa isang anti-drugs operation ng PNP, na nagdulot ng magkahalong reaksyon mula sa publiko at mga opisyal. Ilang senador, kabilang si Senator JV Ejercito ng Senate Majority block, ay nagpahayag ng pagkabahala sa social media, habang si Senator Risa Hontiveros ay naglabas ng pahayag sa isang press conference tungkol sa umano’y pag-abuso ng PNP, na naging viral at pinag-usapan ng mga netizens na may iba-ibang opinyon. Ayon sa panayam ng TV5, iginiit ng mga magulang ni Kian na hindi totoong nagpaputok ng baril ang kanilang anak dahil naka-boxer shorts lamang ito at imposible raw na may dalang baril, kaya’t naghinala silang posibleng itinanim lang ito ng pulisya lalo na’t kaliwa ang hawak ng baril gayong hindi naman kaliwete si Kian.</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>17 YEARS OLD NA HIGH SCHOOL STUDENT SA CALOOCAN,NAPATAY SA ANTI-DRUGS OPERATION NG PNP Magkahalong reaksyon ng pag supporta at pagkundena sa ginawang 1 time big time anti-drugs operation ng PnP coloocan, ito ay matapos na mapatay si Kian Delos Santos, 17 years old ng Caloocan city, Metro Manila Magkahalong mga reaksyon din na lumabas mula sa iilang mga senators kabilang na ang mga pagkabahang reaksyun ni senator JV Ejercito na membro ng Senate Majority block na nagsabi sa kanyang twitter account. " The killing of 17 year old Kian Llyod Delos Santos in the latest war against drugs is very-very disturbing. Samantala, umani naman ng magkakahalong reaksyun ang mga netizens matapos na lumabas sa social media facebook ang press conference ni senator Risao Hontiveros kaugnay sa naging pahayag nito na d umanoy pag abuso ng PNP sa nasabing operasyon na naging daan sa pagkamatay ni Kian. narito ang nasabing video. Ang video na ito ay kaagad na nag trending sa social media at umani ng sari-saring kumento ng anti at pro government. Samantala, sa interview na ginawa ng TV5, mariing pinag gigiitan ng mga magulang ni Kian na gawa-gawa lamang ng pulisya na nag paputok ng baril ang kanilang anak dahil imposibleng magkapag sukbit ito ng baril samantalang naka boxer short lamang ito ng mga panahong iyun. labis naman na nag palakas ng hinala na planted umano ang baril dahil kung totoong namaril ito ay dapat ay wala sa kaliwa kamay ni Kian ang baril dahil hindi naman ito kaliwete.</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -1818,17 +2001,20 @@
           <t>Nilinaw ni Presidential Communications Operations Secretary Herminio Coloma Jr. na ang Pebrero 25 ay special holiday para lang sa mga paaralan sa bansa at mananatiling isang working day para sa mga empleyado.</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C51" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -1843,17 +2029,20 @@
           <t>Ang mga nasabing stickers ay tila nagbibigay-suporta para sa ikalawang pinakamataas na opisyal ng bansa sa gita ng mga alegasyon ng korupsyon na kanyang kinakaharap.</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C52" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -1868,17 +2057,20 @@
           <t>MAYNILA, Pilipinas - Lumapag na sa Ninoy Aquino International Airport (NAIA) nitong Miyerkules, ika-29 ng Agosto, ang eroplanong sinasakyan ng mahigit 100 Filipino na nakauwi sa bansa matapos maaprubahan ang kanilang amnesty sa United Arab Emirates (UAE). Umabot sa 129 ang bilang nga mga Pinoy na nakabalik na sa bansa lulan ng Philippine Airlines flight PR657 bandang 8:40 ng umaga. Sila ang pangalawang batch ng amnesty beneficiaries na nakauwi na sa Pilipinas. Karamihan sa kanila ay nagmula sa Abu Dhabi at Al Ain at pinalad na maaprubahan ang aplikasyon sa amnesty program na inialok ng UAE mula Agosto 1 at magtatagal hanggang Oktubre. Dahil dito umabot na sa 345 ang kabuuang bilang ng mga Pinoy na nabigyan ng amnesty at nakabalik sa Pilipinas. Ang unang batch na umabot sa 216 ay lahat nagmula sa Dubai at dumating sa bansa noong Agosto 16. "This is the first mass repatriation of amnesty-seekers carried out by the Philippine Embassy in Abu Dhabi since the amnesty started on August 1," ani Von Ryan G. Pangwi; third secretary at vice-consul ng Philippine Embassy sa Abu Dhabi, sa panayam ng Gulf News. Ayon pa kay Pangwi, umabot na sa mahigit 2,000 Pinoy ang nag-apply ng amnesty at ginagawa nila ang lahat para maaprubahan ang kanilang dokumento. Karamihan umano sa mga ito ay mga overstaying. Ganunpaman, mahigit sa 90 porsiyento ng mga amnesty seekers sa Abu Dhabi ay gusto pa ring manatili sa UAE upang maghanap ng trabaho sa loob ng anim na buwan. Ang Department of Foreign Affairs (DFA) ang sumagot sa mga immigration fees at plane tickets ng umuwing mga Pinoy. Bukod dito, nakatanggap din sila ng $100 (P5,000) mula sa DFA bilang tulong pinansiyal.</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C53" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>international news</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -1893,17 +2085,20 @@
           <t>Matapos maaresto nitong mga nakaraang araw ang 17-anyos na suspek sa pagpatay at pagbalat sa mukha ni Christine Lee Silawan, pinakawalan ito mula sa kustodiya ng Department of Social Welfare and Development (DSWD). Ipinag-utos ng Prosecutor Office sa Lapu-Lapu Cty ang paglaya ng suspek dahil sa inbalidong warrantless arrest. Hindi daw kasi natupad ang "hot pursuit" doctrine. Nangyare daw kasi ang pag-aresto sa salarin lagpas isang linggo nang mangyari ang krimen. Ang paglaya ng suspek ay kinumpirma mismo ng nanay nito. Ang menor de edad na suspek ay dating kasintahan ng biktima. Ayon sa ilan ulat, nag-ugat daw ang krimen dahil sa matinding selos nito sa dalaga. Nai-ugnay ang salarin sa krimen dahil sa nakalap na pag-uusap ng biktima at ng suspek sa cellphone at ilang CCTV footage. Inihatid naman ngayong araw sa huling hantungan si Silawan.</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C54" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -1918,17 +2113,20 @@
           <t>"As chair of the Senate peace, reconciliation and unification committee, and as a senator from Mindanao, I am calling today for the creation of truth commission which will conduct a thorough and impartial probe on the massacre of more than 40 members of our elite Special Action Force Unit of the Philippine National Police in Mamasapano, Maguindanao. It will be a cruel injustice if the truth behind the incidents that led to their death is not uncovered," ani Guingona.</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C55" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -1943,17 +2141,20 @@
           <t>Kaninang umaga, umugong sa social media ang balitang diumano’y may lihim na kasunduan sa pagitan ni Secretary Alonzo Rivera at ilang dayuhang negosyante kung saan pinapayagan umanong magtayo ng underground data center sa loob mismo ng isang government facility kapalit ng milyong pisong “consultancy fee” na hindi umano idinedeklara sa opisyal na talaan; ayon sa isang anonymous na source na nagpakilalang dating empleyado ng ahensya, matagal na raw pinaplano ang proyekto at ginagamit ang mga confidential fund para itago ang mga transaksyon, kaya’t marami ang nagtatanong kung bakit biglang dumami ang high-tech na kagamitan at kakaibang security protocols sa paligid ng opisina ni Secretary Rivera, dahilan para magdulot ng pagdududa sa publiko kung may mas malalim pang layunin sa likod ng proyektong ito na hindi sinasabi sa mga ordinaryong mamamayan.</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C56" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -1968,17 +2169,20 @@
           <t>Viral ngayon ang post ng magandang anak ni Attorney Larry Gadon na si Alarice. Sa kanyang social media post, ipinagmalaki niya ang katangian ng kanyang ama at kung bakit iboboto niya ang kanyang tatay. Ayon kay Alarice, iboboto niya si Attorney Gadon hindi dahil daddy niya ito. "#BOBOto ko sya not just because he's my dad. Iboboto ko sya dahil alam ko kung paano sya magmahal. Mapagmamalaki ko din na he's the type na hindi humihingi ng kapalit. Katunayan nyan, sa dami ng tinulungan ng papa ko, hindi sya yumaman sa pera. Yumaman sya sa mga kaibigan ," kwento ni Alarice. Ayon kapa kay Alarice, matalas lang daw talaga ang dila ng kanyang ama dahil passionate daw ito sa mga bagay na pinaniniwalaan. "Hindi din sya plastic, matalas man minsan ang dila nya pero it's because he's very passionate with the things he really believes in," sabi pa ni Alarice. Noong una raw ay ayaw da ni Alarice na pasuking ng kanyang ama ang mundo ng pulitika dahil alam niya kung gaano kagulo ito. Pero naniniwala siya ng lubos na may maitutulong ang kanyang ama sa bayan. "Sabi ko nga nung 2016 sa post ko, ayoko sana sya tumakbo dahil magulo ang mundo ng pulitika. Gusto ko man syang ipagdamot, mas naniniwala akong may maitutulong sya lalo na kung mahal nya yung ginagawa nya... #Boboto kita Atty Larry Gadon dahil alam kong mamahalin mo ang magiging tungkulin mo kung sakaling pagpalain ka. Iboboto kita dahil alam ko kung paano ka magmahal, maglaan ng oras at magsakripisyo," dagdag ni Alarice. Ibinunyag din ni Alarice na ika-61 kaarawan na din ni Atty. Gadon. "Birthday nya today and my only wish is for him to have more healthy years to come, kasi kailangan nya maging strong para sa mga bagay na mahal nya.... Happy 61st birthday Papa, dati pa man ikaw lang Senator ko," pagbati ni Alarice sa kanyang ama. Banag isiusulat ang blog post na ito ay umabot na sa 2,000 mahigit ang nag-share ng post ni Alarice at bumohos angpagbati sa kanyang ama sa coment section.</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C57" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -1993,17 +2197,20 @@
           <t>Hindi magtatagumpay ang anumang impeachment complaint laban kay Pangulong Benigno S. Aquino III na may kaugnayan sa madugong Mamasapano operation dahil wala itong basehan, ayon sa isang opisyal ng Palasyo. At dahil kumpiyansa rin ang Malacanang na hindi susuportahan ng mga mambabatas ang ano mang hakbang na patalsikin si Pangulong Aquino, naniniwala rin si Presidential Communications Operations Secretary Herminio Coloma Jr. na hindi nilabag ng Punong Ehekutibo ang Konstitusyon o trinaydor ang sambayanan hinggil sa naturang isyu. "The President has kept faith with the people's mandate. In all of his actions, he has abided by his sworn duty to preserve and defend the Constitution, do justice to every Filipino and promote the national interest," pahayag ni Coloma sa text message. "Fair minded representatives will find no basis for an impeachment complaint," dagdag niya. Ito ang reaksiyon ni Coloma sa mga ulat na tinutumbok ng ilang mambabatas ang posibilidad na maghain ng impeachment complaint laban kay Aquino dahil sa pumalpak na operasyon ng Philippine National Police-Special Action Force (PNP-SAF) sa Mamasapano, Maguindanao noong Enero 25, na 44 na police commando ang brutal na pinatay. Lumutang ang usapin sa impeachment matapos ihayag ng PNP Board of Inquiry na nilabag ng Pangulo ang chain of command matapos niyang pahintulutan ang suspendidong PNP chief na si Director General Alan LM Purisima na makialam sa operasyon laban sa wanted na Malaysian bomb expert na si Zulkifli Bin Hir, alyas "Marwan," at kanyang Pinoy na kakutsaba na siya Basit Usman. Binatikos ng Malacanang ang BOI report dahil sa pag-akusa kay Aquino na binalewala ang chain of command sa Mamasapano operation.</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C58" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -2018,17 +2225,20 @@
           <t>Ngunit sa isang ulat para markahan ang World AIDS Day noong Disyembre 1, nagbabala ang ONE campaign, isang advocacy group na nagtatrabaho upang wakasan ang kahirapan at preventable disease sa Africa, na ang pag-abot sa milyaheng ito ay hindi nangangahulugan na malapit nang magwakas ang AIDS. "We've passed the tipping point in the AIDS fight at the global level, but not all countries are there yet, and the gains made can easily stall or unravel," sabi ni Erin Hohlfelder, director of global health policy ng ONE. Ang human immunodeficiency virus (HIV) na nagdudulot ng AIDS ay naikakalat sa pamamagitan ng dugo, semen at gatas ng ina. Wala pang gamot para sa impeksiyon, ngunit ang AIDS ay maaaring maantala sa loob ng maraming taon sa tulong ng paginom ng maraming antiretroviral drugs. Ipinakikita ng datos ng United Nations na noong 2013, 35 milyon katao ang nabubuhay na may HIV, 2.1 milyong katao ang bagong nahawaan ng virus at may 1.5 milyong katao ang namatay sa AIDS. Sa talang ito, ang pinakamalaking bahagi ng bigat ng HIV/AIDS ay nasa sub-Saharan Africa. Ang pandemya ng AIDS ay nagsimula mahigit 30 taon na ang nakalipas at pumatay na ng umaabot sa 40 milyong katao sa buong mundo. Sinabi ng United Nations AIDS agency, UNAIDS, na nitong Hunyo 2014, may 13.6 milyong katao sa buong mundo ang mayroon nang access sa AIDS drugs, isang malaking pagbabago sa 5 milyon na nakakukuha ng treatment noong 2010. "Despite the good news, we should not take a victory lap yet," sabi ni Hohlfelder. Binigyang diin niya ang ilang banta sa kasalukuyang progreso, kabilang na ang $3 bilyong kakulangan sa pondo na kinakailangan bawat taon para kontrolin ang HIV sa buong mundo.</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="C59" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>health misinformation</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -2043,17 +2253,20 @@
           <t>Ayon sa mga source na malapit sa industriya ng showbiz, umugong ang balita ngayong araw na nahuli umano sa isang sikretong party si Maxine Villanueva, ang rising star ng teleserye “Pusong Ligaw,” habang palihim na nakikipagkita sa isang kilalang producer na kasalukuyang may asawa, dahilan para umani ng batikos at intrigang nag-viral agad sa social media; ayon pa sa mga nakasaksi, nagkaroon pa raw ng mainit na pagtatalo sa pagitan ni Maxine at ng asawa ng producer nang biglang dumating ito sa venue, kung saan narinig pa umano ang malalakas na sigawan at may mga basong nabasag, kaya’t hindi naiwasan ng mga netizen na maglabas ng sari-saring opinyon at memes tungkol sa umano’y love triangle, habang nananatiling tikom ang bibig ng kampo ni Maxine at ng producer ukol sa tunay na nangyari sa kontrobersyal na gabi.</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C60" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -2068,17 +2281,20 @@
           <t>Hindi tinanggap ni Vice President at Liberal Party (LP) chairman Leni Robredo ang pagbibitiw sa pwesto ng ni Sen. Francis "Kiko" Pangilinan bilang presidente ng partido. Mababatid rin na nag-resign si Quezon City Representative Christopher "Kit" Belmonte bilang secretary general ng partido. Sa inilabas na pahayag, sinabi ni Atty. Barry Gutierrez, tagapagsalita ni Robredo, marami pang kailangang gawing trabaho at kailangan itong gawin ng dalawa nang magkasama. Nagbitiw si Pangilinan para akuin ang responsibilidad sa pagkatalo ng Otso Diretso sa katatapos na 2019 midterm elections. Sa walong pambatong senador ng LP, si re-electionist senator Bam Aquino ang nakakuha ng pinakamataas pwesto na ika-14. Si dating LP president at DILG Secretary Mar Roxas naman ay nasa pang-16 na pwesto.</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="C61" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -2093,17 +2309,20 @@
           <t>Ang militanteng natatakpan ng itim na tela ang mukha habang may hawak na kutsilyo ang napanood sa mga video na inilabas ng Islamic State sa pagpugot sa mga bihag, kabilang ang ilang Amerikano, Briton at Syrian.</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C62" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>international news</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -2118,17 +2337,22 @@
           <t>Naaresto sa entrapment operation ng Philippine National Police - Criminal Investigation Detection Group (PNP-CIDG) at Presidential Anti-Corruption Commission (PACC) sina Bethshiba Bautista, Revenue District Officer ng Manila Bureau of Internal Revenue (BIR), at Rachel Villanueva, isang BIR Examiner, at mahaharap sila sa kasong direct bribery matapos mahuli sa 3rd floor ng BIR building sa Intramuros, Manila. Ayon kay CIDG Deputy Director for Administration C/Supt. John Luglug, agad nilang nakuha ang perang ginamit sa operasyon mula mismo sa mga suspek. Sinabi ng mga otoridad na layunin nilang matigil ang korapsyon sa BIR, at ayon kay PACC Commissioner Greco Belgica, kailangang bawasan ang kapangyarihan at diskresyon ng mga examiner, RDO, at supervisor, gayundin ang pagsimplify ng proseso at tax rates upang mawala ang pagkakataon ng mga opisyal ng BIR na magtakda ng halaga ng babayarang buwis. Maraming kababayan ang nagbigay ng komento ukol sa pagkakahuli ng dalawang kawani ng BIR.</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>Huli sa isinagawang entrapment operation ng Philippine National Police - Criminal Investigation Detection Group (PNP-CIDG) at ng Presidential Anti-Corruption Commission (PACC) sina MANILA Bureau of Internal Revenue (BIR) - Revenue District Officer Bethshiba Bautista at si Manila BIR Examiner Rachel Villanueva. Mahaharap ang mga suspek sa kasong direct bribery. Ginawa ang pambibitag sa dalawa sa 3rd floor ng BIR building sa Intramuros, Manila. "Pagbigay ho ng pera, kaagad-agad ay umakyat na ang mga tao na natin doon and nakuha mismo sa suspek yung money na ginamit," sabi ni CIDG Deputy Director for Administration C/SUpt. John Luglug. Ayon sa otoridad, nais nilang maalis ang kalakaran ng korapsyon sa BIR. "The powers of examiners, the RDO and supervisors has to be cut and they will have no more power and discretion over assessment, process has to be simplified, tax rates has to be simplified, para 'yung kapangyarihan ng mga examiners at BIR officials sa discretion kung magkano ang babayaran mo ay mawawala," pahayag naman ni PACC Commissioner Graco Belgica.. Basahin ang naging komento ng ilan nating kababayan sa pagkakahuli sa dalawang kawani ng BIR.</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -2143,17 +2367,20 @@
           <t>Kinumpirma umano ng ilang netizens na nagkaroon ng kakaibang pag-ulan ng mga kulay asul na isda sa kabisera ng bansang Frantovia nitong nakaraang linggo, dahilan para magdulot ng matinding trapik at pagkaantala ng mga klase sa lungsod; ayon sa mga post sa social media, nagulat daw ang mga residente nang biglang bumagsak mula sa langit ang daan-daang maliliit na isda na tila raw galing sa dagat, at may mga nagsabing nagkaroon pa ng amoy-alat sa paligid na umabot hanggang sa mga opisina at palengke, kaya’t naglabas ng abiso ang lokal na pamahalaan na mag-ingat sa paglabas ng bahay habang iniimbestigahan pa ng mga eksperto ang posibleng sanhi ng insidente, ngunit marami ang naniniwala na ito raw ay senyales ng paparating na pagbabago sa klima ng Frantovia na dati nang napabalitang may kakaibang lagay ng panahon.</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C64" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>international news</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -2168,17 +2395,20 @@
           <t>Ano nga ba ang tunay na nangyari sa likod ng madramang police operation sa Barangay Mabini kagabi na ikinagulat ng buong komunidad? Ayon sa mga ulat, biglang bumalot ang tensyon sa lugar nang magsagawa ng sabayang raid ang mga pulis sa tatlong magkaibang bahay na umano’y ginagamit bilang taguan ng mga pekeng pera at iligal na paputok; kitang-kita raw ng mga residente ang mga armadong operatiba na bumaba mula sa mga itim na sasakyan at sabay-sabay na sumugod habang sumisigaw ng “Lupa!” dahilan para magtakbuhan ang ilang kapitbahay at may mga nagsabing narinig pa nila ang malalakas na putok na umalingawngaw sa buong kalsada, kaya’t mabilis na nag-viral sa social media ang mga kuha ng insidente at samu’t saring haka-haka ang lumabas kung may mga hinuli bang sindikato o kung may nakatakas pa, habang nananatiling tikom ang bibig ng mga opisyal tungkol sa buong detalye ng operasyon na ngayon ay tinaguriang “Operation Bagyong Itim” ng mga netizen.</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="C65" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -2193,17 +2423,20 @@
           <t>Isang malaking kaganapan ang nangyari ngayon araw. Sumuko na sa otoridad si Joemel Advincula, ang lalaking nagpakilalang si alyas "Bikoy". Ayon kay alyas Bikoy, scripted lang daw ang mga sinabi niya sa video series na naninira sa pamilya ni Pangulong Rodrigo Duterte at sa mga malalapit na tao sa Presidente. Base sa pagbubunyag ni Advincula, si Senador Antonio Trillanes at ilang personalidad sa Liberal Party ang kasama sa paggawa ng mapanirang video. Isiniwalat din niya na plano daw ni Trillanes na mailuklok sa pwesto si Vice President Leni Robredo bago matapos ang termino ng senador ngayon taon. "Ilang beses kami nagpupulong (ni Trillanes), nagpa-plano upang isakatuparan ang Project Sodoma. Ang project Sodoma ay isang proyekto para pabagsakin si Presidente Duterte at ang makaupo sa posisyon ay si Vice President Leni Robredo. Hinahabol ni Senator Trillanes bago magtapos ang term niya ngayong June 30, 2019," sabi ni Advincula. Ayon kay Advincula, nasilaw daw siya sa mga ipinangako sa kanya. Ilan sa ipinangako ay pagpapardon sa mga kasalukuyang kasong kanyang kinhaharap kung sakaling masira si Presidente Duterte at maupo sa Malacanang si Robredo. Isa pa sa ipinangako daw kay Advincula ay pwesto sa gobyerno. Panoorin ang ulat ng PTV ukol dito. Ito naman po ang buong press conference ni Advincula mula sa Facebook page ng PNP.</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C66" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -2218,17 +2451,20 @@
           <t>Ang hindi inaasahan na sagot ni dating pangulong Aquino sa mga paunang tanung ng Rappler,</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="C67" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -2243,17 +2479,20 @@
           <t>Kaninang umaga, nagulantang ang publiko matapos kumalat sa social media ang balita tungkol sa bagong patakaran ng gobyerno na tinatawag na “Piso Para sa Boto” kung saan diumano’y bawat registered voter ay bibigyan ng isang pisong insentibo tuwing eleksyon, na ayon sa mga opisyal ay layuning pataasin ang voter turnout at hikayatin ang partisipasyon ng mamamayan; mabilis namang nahati ang opinyon ng netizens, may mga nagsasabing makakatulong ito para mapalakas ang demokrasya habang ang iba ay nagdududa kung ito nga ba ay tunay na makabubuti o baka raw ginagamit lang ito para manipulahin ang resulta ng halalan, kaya’t marami ang nananawagan ng masusing imbestigasyon at transparency kaugnay ng implementasyon ng nasabing polisiya.</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="C68" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -2268,17 +2507,20 @@
           <t>Hindi napigilan ng kilalang matapang na broadcaster na si Ben Tulfo na banatan ang tweet ng Songbird na si Regine Velasquez patungkol sa pahayag ni Department of Foreign Affairs (DFA) Secretary Teddy Locsin na may kinalaman sa pangunguha diumano ng clams ng ilang Chinese fishermen sa Scarborough Shoal. Ayon kay DFA secretary Locsin, "I am not going down in history as a clam defender, okay? It's a complaint; we're looking into it; but these are just fucking food; no one goes to war for clams (maybe Oysters of Locquemariaquer) but they just happen to be our food. They should pay for them like in fish market." Dito binanatan ni Regine sa Twitter si DFA secretary dahil sa pagpapabaya umano nito sa mga Chinese na kumuha ng taklobo (giant clams) sa Scarborough Shoal. "Ang akala ko pa naman matalino ka. Ako ay [simpleng] tao lamang na may simpleng pagiisip. These people are invading our territory they are not just taking food [sinisira] nila ang ating karagatan!!!!" Sumagot naman si DFA secretary Locsin kay Regine: "Pero ang problem ay hindi po territorio natin yun. EEZ." Depensa ng kalihim na hindi raw ito teritoryo ng Pilipinas ngunit exclusive economic zone lamang. "We had no idea there were clams there and really I will not let this country go down to war or lose a useful economic partner just over environmental concerns for a world I care nothing about. I care only for my people and country," dagdag ng kalihim. Sa isang Facebook Live ni Ben Tulfo ito ang kanyang mga komento, "Ang mensahe ko sa 'yo, Regine Velasquez, next time you open your mouth, think. Make sure na may laman ang utak mo. Hindi mo ito balwarte. Yung kaalaman mo, itago mo na lang. Gawin mo na lang, una, kung paano ka manumbalik sa publiko na kilala ka pa, The Songbird of Asia." "Ano bang alam nitong si Regine Velasquez other than kumanta lamang? Ang isang entertainer na I'm not trying to pull down, I question yung kanyang credentials when it comes to college, I don't even know if she does have any subject in Political Science." "So, yung statement nitong si Regine Velasquez, for me, is something na nakisawsaw, nakiangkas sa isyu na wala naman talagang alam." Binanatan din ni Tulfo si Vice President Leni Robredo dahil sa pag-uudyok umano nito sa mga artista na magsalita tungkol sa isyu. "VP Leni, if I were have to talk to you about this, please don't encourage celebrities because they are not expert in the field. Huwag mong hikayatin ang mga celebrities lalung-lalo na ang mga pipit at mga laos na. Kasi naghahanap lang ng career ang mga iyan sas ocial media para mapansin," ani Tulfo. WATCH: REGINE, FEELING MAS MATALINO KAY TEDDY LOCSIN!</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="C69" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -2293,17 +2535,20 @@
           <t>Sa kanyang pahayag sa programang Harapan 2019, sinabi ni Otso Diretso Senatorial Candidate Attorney Romulo Macalintal na hindi sapat ang free tuition fees dapat daw ay may baon ang mga estudyante na ibibigay ng gobyerno. "Oo nga, binigyan mo nga siya ng libreng tuition fees. Eh pano ang kanyang baon papunta sa eskwelahan? Yan ang problema sa ating bansa, bigay tayo ng bigay ng free tuition fees pero hindi natin naiisip na kailangan ang sustenance para sila ay makapag-aral... Kaya para sakin, allowance ng mga estudyante ay dapat mabigay ng ating pamahalaan," sabi ni Macalintal Magugunitang pinirmahan ni Pangulong Rodrigo Duterte noong 2017 ang Republic Act 10931 o ang Universal Access to Quality Tertiary Education Act. Kayon ng batas na gawing libre ang matrikula sa mga state universities at colleges sa buong bansa. Ang pahayag naman ni Macalintal tungkol sa free tuition fee ay pinalagan ng ilang netizens. Ang pahayag naman ni Macalintal tungkol sa free tuition fee ay pinalagan ng ilang netizens. "Nilibre na nga ng tuition pati ba naman pang baon problemahin pa ng gobyerno? Aba eh gusto ata ni Macalinta..maging palabigasan ang gobyerno.," sabi ni A. Dela Cruz. "Tongue ina. Buti na nga libre na eh. Nung panahon natin dyamante pa lahat. Sarap sagasaan itong mamang ito," sabi ni M. Santos. "hnd lahat libre. taeh boplaks ng ampaw nato. kami ngang nagddialysis may libreng 90 session from philhealth alangang umasa pa kmi libre gamot galing saknila. tinuturuan mo mga kabataan maging pala asa. tse!," sabi ni P. Lealrvian.</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C70" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -2318,17 +2563,22 @@
           <t>Matapos maaresto si Rappler CEO Maria Ressa dahil sa kasong cyber libel na isinampa ng negosyanteng si Wilfredo Keng, nagtipon ang ilang grupo at mamamahayag upang kundenahin ang nangyari sa kanya, at inilathala ng Rappler ang mga larawan mula sa ginanap nilang Black Friday protest, bagaman kapansin-pansin na walang aerial shots na kasama. Ang kaso ay nag-ugat sa isang artikulo ng Rappler noong 2012 kung saan naiuugnay si Keng sa smuggling ng bawal na gamot at human trafficking, at ayon kay Keng, sinubukan niyang makipag-usap sa Rappler upang ipatanggal ang artikulo ngunit hindi ito ginawa ng nasabing news site. Inaresto si Ressa ng National Bureau of Investigation (NBI) noong Miyerkules, at matapos magpalipas ng magdamag sa NBI, nakalaya siya kinabukasan matapos magpiyansa. Ibinahagi rin ng Facebook page na VOVph ang ilang larawan kaugnay ng mga kaganapan.</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>Matapos maging laman ng social media at ng balita si Rappler Chief Executive Officer Maria Ressa dahil sa pagkaka-aresto nito sa kasong cyber libel, nagtipon-tipon ang ilang grupo at journalists para kundenahin ang sinapit ni Ressa. Inilathala ng Rappler ang ilang larawan sa ginawang nilang Black Frieday protest pero kapansin-pansin na tila walang bird's eye view shots o aerial shots. Si Ressa ay nahaharap sa kasong cyber libel na isinampa ng negosyanteng si Mr. Wilfredo Keng. Si Keng ay naiugnay sa smuggling ng bawal na gamot at human trafficking sa isang artikulo ng Rappler noong 2012. Sa isang pahayag, sinabi i Keng na nakipag-usap daw siya noon sa Rappler para ipatanggal ang nasabing artikulo pero hindi daw ito ginawa ng Rappler. Si Ressa ay inaresto ng mga tauhan ng National Bureau of Investigation (NBI) noong Miyerkules. Namalagi si Ressa ng magdamag sa NBI pero nakalaya din matapos makapagpiyansa noong sumunod na araw. Ito naman po ang mga larawan na ibinahagi ng Facebook page na VOVph.</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -2343,17 +2593,22 @@
           <t>Usap-usapan ngayon sa social media ang diumano’y panggagaya ng kinatawan ng Thailand na si Ingchanok Prasart sa trademark na "lava walk" ni Miss Universe 2018 Catriona Gray sa Miss Intercontinental 2018, matapos mapansin ng netizen na si Marnie Raro sa Twitter ang paraan ng paglalakad at pag-project ni Miss Thailand na tila kinopya ang estilo ni Catriona. Bukod dito, napansin din ng mga netizens ang pagkakahawig umano ng "Mayon Volcano gown" ni Miss Vietnam sa gown ni Catriona. Inamin naman ng dalawa na hinahangaan at inspirasyon nila si Catriona Gray. Nagkaroon ng iba’t ibang reaksyon mula sa netizens, kung saan may ilan na nagsabing malaki ang impluwensya ni Catriona at kahit gayahin man siya, siya pa rin ang orihinal. Maraming aspiring beauty pageant candidates ang tumitingala kay Catriona, hindi lang sa Pilipinas kundi sa buong mundo, at inamin din ito ng maraming kandidata sa pageant. Ang 47th edition ng Miss Intercontinental ay ginanap noong Enero 26, 2019 sa SM Mall of Asia Arena sa Pasay, Metro Manila, Philippines, kung saan kinoronahan ni Miss Intercontinental 2017 Veronica Salas Vallejo ng Mexico ang Pilipinang si Karen Juanita Gallman, at ito rin ang unang beses na naging host ang Pilipinas sa pageant na ito matapos piliin ng Japan organizers ang bansa bilang venue dahil abala ang Japan sa paghahanda para sa 2020 Summer Olympics.</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>Usap-usapan ngayon sa social media ang umano'y panggagaya ng kinatawan ng Thailand na si Ingchanok Prasart sa ginanap na Miss Intercontinental pageant 2018 sa trademark ni Miss Universe 2018 Catriona Gray na "lava walk." Isang netizen sa Twitter na nagngangalang Marnie Raro ang nakapansin sa paraan ng paglalakad at pag-project ni Miss Thailand na parang kinokopya ang "lava walk" ni Catriona. Bukod kay Miss Thailand, napansin din ng mga netizens ang pagkopya umano sa "Mayon Volcano gown" ni Miss Vietnam. Aminado naman ang dalawa na labis nilang hinahangaan at inspirasyon nila si Miss Universe 2018 Catriona Gray. Halo-halo naman ang naging reaksyon ng mga netizens hinggil dito. "So now everyone looks like Catriona Gray. From hair to stance to gowns. The influence. Only legends do that." "Catriona Gray's walk can never be perfect without her walking it." "I think so? Even the hand gesture of Miss Thailand seems copied too. Catriona Gray is indeed a queen." "Yet they can't copy the original. Because there will be only one Lava Walk and Catriona Gray." "Kayo na 'yung may mga originality... hala gawa kayo sarili niyong pageant, ano ba naman yung hayaan niyo na lang sila hays....daming toxic." Isang patunay lamang ito na maraming mga aspiring beauty pageant candidates, hindi lamang sa Pilipinas kundi maging sa buong mundo, ang tumitingala at humahanga kay Catriona. Aminado naman dito ang marami sa mga kandidata ng naturang katatapos na pageant. Ang 47th edition ng Miss Intercontinental 2018 ay ginanap noong Enero 26, 2019, sa SM Mall of Asia Arena sa Pasay, Metro Manila, Philippines. Kinoronahan ni Miss Intercontinental 2017 Veronica Salas Vallejo ng Mexico ang kandidata ng Pilipinas na si Karen Juanita Gallman. Ito ang kauna-unahang pagkakataong naging host ang Pilipinas sa pageant na ito. Pinili ng Japan organizers ang Pilipinas na maging venue ng pageant dahil abala ang bansang Japan sa mga paghahanda para sa 2020 Summer Olympics. Narito ang buong Twitter post ng netizen:</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -2368,17 +2623,20 @@
           <t>Paalala sa mga kababayan natin sa Singapore: maging maingat at panatilihin ang kalinisan at sanitasyon sa lahat ng oras. Naitala ngayon sa Singapore ang kauna-unahang kaso ng rare monkeypox virus na nakapasok sa kanilang bansa, mula sa ulat ng ABS-CBN News at Rappler. Ang nasabing monkeypox ay kahalintulad umano ng human smallpox na tuluyang napawi noong 1980, kasunod ng global immunization campaign sa pangunguna ng World Health Organization. Hindi naman umano madaling maikalat at makahawa ang nabanggit na monkeypox subalit sa mga ilang pagkakataon, maaari itong magdulot ng kamatayan sa magiging biktima nito. Karaniwan daw na tumatagal ang monkeypox sa loob ng dalawa hanggang apat na linggo. Magsisimula ito sa mataas na lagnat o trangkaso, at di kalauna'y magdudulot ng "bumps" na kung tawagin ay "pustules" at kumakalat sa iba't ibang bahagi ng katawan ng pasyente. Ayon sa US-based Centers for Disease Control and Prevention, tatlong beses pa lamang nakapagtala ng mga kaso ng monkeypox infections sa labas ng Africa, sa United States, sa United Kingdom at Israel. Batay sa ulat ng Ministry of Health (MOH) ng Singapore nitong Huwebes, nakapasok ang nasabing monkeypoxvirus sa kanilang bansa dala ng isang 38-taong gulang na Nigerian na dumating sa Singapore noong Abril 28 ng kasalukuyang taon. "While risk of spread is low, MOH is taking precautions," saad ng Singapore Ministry of Health. Sa imbestigasyon ng mga awtoridad, bago umano dumating sa Singapore ang nasabing monkeypox virus-infected na Nigerian ay dumalo muna ito sa isang kasalan sa Nigeria. Maaari umanong nakakain ito roon ng bushmeat na siyang posibleng pinagmulan ng virus transmission. Ang "bushmeat", o 'yung tinatawag ding "wildmeat", ay bahagi ng dyeta ng mga Africano na maaaring mula sa karne ng gorilla, chimpanzee, antelope, birds, o maging rodents. Kasalukuyan na rin umanong naka-quarantine ang 23 kataong nagkaroon ng close contact sa nasabing Nigerian at oobserbahan sila sa loob ng 21 araw.</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
+      <c r="C73" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>health misinformation</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -2393,17 +2651,22 @@
           <t>Umani ng iba’t ibang reaksyon mula sa netizens ang isang larawang kumalat sa social media kung saan makikita ang opposition coalition na Otso Diretso, kabilang si LP Senatorial Candidate Samira Gutoc Tomawis, na dumalo sa misa sa Caloocan Cathedral matapos ang kanilang kick-off rally. Si Tomawis, na dating miyembro ng Bangsamoro Transition Commission na tumulong sa pagbalangkas ng Bangsamoro Basic Law, ay pinuna ng ilang netizens dahil sa kanyang pagdalo sa misa bilang isang Muslim. Ayon kay Hasmin Min, na-turn off siya sa pagsama ni Tomawis sa loob ng simbahan at sinabi pang naiintindihan naman dapat ng kanyang mga kaalyado ang kanyang relihiyon. May mga netizens din na tinawag na "pakitang-tao" ang pagdalo ng grupo sa misa, tulad ng komento ni M. Castro na nagulat na pati ang isang Muslim ay sumama sa simbahan. Bukod dito, may ilan ding pumuna na ginagamit umano ng ilang pulitiko ang simbahan para sa kanilang kampanya, gaya ng matinding komento ni G. Tolentino. Gayunpaman, may mga netizens na nagtanggol sa mga kandidato at sinabing bahagi lamang ito ng pakikisama, at ipinunto na ipinagdarasal din naman sila ng mga taga-simbahan.</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>Umani ng samu't saring batikos mula sa ilang netizens ang isang larawang naka-post sa social media, kung saan makikitang dumalo sa isang misa sa Caloocan Cathedral ang opposition coalition na Otso Diretso. Ang nasabing larawan ay kuha umano matapos ang kick-off rally ng kuwalisyon, kung saan kabilang ang LP Senatorial Candidate na si Samira Gutoc Tomawis. Matatandaang si Tomawis ay naging miyembro ng Bangsamoro Transition Commission na naatasan sa pagbalangkas ng Bangsamoro Basic Law o BBL. Komento ng isang netizen, kataka-taka umano ang pagpasok sa isang simbahan at pagdalo ng misa ni Tomawis. "Ibubuto ko sana si samira gutoc ,kaso na na turn off na ako sa pagsama niya pati sa loob ng simbahan ,pwd naman hindi siya sumali jn maitindihan naman ng mga ka line up niya dahil isa siyang muslim," sabi ni Hasmin Min. Tinawag ding "pakitang-tao" ng ilang netizens ang pagdalong ito ni Tomawis at ng kanyang mga kaalyado sa nasabing misa. "Hala bakit pati ung muslim na babae nag simba rin.Ano pakitang tao hahaha," sabi ni M. Castro. Samantala, pinuna rin ng ilan ang tila umano "paggamit" ng ilang pulitiko sa Simbahan para sa kanilang pangangampanya. "OTSO DIRETSO SA INODORO. T-- -- nyo talaga pati simbahan ginagamit nyo na sa pamumulitika mga animal kayo.," sabi ni G. Tolentino. Sa kabilang dako, kinontra rin naman ng ibang netizens ang mga nasabing pahayag ng ilan dahil ayon sa kanila, bahagi lang umano ito ng "pakikisama" ng mga nabanggit na kandidato Tignan niyo po kung paano na lang ipag-pray over ng mga taga-simbahan ang mga oposisyon. Ano'ng masasabi niyo, mga kaibigan?</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>religion</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -2418,17 +2681,20 @@
           <t>Hinadlangan ng masamang panahon ang paghahanap, kayat hindi maaninag ng divers ang wreck ng Airbus A320-200, na bumulusok noong Linggo sa biyahe nito mula sa lungsod ng Surabaya sa Indonesia patungong Singapore sakay ang 162 katao.</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
+      <c r="C75" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>international news</t>
         </is>
       </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -2443,17 +2709,20 @@
           <t>Pinangunahan ni Konrad Krajewski, ang arsobispong namamahala sa charity work ng papa, ang operasyon ng isang minibus na puno ng 400 sleeping bags na may papal ensign na umikot sa buong kabisera ng Italy noong Miyerkules ng gabi at naghahanap ng mga taong mapagbigyan nito.</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
+      <c r="C76" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>sports</t>
         </is>
       </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -2468,17 +2737,22 @@
           <t>Napakahirap maging biktima ng aksidente dahil bukod sa pagkawala ng buhay at ari-arian, mas lalong masakit kapag imbes na tulungan ay pinagnanakawan pa ang mga biktima. Ganito ang dinanas ng ilang nakaligtas sa banggaan ng isang truck at pampasaherong bus sa Atimonan, Quezon noong Lunes ng gabi, ayon sa ulat ng GMA News. Ayon sa survivor na si Izen Maghiran, nang balikan niya ang bus para kunin ang gamit niya, nadatnan niyang may mga hindi pasahero sa loob, kabilang na ang mga lalaking nakahubad na naghahalungkat ng mga bag at nagnanakaw ng pitaka at pagkain. Sa insidenteng ito, tatlo ang namatay kabilang ang drayber at assistant ng truck at isang pasahero ng Elavil AMV Travel and Tours bus, habang 73 ang nasugatan. Ang bus ay patungong Bicol at nakabangga ng 10-wheeler cargo truck na papuntang Maynila sa Diversion Road, Barangay Sta. Catalina. Batay sa imbestigasyon ng pulisya, sirang preno ng bus ang sanhi ng aksidente at ayon kay Police Major Michael Encio, may mga pasaherong nagsabing mula pa Maynila ay may problema na ang bus at nawalan ito ng kontrol habang nag-overtake, dahilan para magsalpukan ang dalawang sasakyan. Inamin din ng bus driver na si Maximo Leorigo na may problema na ang preno ng bus at ibang drayber ang nagmaneho nito bago siya, at kasalukuyan siyang nasa kustodiya ng pulisya.</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>Napakahirap maging biktima ng trahedya o aksidente. Maraming buhay ang nawawala, mahahalagang gamit ang nasisira, at mga pangarap na gumuguho, para sa mga nawawalan ng mga mahal sa buhay sa mga ganitong di-inaasahang pagkakataon. Doble pa ang sakit kapag 'yung mga inaaasahan mong taong tutulong sa'yo ay gagawan ka pa ng masama. Mabigat ang loob ng ilan sa mga nakaligtas sa naganap na banggaan ng isang truck at pampasehorong bus sa Atimonan, Quezon nitong nkaraang Lunes nang gabi, mula sa ulat ng GMA News. Kuwento kasi ng ilang pasahero, sa halip na tulungan umano sila sa pagkakaaksidente ay pinagnakawan pa umano sila ng mga kawatang nakapasok sa loob ng bus na kanilang sinasakyan. "Bumalik ulit ako ng bus para kunin ang mga gamit ko. Pag-akyat ko sa bus, meron nang mga hindi pasahero. May mga nakahubad na lalaki. Hinahalungkay 'yung.. 'yung iba naghahalungkay ng bag. 'Yung isa nakakuha ng dalawang pitaka. Pinasok niya sa bulsa niya. Imbes na tumulong eh ninakawan pa kami ng pera, pagkain," kuwento ng isang survivor na si Izen Maghiran. Tatlo ang namatay sa nasabing insidente, habang 73 naman ang iniulat na nasugatan. Kabilang sa mga nasawi ang drayber ng truck, ang kanyang assistant, at isang pasaherong nakasakay sa bus ng Elavil AMV Travel and Tours. Papunta sana sa Bicol ang nasabing bus nang makabanggan nito ang 10-wheeler cargo truck na pa-Maynila sa Diversion Road sa Barangay Sta. Catalina. Ayon sa imbestigasyon ng pulisya, napag-alaman na sirang preno ng bus ang naging dahilan ng pagkakasalpok nito sa truck. "Sa pag-iimbestiga namin, may kausap kaming mga pasahero dun ng bus. Mula pa lang sa Manila pumapalya na 'yun. Noong siya daw ay nag-over take ay nag-lose control. Tapos ay nagkataoon naman mayroong parating na truck. Nagkasalpukan," saad ni Police Major Michael Encio, hepe ng Atimonan Police. Samantala, aminado naman ang drayber ng bus na si Maximo Leorigo na nauna nang nagkaroon ng problema ang bus. Ibang drayber umano ang naunang nagmaneho nito, at hindi raw siya ang on-wheel sa Laguna. "Doon pa lang po sa taas, mababa na ang hangin ng preno ng aking bus," pahayag ni Leorigo na kasakalukuyang nasa kustodiya ng pulisya.</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>lifestyle / human interest</t>
         </is>
       </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -2493,17 +2767,20 @@
           <t>Isang OFW na nagngangalang Marlon Reyes mula sa isang maliit na bayan sa Pilipinas ang biglang sumikat sa social media matapos niyang umano’y iligtas ang buong gusali ng pinagtatrabahuhan niya sa Dubai mula sa isang kakaibang insidente ng pag-atake ng mga kuwago na nagdulot ng takot sa mga empleyado, ayon sa viral na video na kumakalat ngayon; makikita raw sa footage na walang takot na hinarap ni Marlon ang mga nagliparang kuwago gamit lamang ang walis tambo at isang lumang payong, dahilan upang palakpakan siya ng mga kasamahan at bigyan ng parangal ng kanilang kumpanya, kaya’t marami sa mga netizens ang humanga sa tapang ng Pinoy at may ilan pa ngang nagsabing dapat siyang gawing honorary citizen ng Dubai dahil sa ipinakitang kabayanihan, habang patuloy namang pinag-uusapan sa social media kung paano napadpad ang mga kuwago sa gitna ng disyerto at kung may kinalaman daw ba ito sa kakaibang init ng panahon ngayon.</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="C78" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>international news</t>
         </is>
       </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -2518,17 +2795,20 @@
           <t>Ayon sa ulat ng hindi pinangalanang foreign news agency, diumano’y nagdeklara ang pamahalaan ng bansang Norvonia ng “National Pajama Day” kung saan ipinag-utos umano sa lahat ng mamamayan na magsuot lamang ng pajama kahit sa opisina, paaralan at pampublikong lugar bilang bahagi raw ng kanilang kampanya para sa mental health awareness; mabilis na kumalat ang balitang ito sa social media na naging dahilan ng pagdagsa ng mga memes at reaksyon mula sa iba’t ibang bansa, habang may ilang netizens na nagtanong kung totoo nga ba na may multa ang sinumang mahuling hindi naka-pajama sa araw na iyon, at may mga nagsasabing baka raw ito ay hakbang ng Norvonia upang makilala bilang pinaka-relaxed na bansa sa buong mundo, kahit na wala namang opisyal na kumpirmasyon mula sa kanilang embahada tungkol sa naturang polisiya.</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
+      <c r="C79" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>international news</t>
         </is>
       </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -2543,17 +2823,20 @@
           <t>Nagsalita na sa unang pagkakataon sa harap ng media si Pangulong Rodrigo Duterte tungkol sa krimen na kinasasangkutan ni dating Bayan Muna Congressman Satur Ocampo at ng mga kasama nito. Ayon sa Presidente, kidnapping daw talaga ang ginawa ng kampo ni Ocampo dahil walang pahintulot ng mga magulang ang ginawang pagbiyahe sa mga kabataang lumad. Banat pa ng Pangulo, nialalgay sa kapahamakan ng mga komunista ang mga lumad. Nagpahayag din ng suporta ang Pangulo sa mga pulis at militar. "I support the police and the military. You know an ordinary person, lalo na kung senador (mambabatas) ka, you must be aware that you cannot remove children from one community to another without the consent of the parents. That is actually kidnapping... Eh nagreklamo 'yung mga victims. You heard they were lectured upon by the Lumads. And it's like controlling the lives of the natives... Iyan ang mahirap sa komunista, ginagamit nila ang Lumad. Kaya ang karamihan ngayon ang namamatay Lumad.... When they started to go to the mountains and wage a war there, they recruited ang pinaka vulnerable... Bakit pa tayo magbobolahan? Satur Ocampo is fronting Bayan. Bayan is a front of the CPP. We know that KMU, Gabriela, they're all communist fronts or being used by the communists. Alam ninyo lahat yan.,"sabi ng Pangulo. Basahin ang reaksyon ng mga tao sa naging pahayag ni Presidente Duterte sa isyu nila Satur Ocampo.</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
+      <c r="C80" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -2568,17 +2851,20 @@
           <t>Game na game sa pagsayaw ang first lady ng Uptown Funk ni Bruno Mars kasabay si Ellen at back up dancers. "There is some hip-thrusting," pabirong sabi ng first lady, 51, nang mahulog ang kanyang mikropono. "There is a lot of it."</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
+      <c r="C81" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -2593,17 +2879,20 @@
           <t>Viral ngayon sa social media ang babala tungkol sa isang bagong app na tinatawag na “FaceMorph Pro” na umano’y mabilis kumalat sa mga smartphone ng kabataan dahil sa kakayahan nitong gawing cartoon o anime-style ang mga larawan, ngunit ayon sa mga nag-post ng karanasan sa mga online group, napansin nilang biglang bumagal ang kanilang mga cellphone matapos gamitin ang app at may ilan pa na nawalan ng access sa kanilang mga personal na files; sinasabi ring may kakaibang pop-up messages na lumalabas tuwing gabi na nag-uudyok sa user na mag-click ng mga link na hindi nila alam ang pinagmulan, kaya’t naglabas ng paalala ang ilang tech enthusiast na i-uninstall agad ang FaceMorph Pro at huwag basta-basta magbigay ng permissions lalo na’t hindi pa raw ito verified ng mga kilalang app stores, dahilan upang dumami ang nag-aalala na baka posibleng ginagamit ang app para magnakaw ng data o magkalat ng malware sa mga gadgets ng unsuspecting na Pinoy users.</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
+      <c r="C82" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>technology</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -2618,17 +2907,20 @@
           <t>Ito ang napag-alaman sa isang mataas na opisyal ng POC na matagal nang ipinag-utos ang pagpapatawag ng isang general assembly sa asosasyon matapos magsumite ng kanyang indefinite leave of absence ang dating pangulo na si Gener Dungo subalit hindi naganap sa nakalipas na dalawang taon.</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
+      <c r="C83" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -2643,17 +2935,20 @@
           <t>Matapos ang ilang linggong pagod at stress sa trabaho, biglang naging viral online ang kwento ng isang barangay sa gitnang Luzon kung saan umano’y sabay-sabay na nagbakasyon ang lahat ng residente sa loob ng tatlong araw, iniwan ang kanilang mga bahay na bukas at walang bantay ngunit pagbalik nila ay wala ni isang gamit na nawala at mas malinis pa raw ang paligid nila kaysa dati; ayon sa mga post ng netizens, nangyari raw ito dahil nagkaisa ang mga taga-barangay na magtiwala sa isa’t isa at magtulungan, kaya’t habang nag-eenjoy ang lahat sa isang malapit na resort ay may ilang volunteer na naglinis ng paligid at nagbantay ng mga alagang hayop, dahilan para maging inspirasyon sa buong bansa ang kanilang samahan at pagtutulungan, kaya’t marami ang nagkomento na sana raw ay tularan ito ng ibang lugar at maging simula ng mas mapagkakatiwalaang komunidad sa Pilipinas.</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
+      <c r="C84" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>lifestyle / human interest</t>
         </is>
       </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -2668,17 +2963,20 @@
           <t>Hiniling din nito sa hukuman na bigyan sila ng sapat na panahon upang maisumite ang dokumento sa korte dahil karamihan aniya sa mga ito ay confidential alinsunod na rin sa mga batas sa bank secrecy at anti-money laundering. Agad namang tinutulan ito ni Paul Arias, abogado ni Senator Jinggoy Estrada kung saan sinabing binigyan na sila (ALMC) ng sapat na oras upang maihanda ang tinutukoy na dokumento at maaaring magpapaantala lamang ito sa pagdinig. Ibinasura ng anti-graft court ang argumento ni Arias at sinabi ng korte na humihingi lamang ng karagdagang panahon ang AMLC upang maiprisinta ang dokumento.</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
+      <c r="C85" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -2693,17 +2991,20 @@
           <t>Viral ngayon sa social media ang nakakatuwang kwento ni Jace Villanueva, isang aspiring singer na biglang sumikat matapos mag-trending ang video kung saan nag-perform siya sa isang maliit na kainan gamit ang improvised microphone na gawa sa plastic cup at cellphone, at kahit simple lang ang setup, napabilib niya ang lahat dahil sa kanyang malinis na boses at natural na charm; maraming netizens ang humanga sa dedikasyon ni Jace na kahit walang propesyonal na gamit ay ipinakita pa rin ang kanyang talento, kaya’t marami ang nagpaabot ng suporta at mensahe ng inspirasyon sa kanya, at ayon pa sa mga comments, nagsilbing motivation si Jace sa mga nangangarap makilala sa larangan ng musika na hindi hadlang ang kakulangan sa resources basta’t may tunay na passion at determinasyon.</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
+      <c r="C86" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -2718,17 +3019,20 @@
           <t>Iba talaga pahalagaan ni Pangulong Rodrigo Duterte ang mga kababyan natin Overseas Filipino Workers (OFW). Kaya hindi nakakapagtaka kung bakit marami sa mga kababayan nating OFW ang sumusuporta sa kanya. Sa kanyang talumpati, sinabi ng Pangulo na kung maari ay walang "human contact" sa mga kababayan natin para masigurado ang seguridad ng mga bagahe. "Kung mayroon improvement sa public service airport, one is that no more inspection sa bagahe papasok. Dala kayong dinamita, bala, marijuana, ok lang, walang bukas na iyan, pero pagdating mo sa labas doon naghihintay ang PDEA pati ang mga pulis. Pero I'd make it a point kasi gusto ko lang na no more opening of the bag at ngayon po wala na 'yung human contact sa immigation. All you have to do is to slide mo lang ang ano mo diyan. You just swipe your passport angd you can go, no more questions sa immigration. Ayt 'yung pagbalik palabas, I'm requiring them altogether to adapt the same system. Paglabas ninyo, swipe lang ninyo. No more human (contact) or question," sabi ni Presidente Duterte. Basahin ang naging komento ng mga kababayan natin sa naging pahayag ni Pangulong Duterte tungkol sa pagbabawal sa inspeksyon sa mga bagahe ng OFW.</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
+      <c r="C87" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>international news</t>
         </is>
       </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -2743,17 +3047,20 @@
           <t>Ang mga curators na mag-a- assess sa mga kasagutan at magdedetermina sa playlist ay kinabibilangan ng British singer-songwriters na sina Ed Sheeran at James Blunt, US singer-songwriter John Legend, French DJ David Guetta at Portuguese pop star David Carreira. Inanunsiyo ni UN Secretary-General Ban Ki-moon, na hindi nakilala sa kanyang rock star persona, ang inisyatiba sa isang MTV-style video kung saan ibinigay niya ang kanyang boto sa 1970 hit ni Stevie Wonder na "Signed, Sealed, Delivered." Sinabi ni Ban na ang awitin - kilalang paborito ni US President Barack Obama - ay kumatawan sa kanyang mga pag-asa para sa isang matagumpay na kasunduan sa climate change sa isang UN-led conference sa Paris sa huling bahagi ng taong kasalukuyan. Idineklara ng United Nations noong 2012 ang International Day of Happiness - na kasabay ng unang araw ng tagsibol sa Northern Hemisphere - matapos ang inisyatiba ng Bhutan, ang lupain sa Himalayan na sumusukat sa "Gross National Happiness" imbes na sa standard economic indicator. "On this day we are using the universal language of music to show solidarity with the millions of people around the world suffering from poverty, human rights abuses, humanitarian crises and the effects of environmental degradation and climate change," ani Ban. Noong nakaraang taon, ang International Day of Happiness ay inimbitahan ang music fans sa buong mundo na sumayaw sa patok na awitin ni Pharrell Williams na "Happy," na naging viral sensation.</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
+      <c r="C88" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -2768,17 +3075,22 @@
           <t>Ayon sa ulat ng Commission on Audit (COA), pumangalawa si Senador Antonio Trillanes sa may pinakamalaking ginastos sa Senado noong 2017, na umabot sa P87 milyon, kabilang na rito ang P15.7 milyon na ibinayad niya para sa mga consultants; si Senador Koko Pimentel naman ang may pinakamalaking nagastos na umabot sa P127 milyon noong siya pa ang Senate President, at paliwanag niya, inaasahan na mas mataas ang budget ng Senado dahil sa dagdag na responsibilidad ng lider nito. Hindi nakaligtas si Trillanes sa mga batikos mula sa mga tagasuporta ni Pangulong Duterte, na nagkomento tungkol sa laki ng gastos para sa mga consultant at kinuwestiyon ang paggamit ng pondo ng bayan, habang may ilan ding nagsabing mas mainam sana kung napunta na lang ang malaking halagang ito sa mga nangangailangan, tulad ng mga taga-Marawi at mahihirap na mamamayan.</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>Ayon sa ulat ng Commission on Audit (COA), pumapangalawa si Senador Antonio Trillanes na may pinakamalking ginastos sa senado noong 2017. Base sa COA report, may ginastos na P87 milyon ang pinakamalalang kritiko ni Pangulong Rodrigo Duterte. Nagbayad din daw si Trillanes ng P15.7 million para sa kanyang mga consultants. Ang senador na may pinakamalaking ginasta ay si Senador Koko Pimentel. Ayon sa ulat, P127 milyon ang ginastos nito noong Senate President pa ito noong 2017. Sa isang pahayag, sinabi ni Pimentel na expected daw ang halagang ginastos niya dahil siya ang namumuno sa senado. "The Senate President is allocated a higher budget because as the head of agency, he also has many additional responsibilities and functions," sabi ni Pimentel Hindi naman nakaligtas si Trillanes sa mga komento ng mga taga-suporta ni Pangulong Duterte. "Si asong u--, 15.7 Million binayad para sa mga consultants niya pero excel sheet, kathang isip na michael de mesa at kwentong barbero lang ang kayang ilabas nyang patunay sa mga kanyang mga alegasyon laban kanino man," sabi ni Moses Adaza "wala namang ginawa bukod sa paupo upo at presscon lang ganun na kalaki gastos ng mga gunggong na yan dami namin nghihirap sana sa mga nangangailngan nalang nilustay ganun kalaking pera," sabi ni Raymond Guzman "pera ng taong bayan ang pinagagastos nyo nagbabayad kami ng tax ngayon ginagamit nyo sa hnd magandang kalakaran!lalo na ikaw Tonyo ang laki ng pasahod mo sa mga consultant mo," sabi ni Venancio lazarte "Ang laki-laki ng gastos para lang sa mga taong naninira sa gobyerno! nagmamagaling dami palang consultant na tagabulong! haha," sabi ni Wendell Sarsonas "Maraming bahay na sana naipatayo para sa mga taga marawi.. Sayang lang pera nang taong bayan," sabi ni Eric Buenavista "Grabe ang expenditures nina Pemintel at trillanes... mahigit 200 million ang ginastos nila sa loob ng isang taon gamit ang pera ng bayan samantalang halus hindi makakain ang mga naghihikahus na dukhang mamamayan...," sabi ni Geron Traspoto</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -2793,17 +3105,20 @@
           <t>Usap-usapan ngayon sa social media ang umano'y panggagaya ng kinatawan ng Thailand na si Ingchanok Prasart sa ginanap na Miss Intercontinental pageant 2018 sa trademark ni Miss Universe 2018 Catriona Gray na "lava walk." Isang netizen sa Twitter na nagngangalang Marnie Raro ang nakapansin sa paraan ng paglalakad at pag-project ni Miss Thailand na parang kinokopya ang "lava walk" ni Catriona. Bukod kay Miss Thailand, napansin din ng mga netizens ang pagkopya umano sa "Mayon Volcano gown" ni Miss Vietnam. Aminado naman ang dalawa na labis nilang hinahangaan at inspirasyon nila si Miss Universe 2018 Catriona Gray. Halo-halo naman ang naging reaksyon ng mga netizens hinggil dito. "So now everyone looks like Catriona Gray. From hair to stance to gowns. The influence. Only legends do that." "Catriona Gray's walk can never be perfect without her walking it." "I think so? Even the hand gesture of Miss Thailand seems copied too. Catriona Gray is indeed a queen." "Yet they can't copy the original. Because there will be only one Lava Walk and Catriona Gray." "Kayo na 'yung may mga originality... hala gawa kayo sarili niyong pageant, ano ba naman yung hayaan niyo na lang sila hays....daming toxic." Isang patunay lamang ito na maraming mga aspiring beauty pageant candidates, hindi lamang sa Pilipinas kundi maging sa buong mundo, ang tumitingala at humahanga kay Catriona. Aminado naman dito ang marami sa mga kandidata ng naturang katatapos na pageant. Ang 47th edition ng Miss Intercontinental 2018 ay ginanap noong Enero 26, 2019, sa SM Mall of Asia Arena sa Pasay, Metro Manila, Philippines. Kinoronahan ni Miss Intercontinental 2017 Veronica Salas Vallejo ng Mexico ang kandidata ng Pilipinas na si Karen Juanita Gallman. Ito ang kauna-unahang pagkakataong naging host ang Pilipinas sa pageant na ito. Pinili ng Japan organizers ang Pilipinas na maging venue ng pageant dahil abala ang bansang Japan sa mga paghahanda para sa 2020 Summer Olympics. Narito ang buong Twitter post ng netizen:</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
+      <c r="C90" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -2818,17 +3133,20 @@
           <t>Ayon sa ulat ng isang anonymous na source mula sa online community group ng Barangay Maligaya, kabi-kabila na raw ang reklamo ng mga residente tungkol sa umano’y “Kulay Itim Gang” na sinasabing responsable sa sunod-sunod na pagkawala ng mga alagang hayop, appliances, at pati na rin mga motor sa loob ng subdivision tuwing madaling araw; kwento ng ilang biktima, tila may kakaibang paraan ang grupo dahil hindi raw nag-iiwan ng anumang bakas at palaging sabay-sabay ang pagkawala ng gamit sa magkakalapit na bahay, dahilan para magdulot ng matinding takot at kaba sa buong lugar, lalo na’t may mga nagsasabing nakakatanggap sila ng misteryosong text messages bago mangyari ang insidente na tila ba tinatakot pa ang mga target, kaya ngayon ay halos walang gustong lumabas ng bahay sa gabi at nagkakaisa ang mga residente na magpatrolya at maglagay ng dagdag na CCTV, habang patuloy na nagkakagulo ang social media sa pagkalat ng mga haka-haka na baka raw may kasabwat na taga-loob ang grupo at mas malala pa ang maaaring mangyari kung hindi ito agad masolusyunan ng mga awtoridad.</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
+      <c r="C91" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -2843,17 +3161,20 @@
           <t>PATAY ang isang chairman ng barangay matapos pagbabarilin ng dalawang hindi pa nakikilalang riding-in-tandem sa Tondo, Maynila Martes ng hapon. Binaril si Marcelino Ortega, chairman ng Barangay 199, Zone 18 sa panulukan ng Hermosa at Pilar st. ganap na alas-2:58 ng hapon, ayon kay Police Officer 3 Jimmy Pelagio. Idinagdag ni Pelagio na dinala si Ortega sa ospital bagamat idineklarang dead on arrival. Nagsasagawa na ng imbestigasyon ang mga otoridad kaugnay ng motibo sa pagpatay.</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
+      <c r="C92" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -2868,17 +3189,20 @@
           <t>Kung laging delayed ang sahod ng OFW sa Saudi Arabia , tumawag sa Ministry of Labor hotline no. 19911 at i-report ang employer na laging delay magpasahod</t>
         </is>
       </c>
-      <c r="C93" s="2" t="inlineStr">
+      <c r="C93" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>international news</t>
         </is>
       </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -2893,17 +3217,22 @@
           <t>Usap-usapan ngayon sa social media ang umano'y panggagaya ng kinatawan ng Thailand na si Ingchanok Prasart sa signature "lava walk" ni Miss Universe 2018 Catriona Gray sa Miss Intercontinental 2018 pageant, matapos mapansin ng netizen na si Marnie Raro sa Twitter ang paraan ng paglalakad at pag-project ni Miss Thailand na kahawig ng kay Catriona. Bukod dito, napansin din ng mga netizens ang pagkopya umano ni Miss Vietnam sa "Mayon Volcano gown" ni Catriona. Inamin naman ng dalawang kandidata na hinahangaan at inspirasyon nila si Catriona Gray. Iba-iba ang naging reaksyon ng mga netizens, may nagsabing malaki ang impluwensya ni Catriona sa mga kandidata, habang may ilan namang nagsabing hindi matutularan ang orihinal na "lava walk." Marami ring aspiring beauty pageant candidates, hindi lang sa Pilipinas kundi pati sa ibang bansa, ang humahanga kay Catriona, bagay na inamin ng ilang kandidata ng pageant. Ang 47th Miss Intercontinental 2018 ay ginanap noong Enero 26, 2019 sa SM Mall of Asia Arena sa Pasay, Metro Manila, kung saan kinoronahan ni Miss Intercontinental 2017 Veronica Salas Vallejo ng Mexico ang kandidata ng Pilipinas na si Karen Juanita Gallman, at ito ang unang beses na naging host country ang Pilipinas, matapos piliin ng Japan organizers ang bansa bilang venue dahil abala ang Japan sa paghahanda para sa 2020 Summer Olympics.</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>Usap-usapan ngayon sa social media ang umano'y panggagaya ng kinatawan ng Thailand na si Ingchanok Prasart sa ginanap na Miss Intercontinental pageant 2018 sa trademark ni Miss Universe 2018 Catriona Gray na "lava walk." Isang netizen sa Twitter na nagngangalang Marnie Raro ang nakapansin sa paraan ng paglalakad at pag-project ni Miss Thailand na parang kinokopya ang "lava walk" ni Catriona. Bukod kay Miss Thailand, napansin din ng mga netizens ang pagkopya umano sa "Mayon Volcano gown" ni Miss Vietnam. Aminado naman ang dalawa na labis nilang hinahangaan at inspirasyon nila si Miss Universe 2018 Catriona Gray. Halo-halo naman ang naging reaksyon ng mga netizens hinggil dito. "So now everyone looks like Catriona Gray. From hair to stance to gowns. The influence. Only legends do that." "Catriona Gray's walk can never be perfect without her walking it." "I think so? Even the hand gesture of Miss Thailand seems copied too. Catriona Gray is indeed a queen." "Yet they can't copy the original. Because there will be only one Lava Walk and Catriona Gray." "Kayo na 'yung may mga originality... hala gawa kayo sarili niyong pageant, ano ba naman yung hayaan niyo na lang sila hays....daming toxic." Isang patunay lamang ito na maraming mga aspiring beauty pageant candidates, hindi lamang sa Pilipinas kundi maging sa buong mundo, ang tumitingala at humahanga kay Catriona. Aminado naman dito ang marami sa mga kandidata ng naturang katatapos na pageant. Ang 47th edition ng Miss Intercontinental 2018 ay ginanap noong Enero 26, 2019, sa SM Mall of Asia Arena sa Pasay, Metro Manila, Philippines. Kinoronahan ni Miss Intercontinental 2017 Veronica Salas Vallejo ng Mexico ang kandidata ng Pilipinas na si Karen Juanita Gallman. Ito ang kauna-unahang pagkakataong naging host ang Pilipinas sa pageant na ito. Pinili ng Japan organizers ang Pilipinas na maging venue ng pageant dahil abala ang bansang Japan sa mga paghahanda para sa 2020 Summer Olympics. Narito ang buong Twitter post ng netizen:</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -2918,17 +3247,20 @@
           <t>Mga kababayan, hindi niyo gugustuhing palampasin ito: isang matinding balita ang sumabog ngayong umaga matapos umanong madiskubre na may lihim na grupo sa loob ng Kongreso na tinaguriang “Project Agila” kung saan diumano’y pinagpaplanuhan ng ilang mambabatas ang pagmanipula ng pondo ng bayan para sa personal nilang kampanya sa susunod na eleksyon, ayon sa mga nag-leak na dokumento na biglang kumalat sa social media; umani agad ito ng matinding galit mula sa netizens na nagtrending ng #AgilaExpose, at marami ang nagdududa kung sino-sino pa ang kasabwat sa kontrobersiyang ito na sinasabing may kinalaman din sa misteryosong pagkawala ng ilang mahahalagang government files, kaya naman nagkakagulo na sa mga opisina ng gobyerno at hinihiling ng taumbayan ang agarang imbestigasyon at pagbibitiw ng mga sangkot, habang patuloy na umaapaw ang mga teorya at memes online tungkol sa kung paano raw nagawang maitago ng grupo ang kanilang plano sa loob ng maraming buwan nang hindi nabubuking.</t>
         </is>
       </c>
-      <c r="C95" s="2" t="inlineStr">
+      <c r="C95" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -2943,17 +3275,20 @@
           <t>Kaninang madaling araw, nagulantang ang online world matapos pumutok ang balitang naghiwalay na raw sina Carla Dimapilis at Jace Rivas, ang tinaguriang “Power Couple” ng showbiz, dahil umano sa matinding selosan at palihim na pagme-message ni Jace sa isang rising starlet na si Mika Villanueva; ayon sa mga kumakalat na screenshots sa social media, nagkaroon daw ng mainit na sagutan sa isang private party ang dalawa at nauwi raw ito sa pag-alis ni Carla habang umiiyak, kasabay ng pag-unfollow nila sa isa’t isa sa lahat ng social media platforms, dahilan ng pagdagsa ng libo-libong comments at memes mula sa mga fans na hindi makapaniwala sa biglaang pagputol ng kanilang limang taong relasyon, at may mga nagsasabing posibleng mauwi pa ito sa public confrontation sa susunod na episode ng isang sikat na talk show.</t>
         </is>
       </c>
-      <c r="C96" s="2" t="inlineStr">
+      <c r="C96" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -2968,17 +3303,20 @@
           <t>Naghain na ng reklamo ang National Bureau of Investigation (NBI) laban kay Ramon O. Cojuangco, Jr., pinsan ni dating Pangulong Noynoy Aquino at presidente ng Palay Asya, Resort, Incorporated. Ayon sa ulat ng GMA News, kasama din sa kinasuhan ay ang 7 pang opisyal ng kumpanya at 7 opisyal ng aklan dahil sa paglabag sa Revised Forestry Code of the Philippines. Ilan sa mga provision na pinagbasehan ng reklamo ay ang hindi naayon sa batas na pag-okupa ng lupa at pagsira ng kalikasan. Ang Playa Asya ang nag-o-operate ng Asya Boracay at Asya Premier Suites. Ang Asya Premier Suites ay nakatayo sa 4,666 square meters ng forest land. Mahaharap din sa reklamong Anti-Graft and Corrupt Practices Act and the Local Government Code of 1991 sina Cojuangco, Malay, Aklan mayor Ceciron Cawaling, dating alkalde John Yap 18 pang opisyal. Inihain ng gobyerno ang relklamo laban sa mga akusado, ilang lingo matapos buksan muli ang Boracay sa mga turista. Matatandaang ipinasara ni Pangulong Duterte ang Borcay para sa rehabilitasyon dahil nabababoy na ng husto ang isla dahil sa maling pamamalakad ng mga lokal na opisyal dito. Basahin ang reaksyon ng ilang kababayan natin sa balitang ito.</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
+      <c r="C97" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -2993,17 +3331,22 @@
           <t>Ipinahayag ni Department of Public Works and Highways Secretary Mark Villar ang matagumpay na final inspection at dry run ng North Luzon Expressway Harbor Link Segment 10 bilang paghahanda sa opisyal na pagbubukas nito sa Martes, Pebrero 26, kung saan tinatayang makikinabang ang 30,000 motorista at malaki ang mababawas sa oras ng biyahe mula Valenzuela City hanggang C-3 sa Caloocan, mula isang oras ay magiging limang minuto na lang kapag nagbukas na ang kalsada. Maraming netizens ang humanga at nagbahagi ng post ni Secretary Villar, na umabot na sa mahigit 6,000 shares at libo-libong reaksyon habang sinusulat ang balitang ito. Sa kanyang Facebook post, binigyang-diin ni Secretary Villar na magiging malaking pagbabago sa daloy ng trapiko ang proyekto, at nagpasalamat ang ilang netizens sa administrasyong Duterte at kay Secretary Villar para sa kanilang pagsisikap at tagumpay ng proyekto, na itinuturing nilang patunay ng tunay na pagbabago sa ilalim ng kasalukuyang pamahalaan.</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>Ibinida ni Department of Public Works and Highway Secretary Mar Villar ang final inspection at dry run ng Noth Luzon Expressway Harbor Link Segment 10 para sa pagbubukas nito sa susunod na linggo (Martes, Pebrero 26). Ayon sa kalihim aabot sa 30,000 na motorista ang maseserbisyuhan ng proyekto at matatapiyasahan ng lubos ang oras ng pagbiyahe mula sa Valenzuela City hanggang C-3 sa Kalookan. Kung dati ay umaabot daw ng isang ras ang biyahe, magiging 5 munuto na lang daw pag binuksan na ang nasabing kalsada. Lubos na hinangaan ng mga kababayan natin ang naturang post ni Secretary VIllar. habang sinusulat ang blog post na ito ay umabot na sa mahigit 6,000 ang nagbahagi ng nasabing post at umani na rin ito ng libo-libong reaksyon mula sa mga netizens. "The NLEX Harbor Link Segment 10 will be a traffic game changer since this will drastically cut travel time from Caloocan to NLEX from one hour to only five minutes. It will be opened next Tuesday - Feb 26" sabi ni Secretary Villar sa kanyang Facebook post. Panoorin ang video mula sa DZBB. Ito po ang ilan sa mga naging komento ng ilang kababayan natin sa isa na namang matatapos na proyekto sa ilalim ng DUterte Government. "Tatak Duterte! Mabuhay ang administrasyong Duterte. Thank you Sir Mark Villar, great job po! " sabi ni R. Dela Cruz. "Mark Villar and Art Tugade. Two names I will never forget if ever you two decide to run as Senators. Mabuhay po kayo," sabi ni N. Mercado. "Grabe talaga ang mga cabinete ng Duterte admin, nagpapaligsahan sa galing! Salamat po Sec Mark Villar sa taimtim na pagtulong sa mahal na pangulo." sabi ni O. Ocitog. "Sec Mark yung mga dilawan hinahanap yung mga nagawa ng DPWH at ng administrasyon .. paki Sampal nga po sa kanila itong harbor link..thanks .. and by the way congrats sec.. for the job well done," sabi ni Y. Jesalva. "Yan ang tunay ng pagbabago may gawa at maasahan sina Tatay Digong, Mark Villar at iba pang membro ng DDS salamat at mabuhay mahal nga pangulo!!!," sabi ni L. Aboloc.</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>economy / business</t>
         </is>
       </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -3018,17 +3361,20 @@
           <t>TULUY-TULOY ang Midas Touch ni Bossing Vic Sotto, hindi lamang sa kanyang sarili kundi maging sa mga alaga niyang sina Ryzza Mae Dizon ngayon at kay Aiza Seguerra noon. Hindi niya tinatantanan ang pag-aalaga at paghuhubog sa kanila hindi lamang sa umpisa kundi hanggang sa paglaki at posibleng habang-buhay na rin. No kidding.</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
+      <c r="C99" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -3043,17 +3389,20 @@
           <t>Bandang alas-dos ng hapon ngayong araw, nagdulot ng matinding takot at kaguluhan sa buong bayan ng San Pedro nang biglang lumitaw ang napakalaking buhawi na sinasabing kasing laki ng limang gusali at may kasamang bugso ng apoy na tila sumisipsip ng lahat ng madaanan, mula sa mga bahay hanggang sa mga sasakyan; ayon sa mga residente, hindi raw nila inaasahan ang ganitong kalaking sakuna dahil wala namang babala mula sa lokal na pamahalaan, kaya’t nagkanya-kanyang takbo ang mga tao habang may mga ulat ng nawawalang alagang hayop, nasirang linya ng kuryente at ilang bahagi ng kalsada na tila naglaho na lang bigla, dahilan upang magdulot ng matinding panic sa social media kung saan nag-viral agad ang mga video at larawan ng kakaibang kalamidad, at marami ang nag-aalala na baka raw hindi ito ordinaryong buhawi kundi isang palatandaan ng mas malalang sakuna na posibleng tumama pa sa mga susunod na araw.</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
+      <c r="C100" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>disaster / environment</t>
         </is>
       </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -3068,17 +3417,20 @@
           <t>Kapag muling binalikan ang science, malalaman na walang dapat ipag-alala--sa katunayan, makakatulong ang patatas upang mabawasan ang timbang. Sa isang pag-aaral na isinagawa sa Australia, nadiskubre ng mga mananaliksik na ang patatas ay mas nakakapag-satisfy kumpara sa "healthy" carbs katulad ng brown rice at oatmeal. Coconut Oil</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr">
+      <c r="C101" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>international news</t>
         </is>
       </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -3093,17 +3445,22 @@
           <t>Sa illustration na ipinakita ng NEW5, makikita ang koneksyon ng matandang Parojinog, na siyang ama ng mayor ng Ozamiz City, na kamakailan ay napatay sa isinagawang raid sa kanilang compound sa Ozamiz City.</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>PLAY FULL VIDEO BELOW Sa illustration na ito ng NEW5, pinakikita ang connection ng matandang Parojinog na ama ng Osamiz City mayor Parojinog na napaslang kamakailan sa isang raid sa compound nito sa Osamiz city.</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -3118,17 +3475,20 @@
           <t>Umani ng palakpakan at tawanan mula sa audience at maging sa tatlong judges na sina Gary Valenciano, Jed Madela at Sharon Cuneta ang performance ni Melai with matching nunal sa pisngi maging ang buhok ng aktres. "Noong pumasok ka, sabi ko kay Jed, 'Si Ate Guy ba 'to, o si Maria Leonora Teresa?' Ang galing ng pagkaka-interpret mo, pero siyempre 'pag si Ate Guy, talagang ano siya, hindi siya comedy. Pero 'yun naman ang naging tatak ni Melai," sabi ni Sharon. "Alam natin na sobrang hirap i-impersonate si Ate Guy, kasi iconic eh, iconic 'yung kanyang mukha, 'yung kanyang boses, 'tapos huli ka pa, di ba, so sobrang hirap," sabi naman ni Jed. "Sobra akong bilib sa 'yo, you took the challenge, at napasaya mo kaming lahat." Bilib din si Gary V. sa ginawa ni Melai. "Kung ang mga ibang artist, eh, ginaya nila, at talagang kamukhang-kamukha nila 'yung artist na in-impersonate nila, ikaw, alam mo 'yung mga caricature?" pabirong sabi ni Mr. Pure Energy. "Pero grabe 'yung ginawa mo kanina, kaya challenge din ngayon sa iba kasi ikaw, caricature na maganda 'yung pagka-emote. Kung isa ako sa nanonood ngayon, kunyari may listahan na sila, ito 'yung ranggo, pero paglabas mo, parang malilito sila." Kasama sa celebrity performers sina Karla Estrada na ginaya si Sharon Cuneta; Nyoy Volante bilang Michael Jackson; Jay-R na si Pepe Smith naman ang ginaya; Tutti Caringal as Freddie Aguilar; Maxene Magalona bilang si Taylor Swift; Edgar Allan Guzman na kopyang-kopya ang impersonation kay Usher; at si Jolina Magdangal as Lady Gaga.</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
+      <c r="C103" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -3143,17 +3503,20 @@
           <t>Kagabi, biglang naging usap-usapan sa mga online forum ang bagong patakaran ng pamahalaan ng Lungsod ng Buenavista na naglalayong ipagbawal ang pagbebenta ng street food sa lahat ng pampublikong lugar simula sa susunod na linggo, at ayon sa mga post ng ilang netizen, ito raw ay para umano “mapanatili ang kalinisan at kaayusan” sa lungsod; ngunit marami ang nagdududa dahil may mga kumakalat na haka-haka na ang tunay na dahilan ay para bigyang-daan ang isang malaking kumpanya na balak magtayo ng exclusive food park sa gitna ng bayan, kaya naman nagiging mainit ang diskusyon kung sino ba talaga ang makikinabang sa polisiya na ito, at may mga nagsasabing tila mas pinapaboran ng lokal na pamahalaan ang malalaking negosyante kaysa sa maliliit na vendor na matagal nang umaasa sa kita mula sa pagtitinda ng fishball, kwek-kwek, at iba pang paboritong pagkain ng masa.</t>
         </is>
       </c>
-      <c r="C104" s="2" t="inlineStr">
+      <c r="C104" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -3168,17 +3531,20 @@
           <t>Sinabi ng biktima na nakilalang si Rocky Mhar Dalangin, residente ng Lot 15, Block 233 Pioneer St., Makati City na sakay sa ng isang taxi na may plakang UVU-793 nang magdeklara ang driver nito ng holdap sa C-5 Road, Barangay Ugong, Pasig dakong 4:30 noong Miyerkules ng madaling araw.</t>
         </is>
       </c>
-      <c r="C105" s="2" t="inlineStr">
+      <c r="C105" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -3193,17 +3559,20 @@
           <t>Hindi mo ba alam? Usap-usapan ngayon sa social media ang diumano’y palihim na pag-aaway ng dalawang sikat na aktor, sina Marco Villanueva at Lianne Cruz, matapos kumalat ang video na nagpapakitang nagbabangayan sila sa likod ng set ng kanilang bagong teleserye; ayon sa ilang crew na hindi na nagpakilala, matagal na raw may tensyon sa pagitan ng dalawa dahil sa umano’y selosan at hindi pagkakaintindihan sa mga eksena, at sinasabing umabot pa ito sa punto na muntik nang hindi matuloy ang taping ng ilang araw, dahilan para mangamba ang mga fans na baka magbago ang takbo ng istorya ng palabas, habang patuloy namang tumatanggi ang management na maglabas ng opisyal na pahayag tungkol sa isyu.</t>
         </is>
       </c>
-      <c r="C106" s="2" t="inlineStr">
+      <c r="C106" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -3218,17 +3587,20 @@
           <t>DAHIL sa patuloy na sobrang mataas na ratings ay extended ang seryeng Two Wives hanggang Marso. Ito ang tsika sa amin ni Erich Gonzales, ang isa sa mga bida ng primetime series. Kaya masayang-masaya si Erich, hindi lang dahil sa mga papuring natatanggap niya kundi pati na sa pagkakaroon ng loyal viewers na hindi bumibitaw sa pagsubaybay sa teleserye nila.</t>
         </is>
       </c>
-      <c r="C107" s="2" t="inlineStr">
+      <c r="C107" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -3243,17 +3615,20 @@
           <t>Paano nga ba nasangkot si Kapitana Liza Montemayor sa isang malaking anomalya sa Barangay Mabini? Ayon sa ulat ng mga awtoridad, natuklasan umano sa isang surprise inspection ang ilang kahon ng smuggled na gadgets at mamahaling relo sa mismong opisina ng kapitana, na sinasabing ginagamit bilang taguan ng mga kontrabando na ipinuslit mula sa ibang bansa; lumalabas din sa imbestigasyon na may mga pirma umano si Kapitana Liza sa ilang papeles na konektado sa ilegal na transaksyon, dahilan upang agad siyang ipatawag para magpaliwanag habang nagkakagulo ang mga residente at nagtatanong kung paano napunta sa kanya ang mga ebidensya, at sa ngayon ay patuloy ang pagbusisi ng mga pulis kung may iba pang opisyal na sangkot sa sinasabing sindikato ng smuggling sa kanilang lugar.</t>
         </is>
       </c>
-      <c r="C108" s="2" t="inlineStr">
+      <c r="C108" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -3268,17 +3643,20 @@
           <t>Halos marami na nga sa mga Pilipino ang nahuhumaling sa paglalaro ng online games ngayon, kaya naman itinuturing na itong isang uri ng isports na tinatawag na "e-sports". Patunay nito ang paglahok sa ilang online games sa darating na Southeast Asian Games na gaganapin sa Pilipinas bilang medal sports. Kaya naman ang malaking tanong, handa na ba ang Department of Education na isama sa "Palarong Pambansa" ang mga online games? Ayon sa panayam ng ABS-CBN News, inamin ni Palarong Pambansa 2019 Secretary-General at DepEd Undersecretary Revsee Escobedo na wala pang pag-uusap sa pagitan ng mga opisyal ng Palaro Board hinggil sa ideya ng posibilidad na paglahok sa e-sports tulad ng Mobile Legends at DOTA sa taunang kompetisyon. Aniya, mas pinili nilang isagawa ang mga "Larong Pinoy" ngayong taon alinsunod na rin sa hiling ni Secretary Leonor Briones. "The secretary wants to include Larong Pinoy in the regular Palarong Pambansa sports. Maybe next year, we have larong Pinoy as demo sports with other sports. But not online games. Larong Pinoy is no longer part of the regular sports. But these larong Pinoy, these are cultural heritage that we cherish. This indeed a cultural treasure to Filipinos," saad ni Escobedo. Prayoridad umano ng Palaro Board na maibalik ang mga larong nakapagpapalakas at nakapagpapabuti sa motor at physical skills ng mga batang manlalaro. "There are positive and negative observations with regards to online games. What is important is we have to balance. What is important to us, the officials of DepEd, is the holistic development of our lifelong learners," ani Escobedo. Hindi pa man napag-uusapan ngayon, nilinaw niyang hindi nila isinasarado ang pinto para sa e-sports. Nais lamang nilang pag-aralang maigi ang mga benepisyong maaaring makuha ng mga manlalaro dito. Samantala, patuloy naman ang mga inobasyon sa pagsasagawa ng taunang Palarong Pambansa lalo pa't marami sa mga isport ay nangangailangan na ng teknolohiya. Kailangan umanong makipagsabayan ng DepEd sa teknolohiya sa tulong na rin ng Philippine Sports Commission (PSC). "Yes, we are adapting to the technology. We are implementing technological innovations. The PSC is very strict when it comes to compliance with international rules and standards," paliwanag ni Escobedo. "Some of the equipment we will use in Palarong Pambansa are borrowed from PSC like in swimming," dagdag pa nito. Ang Palarong Pambansa ay isasagawa sa Davao City mula Abril 27 hanggang May 4, 2019.</t>
         </is>
       </c>
-      <c r="C109" s="2" t="inlineStr">
+      <c r="C109" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>sports</t>
         </is>
       </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -3293,17 +3671,20 @@
           <t>Ang pagsasanib ay kinabibilangan ng pagpapabuti sa Department of Social Welfare and Development's (DSWD) National Resource Operation Center sa Pasay City at sa kanyang mga bodega sa mga rehiyon sa pag-preposition ng relief items at operational support equipment, gayundin ang development at implementasyon ng mga training program ng gobyerno na nagbibigay-diin sa disaster response, logistics at supply chain management.</t>
         </is>
       </c>
-      <c r="C110" s="2" t="inlineStr">
+      <c r="C110" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>economy / business</t>
         </is>
       </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -3318,17 +3699,20 @@
           <t>Umaani ngayon ng batikos si Magdalo Representative Gary Alejano mula sa mga netizens dahil sa mga lumabas sa kanyang bunganga. Sa isang talumpati na nakunan ng video, sinabi ni Alejano na mauuna daw na papanaw si Pangulong Rodrigo Duterte. Ayon sa ilang impormasyon, sinabi daw ito ni Alejano sa harap ng iilang Pilipino sa United Kingdom. "It's a start! You have to go thorugh that. Kung mayroon man tayong dinadaanang kahirapan, o may present situation tayo ngayon, dadaan lang iyan. Si Duterte dadaan lang yan, naniniwala ba kayo? Dadaan lang sya dahil ang term nya 2022 na noh. Puwede ng matapos yung term nya, e puwede na rin syang matapos sa mundong ito. Ganun lang yun no. I BELIEVE MAUUNANG MAMATAY SA ATIN YUN KASI MATANDA NA SYA E 'DI BA? Baka sabihin na naman pinagdadasal natin," sabi ni Alejano.</t>
         </is>
       </c>
-      <c r="C111" s="2" t="inlineStr">
+      <c r="C111" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -3343,17 +3727,20 @@
           <t>Ang nanalo bilang Best Actor in a Leading Role ay si Pierre Png (para sa kanyang pagganap sa Zero Calling ng MediaCorp Pte Ltd/Channel 5) ng Singapore. Nominado rin si Pierre sa The Journey: A Voyage ng MediaCorp Pte Ltd/Channel 8. Siya lang ang nag-iisang aktor na tumanggap ng dalawang nominasyon sa ATA2014. Nominado naman si Dennis sa role niya bilang Eric del Mundo sa My Husband's Lover ng GMA Network, ang nagpanalo sa kanya sa 5th Golden Screen TV Awards ng Entertainment Press Society (Enpress, Inc.) nitong nakaraang Marso bilang Outstanding Performance by an Actor in a Drama Program. Second nomination na ito ng aktor ng Hiram Na Alaala sa ATA. In 2007, nakakuha rin siya ng nominasyon sa APT-produced Unico Hijo sa 12th Asian TV Awards. Hindi na rin nasayang ang pagpunta ng bida sa "Ulam" episode ng Shake, Rattle &amp; Roll XV ng Regal Entertainment dahil sa ipinagkaloob sa kanyang certificate citing him as highly commended. Hindi rin naman umaasang maiuuwi ni Dennis ang tropeo.</t>
         </is>
       </c>
-      <c r="C112" s="2" t="inlineStr">
+      <c r="C112" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -3368,17 +3755,20 @@
           <t>Kasabay nito, tiniyak ni Senate Finance Committee chairman Senator Francis Escudero na ipaglalaban ng Senado ang sarili nitong bersyon sa pambansang pondo na aniya'y hindi taglay ang "pork barrel" taliwas sa akusasyon ni Sen. Miriam Defensor-Santiago.</t>
         </is>
       </c>
-      <c r="C113" s="2" t="inlineStr">
+      <c r="C113" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -3393,17 +3783,20 @@
           <t>SINABI ni National Capital Region Police Office (NCRPO) chief Director Guillermo Eleazar na hindi totoo ang isang mensahe na umiikot sa social media kaugnay ng umano'y bantang pambobomba sa SM supermalls. Ito'y matapos naman ang mensahe mula sa isang Kyla Avonahceh na nakatanggap ang mga opisyal ng shopping mall mula sa Abu Sayyaf Group at humingi ng $15 million "or else they're going to bomb the mall." Hindi naman binanggit ng mensahe ang partikular na SM branch. "This is a replay of a similar hoax meant to sow alarm and panic among the citizens in Metro Manila and done by people who are clearly enemies of the State or by irresponsible pranksters," sabi ni Eleazar sa isang pahayag. Idinagdag ni Eleazar na ganito rin ang umikot sa social media matapos ang pamboboma sa Roxas Night Market in Davao City noong Setyembre 2016, kung saan 15 ang namatay. "Moreover, if the said threat is real, a more responsible company and a sane organization like SM would immediately go to us here at the NCRPO and any announcement will likely be done in the sober traditional media such as television, radio and print, rather than just in social media where fake news is already a permanent fixture," ayon pa kay Eleazar. "Let us go by the required daily activities of life with our families, friends and co-workers. Let's continue to enjoy our lives. I ask our fellow Metro Manilans to be patient and cooperative with our heightened security procedures which is for the good of all," ayon pa kay Eleazar.</t>
         </is>
       </c>
-      <c r="C114" s="2" t="inlineStr">
+      <c r="C114" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>economy / business</t>
         </is>
       </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -3418,17 +3811,20 @@
           <t>Alam mo ba na may bagong patakaran ang gobyerno na tinatawag na “One Family, One Permit” kung saan limitado na lang sa isang miyembro ng bawat pamilya ang puwedeng kumuha ng anumang benepisyo mula sa mga programa ng pamahalaan, at ayon sa mga umano’y insider, layunin daw nitong bawasan ang umano’y pag-abuso sa ayuda pero marami ang nagrereklamo online dahil tila mas pabor pa raw ito sa mga mayayaman na kayang mag-diversify ng apelyido at address para makalusot, samantalang ang mga ordinaryong mamamayan ay napipilitang magsakripisyo at hindi na makakuha ng sapat na tulong lalo na kung marami silang anak o magulang na umaasa sa kanila; lumalakas tuloy ang panawagan ng masa na ibasura ang polisiya dahil mas nakikinabang lang daw dito ang mga may koneksyon at mas lalong nadedehado ang mga tunay na nangangailangan.</t>
         </is>
       </c>
-      <c r="C115" s="2" t="inlineStr">
+      <c r="C115" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -3443,17 +3839,20 @@
           <t>Mga kababayan, alam niyo ba na may lumalabas na balita tungkol sa isang mataas na opisyal ng gobyerno na umano’y may lihim na kasunduan sa isang misteryosong grupo para manipulahin ang resulta ng mga paparating na eleksyon? Ayon sa mga hindi pinangalanang source, sinasabing ginagamit daw ng opisyal ang pondo ng bayan para pondohan ang mga proyekto ng grupong ito kapalit ng tiyak na suporta at proteksyon sa kanyang puwesto. Kumakalat pa ang usap-usapan na may mga lihim na pagpupulong na ginaganap tuwing gabi sa isang sikretong lugar kung saan pinag-uusapan daw ang mga estratehiya para kontrolin ang impormasyon at pigilan ang oposisyon. Maraming netizen ang nagtatanong kung bakit tila hindi natutunton ang mga anomalya at kung sino-sino pa raw ang kasabwat sa likod ng mga misteryosong galaw ng opisyal na ito, kaya’t marami ang nag-aabang sa mga susunod na rebelasyon.</t>
         </is>
       </c>
-      <c r="C116" s="2" t="inlineStr">
+      <c r="C116" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -3468,17 +3867,20 @@
           <t>NASAWI ang isang lalaki at sugatan ang kanyang asawa nang pagtatagain ng kanilang anak, sa Negros Occidental nitong Martes. Matapos mapatay ang 55-anyos na amang si Helardo Benarao ay sinunog pa ng suspek na si Jun-Jun Benarao, 36, ang katawan ng una, ayon sa ulat ng Negros Occidental provincial police. Patuloy namang nilulunasan sa isang pagamutan sa Bacolod City ang 58-anyos na si Sinona Benarao, ang ina ng suspek, dahil sa taga sa iba-ibang bahagi ng katawan. Naganap ang insidente dakong alas-8:30 ng umaga, sa masukal na hangganan ng Sitio Kinabong 3, Brgy. Igmayaan, Don Salvador Benedicto, at Brgy. Minoyan, Murcia. Pinagtataga ni Jun-Jun ang magulang gamit ang isang itak, at nang mapatay ang ama'y sinilaban pa ang katawan nito, ayon sa ulat. Nakatanggap ang pulisya ng impormasyon na tumakas ang suspek patungo sa Brgy. Codcod, San Carlos City, kaya nagsagawa ng pagtugis doon, pero di ito natagpuan. Patuloy pang pinaghahanap ng pulisya ang suspek at inaalam kung anong nagtulak dito para pagtatagain ang magulang.</t>
         </is>
       </c>
-      <c r="C117" s="2" t="inlineStr">
+      <c r="C117" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -3493,17 +3895,20 @@
           <t>Viral ngayon sa social media ang balitang isang buong pamilya sa Barangay Maligaya ang umano’y sabay-sabay na naglaho matapos mahulog ang kanilang bahay sa isang malalim na butas na biglang bumukas sa gitna ng gabi, at ayon sa mga kapitbahay ay may mga kakaibang tunog at ilaw na nakita bago tuluyang lamunin ng lupa ang buong bahay, na sinasabing may kinalaman daw sa isang sindikatong nagtatago ng mga ninakaw na yaman sa ilalim ng lupa; dahil dito, nagdulot ng matinding takot at pagkabahala sa buong komunidad ang insidente, at marami ang naniniwala na may mas malalim pang krimen ang bumabalot sa likod ng misteryosong pagkawala, kaya’t dagsa ang mga pulis at media sa lugar habang patuloy na hinahanap ang mga nawawalang miyembro ng pamilya at iniimbestigahan kung sino o ano ang tunay na responsable sa nakakatakot na pangyayaring ito.</t>
         </is>
       </c>
-      <c r="C118" s="2" t="inlineStr">
+      <c r="C118" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -3518,17 +3923,22 @@
           <t>Para sa mga naghihintay ng Social Security Contribution Table para sa taong 2019, narito ang magiging gabay para sa lahat ng miyembro. Ang iskedyul ng mga kontribusyon ay inilaan para sa mga self-employed, Overseas Filipino Workers at boluntaryong miyembro, kaya maaaring tingnan ang listahan ng mga kontribusyon sa ibaba. Mahalaga ring tandaan na ang minimum salary credit para sa mga OFW na miyembro ay P5,000.</t>
         </is>
       </c>
-      <c r="C119" s="2" t="inlineStr">
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>Para sa mga nag aabang ng Social Security Contribution Table as taong 2019 narito ang maging guide natin. Naka-iskedyul ng mga kontribusyon para sa self-employed, Mga Overseas Filipino Worker at boluntaryong mga miyembro, tingnan ang listahan sa ibaba. Scheduled of contributions for self-employed, Overseas Filipino Workers and voluntary members, see the list below. Note that the minimum salary credit for OFW member is P5,000.</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>international news</t>
         </is>
       </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -3543,17 +3953,20 @@
           <t>Viral ngayon sa social media ang balitang sinasabing may sikretong kasunduan umano ang aktor na si Jolo Ramirez at isang kilalang TV network matapos mapansin ng mga netizen na tila laging siya ang nauunang makuha ang mga major lead roles sa bagong serye kahit mas marami pang senior artists na auditioned, kaya’t umusbong ang mga spekulasyon na may “palakasan” at under-the-table na nangyayari sa likod ng kamera; dagdag pa rito, may mga lumabas na screenshots ng private group chat kung saan tila may usapan tungkol sa exclusive perks at bonus na natatanggap lang daw ni Jolo, dahilan upang mag-init ang ulo ng ilan sa mga co-stars at mag-trending ang hashtag #JoloFavoritism, habang tikom pa rin ang bibig ng kampo ng aktor at ng network tungkol sa isyung patuloy na pinag-uusapan ng mga netizen.</t>
         </is>
       </c>
-      <c r="C120" s="2" t="inlineStr">
+      <c r="C120" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -3568,17 +3981,22 @@
           <t>Sa isang pahayag na ipinadala sa media, isiniwalat ng dating miyembro ng Communist Party of the Philippines (CPP) na si Ka Danny ang umano’y mga katiwalian ng New People’s Army, ayon sa ulat ng GMA News. Ayon kay Ka Danny, ang mga party-list groups gaya ng Bayan Muna, Anakpawis, at ACT-Teachers ay nagsisilbing “legal fronts” ng CPP. Inamin din niyang mahigit 18 taon siyang naging miyembro ng CPP at nagsilbi bilang opisyal sa Legal and Unification Committee, at iginiit niyang mabibigo ang mga pagkilos ng mga komunista dahil sa kanilang kasamaan at panlilinlang sa masa. Sinabi pa ni Ka Danny na ginagamit lamang daw ng mga komunista ang mga nakaraang peace talks para linlangin ang kabataan at ituro sa kanila na bulok ang sistema ng pulitika sa bansa. Binatikos din niya si CPP Founder Jose Maria “Joma” Sison, aniya habang nakikipaglaban ang mga miyembro, namumuhay nang kumportable si Sison at iba pang matataas na opisyal sa ibang bansa, dahilan kaya siya at iba pa ay umalis sa kilusan. Samantala, ibinunyag din ni Mario Ludades ng No to Communist Terrorist Group Coalition (NTCC) at isa sa mga 18 founder ng CPP ang iba pang legal fronts ng CPP tulad ng League of Filipino Students, National Union of Journalists of the Philippines, College Editors Guild of the Philippines, at Students Christian Movement of the Philippines.</t>
         </is>
       </c>
-      <c r="C121" s="2" t="inlineStr">
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>Sa isang pahayag na ipinadala sa mga media, ibinunyag ng umano'y dating miyembro ng Communist Party of the Philippines (CPP) na si Ka Danny ang mga kabalastugan ng New People's Army. Ayon sa ulat ng GMA News, sinabi ni Ka Danny na ang mga party-list groups na Bayan Muna, Anakpawis at ACT-Teacher ay mga "legal fronts" ng CPP. Inamin din ni Ka Danny na pagkilos ng mga komunista ay mabibigo lang dahil sa mga kasamaan at kasinungalingan nito sa masa. Ayon ka kay Danny, naging miyembro siya ng CPP ng mahigit 18 taon at nagsilbi bilang opisyal sa Legal and Unification Committee. "If they (communists) are really sincere in what they are fighting for, there will come a time that they will succeed. But in reality, they are just using past peace talks to deceive the youth and try to teach them that the country is experiencing a rotten political system," sabi ni Ka Danny. Binanatan din ni Ka Danny si CPP Founder Jose Maria "Joma" Sison. Habang ang mga miyembro ay nagkikipag-giyera, si Joma daw at mga matataas na miyembro ay may kumportableng buhay sa ibayong-dagat. "This is one of the reasons why we left the organization. While we stake our lives in the war we are waging, Jose Maria Sison and other members of the higher organ are living comfortable lives abroad," dagdag ni Ka Danny. Panoorin ang kaugnay na ulat tungkol sa ika-50 anibersaryo ng CPP. Ibinunyag naman ni Mario Ludades ng No to Communist Terrorist Group Coalition (NTCC) at isa sa mga 18 founders ng CPP ang mga iba pang legal fronts ng CPP. Ilan sa mga pinagalanan niya ay ang League of Filipino Students, National Union of Journalists of the Philippines, College Editors Guild of the Philippines, and Students Christian Movement of the Philippines. Basahin ang reaksyon ng mga tao sa mga pagbubunyag ng mga dating miyembro ng kilusan.</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -3593,17 +4011,20 @@
           <t>SA halip na i-cite for contempt, sasampahan na lamang ng kaso ng mga mambabatas si Budget Sec. Benjamin Diokno kaugnay sa maanomalyang proyekto na napunta sa kompanya ng kanyang balae. Ayon kay House committee on appropriations chairman Rolando Andaya Jr., ipagpapatuloy ng House oversight committee na pinamumunuan ni Quezon Rep. Danilo Suarezang pagdinig . "Unang-una (po si Sec. Diokno for) conflict of interest ho 'yan. Kaso po 'yan. 'Pag nakinabang ang anak ng isang opisyal, ba-wal po 'yon," ani Andaya. Ang oversight committee ang inaasahang mag-rerekomenda ng mga kasong isasampa kay Diokno at iba pang sangkot sa ire-gularidad sa Office of the Ombudsman. "Inaayos na po [ang mga dokumento]. Kinukuha na sa akin...tina-transfer ko na 'yong mga dokumento sa kanya (Suarez)," dagdag pa ni Andaya. Naglaan si Diokno ng bilyong pondo sa mga proyekto sa Casiguran, Sorsogon at nakuha ito ng CT Leoncio Construction and Trading na mayroong joint venture sa Aremar Construction, na pagmamay-ari ng balae ni Diokno. Itinanggi ni Diokno na alam niya na nakaupo sa puwesto ang kanyang balae kung saan napunta ang kinukuwestyong mga proyekto at ang nanalong bidder ay may kaugnayan sa Aremar. Sinabi ni Andaya na ipagpapatuloy rin ang pag-imbestiga sa P75 bilyong isiningit na pondo ni Diokno sa Department of Public Works and Highways. Inilagay umano ang P75 bilyong proyekto ma-tapos na magsumite ng budget proposal ang DPWH.</t>
         </is>
       </c>
-      <c r="C122" s="2" t="inlineStr">
+      <c r="C122" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>economy / business</t>
         </is>
       </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -3618,17 +4039,20 @@
           <t>Una nang sinuspinde ng Comelec ng dalawang linggo (Disyembre 20-Enero 4) ang nationwide voters' registration bilang pagbibigay-daan sa pagdiriwang ng Pasko at Bagong Taon, alinsunod sa Comelec Resolution 9853.</t>
         </is>
       </c>
-      <c r="C123" s="2" t="inlineStr">
+      <c r="C123" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -3643,17 +4067,22 @@
           <t>Sa isang panayam kay dating Sulu Governor Abdusakur Tan ng US-based pro-Duterte blogger na si Maharlika, isiniwalat ni Tan na 70% hanggang 80% ng mga pisikal na balota sa Autonomous Region in Muslim Mindanao (ARMM) ay umano’y ginamit sa pandaraya ng mga pekeng botante, batay sa technical examination ng Commission on Elections (COMELEC) kung saan natuklasan na hindi tugma ang mga pirma at thumbmark ng mga rehistradong botante kumpara sa aktuwal na ginamit sa pagboto noong Halalan 2016; ayon pa kay Tan, ito ay patunay ng malawakang dayaan, at binanggit din ni Attorney Glenn Chong sa kaniyang Facebook post na kung mapapatunayan na mahigit 50% ng mga boto ay pineke, posible raw mapawalang-bisa ang resulta ng eleksyon sa ARMM, bagay na maaaring makaapekto sa protesta ni BBM laban kay Leni Robredo dahil malaki ang lamang ni Robredo sa mga lugar na ito at kapag nabawas ang mga boto, posibleng maungusan siya ni BBM.</t>
         </is>
       </c>
-      <c r="C124" s="2" t="inlineStr">
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>Sa panayam ni US-based pro-Duterte blogger na si Maharlika kay dating Sulu Governor Abdusakur Tan, isiniwalat ng dating opisyal na 70% hanggang 80% umano ng mga pisikal na balota ay ginamit sa pandaraya ng mga pekeng botante. Nahayag daw sa technical examination na hindi parehas ang mga lagda at thumbmark ng mga rehistradong botante sa aktuwal na lagda at thumbmark ng mga bumoto sa Autonomous Region in Muslim Mindanao (ARMM). Ito ay isang patunay daw na ang mga botante na bumoto noong Halalan 2016 ay mga peke. Commission on Election (COMELEC) na raw ang gumawa ng technical examinations sa mga pisikal na balota mula sa ilang lugar sa ARMM at partial results pa lamang ang mga ito. "Lumabas na ang technical examination ng Comelec, ang findings 70 to 80% ng mga pirma sa ARMM hindi tugma o peke. Hindi tugma yung thumbprints ng tunay na registered voters at saka yung mga bumoto, ganun din ang mga signatures. Kitang-kita ang pagnanakaw ng boto" pagbubunyag ni Tan. Sa opinyon ni Attorney Glenn Chong na inilathala niya sa kanyang Facebook account, kapag napatunayan na pineke nga ang 50% ng mga boto sa ARMM, maaring mapawalang-bisa ang resulta ng eleksyon noong 2016 sa naturang lugar. "Sa ilalim ng umiiral na jurisprudence ngayon, kapag napatunayan na higit 50% ng mga balota ay apektado ng ganitong uri ng anomalya, maaring mapawalang-bisa ang resulta ng halalan. May malaking epekto ito sa protesta ni BBM laban kay Leni Robredo. Dahil 70%-80% ng mga bumoto ay peke o "multo... maari itong mapawalang-bisa. Dahil malaki ang panalo ni Leni Robredo sa mga lugar na ito, kapag nakaltas ang mga botong ito sa official tally, malaking boto ang mawawala kay Leni Robredo. Baka ma-overtake na siya ni BBM dito pa lang sa mga lugar na ito. TIYAK MANGINGINIG SA KABA SI LENI ROBREDO SA BALITANG ITO!" pagbubunyag ni Tan. Basahin ang naging reaksyon ng ilang nating kababayan sa pagbubunyag ni former ARMM Governor Tan.</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -3668,17 +4097,20 @@
           <t>Viral ngayon ang isang babaeng nangunguha umano ng bata. Pinag-iingat ng netizen na si Danalyn Orella Tayag ang publiko sa babaeng na sa kanyang social media post. Ayon kay Tayag, nahuli sa Barangay 870 ang naturang babae Naaktuhan umano na papasok na ng gate ng isang bahay ang suspek. Base sa pahayag ng babae, may kasama daw siya na nangunguha ng bata. Paratang ni Tayag, dumating daw sa punto na nagbabaliw-baliwan at paiba-iba ang sinasabi ng babae. Pinakawalan din ang babae ng mga otoridad. Habang isinusulat ang blog post na ito ay umabot na sa mahigit 17,000 ang nagbahagi ng ng video at umani na rin ng sari-saring komento sa mga kabaayan natin. Ayon sa post ni Tayag, nangyari daw ang babae sa barangay 870. Base sa Google Map, ito ay nasa Pandacan sa Manila. Ito po ang video ng kumprontasyon sa pagitan ng mga mamamayan ng Barangay 870 at ng babaeng nangunguha ng bata.</t>
         </is>
       </c>
-      <c r="C125" s="2" t="inlineStr">
+      <c r="C125" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -3693,17 +4125,22 @@
           <t>Usap-usapan ngayon sa social media ang umano’y panggagaya ng kinatawan ng Thailand na si Ingchanok Prasart sa trademark “lava walk” ni Miss Universe 2018 Catriona Gray sa Miss Intercontinental 2018, matapos mapansin ng netizen na si Marnie Raro sa Twitter ang pagkakahawig ng lakad at projection ni Miss Thailand kay Catriona. Bukod dito, napansin din ng mga netizens ang pagkopya umano ni Miss Vietnam sa “Mayon Volcano gown” ni Catriona. Inamin ng dalawang kandidata na hinahangaan at inspirasyon nila si Catriona Gray, at naglabasan ang iba’t ibang reaksyon ng netizens tungkol dito, kabilang ang mga nagsasabing malaki ang impluwensya ni Catriona at mahirap pantayan ang kanyang “lava walk.” Patunay ito na maraming beauty pageant candidates mula sa iba’t ibang bansa ang humahanga kay Catriona Gray, bagay na inamin din ng marami sa mga kandidata ng Miss Intercontinental 2018. Ang ika-47 na edisyon ng Miss Intercontinental ay ginanap noong Enero 26, 2019 sa SM Mall of Asia Arena sa Pasay, Metro Manila, kung saan kinoronahan ni Miss Intercontinental 2017 Veronica Salas Vallejo ng Mexico ang kandidata ng Pilipinas na si Karen Juanita Gallman, at ito rin ang unang pagkakataong naging host ang Pilipinas para sa pageant na ito, matapos piliin ng Japan organizers ang bansa bilang venue dahil abala ang Japan sa paghahanda para sa 2020 Summer Olympics.</t>
         </is>
       </c>
-      <c r="C126" s="2" t="inlineStr">
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>Usap-usapan ngayon sa social media ang umano'y panggagaya ng kinatawan ng Thailand na si Ingchanok Prasart sa ginanap na Miss Intercontinental pageant 2018 sa trademark ni Miss Universe 2018 Catriona Gray na "lava walk." Isang netizen sa Twitter na nagngangalang Marnie Raro ang nakapansin sa paraan ng paglalakad at pag-project ni Miss Thailand na parang kinokopya ang "lava walk" ni Catriona. Bukod kay Miss Thailand, napansin din ng mga netizens ang pagkopya umano sa "Mayon Volcano gown" ni Miss Vietnam. Aminado naman ang dalawa na labis nilang hinahangaan at inspirasyon nila si Miss Universe 2018 Catriona Gray. Halo-halo naman ang naging reaksyon ng mga netizens hinggil dito. "So now everyone looks like Catriona Gray. From hair to stance to gowns. The influence. Only legends do that." "Catriona Gray's walk can never be perfect without her walking it." "I think so? Even the hand gesture of Miss Thailand seems copied too. Catriona Gray is indeed a queen." "Yet they can't copy the original. Because there will be only one Lava Walk and Catriona Gray." "Kayo na 'yung may mga originality... hala gawa kayo sarili niyong pageant, ano ba naman yung hayaan niyo na lang sila hays....daming toxic." Isang patunay lamang ito na maraming mga aspiring beauty pageant candidates, hindi lamang sa Pilipinas kundi maging sa buong mundo, ang tumitingala at humahanga kay Catriona. Aminado naman dito ang marami sa mga kandidata ng naturang katatapos na pageant. Ang 47th edition ng Miss Intercontinental 2018 ay ginanap noong Enero 26, 2019, sa SM Mall of Asia Arena sa Pasay, Metro Manila, Philippines. Kinoronahan ni Miss Intercontinental 2017 Veronica Salas Vallejo ng Mexico ang kandidata ng Pilipinas na si Karen Juanita Gallman. Ito ang kauna-unahang pagkakataong naging host ang Pilipinas sa pageant na ito. Pinili ng Japan organizers ang Pilipinas na maging venue ng pageant dahil abala ang bansang Japan sa mga paghahanda para sa 2020 Summer Olympics. Narito ang buong Twitter post ng netizen:</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -3718,17 +4155,22 @@
           <t>Kahapon, binatikos ni Pangulong Rodrigo Duterte si outgoing senator Antonio Trillanes matapos lumabas ang balitang nagbago ng pahayag si Peter Joemel "Bikoy" Advincula, na ngayon ay itinuturo si Trillanes bilang utak sa likod ng video series na bumabatikos sa pamilya Duterte. Sinabi ni Duterte, "Anong ginawa mo? Binaboy mo ang Senado. And you use that power to run after people... This time, si Bikoy naman ang source mo. Henyo ka talaga, Duts." Sa kabilang banda, ngayong araw ay bumuwelta si Trillanes at tinawag na palpak ang Pangulo, sabay sabing, "Ayan ka na naman. Hindi ka pa nga nakakabawi sa kapalpakan mo dun sa inimbento mong offshore bank accounts na bintang mo sa akin, pati na rin dun sa mga sinabi mo laban sa Nanay ko, tapos may bago ka na namang bintang." Tinuligsa rin ni Trillanes si Duterte dahil kay Bikoy ang ginawang source ng Pangulo, at inulit pa ang banat na, "This time, si Bikoy naman ang source mo. Henyo ka talaga, Duts." Mapapansin na iba na ang tono ni Trillanes ngayon kumpara noong Abril 5, kung saan pinuri niya ang Bikoy videos at binati pa ang mga gumawa ng mga ito dahil sa matindi at malinaw na mga akusasyon laban sa pamilya Duterte.</t>
         </is>
       </c>
-      <c r="C127" s="2" t="inlineStr">
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>Kahapon ay binanatan ni Pangulong Rodrigo Duterte si outgoing senator Antonio Trillanes matapos pumutok ang balita ng pagbaliktad ni Peter Joemel "Bikoy" Advincula na ngayo'y itinuturo si Trillanes bilang may pakana ng video series na naninira sa pamilya DUterte. "Anong ginawa mo? Binaboy mo ang Senado. And you use that power to run after people... This time, si Bikoy naman ang source mo. Henyo ka talaga, Duts," banat ng Pangulong Duterte. Ngayong araw ay bumoladas naman si Trillanes laban sa Presidente ng Pilipinas. Para kay Trillanes, palpak daw ang Pangulo. "Ayan ka na naman. Hindi ka pa nga nakakabawi sa kapalpakan mo dun sa inimbento mong offshore bank accounts na bintang mo sa akin, pati na rin dun sa mga sinabi mo laban sa Nanay ko, tapos may bago ka na namang bintang," boladas ni Trillanes. Kinutya niya pa ni Trillanes si Pangulong Duterte dahil si Bikoy daw ang napiling source ng Presidente. "This time, si Bikoy naman ang source mo. Henyo ka talaga, Duts," dagdag pa ni Trillanes. Ang boladas ni Trillanes laban sa Presidente at kay alyas Bikoy ay tila iba ang tono laban sa pahayag niya noong Abril 5. Magugunitang pinuri ni Trillanes ang mga Bikoy videos noong unang lumabas ang mga ito. "First of all, let me congratulate the people behind the videos that linked the Duterte family to illegal drugs! The accusations of the witness were very serious, quite pointed and well-explained," sabi ni Trillanes noong unang lumabas ang mga Bikoy videos.</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -3743,17 +4185,22 @@
           <t>Sumagot na si Kris Aquino sa isyu ng pagpopondo kay anti-Duterte blogger Jover Laurio ng Pinoy Ako Blog at umamin siyang siya nga ang nagpondo dito. Ilang oras matapos ang kanyang pag-amin, nag-live si Kris kasama ang kanyang legal team sa social media para talakayin ang isyu kaugnay ng kanyang dating financial manager na si Nicko Falcis, na kinasuhan niya dahil umano sa paglustay ng pera. Sa live video, emosyonal na pinag-usapan ni Kris ang kanyang kalusugan at ang kinabukasan ng kanyang mga anak, ngunit hindi niya binanggit o sinagot ang #PABoost isyu na tumutukoy sa umano'y pagpopondo niya kay Jover Laurio gamit ang credit card na hawak ni Nicko, batay sa mga leaked chats na inilabas ni Attorney Jesus Falcis, kapatid ni Nicko. Nagbigay ng reaksyon ang ilang pro-government bloggers sa hindi pagsagot ni Kris sa isyu, kabilang sina Atty. Trixie Cruz-Angeles at Krizette Laureta Chu, na parehong nagkomento tungkol sa kanyang pananahimik at ang posibleng epekto nito sa kanyang endorsements at imahe. Sa live, inamin din ni Kris na may lupus siya, allergic siya sa mga gamot, at maaaring mawalan siya ng limang kontrata dahil dito, kaya lilipad siya papuntang Singapore para magpagamot at pansamantalang magpapahinga sa social media ayon sa payo ng kanyang mga doktor.</t>
         </is>
       </c>
-      <c r="C128" s="2" t="inlineStr">
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>Update: Sumagot na si Kris sa isyu ng pagpopondo kay anti-du30 blogger Jover Laurio (Pinoy Ako Blog). Umamin ang aktress na pinondohan nga niya. Basahin ang kanyang pag-amin dito. Ilang oras lang ang nakakalipas ay nag live sa kanyang mga social media account si Kris Aqino at ang kanyang legal team para pag-usapan ang isyu patungkol sa dati niyang financial manager na si Nicko Falcis. Matatandaang kinasuhan ni Kris si Nicko dahil umano pagdispalko ng financial maanger sa pera ng aktress. Maluha-luhang tinalakay din ni Kris ang tungkol estado ng kanyang kalusugan at ang kinabukasan ng kanyang mga anak. Kapansin-pansin sa naturang video na hindi nag-komento si Kris sa isyu tungkol sa #PABoost. Ang #PABoost isyu ay tungkol sa pagpopondo umano ni Kris sa anti-government blogger at kritiko ni Presidente DUterte na si Jover Laurio aka Pinok Ako Blog (PAB). Sa mga naturang leaked chat conversations na inilabas ng kapatid ni Nicko na si Attorney Jesus Falcsis, makikita na tumatanggap ng pondo si PAB kay Nicko na may hawak ng credit card ni Kris. Basahin ang reaksyon ng ilang pro-government bloggers sa hindi pag-komento ni Kris sa isyu ng #PABoost. "So, to recap. Kris Aquino went Live on various socmed platforms, had her lawyers "argue" against the Falcis brothers. Then, she made an announcement. With great drama she says she was not entirely truthful about her disease (but she "did not lie," daw, ha) but that she has a form of lupus and that she is allergic to everything that can cure her. Then she went on to say that the admission might cost her 5 pending contracts. But ... Anyway she starts crying about her boys...and then says she should not be stressed or she might die (her sons might "lose her") Then she announced she is flying out to Singapore tomorrow for 14 days and that she is quitting all forms of socmed bec her doctors say she might get stressed. Then ended the Live. Interesting that she did not address the PAB issue. Made no mention of the Falcis revelation that she was funding the virulent anti Admin posts. There is a principle in evidence that says, that when the occasion calls for a Denial and one does not, then one's silence is an admission. Kris had the chance to loudly deny funding PAB. But SHE DID NOT. Make your conclusions now. sabi naman ng Pro-Duterte lawyer na si Atty. Trixie Cruz-Angeles. "Daming hanash ni Kris, di na lang sagutin kung destabilizer sya. Calling the companies who hire her, please don't get an endorser who is a destabilizer. Unless she is able to clear herself, everyone should know that destabilization efforts ruin the economy, which is bad for your business," sabi naman ni Krizette Laureta Chu.</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -3768,17 +4215,20 @@
           <t>Totoo nga bang may lihim na relasyon ang singer-actor na si Marco Saldana at ang kanyang dance coach na si Yani Cruz, kaya’t biglang nagbago ang ugali ni Marco sa set ng kanyang bagong musical TV series? Ayon sa mga kumakalat na screenshots ng group chat ng production team, napansin umano ng ilang staff na madalas na nagtatagal si Marco sa rehearsal room kasama si Yani kahit tapos na ang kanilang practice at may mga pagkakataon pa raw na sabay silang umaalis ng studio nang hindi nagpapaalam sa iba, dahilan kung bakit may mga nagtatanong kung ito raw ba ang dahilan ng biglaang pag-cancel ni Marco sa ilang guestings at ang pag-iwas niya sa mga press conference nitong mga nakaraang linggo; dagdag pa ng ilang insiders, tila nagiging distracted na raw si Marco sa trabaho at may mga eksenang hindi niya natatapos nang maayos, kaya’t usap-usapan sa social media kung mauuwi ba ito sa disciplinary action mula sa management o kung may mas malalim pang dahilan sa likod ng kanilang madalas na pagkikita ni Yani na ngayon ay iniintriga na ng mga fans at netizens.</t>
         </is>
       </c>
-      <c r="C129" s="2" t="inlineStr">
+      <c r="C129" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -3793,17 +4243,20 @@
           <t>Sa panayam kay Abu Misry Mama, tagapagsalita ng BIFF, sa isang lugar sa Maguindanao, tiniyak niya ang paninindigan ng kanilang grupo sa "Separate Islamic State in Mindanao" na tanging opsiyon para mapayapa ang rehiyon.</t>
         </is>
       </c>
-      <c r="C130" s="2" t="inlineStr">
+      <c r="C130" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>religion</t>
         </is>
       </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -3818,17 +4271,20 @@
           <t>Ikinagulat ng marami ang anunsyo ng pamahalaan ngayong linggo tungkol sa pagpapatupad ng “Bayanihan Tax Credit” na naglalayong bigyan ng 10% diskwento sa buwis ang lahat ng sumusuporta sa mga proyekto ng lokal na gobyerno, kaya’t dagsa ngayon ang mga post sa social media ng mga mamamayan na nagpapakita ng kanilang pakikilahok sa mga community clean-up drive at tree planting activities para lamang makakuha ng sertipikasyon na magagamit sa tax discount; ayon sa mga opisyal, layunin daw ng patakarang ito na palakasin ang diwa ng bayanihan at hikayatin ang lahat na maging aktibo sa mga gawaing pampamayanan, ngunit may ilan ding nagsasabing baka raw ito ay paraan lang para tumaas ang popularidad ng kasalukuyang administrasyon, habang mas marami pa rin ang nagpapahayag ng suporta at umaasang magiging tuloy-tuloy na ang ganitong mga insentibo na umano’y makakatulong hindi lang sa bulsa kundi pati sa pag-unlad ng kanilang barangay.</t>
         </is>
       </c>
-      <c r="C131" s="2" t="inlineStr">
+      <c r="C131" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -3843,17 +4299,20 @@
           <t>Matagal nang nangangarap si Lianne Cruz na makilala bilang isang visual artist, at nitong linggo ay bigla siyang napansin ng online community matapos mag-viral ang kanyang mga painting na gawa lamang sa recycled materials tulad ng lumang karton, plastic bottle caps, at sirang tela; maraming netizens ang humanga sa kanyang malikhaing paraan ng paglikha ng obra at sa mensaheng dala nito tungkol sa kalikasan, kaya’t agad siyang nakatanggap ng mga imbitasyon mula sa iba’t ibang art groups at online shows, at ayon kay Lianne, hindi raw niya inasahan na ang simpleng hobby na ginagawa niya tuwing libre ay maghahatid ng inspirasyon sa iba, lalo na sa mga kabataang walang pambili ng mamahaling art materials, kaya’t patuloy siyang gagawa ng mga likhang sining na nagpapakita na hindi hadlang ang limitadong resources basta’t may tiyaga, pagkamalikhain, at malasakit sa kapaligiran.</t>
         </is>
       </c>
-      <c r="C132" s="2" t="inlineStr">
+      <c r="C132" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -3868,17 +4327,20 @@
           <t>Hindi na nakapagtimpi si Senator Sherwin Gatchalian sa isyu na kinasasangkutan ng basagulerong atenista. Ayon sa mambabatas, ilang araw na ang lumipas pero hindi pa rin daw humihingi ng paumanhin ang mga magulang ng salarin. Dagdag pa ng senador, kung nagkataon na siya ang magulang ng bata ay agad-agad daw siya magpapaumanhin. Para kay Gatchalian, kinikunsinte daw ng mga magulang ang anak. "Dalawang araw nang nangyari 'to pero 'yung magulang ay hindi pa humihingi ng paumanhin doon sa naging biktima at hindi pa humihingi ng paumanhin sa nangyari, so kinukunsinte ito ng kanyang magulang...Dahil kung ako 'yung magulang, kaagad akong hihingi ng paumanhin du'n sa biktima at hihingi ako ng dispensa,"sabi ni Gatchalian. Sa hiwalay na pahayag, sinabi ni Gatchalian na dapat makatapat ng bata si Senator Manny Pacquiao. "Sasabihin ko sa aking colleague na si Senator Manny Pacquiao na pagsabihan niya itong bully ng Ateneo... Tingin ko hindi makakapalag itong bully kay Sen. Manny at baka matanto nitong tao ang masamang ginawa niya sa kapwa... Mag 'one-on-one' sila at pagusapan nila na hindi dapat ginagawa iyan sa kapwa estudyante. Itong tao ay dapat makausap ng masinsinan ng isang katapat niya - Sen Manny Pacquiao ang pwede... Responsibilidad 'yan nga mga magulang. Sila ang dapat managot sa ginagawa ng kanilang mga anak,"pahayag ni Gatchalian. Ang ginawa ng basagulerong atenista ay nagdulot ng lubos na galit sa mga kababayan natin. Ang iba ay gumawa pa ng mga reaksyon videos para kastiguhin ang mga magulang ng salarin. Basahin ang ilang opinyon ng mga kababayan natin sa naging pahayag ni Senador Gatchalian.</t>
         </is>
       </c>
-      <c r="C133" s="2" t="inlineStr">
+      <c r="C133" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>education</t>
         </is>
       </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -3893,17 +4355,20 @@
           <t>Totoo nga bang may bagong sindikato na gumagamit ng mga robot para magnakaw sa mga bahay? Usap-usapan ngayon sa Barangay Mabini ang diumano’y “Robotong Magnanakaw” na sinasabing pumapasok sa mga bahay tuwing madaling araw gamit ang maliliit na makina na kayang magbukas ng mga pintuan at bintana nang hindi naririnig ng mga residente; ayon sa ilang kwento ng kapitbahay, biglang naglaho ang kanilang mga cellphone, wallet at pati na raw ang isang ref nang walang bakas ng puwersahang pagpasok, kaya’t marami ang natakot at nag-post ng mga video sa social media na nagpapakita ng tila gumagalaw na anino ng robot sa kanilang sala, dahilan upang magpatuloy ang takot at haka-haka na baka raw may mastermind na nag-eeksperimento ng bagong paraan ng pagnanakaw na hindi kayang pigilan kahit ng mga aso o CCTV camera, at dahil dito ay nagdagsaan ang mga tanong kung ligtas pa nga bang matulog sa sariling bahay kapag may teknolohiyang gamit ang mga kriminal.</t>
         </is>
       </c>
-      <c r="C134" s="2" t="inlineStr">
+      <c r="C134" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -3918,17 +4383,20 @@
           <t>PIRMA na lamang ni Pangulong Duterte ang kulang para maging ganap na batas ang panukalang magpapataw ng parusa sa mga sisipol at mambabastos sa mga babae. Ito'y matapos na ratipikahan ito ng Kamara de Representantes. Nakatakdang ipadala sa Malacanang para papirmahan kay Duterte upang ito ay maging isang batas. Sa ilalim ng panukala, ituturing na gender-based street and public spaces harassment ang wolf-whistling, cat-calling at mga katulad na bagay. Ang parusa rito at P10,000 multa at 12 oras na community service at Gender-Sensitivity Seminar sa Philippine National Police. Sa ikalawang paglabag ang multa ay P20,000 at kulong na hanggang 30 araw. Sa ikatlo at P30,000 multa at hanggang 30 araw na pagkakakulong. Ang mga maglalabas naman ng ari o gagawa ng offensive body gesture ay pagmumultahin ng P30,000 at 12 oras na community service at seminar. Sa ikalawang paglabag ay hanggang 30 araw na kulong at P40,000 multa at sa ikatlo ay P50,000 multa at isa hanggang anim na buwang pagkakakulong. Ang manghihipo naman ay parurusahan ng P100,000 multa, hanggang 30 araw na kulong sa unang paglabag at seminar. Sa ikalawa ay P150,000 multa at kulong na isa hanggang anim na buwan. Sa ikatlo ay P200,000 multa at isa hanggang anim na buwang kulong. Gender-based online harassment naman o sexual harassment sa pamamagitan ng internet ay may parusang P100,000-P500,000 multa at kulong na anim na buwan hanggang anim na taon. "We want to replace this pervasive culture of machismo with a culture of respect and acceptance. Women, LGBT persons, and even men do not deserve to be the target of sexist, misogynist, homophobic or transphobic remarks or become the target of harassment," ani Siquijor Rep. Rav Rocamora, isa sa may-akda ng panukala.</t>
         </is>
       </c>
-      <c r="C135" s="2" t="inlineStr">
+      <c r="C135" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -3943,17 +4411,20 @@
           <t>Nagulantang ang buong showbiz industry nang kumalat ang balitang nagkaroon umano ng matinding sagutan sa backstage ng isang sikat na variety show ang magka-love team na sina Lira Dela Cruz at Jace Rivera, matapos umanong mahuli ni Lira na may ka-text si Jace na isang mysterious na “A” habang nagre-rehearse pa lamang sila; ayon sa mga nakasaksi, hindi na raw napigilan ni Lira ang kanyang emosyon at nag-walkout ito habang si Jace ay naiwang tulala at hindi na natapos ang kanilang prod number, dahilan upang agad mag-trending ang hashtag na #LiraJaceBreakup at maglabasan ang samu’t saring teorya ng mga fans kung sino nga ba si “A” at kung may third party nga ba sa likod ng kanilang hiwalayan, habang may mga nagsasabing scripted lang daw ito para sa promo ng bagong pelikula nila ngunit mas marami pa rin ang naniniwala na tunay at matindi ang away ng dalawa kaya’t abangan na lang daw ang susunod na update sa kanilang kontrobersyal na relasyon.</t>
         </is>
       </c>
-      <c r="C136" s="2" t="inlineStr">
+      <c r="C136" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -3968,17 +4439,20 @@
           <t>"It is the best that the Senate Blue Ribbon Committee resume its investigation in order that those named in the video, Mr. Duterte and Agriculture Undersecretary Waldo Carpio can clear their names." Ganito ang isa sa mga naging pahayag ni Senate Minority Leader Franklin Drilon sa Kapihan forum sa Senado nitong Huwebes, mula sa ulat ng Inquirer. Ang suhestyon na ito ay sinabi ni Drilon matapos umanong kumalat sa mga balita, gayundin sa social media ang isang video, kung saan idinadawit ang dating Bise Alkalde ng Davao City at anak ni Pangulong Duterte na si Paolo Duterte, na may kinalaman umano ito sa mga transaksyon ng ilegal na droga. Matatandaang noong Setyembre 2017 ay dumalo si Duterte sa isang hearing ng committee tungkol sa umano'y smuggling ng may P6 Milyong halaga ng shabu sa bansa. "The Senate Blue Ribbon Committee will provide him (Paolo Duterte) with the opportunity to disprove all of these allegations which to him are invented and unfounded," dagdag pa ni Drilon. Samantala, sa kanyang social media account ay may patutsada naman si Paolo Duterte sa isang tinawag niyang "J.S", kaugnay ng nabanggit na video na nagdadawit sa kanyang pangalan sa mga transaksyon ng ilegal na droga, mula sa ulat ng Philstar Global. "Wow ha, kung makaimbento ka wagas. Galit ka kay Waldo kasi binabara niya lahat ng smuggling mo ng bigas at asukal diba JS. Galit ka sa akin kasi diba hindi kita pinansin sa eroplano kasi hambog ka! Ngayon pansinin na kita kasama ng kamay ko na kasinglaki ng mukha mo kapag nangyari iyan. 'Yan ang totoong balita," ani Paolo Duterte sa kanyang Facebook Page. Ayon naman kay Philippine National Police Chief Oscar Albayalde, kwestyunable umano ang "timing" at motibo sa likod ng nasabing kumakalat na video., na lumabas isang buwan bago ang midterm elections. 'I don't even know if that is admissible in court because anybody can do that video. We are warning netizens of these videos that are self-serving," ani Albayalde.</t>
         </is>
       </c>
-      <c r="C137" s="2" t="inlineStr">
+      <c r="C137" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -3993,17 +4467,20 @@
           <t>Umaani ngayon ng batikos ang ABS-CBN host na si Robi Domingo dahil sa naging social media post nito noong mga nakaraang araw. Ayon kasi sa twitter post ni Domingo, hindi daw ibinebenta ang Pilipinas. Ipinost ni Domingo ang kanyang tweet habang bumibisita si Chinese President Xi Jinping sa bansa. Sa pagbisita ni President Xi, matatandaang lumagda ng 29 na kasunduan ang Pilipinas at China. Hindi naman nagustuhan ng ilang netizens ang mga pinagsasabi ni Domingo. Ito po ang ilan sa kanilang reaksyon.</t>
         </is>
       </c>
-      <c r="C138" s="2" t="inlineStr">
+      <c r="C138" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -4018,17 +4495,20 @@
           <t>"I would need your help." Ganito ang naging hiling ni Attorney Glenn Chong sa Pro-DUterte Lawyer na si Attorney Trxie Cruz-Angles kaugnay sa pagkakapatay ng kanyang bodyguard at aide na si Richard Santillan sa kamay ng mga pulis sa Cainta. Sa isang maikling sagot, kinumpirma ni Attorney Trixie na tutulong sila para mapanagot ang mga may sala. "We weill help you in anyway that we can. Nire-request ko rin sa lahat ng mga followers ko dito to remember Attorney Chong in your prayers ang kung may kailanganin kami ay mananawagan kami," sabi ni Trixie. Nagnawagan din si Attorney Chong sa mga followers ni Attorney Trixie na panatilihing buhay ang isyu kaugnay sa pagkakapatay kay Santillan. "Ang aking pong panawagan sa ating kababayan is huwag po nating payagang mawala ang isyu kay Richard Santillan. I really ask for your help," sabi ni Chong. Basahin po ang reaksyon at mensahe ng mga tao sa bagong kaganapan sa kaso ng pagpatay kay Santillan.</t>
         </is>
       </c>
-      <c r="C139" s="2" t="inlineStr">
+      <c r="C139" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -4043,17 +4523,22 @@
           <t>Pinag-uusapan ngayon ng maraming Pilipino ang viral na video sa social media tungkol sa umano’y dayaan sa raffle promo ng SM Bacoor kung saan ang premyo ay isang Suzuki Dzire Swift. Nagsimula ang pagdududa ng mga netizen nang mapansin nila na hindi inalis ng opisyal ng SM ang kanyang kaliwang kamay sa bulsa habang kumukuha ng raffle entry mula sa tambiolo, at nang mabunot ang panalong entry ay ginamit pa raw nito ang parehong kamay bago ito ibinigay sa kawani ng Department of Trade and Industries (DTI). Ayon kay Norman Sanez Ramirez, ang uploader ng video, nakuha niya ito mula sa Facebook page ng SM Bacoor ngunit agad din daw itong binura sa nasabing page. Nilinaw ni Ramirez na ang layunin ng kanyang post ay para malaman ng publiko kung may naganap bang pandaraya at hindi para manira ng ibang tao. Kahit tinanggal na ang orihinal na video, kumalat pa rin ito sa iba’t ibang Facebook pages at umabot na sa mahigit 30,000 shares, dahilan para umani ito ng iba’t ibang reaksyon mula sa mga netizen. Habang wala pang opisyal na pahayag, patuloy ang diskusyon kung may nangyaring hokus-pokus sa nasabing raffle draw.</t>
         </is>
       </c>
-      <c r="C140" s="2" t="inlineStr">
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t>Pinagpi-piyestahan ngayon ng mga kababayan natin ang kumakalat na video sa social media tungkol sa diumano'y dayaan na nangyari daw sa SM Bacoor sa isinagawang raffle promo. Ang premyo sa naturang promo ay isang bagong kotse (Suzuki Dzire Swift). Nag-ugat ang pagdududa ng mga kababayan natin dahil sa naging kilos ng opisyal ng SM Mall habang isinasagawa ang raffle draw. Ayon sa mga netizens, kapansin-pansin daw na hindi inalis ng SM official ang kaliwang kamay nito sa kanyang bulsa habang kumukuha ng raffle entry sa tambiolo. At nang may nakuha daw na winning raffle entry, sabay na ginamit umano ng opisyal ang kanyang kaliwa't-kanang kamay at ibinigay ang winning entry sa kawani ng Department of Trade and Industries (DTI). Ayon sa uploader ng video na si Norman Sanez Ramirez, galing daw ang video sa Facebook page mismo ng SM Bacoor pero binura na daw ito sa FB page ng SM. Nai-save niya daw ang naturang video para malaman kung totoo bang may nangyaring dayaan. "This was originally a live video from Sm Bacoor page but it seems that the video was already been deleted. This post was not intended to hurt or ruin someone else's life or family please stop bashing guys, gusto lang din naman pong malaman nang iba kung totoo ba o hindi yung nakitang pandaraya, i know they are just doing their job haiz"sabi ni Ramirez. Binura na po ng original uploader ang kanyang video, pero may ilang Facebook pages na nakapag-upload ng nasabing video. Habang isinusulat ang artikulong ito ay umabot na sa mahigit 30,000 ang nag-bahagi ng video at umani na rin ng sari-saring reaksyon mula sa mga kababayan natin. May hokus-pokus nga ba na nangyari? Ano sa tingin niyo?</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>lifestyle / human interest</t>
         </is>
       </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -4068,17 +4553,22 @@
           <t>Mahigit 248 na construction equipment na nagkakahalaga ng P1.5 bilyon ang binili ng Armed Forces of the Philippines (AFP) mula sa China para sa rehabilitasyon ng Marawi City at mga karatig lugar. Ayon kay Major General Pio Q Dinoso III, Deputy Chief of Staff for Logistics, makakatulong ang mga kagamitan hindi lang sa patuloy na rehabilitasyon at reconstruction ng Marawi kundi pati na rin sa suporta sa pambansang kaunlaran. Tinanggap ng AFP ang mga equipment mula sa Department of National Defense (DND) sa isang symbolic handover na ginanap sa Camp Aguinaldo. Ang pagbili ng mga bagong kagamitan ay bahagi ng Horizon 2 program ng AFP Modernization Program na may P300 bilyong budget mula sa administrasyong Duterte at ipinatupad mula 2018 hanggang 2022, at nabili ito sa ilalim ng government-to-government deal sa China. Kabilang sa mga biniling equipment ay telescopic cranes, tracked dozers, road graders, scoop loaders, backhoe loaders, road rollers, transit mixers, dump trucks, at water lorries. Ayon kay Department of National Defense Undersecretary Cardozo Luna, na naging Guest of Honor at Speaker sa event, ang pagbili ng mga kagamitan ay resulta ng gumagandang relasyon ng Pilipinas at China at patunay ng lumalalim na bilateral exchanges at suporta ng China sa modernization program ng AFP. Dagdag pa ni Luna, ang AFP Engineering Equipment Acquisition project na may approved budget na P1,560,000,000 ay ang unang proyektong ipinatupad matapos lagdaan ang MOU sa defense logistics cooperation ng Pilipinas at China.</t>
         </is>
       </c>
-      <c r="C141" s="2" t="inlineStr">
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t>Higit 248 units ng construction equipment na nagkakahalaga ng P1.5 billion ang binili ng Armed Forces of the Philippines (AFP) sa China para sa rehabilitasyon ng Marawi City at mga kalapit lugar. Ayon kay Major General Pio Q Dinoso III, Deptuy Chief of Staff for Logistics na "These equipment will not only help the AFP to support the continuous effort of the administration to facilitate the comprehensive rehabilitation and reconstruction of Marawi as a city but also in performing our role in support to national development of the whole country." Tinanggap ng AFP mula sa Department of National Defense (DND) ang mga kagamitan sa isinagawang isang symbolic handover sa Camp Aguinaldo. Ang pagbili sa mga bagong kagamitan ay bahagi ng Horizon 2 program ng AFP Modernization Program at nabili sa ilalim ng government-to-government deal sa China. Ang Horizon 2 program ay may P300 billion budget mula sa Duterte administration na ipinatutupad mula 2018 hanggang 2022. Ilan sa mga nabiling equipment ay mga telescopic cranes, tracked dozers, road graders, scoop loaders, backhoe loaders, road rollers, transit mixers, dump trucks, at water lorries. Ayon kay Department of National Defense Undersecretary Cardozo Luna, Guest of Honor at Speaker sa nasabing event, na ang pagbili sa kagamitan ay resulta ng gumagandang relasyon ng Pilipinas at China. "The implementation of this project and the upcoming donations from China serves as a testament to the growing bilateral exchanges between the Republic of the Philippines and China and its support to the AFP's modernization program," ani Luna. "The AFP Engineering Equipment Acquisition project with an approved budget for the contact in the total amount of one billion five hundred sixty million pesos (P1,560,000,000) is the first project implemented after the signing of the MOU on defense logistics cooperation between RP and China," dagdag ni Luna.</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>international news</t>
         </is>
       </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -4093,17 +4583,20 @@
           <t>Ayon sa PhiVolcs o Philippine Institute of Volcanology and Seismology, dahil sa mga earthquake swarms na nangyari sa Surigao Del Norte kamakailan ay maaaring magkaroon ng Magnitude 8 na lindol sa bansa. Ang earthquake swarms ay mga maliliit na lindol na nangyari ng makailang beses at halos pareho ang mga lakas nito. Ayon din sa PhiVolcs, bagama't hindi nila maituturo kung saan ang lugar ng lindol at kung kailan ito mangyayari, maaari nilang makalkula ang lakas nito. Sa isang panayam kay PhiVolcs director Renato Solidum, may kakayahan ang kanyang tanggapan na i-estimate ang lakas ng susunod na lindol. "'Yung oras kung kailan mangyayari ang malakas na lindol, hindi masasabi. Pero puwede nating matantsa kung ano ang magnitude ng bawat fault na puwedeng ipakilos ng lindol," paliwanag ni Solidum. Sa kabila ng kanilang pahayag, sinabi naman ni Solidum na maaari din namang hindi magtuloy ang malakas na lindol at sa halip ay maliliit na lindol lamang ang maganap. Inilabas nila ang babalang ito hindi upang manakot kundi upang makapaghanda ang mga tao sa disgrasyang dulot ng malakas na lindol. "Ang sinabi namin ang pagdating sa mga trenches, 'yung segment offshore ng Surigao provinces ay may kakayahan magdulot ng magnitude 8 na earthquake. Matagal na po naming sinasabi yan. Puwede pong maliliit na lindol lamang at puwedeng dumiretso sa malalaki. Pero posible din naman na 'yung mga maliliit na paglindol o moderate size na earthquake ay hanggang doon na lamang," dagdag pa ng direktor. Ayon naman sa isang report mula sa Inquirer, ang isang lindol na may Magnitude 8 ay maaaring magdulot din ng isang tsunami o tidal wave. Ito ang dahilan kung kaya't nagbigay paalala ang PhiVolcs ukol sa disgrasyang maaaring maidulot ng malakas na lindol.</t>
         </is>
       </c>
-      <c r="C142" s="2" t="inlineStr">
+      <c r="C142" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>disaster / environment</t>
         </is>
       </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -4118,17 +4611,20 @@
           <t>NASAWI ang isang barangay chairman ng Pili, Camarines Sur, matapos saksakin ng lasing na lalaking kanyang inawat sa panggugulo, Sabado ng madaling-araw. Itinakbo pa sa ospital si Daniel Bismonte, chairman ng Brgy. Tinangis, ngunit di na umabot nang buhay, ayon sa ulat ng Bicol regional police. Naganap ang insidente sa Zone 1B, Upper Lampog, ng Tinangis, dakong alas-12:20. Pinapayapa noon ng 59-anyos na si Bismonte ang di kilalang lalaki, na nanggugulo't may dalang patalim habang lasing. Sa kasagsagan nito'y biglang sinaksak ng lalaki ang leeg ng chairman, ayon sa pulisya. Dinala si Bismonte ng kanyang mga tanod sa ospital ng Army 9th Infantry Division, pero idineklara siyang dead on arrival ng doktor. Pinaghahanap pa ng lokal na pulisya ang suspek, na mabilis tumakas matapos ang insidente.</t>
         </is>
       </c>
-      <c r="C143" s="2" t="inlineStr">
+      <c r="C143" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -4143,17 +4639,20 @@
           <t>Posible nga bang maging inspirasyon sa lahat ang kwento ni Marco Dela Cruz, ang bagong mukha ng OPM na biglang sumikat matapos mag-viral ang kanyang simpleng video na kumakanta sa gilid ng kalsada gamit lang ang lumang gitara ng kanyang lolo? Sa kabila ng hirap ng buhay at kakulangan sa kagamitan, pinatunayan ni Marco na hindi hadlang ang kahirapan para maabot ang pangarap, kaya’t napansin siya ng isang sikat na music producer na nag-alok sa kanya ng recording deal; ngayon, trending na ang kanyang unang single na “Pangarap sa Tabing Daan” at marami ang humahanga sa kanyang dedikasyon, kababaang-loob, at pagmamahal sa musika, dahilan para maging inspirasyon siya ng mga kabataang nangangarap din na maabot ang tagumpay sa kabila ng mga pagsubok.</t>
         </is>
       </c>
-      <c r="C144" s="2" t="inlineStr">
+      <c r="C144" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -4168,17 +4667,20 @@
           <t>Totoo kaya na nagdulot ng tensyon sa pagitan ng Pilipinas at bansang Turania ang diumano’y paglipad ng isang Turanian military drone sa ibabaw ng Palawan nitong nakaraang linggo? Ayon sa mga ulat na kumalat online, biglang napansin umano ng mga lokal na mangingisda ang kakaibang ingay sa himpapawid at nakita nilang may drone na may kakaibang markings na palipad-lipad malapit sa kanilang bangka, dahilan upang agad silang mag-report sa mga awtoridad; sinasabing agad namang nagpadala ng diplomatic note ang Department of Foreign Affairs sa Turania upang humingi ng paliwanag, habang ilang senador ang nagpaabot ng pangamba na baka may kinalaman ito sa isyu ng territorial waters, kaya’t marami ngayon ang nag-aabang kung paano tutugon ang dalawang bansa sa insidenteng ito na nagdulot ng kaba at usap-usapan sa social media.</t>
         </is>
       </c>
-      <c r="C145" s="2" t="inlineStr">
+      <c r="C145" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>international news</t>
         </is>
       </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -4193,17 +4695,20 @@
           <t>Usap-usapan ngayon sa social media ang umano'y panggagaya ng kinatawan ng Thailand na si Ingchanok Prasart sa ginanap na Miss Intercontinental pageant 2018 sa trademark ni Miss Universe 2018 Catriona Gray na "lava walk." Isang netizen sa Twitter na nagngangalang Marnie Raro ang nakapansin sa paraan ng paglalakad at pag-project ni Miss Thailand na parang kinokopya ang "lava walk" ni Catriona. Bukod kay Miss Thailand, napansin din ng mga netizens ang pagkopya umano sa "Mayon Volcano gown" ni Miss Vietnam. Aminado naman ang dalawa na labis nilang hinahangaan at inspirasyon nila si Miss Universe 2018 Catriona Gray. Halo-halo naman ang naging reaksyon ng mga netizens hinggil dito. "So now everyone looks like Catriona Gray. From hair to stance to gowns. The influence. Only legends do that." "Catriona Gray's walk can never be perfect without her walking it." "I think so? Even the hand gesture of Miss Thailand seems copied too. Catriona Gray is indeed a queen." "Yet they can't copy the original. Because there will be only one Lava Walk and Catriona Gray." "Kayo na 'yung may mga originality... hala gawa kayo sarili niyong pageant, ano ba naman yung hayaan niyo na lang sila hays....daming toxic." Isang patunay lamang ito na maraming mga aspiring beauty pageant candidates, hindi lamang sa Pilipinas kundi maging sa buong mundo, ang tumitingala at humahanga kay Catriona. Aminado naman dito ang marami sa mga kandidata ng naturang katatapos na pageant. Ang 47th edition ng Miss Intercontinental 2018 ay ginanap noong Enero 26, 2019, sa SM Mall of Asia Arena sa Pasay, Metro Manila, Philippines. Kinoronahan ni Miss Intercontinental 2017 Veronica Salas Vallejo ng Mexico ang kandidata ng Pilipinas na si Karen Juanita Gallman. Ito ang kauna-unahang pagkakataong naging host ang Pilipinas sa pageant na ito. Pinili ng Japan organizers ang Pilipinas na maging venue ng pageant dahil abala ang bansang Japan sa mga paghahanda para sa 2020 Summer Olympics. Narito ang buong Twitter post ng netizen:</t>
         </is>
       </c>
-      <c r="C146" s="2" t="inlineStr">
+      <c r="C146" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -4218,17 +4723,22 @@
           <t>Matapos ang ilang oras ng paghihintay ng mga netizens, iniulat na rin ng isang primetime news program ang insidente ng pagpatay sa bodyguard o aide ni Former Congressman Atty. Glen Chong. Sa kanilang ulat, ipinakita ang video ng isang SUV na napapalibutan ng mga police mobile habang maririnig ang putok ng baril. Mariing itinanggi ng mga kamag-anak ni Santillan ang mga paratang ng pulis sa nasawi; ayon kay Jeanette Santillan, asawa ni Richard, naggi-gift giving lamang ito kasama ang mga pulis at mismong mga pulis din ang pumatay sa kanya. Hindi rin kumbinsido ang ilang mamamayan sa paliwanag ng mga pulis, at ibinahagi nila ang kanilang mga komento at opinyon tungkol sa nangyari kay Santillan.</t>
         </is>
       </c>
-      <c r="C147" s="2" t="inlineStr">
+      <c r="C147" s="3" t="inlineStr">
+        <is>
+          <t>Matapos ang ilang oras na paghihintay ng mga netizens para ibalita ng mga mainstream media ang nangyaring pagpatay sa bodyuguard/aide ni Former Congressman Atty. Glen Chong, ibinalita na rin sa wakas ng isang primetime news program ang insidente. Kaakibat sa kanilang ulat ay ang footage kung saan makikita ang isang SUV na napapalibutan ng mga police mobile at maririnig din ang alingawngaw ng mga putok ng baril. Mariing tinutulan naman ng mga kamag-anak ni Santillan ang mga paratang ng pulis sa nasawi. "Nag-gi-gift giving siya, kasama niya mga pulis. Tapos ang pumatay sa kanya mga pulis," sabi ni Jeanette Santillan, asawa ni Richard Hindi naman kumbinsido ang ilan nating kababayan sa mga sinabi ng mga pulis. Ito po ang ilan sa kanilang mga komento at opinyon sa nangyari kay Santillan.</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -4243,17 +4753,20 @@
           <t>Ayon sa inilabas na pahayag ng Department of Economic Innovations ngayong umaga, ipapatupad na umano simula susunod na buwan ang bagong patakaran na “One Peso Market Day” kung saan lahat ng pangunahing bilihin sa mga piling pamilihan ay maaaring mabili ng kahit sinong mamamayan sa halagang isang piso bawat item isang beses kada linggo, na layong mapagaan daw ang gastusin ng bawat pamilyang Pilipino at mapalakas ang lokal na ekonomiya. Maraming netizen ang agad nagbahagi ng kanilang tuwa at pag-asa sa social media, habang ilang negosyante naman ang nag-aalala kung paano ito makakaapekto sa kanilang kita at operasyon. Ayon pa sa ahensya, may mga itatalagang “Market Marshals” para tiyaking patas ang distribusyon ng mga produkto at maiwasan ang hoarding, at may parusa raw sa sinumang lalabag sa mga alituntunin ng bagong programa. Bagama’t wala pang inilalabas na listahan ng mga pamilihang kasali at detalye kung paano ipatutupad ang sistemang ito, umaasa ang mga mamamayan na tuloy-tuloy ang ganitong uri ng inisyatiba upang tuluyang mapababa ang presyo ng mga pangunahing bilihin at mapalakas ang kanilang kakayahang bumili sa gitna ng tumataas na gastusin.</t>
         </is>
       </c>
-      <c r="C148" s="2" t="inlineStr">
+      <c r="C148" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>economy / business</t>
         </is>
       </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -4268,17 +4781,20 @@
           <t>Ito ang opinyon ng National Union of Students of the Philippines (NUSP), dahil sa hindi mapigilan ng gobyerno, partikular ng Commission on Higher education (ChEd), ang paglaki ng mga bayarin, partikular ang matrikula.</t>
         </is>
       </c>
-      <c r="C149" s="2" t="inlineStr">
+      <c r="C149" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>education</t>
         </is>
       </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -4293,17 +4809,20 @@
           <t>Binabatikos ngayon ng ilang kababayann ang nagin pahayag ni MADGALO Congressman at Otso Diretso senatorial candidate Gary Alejano tungkol sa mga nadiskubreng bloke-bloke ng cocaine sa karagatan sadalampasigan ng Davao Oriental at Nueva Ecija. Ayon kay Alejano, ito raw ay senyales na palpak ang paglaban sa droga ng kaslukuyang gobyerno. Ang mga cocaine bricks na nakumpiska ay nakakahalaga ng P200 million. "Pagkatapos ipagmalaki ng administrasyon ang mga tagumpay umano ng drug war policy nito, patuloy naman ang pagpapasok ng bulto-bultong ilegal na droga sa ating bansa... The drug war is a failure," sabi ni Alejano. Banat pa ni Alejano, tanda raw ito na kumpiyansa daw ang mga durugista na maipasok ang droga sa bansa dahil hindi daw sila hinahabol ng gobyerno. "Three years of government's crackdown on illegal drugs and thousands of drug suspects killed did not deter the continuous entry of drugs in our country. Those who continue to bring in illegal drugs are obviously confident that the government will not go after them," boladas ni Alejano. Hindi naman pinalampas ng mga kababayan natin ang bagong pahayag ni Alejano. Ayon sa ilang netizens, paano magiging failure ang drug war kung may nadidiskubre at nakukumpiskang droga?</t>
         </is>
       </c>
-      <c r="C150" s="2" t="inlineStr">
+      <c r="C150" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -4318,17 +4837,22 @@
           <t>Kumalat sa Facebook ang post ng netizen na si Krstna Snchez Dizon kung saan ibinahagi niya ang bible reflection mula sa 'Didache - Daily Bible Reflections For Catholics' ngayong araw, Abril 22, na pinamagatang 'The Big One.' Ayon kay Krstna, nasa BDO siya nang maramdaman ang magnitude 6.1 na lindol at ipinakita ng teller ang bible reflection na tumugma sa pangyayari. Ang 'Didache - Daily Bible Reflections For Catholics' ay isang pang-araw-araw na booklet ng bible reflection para sa mga Katoliko. Maraming netizens ang kinilabutan at itinuring itong paalala tungkol sa pananampalataya sa Diyos, lalo na’t naramdaman ang lindol sa malaking bahagi ng Metro Manila bandang alas-5:11 ng hapon. Marami ring netizens ang agad na nagbahagi ng kanilang karanasan sa social media habang lumilindol at pagkatapos ng sakuna, at nagpaalala ang ilan na maging handa, magdasal, at i-save ang mga emergency hotline ng iba't ibang ahensya ng gobyerno para sa oras ng pangangailangan.</t>
         </is>
       </c>
-      <c r="C151" s="2" t="inlineStr">
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>Kumakalat ngayon ang Facebook post na binahagi ng netizen na si Krstna Snchez Dizon kung saan pinakita nito ang bible reflection mula sa 'Didache - Daily Bible Reflections For Catholics' ngayong araw na ito. Kwento ni Krstna, nasa BDO daw siya nang maganap ang pagyanig ng magnitude 6.1 na lindol nang pinakita ng teller doon ang bible reflection sa araw na ito, Abril 22, na may pamagat na 'The Big One.' Ang 'Didache - Daily Bible Reflections For Catholics' ay isang daily bible reflection booklet para sa sa mga katoliko. Maraming netizens ang kinilabutan at naniwalang isa itong paalala sa ating mga Pilipino patungkol sa ating pananampalataya sa Diyos. Ngayong araw, Abril 22 bandang alas-5:11 ng hapon, niyanig ng magnitude 6.1 na lindol ang kalakhang Luzon, na naramdaman sa karamihan ng parte ng Metro Manila. Naging mabilis ang ilang netizens sa pagbabahagi ng mga kaganapan sa kanilang lugar, habang lumilindol at matapos ang sakuna. Samantala, nagbigay paalala ang mga netizen na maging handa sa anumang sakuna at magdasal, at i-save ang mga numero ng ibat-ibang ahensya ng gobyerno na pwedeng tawagan sakaling kailangan ng tulong. ITO ANG BUONG POST NI KRSTNA:</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>religion</t>
         </is>
       </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -4343,17 +4867,20 @@
           <t>Sa gitna ng matinding init ng panahon at kabi-kabilang reklamo tungkol sa biglaang pagkawala ng tubig sa ilang barangay, usap-usapan ngayon online ang teorya ng ilang netizen na sinadyang pinaputol umano ni Mayor Renato Salazar ang supply ng tubig upang mapilitan ang mga residente na bumili ng tubig mula sa isang pribadong kumpanya na diumano’y pag-aari ng kanyang malapit na kamag-anak; ayon sa mga komentaryo, napapansin daw na tuwing may anunsyo ng water interruption ay may mga truck ng tubig na agad nag-iikot at nagbebenta sa mas mataas na presyo, kaya’t hinala ng ilan ay may lihim na kasunduan sa pagitan ng opisina ng alkalde at ng naturang kumpanya, dahilan upang lalong uminit ang diskusyon sa social media at magdulot ng pagdududa sa tunay na motibo sa likod ng paulit-ulit na problema sa tubig sa kanilang lugar.</t>
         </is>
       </c>
-      <c r="C152" s="2" t="inlineStr">
+      <c r="C152" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -4368,17 +4895,22 @@
           <t>Isang Pilipino na naman ang nagbigay ng karangalan sa bansa matapos tanghaling kampeon si John Ivan "Jovan" Aquino sa unang season ng pinakamalaking singing reality show sa United Arab Emirates na "The One." Ayon sa UAE News 24/7, mula sa 800 na nag-audition, 60 lang ang napili, kabilang si Jovan na empleyado sa Aldrich International, isang marketing consultancy firm sa Dubai. Hindi raw niya inaasahan ang pagkapanalo at sinabi niyang in-enjoy lang niya ang kompetisyong tumagal ng isang buwan. Sa kanyang Instagram post, nagpasalamat si Jovan sa Diyos, pamilya, kamag-anak, at mga kaibigan, at binati ang lahat ng Happy New Year matapos siyang ideklarang grand winner limang minuto bago mag-bagong taon. Isa sa mga nakalaban niya ay si Ivy Grace Paredes, isang Pinay na naging contestant din sa X Factor UK noong 2016. Tumanggap si Jovan ng 12,500 Arab Emirates Dirham o halos P179,000 bilang premyo matapos niyang awitin ang "Feeling Good" na pinasikat nina Michael Buble at Nina Simone sa grand finals na ginanap sa IMG Worlds noong Disyembre 31, 2018.</t>
         </is>
       </c>
-      <c r="C153" s="2" t="inlineStr">
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>Isa na namang Pinoy na talentado sa pag-awit ang nagbigay ng karangalan sa bansa matapos niyang masungkit ang kampeonato sa first season ng pinakamalaking singing reality show sa United Arab Emirates na "The One." Ayon sa ulat ng UAE News 24/7, umabot sa 800 ang nag-audition sa "The One" at pumili lang ng 60 singers, kabilang na ang Pinoy na si John Ivan "Jovan" Aquino, na magpapatuloy sa singing competition. Hindi inaasahan ni Jovan, empleyado ng Aldrich International na isang marketing consultancy firm sa Dubai, na makakamit niya ang kampeonato. Aniya, in-enjoy lang niya ang singing competition na tumagal ng isang buwan. "I'm still speechless and I still couldn't believe it. What a way to close 2018's door and what a great start for me this 2019! 5 minutes before the countdown begins, I was announced the grand winner of UAE's largest singing reality show, The ONE UAE Season 1! Lord God, you have paved my way here since the very beginning. To my family, relatives, and friends who never stopped believing in me, THANK YOU! It was a month-long competition which I just enjoyed... not thinking that eventually, I'll be the one. Again, thank you so much for everything, Lord! I LOVE YOU! HAPPY NEW YEAR, EVERYONE!" post ni Jovan sa Instagram matapos niyang mapili bilang "The One." Ang isa sa mga nakalaban ni Jovan sa singing reality show ay si Ivy Grace Paredes, isang Pinay na naging contestant sa X Factor UK noong 2016. Tumanggap si Jovan ng 12,500 Arab Emirates Dirham na katumbas ng P179,000 bilang premyo. Ang winning song na inawit niya ay ang "Feeling Good" na pinasikat ni Michael Buble at Nina Simone. Ginanap ang grand finals sa IMG Worlds noong ika-31 ng Disyembre 2018. Source 1 Source 2 Source 3</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>international news</t>
         </is>
       </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -4393,17 +4925,20 @@
           <t>Kaninang umaga lang ay sumuko sa Philippine National Police (PNP) si Joemel Advincula, ang lalaking nagpakilalang alyas "Bikoy". Ayon kay Advincula, babayaran daw dapat umano siya ng kampo ni Senador Antonio Trillanes ng kalahating milyon para lumabas sa video series na "Ang Totoong Narco List". Ang naturang mga videos ay naglalaman ng mga paninira sa mga kaanak ni Presidente Rodrigo Duterte sa pamamagitan ng pag-uugnay sa mga ito sa kalakalan ng droga. Base sa mga pahayag ni Advincula, kasama din daw si Senadora Risa Hontiveros at ilang personalidad sa Liberal Party sa paggawa ng mga videos. Mukhang hindi naman palalampasin ng bagong halal na kongresista na si Paolo DUterte ang sitwasyon. Balak paimbestigahan ni Paolo ang mga taong sangkot sa ma mapanirang videos. "Without a doubt, as I have said before, Senator Antonio Trillanes was behind it. And now that many names have also surfaced, to include Sen. Risa Hontiveros and several lawyers, I believe a proper investigation is in order," banat ni Davao Representative-elect Paolo Duterte. Layunin daw ng mga videos na sirain ang tiwala ng publiko sa kasalukuyang gobyerno. "It was obviously designed to inspire public disgust against the government... All the lies presented were also meant to crush the trust of the Filipino people in the government and the Duterte administration," dagdag pa ni Paolo. Si Paolo at si Antonio Trillanes ay matagal ng nagkakairingan. Magugunitang ipinatawag ni Trillanes ang presidential son sa isang senate hearing para imbestigahan ito tungkol sa droga.</t>
         </is>
       </c>
-      <c r="C154" s="2" t="inlineStr">
+      <c r="C154" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -4418,17 +4953,22 @@
           <t>Usap-usapan ngayon sa social media ang umano'y panggagaya ng kinatawan ng Thailand na si Ingchanok Prasart sa trademark na "lava walk" ni Miss Universe 2018 Catriona Gray sa Miss Intercontinental 2018, matapos mapansin ng netizen na si Marnie Raro sa Twitter ang paraan ng paglalakad at pag-project ni Miss Thailand na tila ginagaya si Catriona. Bukod dito, napansin din ng mga netizens ang pagkopya umano ni Miss Vietnam sa "Mayon Volcano gown" ni Catriona. Inamin naman ng dalawa na malaki ang paghanga at inspirasyon nila kay Catriona Gray, at iba-iba ang naging reaksyon ng mga netizens hinggil dito, kabilang na ang mga nagsasabing malaki ang impluwensya ni Catriona at may mga nagsasabing hindi kayang tapatan ang orihinal na "lava walk." Patunay ito na maraming aspiring beauty pageant candidates sa Pilipinas at sa buong mundo ang humahanga kay Catriona, na inamin din ng marami sa mga kandidata ng nasabing pageant. Ang 47th edition ng Miss Intercontinental 2018 ay ginanap noong Enero 26, 2019 sa SM Mall of Asia Arena sa Pasay, Metro Manila, Philippines, kung saan kinoronahan ni Miss Intercontinental 2017 Veronica Salas Vallejo ng Mexico ang kandidata ng Pilipinas na si Karen Juanita Gallman, at ito rin ang unang pagkakataon na naging host ang Pilipinas sa pageant na ito matapos piliin ng Japan organizers ang bansa bilang venue dahil abala ang Japan sa paghahanda para sa 2020 Summer Olympics.</t>
         </is>
       </c>
-      <c r="C155" s="2" t="inlineStr">
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>Usap-usapan ngayon sa social media ang umano'y panggagaya ng kinatawan ng Thailand na si Ingchanok Prasart sa ginanap na Miss Intercontinental pageant 2018 sa trademark ni Miss Universe 2018 Catriona Gray na "lava walk." Isang netizen sa Twitter na nagngangalang Marnie Raro ang nakapansin sa paraan ng paglalakad at pag-project ni Miss Thailand na parang kinokopya ang "lava walk" ni Catriona. Bukod kay Miss Thailand, napansin din ng mga netizens ang pagkopya umano sa "Mayon Volcano gown" ni Miss Vietnam. Aminado naman ang dalawa na labis nilang hinahangaan at inspirasyon nila si Miss Universe 2018 Catriona Gray. Halo-halo naman ang naging reaksyon ng mga netizens hinggil dito. "So now everyone looks like Catriona Gray. From hair to stance to gowns. The influence. Only legends do that." "Catriona Gray's walk can never be perfect without her walking it." "I think so? Even the hand gesture of Miss Thailand seems copied too. Catriona Gray is indeed a queen." "Yet they can't copy the original. Because there will be only one Lava Walk and Catriona Gray." "Kayo na 'yung may mga originality... hala gawa kayo sarili niyong pageant, ano ba naman yung hayaan niyo na lang sila hays....daming toxic." Isang patunay lamang ito na maraming mga aspiring beauty pageant candidates, hindi lamang sa Pilipinas kundi maging sa buong mundo, ang tumitingala at humahanga kay Catriona. Aminado naman dito ang marami sa mga kandidata ng naturang katatapos na pageant. Ang 47th edition ng Miss Intercontinental 2018 ay ginanap noong Enero 26, 2019, sa SM Mall of Asia Arena sa Pasay, Metro Manila, Philippines. Kinoronahan ni Miss Intercontinental 2017 Veronica Salas Vallejo ng Mexico ang kandidata ng Pilipinas na si Karen Juanita Gallman. Ito ang kauna-unahang pagkakataong naging host ang Pilipinas sa pageant na ito. Pinili ng Japan organizers ang Pilipinas na maging venue ng pageant dahil abala ang bansang Japan sa mga paghahanda para sa 2020 Summer Olympics. Narito ang buong Twitter post ng netizen:</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -4443,17 +4983,20 @@
           <t>Sa kanyang ulat kay Senior Supt. Rodolfo Recomono Jr., direktor ng Pampanga Police Provincial Office (PPPO), sinabi ni Riego na positibong kinilala si Pangan ng mga saksi bilang may suspek sa pagnanakaw at pagpatay sa mag-inang sina Jovita Salon, 35; at Carl Christian Salon, 9. Sinabi ni Riego na si Pangan ay bayaw ng kapatid ng biktima "kaya madali siyang nakilala ng dalawang batang witnesses na ang tawag pa sa kanya ay Kuya Macmac". Batay sa salaysay ng mga testigo, isang 11-anyos at isang 15-anyos na parehong pamangkin ni Jovita, naulinigan nila ang sigaw ng paghingi ng saklolo ng kanilang tiyahin mula sa silid nito dakong 4:00 ng umaga noong Biyernes. Nang sumilip sila sa kuwarto ay nakita umano ng mga bata ang kanilang "Kuya Macmac" habang tumatakas mula sa terrace ng ikalawang palapag at nang tinangka nitong lapitan sila ay nagtakbuhan sila pabalik sa kanilang silid at ikinandado ito. Bukod sa salaysay ng dalawang menor de edad, sinabi rin ng dalawa pang saksi--sina Ramon Yumul, 57; at Martin Francisco, 42, kapwa kapitbahay ng mga biktima, na nakita nila si Pangan na tumatalilis mula sa bahay ng mga biktima hanggang sa makasakay ng tricycle. Sinabi rin ni Riego na hindi pumalag ang suspek nang arestuhin ng mga pulis, pero halatang tensiyonado at takot ito. "Naiiyak siya at mukhang nakokonsensya sa kanyang ginawa," ani Riego. Sinabing posibleng pinagnanakawan ni Pangan ang bahay nang magising ang mag-ina, idinagdag pa ni Riego na kapwa namatay ang mga biktima sa pagkabasag ng bungo at may tama rin ng matigas na bagay sa mukha at bibig. "Kaawa-awa ang sinapit ng mag-ina sa kamay ng suspect dahil basag ang bungo at wasak ang mukha ng dalawa at halos hindi na makilala sa lakas ng palo," sabi ni Riego.</t>
         </is>
       </c>
-      <c r="C156" s="2" t="inlineStr">
+      <c r="C156" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -4468,17 +5011,22 @@
           <t>Inaasahan ng Philippine National Police na mapapalakas ang kanilang hanay dahil sa bagong biling modernong kagamitan na nagkakahalaga ng P694 milyon, kabilang dito ang 11,245 units ng undershirt bullet proof vest level IIIA, 4,169 units ng waistcoat vest level IIA na may tow plates level IV, 133 units ng high frequency/single sideband manpack, 700 units ng rotary blade o propelled wing unmanned aerial vehicle (UAV) o drones, 20 mini bus at 2,000 units ng Taurus TS9 striker fired pistol. Ginawa ang blessing ng mga bagong kagamitan sa Camp Crame, Quezon City, kung saan ipapamahagi ang mga bullet proof vest sa Police Regional Offices at National Support Units para sa capability enhancement, ang mga baril ay para sa mga bagong recruit ng PNP, at ang mga mini bus ay para sa PROs at Logistics Support Service. Nagpasalamat din ang PNP sa 120 units ng forensic kits na donasyon mula sa Korea, na makakatulong sa kanilang mga imbestigasyon.</t>
         </is>
       </c>
-      <c r="C157" s="2" t="inlineStr">
+      <c r="C157" s="3" t="inlineStr">
+        <is>
+          <t>Inaasahang mapapalakas ng kapulisan ang hanay nito sa bagong biling modernong kagamitan na may halagang P694 milyon. Ang mga bagong biling gamit ay ang Undershirt bullet proof vest level IIIA (11,245 units), waistcoat vest level IIA with tow plates level IV (4,169 units), high frequency/single sideband manpack (133 units), rotary blade/propelled wing unmanned aerial vehicle (UAV) o drones (700 units), mini bus (20 units) at Taurus TS9 striker fired pistol (2,000 units). Ang blessing ng mga nasabing kagamitan ay ginanap sa Philippine National Police Headquarters sa Camp Crame, Quezon City. Ayon sa PNP, ang mga bullet proof vest ay ipapamahagi sa mga Police Regional Offices (PROs) at National Support Units (NSUs) para sa capability enhancement. Ang mga baril naman ay para sa mga PNP recruits. Habang ang PROs and Logistics Support Service ang tatanggap ng mga mini buses. Nagpasalamat din ang kapulisan sa natanggap nilang forensic kits na donasyon mula sa Korea. Sa kabuuan, 120 units ang naibigay ng Korea sa PNP. Makakatulong daw ang mga forensic kits sa mga imbestigasyon ng kapulisan. Basahin ang reaksyon ng ilan nating kababayan sa mga bagong gamit ng pulis at donasyon mula sa Korean Government.</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -4493,17 +5041,22 @@
           <t>Naiproklama na kahapon si Vico Sotto bilang bagong mayor ng Pasig, na nagtapos sa mahigit dalawang dekadang pamumuno ni Bobby Eusebio. Matapos ang bilangan, hindi tinanggap ni Eusebio ang resulta at iginiit na may naganap na dayaan sa kampo ni Sotto, aniya siya pa rin ang tunay na nanalo. Ayon kay Eusebio, mapapatunayan umano nila ang umano’y election fraud sa pamamagitan ng mga kasong kanilang isasampa. Maraming netizen ang nagbigay ng opinyon ukol sa hindi pagtanggap ni Eusebio sa pagkatalo, at karamihan sa kanila ay nagsabing sapat na ang 27 taon ng kanyang serbisyo at panahon na para magbigay daan sa iba. Para sa mga taga-Pasig, ang pagkapanalo ni Vico ay simbolo ng kanilang pagnanais ng pagbabago sa lungsod. Si Vico ay anak nina Vic Sotto at Coney Reyes, at bago maging mayor ay nagsilbi na siyang konsehal sa Pasig. Nagpaabot din ng pagbati kay Vico ang kanyang mga kapatid na sina Oyo at Danica, na anak ni Vic Sotto kay Dina Bonnevie.</t>
         </is>
       </c>
-      <c r="C158" s="2" t="inlineStr">
+      <c r="C158" s="3" t="inlineStr">
+        <is>
+          <t>Kahapon ay naiproklama na ang bagong mayor ng Pasig na si Vico Sotto. Sa pagkapanalo ni Vico ay napatid na ang matagal nang panunungkulan ni Bob an natapos na ang bilangan ay nagpahayag ng hindi pagtanggap sa pagkatalo ang dating mayor at iginiit na may dayaan umano na naganap sa partido ni Sotto. Ayon sa kanya, siya ang tunay na panalo sa botohan. Aniya, ang pagkapanalo ni Vico ay bunsod ng election fraud sa hanay nito. Pahayag nito, "Hindi ko tinatanggap ang resulta dahil alam ng tao kung sino ang nanalo." Dagdag pa ni Eusebio, "Alam ng tao rin kung sino ang ibinoto nila, at ito mapapatunayan natin sa pamamagitan din ng pina-file namin na election fraud." Nagpahayag naman ng samu't saring komento ang mga netizen dahil sa pahayag ng hindi pagtanggap sa pagkatalo ni Eusebio. Anila ay sapat na at sobra pa ang 27 taon na panunungkulan nito sa Pasig. Nagpapasalat ang mga ito sa naging serbisyo nito sa nagdaang dalawang dekada ngunit panahon na umano para tumigil na ito at magbigay daan para sa ibang nais manungkulan. Ang pagkakapanalo umano ni Vico laban kay Bobby ay isang senyales na nais na ng mga taga-Pasig ng pagbabago sa kanilang nasasakupan. Si Vico Sotto ay anak ng komedyante at aktor na si Vic Sotto kay Coney Reyes. Ang 29 na taong gulang bagong mayor ng Pasig ay aktibo sa politika noon pa man. Sa katunayan ay ito ay nanungkulan na din bilang Konsehal sa nasabing syudad. Nagpabatid naman ng pagbati kay Vico sina Oyo at Danica na mga anak din ni Vic Sotto kay Dina Bonnevie.</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -4518,17 +5071,20 @@
           <t>ISINAPUBLIKO ng Quezon City Police District (QCPD) ang composite sketch ng isa sa mga itinuturong pumatay kay Barangay Bagong Silangan chair Crisell Beltran. Sinabi ni QCPD Director Chief Supt. Joselito Esquivel Jr. ginawa ang sketch matapos makalap ang testimonya mula sa isang testigo na nakakita ng pananambang. Idinagdag ni Esquivel na umabot na sa 11 testigo ang nakuhaan ng pahayag. Ani Esquivel, nakita ng isa sa mga testigo ang mukha ng gunman nang tanggalin nito ang kanyang helmet para maglagay ng bala. Idinagdag ni Esquivel na anim na suspek ang tinitingnang bilang ng mga sangkot sa krimen matapos namang tambangan ang sinasakyan ni Beltran at kanyang driver na si Melchor Salita habang binabagtas ang kahabaan ng J.P. Rizal st. sa Barangay Bagong Silangan noong Miyerkules. Sinabi pa ni Esquivel na apat ang tinitingnang anggulo sa pagpatay kabilang ang pulitika, negosyo, ang kaugnayan ni Beltran sa mga illegal settlers, at love angle. "[Tinitingnan] natin dito [ang] apat na direksyon ng imbestigasyon. Meron na rin tayong tinitingnan na persons of interest (We are looking at four directions of the investigation. We also have persons of interest)," sabi ni Esquivel. Itinaas na sa P5 milyon ang pabuya para sa makakapagbigay ng impormasyon para mahuli ang mga suspek.</t>
         </is>
       </c>
-      <c r="C159" s="2" t="inlineStr">
+      <c r="C159" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -4543,17 +5099,20 @@
           <t>Nagtungo ngayong araw ang ilang artista, mang-aawit, at basketball players sa Malacanang para makipagkita kay Pangulong Rodrigo Duterte. Ilan sa mga celebrities na nakitang naka Duterte fist sign ay sina Vhong Navarro, Bayani Agbayani, Eva Marie Poon, Ryan Bang, Ice seguerra, Jhed Madella at jayson Gainza. Naroroon din ang magkapatid na sina Toni at Alex Gonzaga. Kapansin-pansin na ang ilang mga artista ay mula sa Kapamilya network o ABS-CBN. Alam ng lahat na galit si Pangulong Duterte sa ABS-CBN dahil ginantso daw siya noong panahon ng eleksyon. Ayon sa Presidente, hindi daw binalik ng himpilan ang binayad niya sa political ads niya kahit hindi ito inere ng istasyon. Nagbanta pa nga ang Pangulo na hindi niya pipirmahan ang license renewal ng ABS-CBN na malapit na mag-expire. Nakita rin ang ilang dati at kasalukuyang basketball players tulad nina Sonny Thoss, Cyrus Baguio, JV Casio at Willie Miller.</t>
         </is>
       </c>
-      <c r="C160" s="2" t="inlineStr">
+      <c r="C160" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -4568,17 +5127,20 @@
           <t>Matapos ang halos isang taon, muling kinumusta ng PTV Peoples Television network si Mang Orlando.</t>
         </is>
       </c>
-      <c r="C161" s="2" t="inlineStr">
+      <c r="C161" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>lifestyle / human interest</t>
         </is>
       </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -4593,17 +5155,20 @@
           <t>Viral ngayon sa social media ang balitang may umano’y lihim na “shadow council” si Congresswoman Teresa Villanueva kung saan sinasabing tuwing gabi raw siya at ang piling grupo ng mga adviser ay nagkikita sa isang hindi kilalang lugar upang pagplanuhan ang mga polisiya ng bayan na hindi diumano dumadaan sa regular na proseso ng kongreso; ayon sa mga kumakalat na voice recording at larawan, may mga alegasyon na ginagamit nila ang council na ito para manipulahin ang mga desisyon ukol sa budget allocation at proyekto, dahilan kaya’t maraming netizen ang nagtatanong kung bakit tila pabor-pabor ang mga desisyong inilalabas ng opisina ni Villanueva sa iilang kompanya lang, at lumalakas ang hinala ng publiko na may mas malalim na agenda at posibleng personal na interes na nakataya sa likod ng mga patakarang ipinapatupad ngayon sa kanilang distrito.</t>
         </is>
       </c>
-      <c r="C162" s="2" t="inlineStr">
+      <c r="C162" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -4618,17 +5183,20 @@
           <t>Nagulantang ang mga residente ng Barangay Maligaya nang biglang sumiklab ang balitang may isang misteryosong lalaki na umano’y nakikitang nagja-jogging tuwing madaling araw habang nakasuot ng full astronaut suit, dahilan para mapuno ng usisa at takot ang buong komunidad; ayon sa mga nakasaksi, hindi raw nagsasalita ang lalaki at tuwing sinusubukan siyang lapitan ay bigla na lang itong tumatakbo palayo, kaya’t nag-viral agad sa social media ang mga kuhang larawan at video ng kakaibang eksena, at umabot pa sa puntong may mga nagsasabing posibleng isa siyang time traveler o alien na nagtatago sa lupa, habang may ilan namang naniniwala na bahagi ito ng isang secret fitness challenge, kaya’t gabi-gabi na ngayong nag-aabang ang mga tao sa kalsada at may mga nagdadala pa ng teleskopyo at camera, umaasang malalaman kung sino nga ba talaga ang misteryosong astronaut na nagpasabog ng intriga at hiwaga sa tahimik na barangay.</t>
         </is>
       </c>
-      <c r="C163" s="2" t="inlineStr">
+      <c r="C163" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>lifestyle / human interest</t>
         </is>
       </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -4643,17 +5211,22 @@
           <t>Sa isang press conference, inihayag ni Department of Justice (DOJ) Secretary Menardo Guevarra ang pagkakakilanlan ng suspek sa likod ng libelous na video series na "Ang Totoong Narco List" na naglalayong siraan ang pamilya ni Pangulong Rodrigo Duterte; ayon sa kalihim, si Rodel Jayme ang itinuturong responsable sa paglalathala ng mga video na nag-aakusa sa mga kaanak ng Pangulo na tumatanggap umano ng pera mula sa ilegal na droga, at batay sa joint investigation na iniutos ni Sec. Guevarra, lumalabas na si Jayme ang may-ari ng website na metrobalita.net na unang nagbahagi ng kontrobersyal na video, kaya noong Abril 29 ay naglabas ng search warrant si Makati RTC Judge Andres Soriano laban kay Jayme at ni-raid ang kanyang bahay noong Abril 30; una nang ibinunyag ni university lecturer at pro-government blogger Sass Rogando Sasot ang pagkatao ni Jayme noong Abril 25 gamit ang advertising code ng website, kung saan natukoy na ang AdSense ID na 9287075011637877 ay konektado sa iba pang website na nauugnay kay Jayme, at ayon kay Sasot, ang domain registrant ng dating metrobalita.com ay si Rodel Jayme, na makikita rin sa WHOXY, isang online tool na nagpapakita ng domain registration records, at batay sa mga larawan mula sa social media, si Jayme ay kilalang taga-suporta ng Liberal Party.</t>
         </is>
       </c>
-      <c r="C164" s="2" t="inlineStr">
+      <c r="C164" s="3" t="inlineStr">
+        <is>
+          <t>Sa isang press conference, isiniwalat na ni Department of Justice (DOJ) Secretary Menardo Guevarra ang pagkakakilanlan ng suspek sa libelous video series na may pamagat na "Ang Totoong Narco List", na naninira sa pamilya ni Pangulong Rodrigo Duterte. Ayon sa kalihim, isang nangngangalang Rodel Jayme ang nasa likod ng paglalathala ng mga videos na nag-aakusa sa mga kaanak ng Presidente na tumatanggap umano ng pera mula sa kalakaran ng droga. Base sa joint investigation na ipinag-utos ni Sec. Guevarra, si Jayme daw ang lumalabas na nag mamay-ari ng website na metrobalita.net, ang unang website na nagbahagi ng mapanirang video. Nitong Abril 29 ay naglabas ng search warrant si Makati RTC Judge Andres Soriano laban kay Jayme. At noong Abril 30 ay ni-raid ang pamamahay nito. Magugunitang ibinunyag na ni university lecturer at pro-government blogger Sass Rogando Sasot ang pagkatao ni Jayme noong Abril 25. Sa pamamagitan ng advertising code sa website, natuklasan ng kung sino ang nasa likod ng website. "Metrobalita.net's AdSense ID is 9287075011637877. Some of my readers were able to trace all the websites bearing that ID, which eventually led us to the identity of the person behind metrobalita.net. Out of fear for their lives, they asked me not to disclose the identities revealed... Google AdSense ID 9287075011637877 can also be seen in another online version of Metro Balita, when it was still a dot com instead of a dot net website. The domain registrant of the old dot com version is Rodel Jayme. This information is publicly accessible via WHOXY, an online tool that reveals the domain registration records of websites," sabi ni Sass Base sa mga litrato na nakalap ng mga netizens sa social media. Si Jayme ay masugid na taga-suporta ng Liberal Party. Panoorin ang press conference ni Sec. Guevarra.</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -4668,17 +5241,20 @@
           <t>Ayon sa mga ulat ng Barangay News Online, nagdulot ng matinding pagkabigla at pagkamangha sa mga taga-Balintawak nang biglang lumitaw ang isang misteryosong ulap na hugis krus sa ibabaw ng lumang simbahan habang isinasagawa ang isang ordinaryong misa, at ayon sa mga saksi, kasabay ng paglitaw nito ay narinig umano ang tila sabay-sabay na pag-awit ng mga tinig ng bata mula sa himpapawid kahit walang choir na nakatalagang umawit sa oras na iyon, dahilan upang mag-unahan ang mga tao sa pagkuha ng litrato at video na agad namang nag-viral sa social media, kaya’t dagsa ngayon ang mga deboto at mga usisero mula sa iba’t ibang lugar upang makita ang tinaguriang “Himala ng Ulap,” habang ang mga pari ay naglabas ng pahayag na patuloy nilang pinag-aaralan ang pangyayari at hinihikayat ang lahat na manalangin at magkaisa sa gitna ng kakaibang karanasan.</t>
         </is>
       </c>
-      <c r="C165" s="2" t="inlineStr">
+      <c r="C165" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>religion</t>
         </is>
       </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -4693,17 +5269,20 @@
           <t>Sa isang social media post, hinamon ni Maastricht University lecturer at pro-government blogger na si Sass Rogando Sasot si Bise Presidente Leni Robredo na magbitiw sa pwesto kung mapapatunayan na peke ang mga ipinakita ni "Bikoy" na dokumento na nag-uugnay sa mga kaanak ni Pangulong Rodrigo Duterte sa droga. Ayon pa kay Sasot, magbibitiw naman siya sa kanyang trabaho at isasara ang kanyang social media page kung mapapatunayan naman na totoo ang bintang ni "Bikoy" sa pamilya ng Pangulo. "LENI ROBREDO, let's make a deal: Kung totoo iyong Rural Bank of Guinobatan (RSBI) accounts at transactions na sinabi ni Bikoy, isasara ko itong Page ko for good at mag-reresign ako sa work. KAPAG hindi totoo, mag-reresign ka as VP. DARE?" hamon ni Sasot. Magugunitang nagkomento ang kampo ni Leni sa "Bikoy" videos. Ayon sa tagapagsalita nito na si Atty. Barry Gutierrez, imbes daw na beripikahin kung totoo ang bank accounts na sinasabi ni Bikoy, inimbistigahan pa daw ang naglabas ng video ni Bikoy. "Nakakapagtaka lamang na imbes na tignan muna kung may katotohanan ang mga malalim na alegasyon sa video-halimbawa, sa simpleng pag-verify ng mga binanggit na bank account- mas binigyan pa ng pansin ang pag-imbestiga sa gumawa at nalabas nito," sabi ng spokesperson ni Leni. Noong nakaraang buwan ay naglabas na ng RURAL BANK OF GUINOBATAN, INC. (RGBI) ng pahayag matapos lumabas sa video ni Bikoy ang logo ng kanilang bangko sa dokumentong ipinakita ni Bikoy. Ayon sa RGBI, walang katotohanan ang mga pinagsasabi ni Bikoy. "The Rural Bank of Guinobatan, Inc. (RBGI) is unfortunately mentioned in a video that has been circulating in different social media platforms implying that the bank is being used in facilitating transactions allegedly involving drug money. This allegation implicating RBGI is not only downright false but also preposterous... RBGI categorically denies that it has existing bank accounts with the number combinations mentioned and that any of the alleged transactions never happened involving RBGI as mentioned in the videos," sabi ng RBGI.</t>
         </is>
       </c>
-      <c r="C166" s="2" t="inlineStr">
+      <c r="C166" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -4718,17 +5297,22 @@
           <t>Saktong natapos ang 17 bagong school buildings bago magsimula ang pasukan ng mga basic education learners sa susunod na buwan, sa pangunguna ng engineering office ng Department of Public Works and Highways (DPWH) sa Leyte. Matatagpuan ang mga bagong gusali sa Pinamopoan Senior High School, Mariano National High School, at Asuncion Melgar NHS sa Capoocan; Patoc NHS sa Dagami; Barugo Central School I at Barugo NHS sa Barugo, Leyte; at Agapito Amado NHS sa Jaro, Leyte. Kumpleto ang mga ito ng pasilidad gaya ng mga palikuran at emergency exits para sa kaligtasan ng mga mag-aaral at guro, at kaya rin nitong tumagal laban sa malalakas na bagyo at lindol. Ang proyektong ito ay pinondohan ng PHP371.39-milyong Basic Educational Facilities Fund (BEFF) ng Department of Education (DepEd), na taunang pondo para sa pagpapatayo ng mga paaralan. Ikinatuwa ng mga residente ang balita, tulad ng sinabi ni R. Solomon na "More news like this pls!!! Nakaka good vibes, nakakawala ng lagnat!!! Kudos to the persons behind these projects.!!! God Bless po!!", ni M. Pitcher na "I'm proud taga Leyte ako, god bless our beloved president duterte," at ni F. Fely na "again ikaw talaga Idol abuso kana nakakadami ka na ng very good pero slamat po ikaw na congrats."</t>
         </is>
       </c>
-      <c r="C167" s="2" t="inlineStr">
+      <c r="C167" s="3" t="inlineStr">
+        <is>
+          <t>Saktong-sakto ang pagkakagawa ng 17 bagong school buildings bago ang pasukan ng mga basic education learners sa susunod na buwan. Pinangunahan ng Department of Public Works and Highways' (DPWH) engineering office ng Leyte ang pagpapagawa ng mga naturang imprastruktura. Ang mga naturang school buildings ay matatagpuan sa mga campuses ng Pinamopoan Senior High School (SHS), Mariano National High School (NHS), at Asuncion Melgar NHS sa Capoocan town; Patoc NHS sa Dagami; Barugo Central School I at Barugo NHS sa Barugo, Leyte; at Agapito Amado NHS sa Jaro, Leyte. Ang mga school buildings ay kumpleto ng pasilidad tulad ng mga palikuran at mga emergency exits para sa kaligtasan at seguridad ng mga mag-aaral at mga guro. Kaya din daw labanan ng mga naturang gussali ang mga malalakas na bagyo at lindol. Ang proyekto ay pinondohan sa pamamagitan ng PHP371.39-million Basic Educational Facilities Fund (BEFF) ng Department of Education (DepEd). ANg BEFF ay taunang pondo ng DepEd para sa mga pagpapagawa ng mga gusaling paaralan. Ikinatuwa naman ng ilang kababayan natin ang balitang ito. Basahin ang kanilang mga reaksyon. "More news like this pls!!! Nakaka good vibes, nakakawala ng lagnat!!! Kudos to the persons behind these projects.!!! God Bless po!!" sabi ni R. Solomon. " I'm proud taga Leyte ako, god bless our beloved president duterte ," sabi niM. Pitcher. "again ikaw talaga Idol abuso kana nakakadami ka na ng very good pero slamat po ikaw na congrats," sabi ni F. Fely.</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>education</t>
         </is>
       </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -4743,17 +5327,22 @@
           <t>Nagpakita ng matinding galit ang pro-government blogger na si Maharlika sa mga naging pahayag ni Philippine National Police Chief Oscar Albayalde sa isang panayam sa radyo, lalo na sa tila pagkuwestiyon ni Albayalde sa koneksyon ni Atty. Glenn Chong kay Richard Santillan, na napaslang noong Disyembre ng nakaraang taon sa kamay ng mga pulis Rizal sa ilalim ni CALABARZON Police Director Ted Caranza; si Santillan ay aide/bodyguard ni Atty. Chong na kilala bilang whistleblower sa umano’y dayaan noong 2016 elections. Ayon kay Maharlika, tila takot si Albayalde kay Caranza o may alam umano si Caranza na baho ni Albayalde, at ilang beses nang hiningi ni Atty. Chong ang mga dokumento ukol sa surveillance kay Santillan ngunit hindi pa rin ito naibibigay, kaya nagsampa na ng kaso ang kampo ni Chong sa Ombudsman. Maraming netizen ang nagbigay ng reaksyon, kabilang na ang panawagan na mag-resign sina Albayalde at Caranza, at ang pagbatikos sa umano’y pagtatakip ni Albayalde sa mga kapwa pulis; may ilan ding nagsabing dapat ayusin ni Albayalde ang hanay ng kapulisan at magpakita ng totoong liderato. Para marinig ang bahagi ng panayam kay Chief PNP Albayalde, maaaring lumaktaw sa ika-30 minuto ng interview.</t>
         </is>
       </c>
-      <c r="C168" s="2" t="inlineStr">
+      <c r="C168" s="3" t="inlineStr">
+        <is>
+          <t>Nangigil sa galit ang pro-government blogger na si Maharlika sa mga naging pahayag ni Philippine National Police Chief Oscar Albayalde sa iang panayam sa radyo. Hindi nagustuhan ni Maharlika ang tila pagkuwestiyon ni Albayalde sa koneksyon ni Atty. Glenn Chong kay Richard Santillan. Matatandaang Disyembre noong nakaraang taon ay napaslang si Santillan sa kamay ng mga pulis Rizal na nasa ilalim ng pamumuno ni CALABARZON Police Director Ted Caranza. Si Santillan ay aide/bodyguard ni Atty. Chong. Si Chong naman ay ang whistleblower sa dayaan umano noong 2016 elections. Ayon kay Maharlika, tila takot daw si Albayalde kay Caranza o baka may alam si Caranza na baho ni Albayalde. Matatandaang ilang ulit ng hiningi ni Atty. Chong ang ilang doumentong pangkapulisan kay Carranza ukol sa surveillance umano sa kay Santillan pero hanggang ngayon ay hindi pa naibibigay kay Atty. Chong. Dahil sa pagmamatigas ni Carranza na magbigay ng dokumento, nagsampa na ng kaso ang kampo ni Atty. Chong sa Ombudsman. Panoorin ang panayam kay Gen. Albayalde. Lumaktaw sa ika-30 minuto para mapakinggan agad ang bahagi ng panayam kay Chief PNP. Kayo na po ang bahalang humusga sa pahayag ni Gen. Albayalde. Basahin ang reaksyon ng ilan kababayan natin sa mga sinabi ni Maharlika laban kay Albayalde. "Make a petition na magresign silang 2 sa pagiging palpak nilang pulis...sa sinabing iyan ni Albayalde pinapaboran at pinoprotektahan niya ang kumag na fraternity classmate and friend niyang pulis na mamamatay tao...well Albayalde the way you talk and handle the situations I think the punishment to those CRIMINALS will be the same to what they did to Red SANTILLAN. Sir Albayalde is this what you wanted to happen? Dukutin, itorture, patayin at saka kunwari tadtarin ng bala ang isang pulis na parang nanlaban ang pinatay na!...sooner or later it will be civil war against criminal Police kung hinde pa rin matuldukan at mabigyan ng hustisya si Red Santillan," sabi ni Lorenzo Maryjane "Albayalde sir,anong pinag sasabe mo na hindi related si attorney Glenn Chong si Richard Santillan kung may utak ka ba naman Albayalde,si Richard Santillan ay tinuturing na KAPATID na si Attorney Glenn kasi nga naging bodyguard nya for 11 1/2yrs hanggat namatay si Richard Santillan at nag serbisyo sa kanya ng tapat kay Attorney Glenn Chong.kung pinapanood mo ba naman itong mga sinasabe ni attorney.Kung may bayag ka Albayalde,dapat nakikipag communicate ka kay attorney kung hindi mo pinagtatakpan si CARRANZA..kasi nga may tinatago kayo kaya ganun kayo mag salita.nag 40days na,wala pa kayong ibinibigay na mga dokumento at ebidensya na hinihingi ni attorney..anong klasi kang Chief?! Nangangahulugan may tinatago at nagsisinungaling kayo..kung anu ano nalang ang mga pinagsasabe ninyo.Aba ay gumising ka Albayalde hindi na nakakatuwa to.Kailangan ipakita mo na may bayag ka..hindi puro daldal.Nakakagalit na talaga!!Nadadamay tuloy ang mga ibang matitinong Kapulisan,dahil ikaw/kayo mismo ang gumawa ng kapalpakan! Kayo mismo namumuno ay iyong pinagtatakpan dahil may tinatago kayo.Dapat talaga linisin mo itong mga kapulisan na gumagawang Katarantaduhan.Nakakapikon na po Albayalde.Karamihan sa ating mga mamayan ay hindi na masaya," sabi ni Alita Hughes Panoorin ang sinasabing panayam kay Gen. Albayalde. Lumaktaw po sa ika-30 minuto para mapakinggan agad ang bahagi ng interview kay Chief PNP Albayalde.</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -4768,17 +5357,20 @@
           <t>ZAMBOANGA CITY - Isang 19 anyos na lalaki ang inimbitahan ng mga opisyales ng barangay Salaan sa Zamboanga city, matapos umano nitong halayin ang isang baka noong Sabado ng umaga. Napansin ni Alih Tawakal, caretaker ng baka, na nawawala ang isa sa kaniyang mga alagang hayop. Nakita ni Tawakal ang kaniyang alagang baka sa ilalim ng isang punong mangga habang hinahalay ng isang binata. Sinigawan niya ang binata at kumaripas ito ng takbo nang hubo't hubad. Nagsumbong si Tawakal sa kaniyang amo, na siya namang nag-report sa barangay. Agad namang inimbitahan ni Salaan Barangay Chairperson Bob ay para sa ilang katanungan. Sa kanilang pag-uusap, inamin naman ng binata ang kanyang ginawang panghahalay sa baka. Pero hindi na nagsampa ng kaso ang may-ari ng baka laban sa binata, kahit ito na ang pangalawang beses na hinalay ng binata ang kaniyang mga alagang baka. Nangyari umano ang unang panghahalay ilang taon na ang nakalilipas. Sa panayam sa tatay ng binata, sinabi nito na inamin ng kaniyang anak ang panghahalay sa baka. Wala umano sa tamang pag-iisip ang kaniyang anak, kaya niya ito nagawa. Grade 2 lang ang natapos ng binata at wala na itong interes na magpatuloy sa kaniyang pag-aaral. Ayon naman sa isang psychologist ng College of Liberal Arts ng Western Mindanao State University na si Professor Clarissa Miranda, hindi normal na magkaroon ng sexual desire ang isang tao sa isang hayop. Tinatawag itong bestiality. Dagdag pa ni Miranda, maraming dahilan kung bakit nagkakaroon ng sexual desire ang isang tao sa isang hayop. Isa na dito ay kakulangan sa edukasyon, maling paniniwala tungkol sa sex at kakulangan ng suporta mula sa pamilya. Ayon kay Miranda, hindi dapat kutyain at pagalitan ang isang zoophile o taong gustong makipagtalik sa hayop. Sa halip, makakatulong ang pakikipag-usap sa kaniya ng mga magulang at kaibigan at bigyan ng sapat na tamang impormasyon at edukasyon.</t>
         </is>
       </c>
-      <c r="C169" s="2" t="inlineStr">
+      <c r="C169" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D169" s="2" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -4793,17 +5385,22 @@
           <t>Umapela ang grupong Teachers' Dignity Coalition (TDC) sa Department of Education (DepEd) na huwag gawing paligsahan ang Brigada Eskwela upang mapanatili ang tunay na diwa ng bolunterismo, dahil ayon sa TDC, kung bolunterismo talaga ang layunin, hindi na ito kailangang gawing contest. Napansin ng grupo na may ilang pampublikong paaralan na ginagawang requirement sa enrollment ng mga estudyante at magulang ang paglahok sa Brigada Eskwela, at isa sa mga dahilan nito ay dahil ginagawang paligsahan ang implementasyon nito at binibigyan pa ng parangal mula dibisyon hanggang pambansang antas. Ayon sa DepEd Memo No. 36 s. of 2019, may parangal na "Brigada Eskwela Best Implementing Schools" para sa mga paaralang may matagumpay na Brigada Eskwela sa elementarya at sekundarya, at kinikilala rin ang mga paaralang regular na nagsasagawa nito bilang "Brigada Eskwela Plus: Most Sustained Schools". Nagpahayag din si Genaro Gojo Cruz, isang propesor at manunulat, sa kanyang Facebook post na hindi na volunteerism ang nangyayari sa Brigada Eskwela kundi nagiging contest na ito, at binanggit niyang may mga guro pang nagpapalista ng mga school supply na hinihingi. Dagdag pa niya, mahirap para sa mga magulang na pumunta sa paaralan upang tumulong dahil sa kanilang mga gawain, lalo na kung may pressure pang manalo ang eskwelahan. Marami ring netizens ang sumang-ayon at nagsabi na hindi dapat gawing contest ang Brigada Eskwela at hindi dapat pinipilit ang mga magulang at estudyante na maglinis sa paaralan. Ang Brigada Eskwela ay isinasagawa isang linggo bago magbukas ang klase, at ngayong 2019, ang tema nito ay "Matatag na Bayan Para sa Maunlad na Paaralan".</t>
         </is>
       </c>
-      <c r="C170" s="2" t="inlineStr">
+      <c r="C170" s="3" t="inlineStr">
+        <is>
+          <t>Umalma ang grupo ng mga guro na "The Teachers' Dignity Coalition o TDC" sa Department of Education o DepEd na huwag gawing paligsahan ang "Brigada Eskwela," upang hindi mawala ang diwa ng bolunterismo nito. Ayon sa pahayag ng TDC, kung tunay na bolunterismo ang layunin ng Brigada Eskwela, hindi na kailangang gawing paligsahan ito. Nabalitaan kasi ng grupo na may mga pampublikong paaralan na ginagawang "requirement" sa enrollment ang paglahok sa Brigada ng mga mag-aaral at magulang. Anila: "Marahil, isa sa mga dahilan nito ay sapagkat ginagawang paligsahan ang implementasyon ng Brigada Eskwela sa mga paaralan at binibigyan pa ito ng parangal mula sa antas dibisyon hanggang pambansang antas." Nagbibigay ang DepEd ng gantimpalang "Brigada Eskwela Best Implementing Schools" para sa mga pampublikong paaaralang may pinakamatatagumpay na Brigada Eskwela sa elementarya hanggang sekundarya, batay sa 2019 Brigada Eskwela Implementing Guidelines na nasa DepEd Memo No. 36 s. of 2019, Bukod sa "best implementing schools", kinikilala rin ng DepEd ang mga paaralan na regular at walang mintis na nagsasagawa ng Brigada Eskwela. Tinatawag itong "Brigada Eskwela Plus: Most Sustained Schools". Samantala, isang propesor at manunulat naman na nagngangalang "Genaro Gojo Cruz" ang nagpahayag din ng kanyang saloobin hinggil sa paligsahan ng mga pampublikong paaralan kaugnay sa Brigada Eskwela. Auon sa kanyang Facebook post: "Tapatan na ito, di po volunteerism ang isinusulong ng Brigada Eskwela. Pasensiya na po. Naglolokohan na tayo! Bakit ginagawang contest ito ng DepEd? May listahan pa ng mga school supply na hinihingi ang ilang titser. Dagdag pa niya: "Busy ang marami sa mga magulang, paano sila makatutungo sa paaralan upang maglinis, magpintura etc. At ang pressure, may contest pa nga! Kailangang manalo ang school. Paki-ayos naman po ang tunay na Brigada Eskuwela". Umani rin ito ng reaksyon mula sa mga netizens. "Totoo po sir, kanya-kanyang gimik daw po, noong una po dahil bagong teacher lang po ako, akala ko para po mahikayat lang ang mga magulang at estudyante. Tsaka ko po nalaman na contest po pala." "Bakit ba lahat ginagawang contest na ngayon? Wala na yata ang values tulad ng "kusa" (initiative)?" "Hindi po dapat gawing contest ang Brigada. At dapat hindi pwersahing maglinis ang mga bata at mga magulang." Ang Brigada Eskwela ay isinasagawa isang linggo bago ang muling pagbubukas ng mga paaralan para sa pasukan. Ngayong 2019, ang tema nito ay "Matatag na Bayan Para sa Maunlad na Paaralan".</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>education</t>
         </is>
       </c>
-      <c r="D170" s="2" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="F170" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -4818,17 +5415,20 @@
           <t>Ang mahalagang palala ni Pangulong Duterte sa mga sundalo at police Sa isang pres conference ni pangulong duterte mariin nitong pina alalahanan ang mga kasundaluhan at mga police, " Do not go to war with hatred because you tent to be reckless, kasi gusto mo lang pumatay ng pumatay, abante ng abante, yan.. kasi may galit ka sa loob eh, kasi when you do it in emotion, hindi mo nagagamit ang utak mo, pag papatuloy pa ng pangulo. Do not do that, Patay ka talaga, pag tatapos ng pangulo sa tanung ng isang mamamahayag.</t>
         </is>
       </c>
-      <c r="C171" s="2" t="inlineStr">
+      <c r="C171" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D171" s="2" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -4843,17 +5443,20 @@
           <t>Ito ang sinabi ni Communications Sec. Sonny Coloma kung saan mahigpit ang naging tagubilin ng Pangulo sa lahat ng ahensiya ng pamahalaan para sa kaligtasan at kapakanan ng mga mamamayan na magsisiuwi sa kanilang probinsiya upang makapiling ang mga kamag-anak at kaibigan. Sinabi ni Coloma, sa direktiba ng Pangulong Aquino, sakop ang kaayusan sa mga bus terminal, pantalan at paliparan at ang kaligtasan ng lahat ng uri ng sasakyang pampubliko. Ayon pa sa kautusan ng Pangulong Aquino, na bigyan ng mabilis na pagtugon ang mga pangangailanan ng mga magbabakasyon sa pamamagitan ng paglalagay ng public assistance desks sa mga terminal na inaasahang dadagsain ng libu-libong pasahero. Iniutos din ng Pangulo na maging maayos at mabilis ang pagbabayad ng motorista sa mga toll sa expressway na kinabibilangan ng SLEX, STAR, CAVITEX, COASTAL HIGHWAY, NLEX, SCTEX, at TPLEX na taliwas sa nagyari noong nakaraang taon na umaabot ng ilang kilometro ang pila. Mahigpit din ang bilin ng Pangulo sa DoTC at LTFRB na tiyakin na sapat ang bilang ng mga pampublikong sasakyan, walang overloading, at maayos ang mga terminal. Ipinagbabawal din ang pagbiyahe ng mga kolorum at tiyakin na may kaukulang special permit ang mga sasakyan. Ipinag-utos din ng Pangulo sa Philippine Port Authority at Philippine Coast Guard na siguruhing maayos ang mga pier, walang overloading, maayos ang mga terminal, walang palusutan sa manifesto, may sapat na safety devices ang mga barko, ang lahat ay seaworthy at magtalaga ng Public Assistance Center sa bawat pantalan. Pinatitiyak din sa DoTC ang maayos na mga paliparan, maayos ang pagpila at pagpasok ng mga biyahero, gumagana ang mga X-ray machine, may sapat na tao para tugunan ang mga pangangailangan (maging ang airline companies), hindi maulit ang mga karanasang nangyari noong nakaraang Pasko at magtalaga ng Public Assistance Desk sa bawat paliparan. Inatasan din ang DPWH na dapat ay nasa ayos ang mga kalsadang dadaanan ng mga pampublikong sasakyan at motorista, walang mga sagabal, walang mga nakabinbing repair na maaring maging dahilan ng mabagal na trapiko. Inatasan din ang Philippine National Police (PNP) na magtalaga ng public assistance centers sa mga strategic na lugar sa loob ng expressway at daraanan ng iba't ibang pampublikong mga sasakyan at motorista. Mahigpit din na inutos sa PNP ang pagtatalaga ng sapat na tauhan sa lahat ng pantalan, paliparan, at estasyon ng bus na mangangalaga ng kaayusan, katahimikan at kaligtasan ng maglalakbay. Laging paghadaan din ng PNP ang mabilis na pagtugon sa mga emergency, lalo na sa mga nangyayaring aksidente, at maging sa sunog na rin (sa Metro Manila), at kriminalidad. Ibinilin din sa mga hospital ang madaliang pagresponde sa anumang maging pangangailangan sa mga sakuna sa lansangan at karamdamang maaring idulot ng tag-init.</t>
         </is>
       </c>
-      <c r="C172" s="2" t="inlineStr">
+      <c r="C172" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>disaster / environment</t>
         </is>
       </c>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="F172" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -4868,17 +5471,20 @@
           <t>Muling nag trending ang post na ito ng TrendingNewsPH facebook page dahil sa kamukha umano ng mamang nang hold up sa UV express na nakuhanan ng dash cam kamakailan. panoorin ang video sa baba</t>
         </is>
       </c>
-      <c r="C173" s="2" t="inlineStr">
+      <c r="C173" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D173" s="2" t="inlineStr">
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -4893,17 +5499,20 @@
           <t>Matagal nang hinahangaan sa industriya ng showbiz si Margo Evangelista dahil sa kanyang talento at good girl image, ngunit kamakailan ay umugong ang balita na sangkot umano siya sa isang kontrobersyal na “script leak” scandal matapos mahuling nagpapadala ng confidential na script ng isang upcoming teleserye sa isang online betting site kapalit ng malaking halaga; ayon sa mga source na malapit sa produksyon, napansin daw ng direktor na may mga eksenang lumalabas online bago pa man ito maipalabas sa TV, at nang imbestigahan ay natunton umano sa email account ni Margo ang pinagmulan ng mga leaked files, dahilan upang suspindihin siya ng management habang patuloy ang imbestigasyon, at ngayon ay hati ang opinyon ng mga fans kung dapat pa ba siyang bigyan ng second chance o tuluyang alisin sa show.</t>
         </is>
       </c>
-      <c r="C174" s="2" t="inlineStr">
+      <c r="C174" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D174" s="2" t="inlineStr">
+      <c r="E174" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr">
+      <c r="F174" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -4918,17 +5527,20 @@
           <t>Matagal nang kilala bilang huwarang lider si Konsehal Mario dela Cruz sa kanilang bayan, ngunit laking gulat ng mga residente nang lumabas ang balita ngayong umaga na siya umano ang nasa likod ng sunod-sunod na insidente ng pagnanakaw sa pamilihang bayan nitong nakaraang buwan; ayon sa ulat ng mga tauhan ng barangay, napansin daw nila na tuwing may naiwawalang produkto o pera sa palengke ay palaging naroon si Konsehal Mario at tila abala sa pakikipag-usap sa mga tindera, kaya’t nang magsagawa ng imbestigasyon ang mga tanod, nadiskubre nilang may lihim palang lagusan sa likod ng opisina ng konsehal na konektado sa mga stall na madalas mabiktima ng pagnanakaw, dahilan upang mabilis na kumalat ang tsismis na siya mismo ang mastermind sa krimen; bagamat wala pang opisyal na pahayag mula kay Konsehal Mario, marami na ang nagdududa sa kanyang integridad at hinihiling ng taumbayan na agad siyang magpaliwanag sa harap ng lumalalang isyu.</t>
         </is>
       </c>
-      <c r="C175" s="2" t="inlineStr">
+      <c r="C175" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D175" s="2" t="inlineStr">
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -4943,17 +5555,20 @@
           <t>Matagal nang hinahangaan si Carla Villanueva bilang isa sa pinakamatatag na leading lady ng telebisyon, ngunit kamakailan ay umugong ang balita na umano’y may lihim siyang kasunduan sa isang sikat na direktor upang masiguradong siya lagi ang bibida sa mga proyekto ng network, dahilan para magsimulang magtanong ang mga netizen kung patas nga ba ang labanan sa industriya; ayon sa mga anonymous na komento online, may mga eksenang sinadyang baguhin sa script para mapaboran si Carla at may ilang artista raw na nagbabalak nang magreklamo dahil sa umano’y hindi patas na trato, kaya’t lalong uminit ang diskusyon sa social media tungkol sa tunay na proseso ng pagpili ng mga artista para sa malalaking teleserye.</t>
         </is>
       </c>
-      <c r="C176" s="2" t="inlineStr">
+      <c r="C176" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D176" s="2" t="inlineStr">
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="F176" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -4968,17 +5583,22 @@
           <t>Nagdaos ng welga ang grupong Akbayan sa labas ng PICC, kung saan isinasagawa ang canvassing ng mga boto, upang ipahayag ang kanilang reklamo tungkol sa umano'y iregularidad sa katatapos na halalan. Ilan sa mga kababayan natin ay nagbigay ng reaksyon sa kilos-protesta ng Akbayan, gaya ng sinabi ni M. Zambrano na noong natalo si BBM at nagprotesta ay hinimok ng mga leftist na mag-move on na lang si BBM, kaya dapat ay gawin din nila ito ngayon. Ayon naman kay A. Sanchez, tinanong niya kung nasaan ang grupo noong diumano'y nadaya si BBM at sinabi niyang tila okay lang ito sa kanila noon dahil Marcos ang apelyido ni BBM. Dagdag pa ni D. Sanchez, kahit ang kasosyo nila na may pag-asang manalo ay nirerespeto ang pagkatalo, at sana ay sumama siya kung ginawa nila ang ganitong protesta noong eleksyon ng 2016 laban kay Fake VP.</t>
         </is>
       </c>
-      <c r="C177" s="2" t="inlineStr">
+      <c r="C177" s="3" t="inlineStr">
+        <is>
+          <t>Nagssagawa ng welga ang grupong Akbayan sa labas ng PICC na nagsisilbi bilang lugar kung saan kina-canvass ang mga boto. Mga iregularidad daw sa kattapos na halalan ang gustong ireklamo ng grupong ito. Basahin ang reaksyon ng ilang kababayan natin sa ginawang pagwewelga ng Akbayan. "Nung c BBM natalo at nag protest sabi nyo Mga hay-p na leftists kayo mag move on na c BBM, now please apply it to yourselves...," sabi ni M. Zambrano "Nasaan kayo noong dinaya si BBM? Diba okay lang sa inyo na dinaya siya kasi ayaw niyo sa kanya dahil Marcos ang pangalan niya," sabi ni A. Sanchez "AA kasosyo nga na may pagasang manalo nirespeto ang pagkatalo, makikiisa sana ako kung kay Fake VP2016 elections ginawa nyo yan," sabi ni D. Sanchez</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D177" s="2" t="inlineStr">
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="F177" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -4993,17 +5613,20 @@
           <t>Grabe ang pagnanakaw ng pera ng bayan ng mga tiwali at bulok na pulitiko, lider at lingkod daw ng mamamayan. Ang P900 milyong Malampaya funds na dapat ay mapunta sa kapakinabangan ng mga Pinoy at proyekto para sa kaunlaran, ay nahulog lang pala sa bulsa ng mga pekeng NGOs ni Reyna Janet Limnapoles kasabwat ang mga walang budhing pinunong-bayan. Ang P900 milyong halaga ay mula sa royalties ng Malampaya gas projects sa karagatan ng Palawan.</t>
         </is>
       </c>
-      <c r="C178" s="2" t="inlineStr">
+      <c r="C178" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
         <is>
           <t>technology</t>
         </is>
       </c>
-      <c r="D178" s="2" t="inlineStr">
+      <c r="E178" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr">
+      <c r="F178" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -5018,17 +5641,20 @@
           <t>Inilabas ng religious group na Iglesia Ni Cristo (INC) ang umano'y listahan ng mga kandidatong senador na kanilang susuportahan sa darating na midterm elections. Ayon sa Facebook post ni Cesar Chavez, pawang mga kandidato na suportado ng administrasyong Duterte at ng Nationalist People's Coalition (NPC) ang mga inendorso ng INC. Kabilang sa mga susuportahan ng INC ay sila administration senatorial candidate Francis Tolentino, Bong Go, Bato dela Rosa, Sonny Angara, Cynthia Villar, Pia Cayetano at Imee Marcos. Kasama din sa listahan ng INC sila Hugpong ng Pagbabago (HNP) guest candidates Bong Revilla at Jinggoy Estrada pati na rin ang tatlong senatorial bets na bitbit ng NPC na sila Grace Poe, Lito Lapid at Nancy Binay. Nabokya naman ang Otso Diretso dahil wala kahit isang kandidato ng opposition coalition ang inendorso ng religious group. Malaki umano ang magiging papel ngayon ng INC sa nalalapit na halalan lalo pa at dikit-dikit ang mga numero ng mga kandidato base sa mga nagsulputang pre-election surveys. Mababatid na ang INC na may hindi bababa sa 3 million members at kilala sa kanilang bloc voting scheme.</t>
         </is>
       </c>
-      <c r="C179" s="2" t="inlineStr">
+      <c r="C179" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
         <is>
           <t>religion</t>
         </is>
       </c>
-      <c r="D179" s="2" t="inlineStr">
+      <c r="E179" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="F179" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -5043,17 +5669,20 @@
           <t>Aniya, bibigyan ng scholarship ang mga naulilang anak ng mga tinaguriang Mamasapano heroes upang masiguro na makatapos sila ng kolehiyo. Sinabi pa ni Luistro na gawing magandang halimbawa ng mga guro sa pagtuturo ang kabayanihan ng mga namatay na PNP-SAF bilang mahalagang leksyon para makamtan ang kaayusan at kapayapaan, hindi lamang sa Mindanao kundi sa buong bansa. "Instill values of heroism, bravery, tolerance, and compassion among Filipino students in paving the path to peace," wika ni Luistro. "We look to our educators to serve as proper beacons of light, faithful to the search for truth, justice, and peace."</t>
         </is>
       </c>
-      <c r="C180" s="2" t="inlineStr">
+      <c r="C180" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
         <is>
           <t>education</t>
         </is>
       </c>
-      <c r="D180" s="2" t="inlineStr">
+      <c r="E180" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="F180" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -5068,17 +5697,20 @@
           <t>WALANG duda, anak ka nga ni Kris Aquino!" Ito ang tanging nasabi ni Vice Ganda nang ibuking siya ni Bimby na Kevin ang pangalan ng boyfriend niya. Nagkatawanan ang lahat ng tao sa studio ng The Buzz noong Linggo dahil sa sinabi ni Bimby. Maging ang ina nitong si Kris Aquino ay tawa nang tawa kasama ni Boy Abunda</t>
         </is>
       </c>
-      <c r="C181" s="2" t="inlineStr">
+      <c r="C181" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
         <is>
           <t>lifestyle / human interest</t>
         </is>
       </c>
-      <c r="D181" s="2" t="inlineStr">
+      <c r="E181" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="F181" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -5093,17 +5725,22 @@
           <t>Nagbabala ang Department of Information and Communications Technology (DICT) na maaaring mapanagot ang sinumang magbahagi o magpakalat ng video scandal ni Jim Paredes, ayon kay DICT acting Secretary Eliseo Rio Jr. Sa isang forum, ipinaliwanag ni Rio na sakop ng cybercrime law ang ganitong uri ng paglabag dahil ang pagpo-post o pag-share ng pornographic na video, kahit hindi ikaw ang orihinal na gumawa, ay labag sa batas at puwedeng magresulta sa kaso. Binigyang-diin din niya na hindi dahilan ang hindi pag-alam sa batas, dahil kahit ang simpleng pag-like o pag-share ay maaaring magdulot ng pananagutan. Handa naman ang DICT na magsagawa ng imbestigasyon tungkol sa pagkalat ng video scandal sa social media, ngunit nilinaw ni Rio na wala pa silang natatanggap na pormal na reklamo mula kay Paredes.</t>
         </is>
       </c>
-      <c r="C182" s="2" t="inlineStr">
+      <c r="C182" s="3" t="inlineStr">
+        <is>
+          <t>Nagbabala ang Department of Information and Communications Technology (DICT) na posibleng mapanagot ang mga magsha-share o magpapakalat ng video scandal ni Jim Paredes. Sa naging forum ni DICT acting Secretary na si Eliseo Rio Jr. kanyang isinaad na sa ilalim ng cybercrime law ay may kalalagyan ang mga magbabahagi ng nasabing mga private video sa ibang tao. "Yung kay Jim Paredes ito ay pornographic in a sense, at kung sino man ang mag-post ng isang pornographic video clip ay puwedeng kasuhan kasi labag sa batas 'yan na mag-post ka niyan sa social media, in that sense kahit hindi ikaw ang original author ng pornographic material na 'yun dahil pinalabas mo, pinost mo ay puwede kang kasuhan, huwag mo pang i-share dahil parang ikaw na rin ang nag-post nun" ayon kay Eliseo. Hindi rin umano dapat magbingi-bingihan ang mga netizen na wala silang alam sa batas dahil mapapanagot pa rin sila. "Ignorance of that law, kapag hindi mo alam na mayroon pa lang punishment na mag-like lang o mag-share, does not excuse you, ikaw ay mahuhuli diyan," dagdag ni Eliseo. Handa naman ang DICT na imbestigahan ang pagkalat ng video scandal ni Jim Paredes sa social media. Gayunman sinabi ni Rio na wala pa silang natatanggap na anumang pormal na reklamo mula kay Paredes. WATCH: SHARERS OF JIM PAREDES SEX VIDEO LIABLE UNDER CYBERCRIME LAW</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
         <is>
           <t>technology</t>
         </is>
       </c>
-      <c r="D182" s="2" t="inlineStr">
+      <c r="E182" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E182" s="2" t="inlineStr">
+      <c r="F182" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -5118,17 +5755,22 @@
           <t>Sa tulong ng US Homeland Security at Philippine Bureau of Immigration, naaresto sa Biliran ang Amerikanong pari na si Fr. Kenneth Bernard Hendricks, 78-anyos, matapos umanong halayin ang tinatayang 50 kabataang karamihan ay mga sakristan, kung saan ang pinakabata ay 7-anyos, ayon sa ulat ni John Consulta; si Hendricks ay naglingkod sa Biliran ng 50 taon bago siya dinala sa Biliran Provincial Hospital at pagkatapos ay inilipat sa Maynila, habang sinabi ni Lorenzana na karamihan sa mga pipiliing miyembro ng squad na lalaban sa NPA ay magmumula sa Intelligence Service of the Armed Forces of the Philippines (ISAFP) at suportado niya ang pagbuo ng squad na ito upang maprotektahan ang militar laban sa mga pag-atake ng NPA hitmen, kasabay ng paglabas ng mga reaksyon ng publiko tungkol sa panibagong insidente ng pangmomolestiya na kinasasangkutan ng simbahan.</t>
         </is>
       </c>
-      <c r="C183" s="2" t="inlineStr">
+      <c r="C183" s="3" t="inlineStr">
+        <is>
+          <t>Sa pinagsamang pwersa ng US Homeland Security at ng Philippine Bureau of Immigration, nadakip sa Biliran ang Amerikanong pari na si Fr. Kenneth Bernard Hendricks, 78-anyos. Base sa ekslusibong ulat ni John Consulta, aabot sa 50 kabataan ang nahalay umano ni Hendricks. Karamihan sa mga biktima ay sakristan at ang pinakabata ay 7-anyos. Si Hendrick ay 50 taon o 5 dekada ng naninilbihan sa Biliran bago ito naaresto. Dinala muna si Hendricks sa Biliran Provincial Hospital bago ito dalhin sa Maynila. Dagdag pa ni Lorenzana, karamihan sa mga pipiliin para makasama sa squad na lalaban sa mga NPA ay manggagaling sa Intelligence Service of the Armed Forces of the Philippines (ISAFP). Ayon kay Lorenzana, suportado niya ang pagbuo ng nasabing squad para ma-protektahan naman ang mga miyembro ng militar sa mga pag-atake ng hitmen ng NPA. Basahin ang naging reaksyon ng mga tao sa bagong insidente ng pangmomolestiya na kinasasangkutan ng simbahan.</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D183" s="2" t="inlineStr">
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -5143,17 +5785,20 @@
           <t>KINUMPIRMA ng Palasyo na tumulak pa-Hong Kong si Pangulong Duterte kasama ang kanyang long-time partner na si Honeylet Avancena at bunsong anak na si Kitty para magbakasyon. Sinabi ni Presidential Spokesperson and Chief Presidential Legal Counsel Salvador Panelo na regalo ito ni Duterte kay Honeylet na nagdiriwang ng kanyang kaarawan. "Yup. He is in Hong Kong with Honeylet. It's the latter's birthday today," sabi ni Panelo. Sinabi naman ni dating Special Assistant to the President Christopher "Bong" Go na si Kitty ang humiling sa kanilang bakasyon sa Hong Kong. "It was actually Kitty who requested her father for the trip, as a gift. Nagawa na ito nila noon kahit nung Mayor pa ng Davao City si PRRD. The weekend getaway is for rest and recreation," sabi ni Go. idinagdag ni Go na itinalaga ni Duterte si Executive Secretary Salvador Medialdea bilang officer in charge. Umalis ang First Family kahapon at nakatakdang bumalik bukas, ayon pa kay Go.</t>
         </is>
       </c>
-      <c r="C184" s="2" t="inlineStr">
+      <c r="C184" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D184" s="2" t="inlineStr">
+      <c r="E184" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E184" s="2" t="inlineStr">
+      <c r="F184" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -5168,17 +5813,22 @@
           <t>Umakyat ang Pilipinas sa ika-46 na puwesto bilang isa sa pinaka-competitive na ekonomiya sa 2019 World Competitiveness Yearbook mula sa ika-50 noong nakaraang taon, ayon sa ulat ng International Institute for Management Development (IMD). Ayon kay Presidential Spokesperson Salvador Panelo, ito ay patunay ng patuloy na kumpiyansa ng mga foreign investor sa bansa at nagpapakita na nananatiling kaakit-akit ang kalakalan ng Pilipinas para sa mga dayuhang negosyo. Binanggit din ni Panelo na isa sa mga dahilan ng pag-angat ng Pilipinas sa ranking ay ang pamumuno ni Pangulong Rodrigo Duterte, partikular ang pagtutok sa pagbawas ng red tape at pagpapadali ng proseso ng negosyo, kasabay ng pagpapatupad ng Build-Build-Build infrastructure program. Ayon pa sa Asian Institute of Management, partner ng IMD sa Pilipinas, nag-improve ang Pilipinas sa lahat ng apat na pangunahing aspeto: ang Economic Performance ay tumaas ng labindalawang pwesto mula ika-50 sa ika-38, Government Efficiency mula ika-44 sa ika-41, at Business Efficiency mula ika-38 sa ika-32. Sa nasabing ulat, nanguna ang Singapore, sinundan ng Hong Kong at Estados Unidos.</t>
         </is>
       </c>
-      <c r="C185" s="2" t="inlineStr">
+      <c r="C185" s="3" t="inlineStr">
+        <is>
+          <t>Pumalo sa ika-46 na puwesto ang Pilipinas na most competitive economy, ayon sa 2019 World Competitiveness Yearbook mula noong nakaraang taon, na nasa ika-50 na puwesto. Ayon kay Presidential Spokesperson Salvador Panelo, ang pag-angat ng Pilipinas ay nagpapakita lang na nanatili ang kumpiyansa ng mga foreign investor sa ating bansa. "The improved ranking of the Philippines in this year's World Competitiveness Yearbook by the International Institute for Management Development (IMD) augurs well for the country and our economy. There is an emerging investor confidence in our country. It shows our trade environment remains attractive and viable to foreign businesses," sabi ni Panelo. Isa rin daw sa naging kadahilanan ng pagbuti ng antas ng Pilipinas sa ranking ay ang pamumuno ni Pangulong Rodrigo Duterte. "The strong and effective style of governance e optimistic that further improvements will take place. Putting premium on cutting down red tape and promoting ease in doing business while we begin to implement the nation's most ambitious infrastructure program, Build-Build-Build, boost the government's strategy for sustained and inclusive growth. There is every reason to look forward to a bright future for our country's economy and our people.," dagdag pa ni Panelo. Ang natural pag-aaral ay isinasagawa kada taon ng Switzerland-based business school International Institute for Management Development (IMD). "The Philippines saw an improvement in the ranking of all four factors. Economic Performance posted a twelve-notch improvement in 2019 - the largest increase among the four factors - from 50th to 38th. Government Efficiency rose from 44th to 41st; while Business Efficiency improved from 38th to 32nd,," sabi naman ng Asian Institute of Management, ang partner ng IMD sa Pilipinas. Nangunguna sa naturang report ang Singapore habang ang Hong Kong naman ay nasa ika-2 puwesto, at Estados Unidos na nasa ika-3 puwesto.</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
         <is>
           <t>economy / business</t>
         </is>
       </c>
-      <c r="D185" s="2" t="inlineStr">
+      <c r="E185" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E185" s="2" t="inlineStr">
+      <c r="F185" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -5193,17 +5843,20 @@
           <t>Bumoladas si Caloocan Bishop Pablo Virgilio David sa naging komento ni Pangulong Rodrigo Duterte patungkol sa mga santo. Ayon sa Facebook post ng obispo, ipagpanalangin na dapat ng publiko si President Duterte dahil "very sick" daw ito. "I think it should obvious to people by now that our country is being led by a very sick man. We pray for him. We pray for our country,"sabi ni David. "Happy All Saints'...Bakit naman...tarantado talaga itong mga Katoliko ang puta, bakit ba may All Souls' Day at All Saints' Day?Hindi natin alam kung sino mga santo na 'yun. Mga gago na iyon, mga lasenggo. Dito na lang kayo. I'll give you a patron. Get hold of a picture of mine, iyan lagay niyo sa altar, Santo Rodrigo,"sabi ng Pangulo sa isang conference noong Huwebes. Hindi naman nagustuhan ng karamihan sa mga kababayan natin ang mga pinagsasabi ng pari laban kay Pangulong Duterte</t>
         </is>
       </c>
-      <c r="C186" s="2" t="inlineStr">
+      <c r="C186" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
         <is>
           <t>religion</t>
         </is>
       </c>
-      <c r="D186" s="2" t="inlineStr">
+      <c r="E186" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E186" s="2" t="inlineStr">
+      <c r="F186" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -5218,17 +5871,20 @@
           <t>Usap-usapan ngayon sa social media ang umano'y panggagaya ng kinatawan ng Thailand na si Ingchanok Prasart sa ginanap na Miss Intercontinental pageant 2018 sa trademark ni Miss Universe 2018 Catriona Gray na "lava walk." Isang netizen sa Twitter na nagngangalang Marnie Raro ang nakapansin sa paraan ng paglalakad at pag-project ni Miss Thailand na parang kinokopya ang "lava walk" ni Catriona. Bukod kay Miss Thailand, napansin din ng mga netizens ang pagkopya umano sa "Mayon Volcano gown" ni Miss Vietnam. Aminado naman ang dalawa na labis nilang hinahangaan at inspirasyon nila si Miss Universe 2018 Catriona Gray. Halo-halo naman ang naging reaksyon ng mga netizens hinggil dito. "So now everyone looks like Catriona Gray. From hair to stance to gowns. The influence. Only legends do that." "Catriona Gray's walk can never be perfect without her walking it." "I think so? Even the hand gesture of Miss Thailand seems copied too. Catriona Gray is indeed a queen." "Yet they can't copy the original. Because there will be only one Lava Walk and Catriona Gray." "Kayo na 'yung may mga originality... hala gawa kayo sarili niyong pageant, ano ba naman yung hayaan niyo na lang sila hays....daming toxic." Isang patunay lamang ito na maraming mga aspiring beauty pageant candidates, hindi lamang sa Pilipinas kundi maging sa buong mundo, ang tumitingala at humahanga kay Catriona. Aminado naman dito ang marami sa mga kandidata ng naturang katatapos na pageant. Ang 47th edition ng Miss Intercontinental 2018 ay ginanap noong Enero 26, 2019, sa SM Mall of Asia Arena sa Pasay, Metro Manila, Philippines. Kinoronahan ni Miss Intercontinental 2017 Veronica Salas Vallejo ng Mexico ang kandidata ng Pilipinas na si Karen Juanita Gallman. Ito ang kauna-unahang pagkakataong naging host ang Pilipinas sa pageant na ito. Pinili ng Japan organizers ang Pilipinas na maging venue ng pageant dahil abala ang bansang Japan sa mga paghahanda para sa 2020 Summer Olympics. Narito ang buong Twitter post ng netizen:</t>
         </is>
       </c>
-      <c r="C187" s="2" t="inlineStr">
+      <c r="C187" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D187" s="2" t="inlineStr">
+      <c r="E187" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E187" s="2" t="inlineStr">
+      <c r="F187" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -5243,17 +5899,22 @@
           <t>Muling binatikos ni Senator Leila De Lima si Pangulong Duterte, at sinabi niyang panahon na para magsagawa ng seryosong pagninilay ang Pangulo. Ayon kay De Lima, hindi niya alam kung alam ba ng Pangulo na dumarami na umano ang mga taong hindi na sumusuporta sa kanya, at binigyang-diin niyang wala pa siyang nakitang ibang Pangulo ng Pilipinas na nakaranas ng ganitong antas ng galit at paghamak mula sa publiko, kahit noong panahon nina dating Pangulong Marcos o Gloria Arroyo. Dagdag pa ng Senadora, tinawag niyang "panatiko" ang mga patuloy na sumusuporta kay Duterte sa kabila ng mga batikos, at inilarawan ito bilang "bulag na pagsunod" na aniya ay nagpapakita ng maling paniniwala sa pagiging hindi matitinag ng kanilang idolo. Hinimok din ni De Lima si Duterte na magmuni-muni kung kaya pa ba nitong magdala ng kabutihan at normalidad sa bansa o kung patuloy na lang itong mapapariwara, at tinanong din niya kung may kakayahan pa ba ang Pangulo na magliwanag ng isipan.</t>
         </is>
       </c>
-      <c r="C188" s="2" t="inlineStr">
+      <c r="C188" s="3" t="inlineStr">
+        <is>
+          <t>May panibago na namang batikos si Senator Leila De Lima kay Pangulong Duterte. Saad ni De Lima, mukhang napapanahon na raw upang magsagawa ng seryosong soul-searching si Duterte. Ayon pa sa Senadora, hindi umano niya alam kung hindi ba nararamdaman ng kasalukuyang Pangulo ng Pilipinas na dumarami na umano ang mga taong umaayaw dito. Ganito ang naging maaanghang na pahayag ni Senator De Lima patungkol kay Pangulong Duterte noong Sabado, mula sa ulat ng Inquirer: "I don't know if Mr. Duterte realizes that more and more people hate him. Really hate him. I haven't seen any other Philippine President in recent memory, or even in our distant history, eliciting so much hatred and contempt. Not even the dictator Marcos or Gloria Arroyo had invited such level of authentic scorn or virulence," ani De Lima. Dagdag pa ng Senadora, tila nagiging "panatiko" na umano ang mga nananatiling sumusuporta kay Pangulong Duterte sa kabila ng mga batikos na ibinabato rito. Tinawag niya ring "bulag na pagsunod" ang ginagawang ito ng mga nasabing supporters ni Pangulong Duterte. "That's what fanaticism is all about- a blind devotion, coupled with a perverse notion about the invincibility of a demagogue idol," saad ni De Lima. "Time to do some serious soul-searching, Mr. President. Are you still capable of bringing any good or righteous normalcy to our country? Or is it now a road to perdition all the way? Are you even capable of pure enlightenment?,"wika pa ng Senadora.</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D188" s="2" t="inlineStr">
+      <c r="E188" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E188" s="2" t="inlineStr">
+      <c r="F188" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -5268,17 +5929,20 @@
           <t>Incident na ikinagulat ng marami ang paglabas ng isang anonymous video ngayong hapon na nagpapakita umano ng isang mataas na opisyal ng gobyerno na palihim na nakikipagpulong sa isang grupo ng mga dayuhang negosyante sa isang kilalang hotel sa Maynila, kung saan pinaniniwalaang pinag-uusapan daw ang planong pag-angkat ng mga hindi rehistradong teknolohiya kapalit ng malaking halaga na ilalagay umano sa mga pekeng proyekto ng pamahalaan; ayon pa sa mga netizen na mabilis na nagbahagi ng video, makikita raw sa likod ng opisyal ang ilang kahon na may kakaibang marka na hindi pamilyar sa mga lokal na brand, dahilan para umusbong ang mga teorya na may nilulutong kasunduan para sa pansariling interes at hindi para sa kapakanan ng bayan, habang nananatiling tikom ang bibig ng nasabing opisyal at wala pang inilalabas na opisyal na pahayag ang kanyang tanggapan, kaya’t patuloy na lumalakas ang panawagan ng publiko na magsagawa ng imbestigasyon at ibunyag ang tunay na nangyayari sa likod ng mga saradong pinto ng gobyerno.</t>
         </is>
       </c>
-      <c r="C189" s="2" t="inlineStr">
+      <c r="C189" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D189" s="2" t="inlineStr">
+      <c r="E189" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E189" s="2" t="inlineStr">
+      <c r="F189" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -5293,17 +5957,20 @@
           <t>Usap-usapan ngayon sa social media ang umano'y panggagaya ng kinatawan ng Thailand na si Ingchanok Prasart sa ginanap na Miss Intercontinental pageant 2018 sa trademark ni Miss Universe 2018 Catriona Gray na "lava walk." Isang netizen sa Twitter na nagngangalang Marnie Raro ang nakapansin sa paraan ng paglalakad at pag-project ni Miss Thailand na parang kinokopya ang "lava walk" ni Catriona. Bukod kay Miss Thailand, napansin din ng mga netizens ang pagkopya umano sa "Mayon Volcano gown" ni Miss Vietnam. Aminado naman ang dalawa na labis nilang hinahangaan at inspirasyon nila si Miss Universe 2018 Catriona Gray. Halo-halo naman ang naging reaksyon ng mga netizens hinggil dito. "So now everyone looks like Catriona Gray. From hair to stance to gowns. The influence. Only legends do that." "Catriona Gray's walk can never be perfect without her walking it." "I think so? Even the hand gesture of Miss Thailand seems copied too. Catriona Gray is indeed a queen." "Yet they can't copy the original. Because there will be only one Lava Walk and Catriona Gray." "Kayo na 'yung may mga originality... hala gawa kayo sarili niyong pageant, ano ba naman yung hayaan niyo na lang sila hays....daming toxic." Isang patunay lamang ito na maraming mga aspiring beauty pageant candidates, hindi lamang sa Pilipinas kundi maging sa buong mundo, ang tumitingala at humahanga kay Catriona. Aminado naman dito ang marami sa mga kandidata ng naturang katatapos na pageant. Ang 47th edition ng Miss Intercontinental 2018 ay ginanap noong Enero 26, 2019, sa SM Mall of Asia Arena sa Pasay, Metro Manila, Philippines. Kinoronahan ni Miss Intercontinental 2017 Veronica Salas Vallejo ng Mexico ang kandidata ng Pilipinas na si Karen Juanita Gallman. Ito ang kauna-unahang pagkakataong naging host ang Pilipinas sa pageant na ito. Pinili ng Japan organizers ang Pilipinas na maging venue ng pageant dahil abala ang bansang Japan sa mga paghahanda para sa 2020 Summer Olympics. Narito ang buong Twitter post ng netizen:</t>
         </is>
       </c>
-      <c r="C190" s="2" t="inlineStr">
+      <c r="C190" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D190" s="2" t="inlineStr">
+      <c r="E190" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E190" s="2" t="inlineStr">
+      <c r="F190" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -5318,17 +5985,20 @@
           <t>"These simple yet challenging meditation practices provide the opportunity for people to expand their nonjudgmental awareness of sensory experiences arising in each moment," ani David Black, ang unang sumulat ng pag-aaral mula sa University of Southern California sa Los Angeles.</t>
         </is>
       </c>
-      <c r="C191" s="2" t="inlineStr">
+      <c r="C191" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
         <is>
           <t>international news</t>
         </is>
       </c>
-      <c r="D191" s="2" t="inlineStr">
+      <c r="E191" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E191" s="2" t="inlineStr">
+      <c r="F191" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -5343,17 +6013,22 @@
           <t>Muling binatikos ni Davao City Mayor Sara Duterte-Carpio si Senador Leila de Lima kaugnay ng isyu ng pagiging tapat ng mga kandidato sa eleksyon, kung saan sa isang open letter ay tinawag niyang “matalinong bobo” si De Lima dahil inatake umano siya nito nang hindi binabasa ang buong konteksto ng kanyang pahayag tungkol sa pagiging tapat na kandidato. Ayon kay Mayor Sara, hindi raw inintindi ni De Lima ang kanyang sinabi at malinaw na ipinapakita nito ang tunay na pagkatao ng senadora. Ipinaliwanag din ni Mayor Sara na ang punto niya ay hindi dapat ang oposisyon ang magtakda kung ano ang dapat sa isang kandidato at hindi raw isyu ang honesty dahil hindi ito requirement para tumakbo sa eleksyon, kaya hindi rin dapat batikusin ng mga “Black Hole candidates” na aniya ay mga sinungaling din. Binanggit din ni Mayor Sara na ginamit niya ang parehong argumento sa usapin ng college degree at inclusion sa narco list. Bukod dito, kinuwestiyon niya ang pagiging tapat ni De Lima bilang senador dahil sa pagkakadawit nito sa iligal na droga at hinamon niya si De Lima na gumawa ng batas na gawing requirement ang honesty para sa lahat ng Pilipino bago tumakbo sa anumang posisyon, upang aniya ay maisalba ang gobyerno mula sa mga katulad ni De Lima, Vice President Leni Robredo, Salvador Panelo, Gary Alejano, Florin Hilbay, at iba pang “De Lima” sa mundo.</t>
         </is>
       </c>
-      <c r="C192" s="2" t="inlineStr">
+      <c r="C192" s="3" t="inlineStr">
+        <is>
+          <t>Muli na namang bumanat si Davao City Mayor Sara Duterte-Carpio laban kay Sen. Leila de Lima dahil sa isyu ng pagiging tapat ng mga kandidato sa eleksyon. Sa isang open letter ni Mayor Sara, tinawag nitong matalinong bobo si De Lima dahil inatake siya nito nang hindi muna binasa ang buong konteksto ng kanyang sinabi patungkol sa isyu ng pagiging tapat na kandidato. Hindi aniya muna inintindi ni De Lima ang buod ng kanyang sinabi kaya malinaw kung anong uri ng pagkatao nito. "I thought it best to write a letter since you probably do not have access to a television. If I am an example of what is wrong and what could be worse for our government, you just described yourself as well. You are the worst because you are intelligent and dumb all in one head. You are the only person from the Black Hole who said it right, dapat ang botante ang nagsasabi kung ano ang hinahanap niya sa kandidato. But you are dumb as well, for attacking me without reading the entire transcription of my statement and comprehending what I said," ani Mayor Sara. "Ang sabi ko, hindi ang opposition ang magsasabi kung ano dapat ang isang kandidato at hindi issue ang honesty dahil hindi yan requirement para ka maging kandidato. Therefore, Black Hole candidates, who are themselves liars, should not attack a candidate in that manner. I used the same argument on the issue of a college degree or inclusion in the narco list," dagdag ni Mayor Sara. Kuwestiyonable rin aniya ang pagiging tapat ni De Lima bilang isang senadora dahil sa pagkakasangkot nito sa iligal na kalakalan ng droga sa bansa. Hinamon naman ni Mayor Sara si De Lima na gumawa ng batas at isama bilang requirement sa lahat ng mga Pilipino ang honesty o katapatan bago sila tumakbo sa puwesto at sa ganitong paraan aniya ay maisalba ang gobyerno sa mga taong katulad niya, kay Vice President Leni Robredo, Presidential Spokesman Salvador Panelo, Congressman Gary Alejano, Florin Hilbay at sa lahat ng "De Lima" sa buong mundo. "You are a senator -- honesty about your involvment in the illegal drugs business under scrutiny by the courts -- how about you make a law adding honesty as a requirement for all Filipinos before they can run for public office. Maybe then you can save the government from yourself, Inday Sara, Leni, Digong, Panelo, Alejano, Hilbay, and the all the De Limas of the universe," ani Mayor Sara.</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D192" s="2" t="inlineStr">
+      <c r="E192" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E192" s="2" t="inlineStr">
+      <c r="F192" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -5368,17 +6043,20 @@
           <t>Viral ngayon sa social media ang balita tungkol sa umano’y “Operation Nightfall” na sinasabing isinagawa ng ilang mataas na opisyal ng isang kilalang partido, kung saan pinaghihinalaang ginamit ang pondo ng bayan para pondohan ang isang lihim na kampanya kontra sa mga kalabang kandidato; ayon sa mga naglabasang screenshots at audio clips na kumakalat sa group chats, may mga alegasyon na nagkaroon daw ng mga midnight meeting sa isang sikretong warehouse at may mga listahan pa raw ng mga pangalan ng opisyal na tumanggap ng cash envelopes bilang kapalit ng pagsuporta sa kontrobersiyal na plano, dahilan para magdulot ng matinding pagkabahala at galit mula sa publiko na nananawagan ngayon ng imbestigasyon, habang tikom pa rin ang bibig ng mga sangkot na opisyal sa kabila ng kabi-kabilang batikos at panawagan para sa transparency.</t>
         </is>
       </c>
-      <c r="C193" s="2" t="inlineStr">
+      <c r="C193" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D193" s="2" t="inlineStr">
+      <c r="E193" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E193" s="2" t="inlineStr">
+      <c r="F193" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -5393,17 +6071,20 @@
           <t>Tinutugis na ngayon ng pulisya si Jessie Garbo matapos nitong mapatay sa bugbog ang anak ng kanyang live-in partner. Kinilala ang biktima na si Erven Piad, 4-anyos, namatay dahil sa pagmamaltrato ng amain sa lungsod ng Bugallon, Pangasinan. Ayon sa pahayag ng ina ng biktima na si Angela San Andres, nakita niyang magkatabi sa higaan ang suspek at ang kanyang anak. Aniya, hinataw ng suspek ng walis sa ulo ang kanyang anak. "Pinapatulog niya po 'yung anak ko, hindi po natulog po 'yung anak ko tapos nung hindi natulog, kinuha niya 'yung walis tambo, pinalo niya sa ulo. Pagkatapos ng pagkapalo niya sa ulo ng anak ko, dumugo 'yung ulo ng anak ko, may hiwa," pahayag ni San Andres. Napansin na raw ni San Andres na tila nanghihina ang anak at namumutla. "'Yung nakikita niya na humihiga 'yung anak ko na parang nanghihina na, binugbog niya po," ani San Andres. Doon na ito nilapitan ng suspek at ginulpi hanggang sa tuluyan nang namatay. Napansin na lamang nila na hindi na gumagalaw ang bata at doon agad nilang isinugod sa ospital ang bata. Ayon kay P/Maj. Jake Isidro, hepe ng Bugallon Police Station, kapag lumabas ang resulta ng kanilang imbestigasyon at nakitang responsable din ang ina ng biktima sa kanyang pagkamatay ay kakasuhan din nila ito. Samantala, sinampahan na ng kasong Homicide na may kinalaman sa Republic Act 7610 o Child Abuse Act ang suspek. Napag-alaman din na may naging kaso na rin ang suspek na may kaugnayan sa pananakit ngunit nauwi sa areglo.</t>
         </is>
       </c>
-      <c r="C194" s="2" t="inlineStr">
+      <c r="C194" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D194" s="2" t="inlineStr">
+      <c r="E194" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E194" s="2" t="inlineStr">
+      <c r="F194" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -5418,17 +6099,22 @@
           <t>Napatay ng mga pulis sa Batangas ang tatlong miyembro ng isang kilalang gun-for-hire group matapos silang manlaban sa operasyon, ayon sa ulat ng GMA News. Kinilala ang lider ng grupo na si Solomon Panan at ang kanyang dalawang kasamahan na sina Vergilio Hernandez at Efren Cruzada. Naalerto ang mga otoridad sa planong operasyon ng grupo laban sa isang negosyante kaya agad silang nakapaghanda. Tatlong baril ang nakuha mula sa mga suspek, na sinasabing sangkot din sa serye ng nakawan at patayan sa Batangas, Metro Manila, Bulacan, at Pampanga. Naniniwala ang kapulisan na mababawasan na ang mga gun-for-hire activities sa Batangas dahil sa pagkakapatay sa mga suspek, at patuloy ang Duterte Administration sa kampanya laban sa kriminalidad para protektahan ang mga mamamayang Pilipino.</t>
         </is>
       </c>
-      <c r="C195" s="2" t="inlineStr">
+      <c r="C195" s="3" t="inlineStr">
+        <is>
+          <t>May napurga na naman na masasamang loob nang manlaban ang mga ito sa kapulisan sa Batangas. Ayon sa ulat ng GMA News, 3 miyembro ng notorious na gun-for-hire group ang naka-engkwentro ng mga pulis. Patay sa operasyon ang lider ng grupo na si Solomon Panan at ang 2 alipores nito na sina Vergilio Hernandez at si Efren Cruzada. Natrimbrehan ng mga otoridad ang gagawing operasyon ng grupo sa isang negosyante kaya nakapag-handa agad ang kapulisan. Tatlong armas ang nakuha sa mga kawatan. Sangkot din daw ang mga miyembro ng sindikato sa mga serye ng nakawan at patayan sa Batangas, Metro Manila, Bulacan at Pampanga. Ayon sa kapulisan, naniniwala sila na mababawasan na ang mga gun-for-hire activities sa Batangas dahil sa pagkakapuksa sa mga suspek. Ito ang patunay na patuloy na ginagawa ng Duterte Administration ang kampanya nito kontra-kriminalidad para protektahan ang mga mabubuting Pilipino Basahin ang reaksyon ng mga kababayan natin sa sinapit ng tatlong kawatan.</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D195" s="2" t="inlineStr">
+      <c r="E195" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E195" s="2" t="inlineStr">
+      <c r="F195" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -5443,17 +6129,22 @@
           <t>Nanawagan ang kampo ng Otso Diretso, sa pangunguna ng kanilang campaign manager at Liberal Party President na si Senator Francis "Kiko" Pangilinan, para sa malinaw na paliwanag mula sa Commission on Elections hinggil sa mga "glitches" at mga isyu sa bilangan ng boto noong nakaraang May Elections, partikular na ang pitong oras na pagkaantala sa paglabas ng resulta sa transparency server na ayon kay Pangilinan ay hindi pa nangyari noon, at biglaang pagkawala ng Otso Diretso sa mga nangungunang puwesto pagkaraan ng madaling araw; binigyang-diin din niya ang kawalan ng agarang paliwanag mula sa Comelec sa loob ng lima hanggang anim na oras habang hindi pa naipapadala ang mga datos, at ang kahalagahan ng transparent na transmission lalo na sa dikit na laban sa ika-12, 13, at 14 na puwesto kung saan si Senator Bam Aquino IV ng Otso Diretso ay kasalukuyang nasa ika-14 na slot batay sa partial at unofficial results; iginiit ni Pangilinan na dapat may malinaw na sagot sa mga katanungan, lalo na’t posibleng makabawi pa ang kanilang mga kandidato sa natitirang boto, habang si Otso Diretso spokesperson lawyer Barry Gutierrez naman ay binatikos ang umano’y malawakang malfunction ng vote counting machines na nagdulot ng pagkakabalam sa pagboto at pagkakailangang iwan ng mga botante ang kanilang balota para election personnel na lang ang magpasok nito, at binanggit din ang insidente sa Tarlac kung saan 14 sa 18 SD cards ay nag-malfunction na maaaring nakaapekto sa 500,000 botante, kaya nananawagan sila ng mas malinaw at sapat na paliwanag mula sa Comelec dahil hindi pa raw natutugunan ng mga kasalukuyang paliwanag ang kanilang mga concern.</t>
         </is>
       </c>
-      <c r="C196" s="2" t="inlineStr">
+      <c r="C196" s="3" t="inlineStr">
+        <is>
+          <t>Eksplanasyon mula sa Commission on Elections. Ito ngayon ang malaking panawagan ng kampo ng Otso Diretso senatorial slate, sa pangunguna ng kanilang campaign manager at Liberal Party President na si Senator Francis "Kiko" Pangilinan, kaugnay pa rin ng nangyaring "glitches" sa nakaraang May Elections, gayundin sa pagbibilang ng mga boto. "Halimbawa 'yung pitong oras na hindi lumabas ang resulta sa transparency server, never naman nangyari ito. Pagkatapos pagdating ng madaling araw, 90 plus percent na, wala na lahat 'yung Otso Diretso. That by itself needs an explanation. How did that happen?" saad ni Pangilinan. Kinuwestiyon din ng senador ang aniya'y lima hanggang anim na oras na walang ibinigay na paliwanag ang Comelec habang hindi pa umano naita-transmit ang mga datos. Hindi rin daw lumabas at hindi nagsalita ang departamento na parang walang nangyaring problema, at dapat umano nila itong linawin. Binigyang-diin din ni Pangilinan ang kahalagahan ng transparent transmission lalo na sa mahigpit at dikit na laban partikular na sa ika- 12, 13. at 14 na puwesto. Si Senator Paolo Benigno "Bam" Aquino IV ng Otso Diretso ang kasalukuyang nasa ika-14 na slot, batay sa partial and unofficial results ng Comelec. "Itong mga ganitong kakaibang pangyayari ay malaking katanungan na dapat magkaroon ng paliwanag," wika ni Pangilinan. "Baka sakaling sa nasabing nalalabing pitong porsyento ay maipanalo pa ng isa o dalawa nating mga kandidato ang kanilang kandidatura. Mananatili tayong mapagbantay hanggang sa dulo," dagdag pa ni Pangilinan. Samantala, binatikos din ni Otso Diretso spokesperson lawyer Barry Gutierrez ang aniya'y pagma-malfunction ng daan-daang vote counting machines sa mismong araw ng halalan. Ilang mga ulat din ang kanilang natanggap na kinailangan umanong iwan ng ilang mga botante ang kanilang mga balota sa mga presinto at hinayaang ang mga election personnel sa lugar ang magpasok ng mga ito sa machine dahil sa pangyayari. Sa Tarlac, na siyang sinasabing balwarte ni Aquino ay may 14 mula sa kabuuang 18 SD cards ang umano'y iniulat na nag-malfunction din, ayon sa kampo ng Otso Diretso. "Obviously, that's a huge source of concern. We're talking about 500,000 voters potentially affected. And if the gap between number 14 where Senator Aquino is right now and number 12 is something like 300,000 votes, that's obviously going to matter," paliwanag ni Gutierrez. "We're not saying na may deliberate conspiracy dito na ginagawa, but what we're saying is merong mga tanong na kailangang sagutin ang Commission on Elections. And right now, the explanations that they have given have not fully addressed 'yung mga concern," dagdag pa nito.</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D196" s="2" t="inlineStr">
+      <c r="E196" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E196" s="2" t="inlineStr">
+      <c r="F196" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -5468,17 +6159,20 @@
           <t>Ayon sa dating actor, nananatili siyang staff ng senadora pero hindi nga lang sumasama sa mga lakad nito sa pangangampanya. Binanggit ni Renzo na magtatatlong taon na siya bilang staff ni Sen. Grace Poe at walong taon ding naging staff ni Sen. Jinggoy Estrada. Kaya regular Senate employee na raw ang kapatid ni Sheryl Cruz at wala raw namang isyu tungkol sa kanilang dalawa ng pinsang si Sen. Poe. Iniiwasan niyang magkomento tungkol sa hidwaan nina Sheryl at Sen. Grace. "Bahala na sila sa bagay na 'yan. Basta walang problema sa amin ni Sen. Grace at hindi rin naman namin pinag-uusapan 'yun ng kapatid kong si Sheryl," sey niya. Kinamusta namin kay Renzo ang mommy niyang si Rosemarie Sonora at ang kapatid niyang si Patrick. Masayang-masaya rin daw ngayon si Partick sa buhay may-asawa nito pero pagdating sa kanilang ina ay hindi pa raw napapanahon na pag-uusapan namin ang bagay na ito.</t>
         </is>
       </c>
-      <c r="C197" s="2" t="inlineStr">
+      <c r="C197" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D197" s="2" t="inlineStr">
+      <c r="E197" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E197" s="2" t="inlineStr">
+      <c r="F197" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -5493,17 +6187,20 @@
           <t>Usap-usapan ngayon sa social media ang umano'y panggagaya ng kinatawan ng Thailand na si Ingchanok Prasart sa ginanap na Miss Intercontinental pageant 2018 sa trademark ni Miss Universe 2018 Catriona Gray na "lava walk." Isang netizen sa Twitter na nagngangalang Marnie Raro ang nakapansin sa paraan ng paglalakad at pag-project ni Miss Thailand na parang kinokopya ang "lava walk" ni Catriona. Bukod kay Miss Thailand, napansin din ng mga netizens ang pagkopya umano sa "Mayon Volcano gown" ni Miss Vietnam. Aminado naman ang dalawa na labis nilang hinahangaan at inspirasyon nila si Miss Universe 2018 Catriona Gray. Halo-halo naman ang naging reaksyon ng mga netizens hinggil dito. "So now everyone looks like Catriona Gray. From hair to stance to gowns. The influence. Only legends do that." "Catriona Gray's walk can never be perfect without her walking it." "I think so? Even the hand gesture of Miss Thailand seems copied too. Catriona Gray is indeed a queen." "Yet they can't copy the original. Because there will be only one Lava Walk and Catriona Gray." "Kayo na 'yung may mga originality... hala gawa kayo sarili niyong pageant, ano ba naman yung hayaan niyo na lang sila hays....daming toxic." Isang patunay lamang ito na maraming mga aspiring beauty pageant candidates, hindi lamang sa Pilipinas kundi maging sa buong mundo, ang tumitingala at humahanga kay Catriona. Aminado naman dito ang marami sa mga kandidata ng naturang katatapos na pageant. Ang 47th edition ng Miss Intercontinental 2018 ay ginanap noong Enero 26, 2019, sa SM Mall of Asia Arena sa Pasay, Metro Manila, Philippines. Kinoronahan ni Miss Intercontinental 2017 Veronica Salas Vallejo ng Mexico ang kandidata ng Pilipinas na si Karen Juanita Gallman. Ito ang kauna-unahang pagkakataong naging host ang Pilipinas sa pageant na ito. Pinili ng Japan organizers ang Pilipinas na maging venue ng pageant dahil abala ang bansang Japan sa mga paghahanda para sa 2020 Summer Olympics. Narito ang buong Twitter post ng netizen:</t>
         </is>
       </c>
-      <c r="C198" s="2" t="inlineStr">
+      <c r="C198" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D198" s="2" t="inlineStr">
+      <c r="E198" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E198" s="2" t="inlineStr">
+      <c r="F198" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -5518,17 +6215,20 @@
           <t>Nagdulot ng matinding pagkabigla at diskusyon sa buong bayan ng San Pedro ang balitang kumakalat tungkol sa umano’y “Miracle Oil” na ipinamahagi ng isang bagong tatag na samahan na tinatawag na Kapatiran ng Ilaw, kung saan sinasabing kaya raw nitong magpagaling ng mabibigat na sakit kapalit ng donasyon, ngunit nabunyag sa isang undercover na ulat ng lokal na pahayagan na ang langis ay ordinaryong mantika lamang na may halong pabango at kulay, dahilan upang umalma ang ilang miyembro at maghain ng reklamo laban sa lider ng grupo na ngayon ay hindi na mahagilap, habang ang ilang residente ay nananawagan ng imbestigasyon dahil umano sa pananamantala sa pananampalataya ng mga tao at pagkalat ng maling pag-asa sa mga nangangailangan.</t>
         </is>
       </c>
-      <c r="C199" s="2" t="inlineStr">
+      <c r="C199" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
         <is>
           <t>religion</t>
         </is>
       </c>
-      <c r="D199" s="2" t="inlineStr">
+      <c r="E199" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E199" s="2" t="inlineStr">
+      <c r="F199" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -5543,17 +6243,22 @@
           <t>Hinimok ng Philippine Drug Enforcement Agency (PDEA) ang mga television networks sa bansa na magsagawa ng surprise at mandatory drug test para sa kanilang mga artista, na maaaring gawin nang pribado at hindi na kailangang ibunyag sa publiko ang mga resulta, ayon kay PDEA director general Aaron Aquino matapos niyang ibunyag na may 31 artista na kabilang sa kanilang drug watchlist. Ayon kay Aquino, sana ay dumalo ang lahat ng celebrity kung sakaling maisagawa ang drug test upang maipakita sa publiko na sila ay malinis. Sa ulat, sinabi ni Aquino na sa 31 artista sa watchlist, 11 ay aktres, 17 ay mga batang aktor na nasa kanilang 20s at 30s, at tatlo naman ay matatandang artista na nasa 40s, kabilang din dito ang ilang love teams. Nagbabala si Aquino na handa ang PDEA na arestuhin ang mga artistang sangkot sa ilegal na droga at sinabi niyang marami na ring nahuling artista kaya huwag nang hintayin na mahuli pa sila, kahit pa nasa hotel, condominium, o exclusive subdivision. Samantala, inamin ni Police Colonel Bernard Banac, tagapagsalita ng PNP, na mahirap mangalap ng ebidensya laban sa mga artistang nasa watchlist at nananatiling hamon ito para sa PNP at PDEA kung paano makakapagbuo ng matibay na kaso laban sa kanila.</t>
         </is>
       </c>
-      <c r="C200" s="2" t="inlineStr">
+      <c r="C200" s="3" t="inlineStr">
+        <is>
+          <t>Hinamon ng Philippine Drug Enforcement Agency (PDEA) ang mga television networks sa bansa na kusang magsagawa ng susrprise at mandatory drug test sa kanilang mga artista. Maaari naman aniya na gawin itong pribado o kompidensyal at hindi na ilalabas sa publiko ang resulta. Ito ang pahayag ni PDEA director general Aaron Aquino matapos niyang isiwalat na 31 artista ang nasa kanilang drug watchlist. "I just hope that na kung mangyari man, lahat sana ng celebrity present just to be, just to show to the public that they are clean," ani Aquino. Sa unang ulat, sinabi ni Aquino na 11 sa 31 na artista sa kanilang drug watchlist ay aktres, 17 ang mga batang aktor, nasa kanilang 20s at 30s, habang ang natitirang tatlo ay matatanda nang artista, nasa 40s at mayroon din umanong mga love teams sa listahan. Nagbabala si Aquino na hindi magdadalawang isip ang PDEA na arestuhin ang mga artista na sangkot sa ilegal na droga. "Marami na rin kaming nahuling mga artista and huwag niyo nang hintayin mahuli namin kayo. Huwag niyo sabihin nasa hotel kayo, condominium, nasa exclusive subdivision, bibirahin namin at bibirahin namin kayo," ani Aquino. Samantala, aminado naman ang pulisya na hindi madali ang pagkalap ng ebidensiya laban sa mga artista na nasa watchlist. "It remains a challenge for PNP and PDEA on how to build a strong case against the persons in the watchlist," sabi ni Police Colonel Bernard Banac, tagapagsalita ng PNP.</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D200" s="2" t="inlineStr">
+      <c r="E200" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E200" s="2" t="inlineStr">
+      <c r="F200" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -5568,17 +6273,20 @@
           <t>Isa na namang ambisiyosong proyekto ang nakakasa na sa ilalim ng Duterte Administration. Ayon sa ulat ng beteranong mamamahayag na si Erwin Tulfo, itatayo daw ang proyekto sa Cagayan. Tatawaging daw ito na "City Polaris". Nakaahalaga daw ito ng $4.5 billion o P237 billion. Papangasiwaan ng Cagayan Economic Zone Authority (CEZA) ang proyekto na inaasahan makukumpleto bago matapos ang termino ng Pangulong Rodrigo Duterte. Walang gagastusin daw ang gobyerno dito dahil ang mga pribadong kumpanya ang sasagot sa pondo. Base sa ulat ni Tulfo, ang ilan sa mga pasilidad sa gagawing syudad ay world-class at moderno. Magtatayo din daw ng theme park sa lugar na kagaya ng Disney Land o Unidersal Studios. "Mayroong mga condominiums, mayroon mga shopping malls, mayroong mga theme parks na itatayo doon. Mayroong silang private villas na itatayo at townships to provide lodging or accomodations to the increasing number of investors coming in," sabi ni CEZA Senior Deputy Administrator Usec. Raymundo Roquero. Ang itatayong bagong siyudad ay malapit sa Palui Island. Balak daw ng pamahalaan na ipalit ito sa Boracay. Nakilala ang ang lugar nang ma-feature ito sa isang programa sa Estados Unidos noong 2013. "Naging attraction tayo globally. Nalaman ng buong mundo na may paradise pala sa North Luzon na hindi pa na-discover. And we want to develop this island. In fact, 3 years ago, we were the only beach in South East Asia which was included in the top 10 in the world ," dagdag pa ni Roquero. Aayusin din daw ng gobyerno ang mga pantalan at mga paliparan para maging kumbinyente ang pagbiyahe ng mga turista. Inaasahan naman makakatulong ang bagong satellite city sa mga residente sa lugar dahil mabibigyan sila ng dagdag kita. Ang ulat na ito ni Tulfo ay kumalat ng husto. Sa katunayan, habang isinusulat itong artikulo, lumagpas na ng 28,000 ang nagbahagi ng istroya at umani na rin ng libo-libong komento mula sa mga netizens.</t>
         </is>
       </c>
-      <c r="C201" s="2" t="inlineStr">
+      <c r="C201" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
         <is>
           <t>economy / business</t>
         </is>
       </c>
-      <c r="D201" s="2" t="inlineStr">
+      <c r="E201" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E201" s="2" t="inlineStr">
+      <c r="F201" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -5593,17 +6301,20 @@
           <t>Dahil sa hindi mabatid na dahilan, kumuha si Llamas ng isang bolo at lumusob sa bahay ng isang Rocky Navnes sa Filemon St., Barangay San Isidro Zone-1, bago tinangay na hostage ang tatlong biktima - sina Rosalie De San Juan Navnes, 25; Ralph Ian Navnes, 15; at Macy Garcia, 21 - dakong 8:00 ng umaga. Sa pakikipagnegosasyon ng mga pulis upang sumuko ang suspek at palayain ang mga biktima, hiniling ni Llamas na makausap ang kanyang kapatid na Cristina. Matapos ang isang oras ng pakikipagnegosasyon ng awtoridad, sumuko na rin si Llamas at ligtas na pinalaya ang mga biktima.</t>
         </is>
       </c>
-      <c r="C202" s="2" t="inlineStr">
+      <c r="C202" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D202" s="2" t="inlineStr">
+      <c r="E202" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E202" s="2" t="inlineStr">
+      <c r="F202" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -5618,17 +6329,22 @@
           <t>Inilabas na ng mga awtoridad ang larawan ng pangunahing suspek sa karumal-dumal na pagpatay kay Christine Lee Silawan, 16-anyos na grade 9 student sa Lapu-Lapu City, Cebu, na bukod sa pinatay at ginahasa ay binalatan pa ang mukha at tinanggalan ng lamanloob. Kinilala ang isa sa tatlong suspek na si Jonas Bueno, na ayon sa imbestigasyon ng pulisya ay hindi residente ng Lapu-Lapu City at kasalukuyang nagtatago sa Cebu. Base sa CCTV, nakita si Silawan na pinasakay sa motorsiklo ng itinuturong suspek bago mangyari ang krimen, at lumalabas din sa imbestigasyon na nagkausap sila sa mensahe, ngunit hindi pa tiyak kung may relasyon sila. Tinitingnan din ng mga pulis ang posibleng koneksyon ng kaso ni Silawan sa pagpatay at pagbalat din sa mukha ng 60-anyos na si Trinidad Batucan noong Enero 11, kung saan pinangalanan ang magkakapatid na sina Junrey, Juvy at Jonas Bueno bilang mga suspek. Ayon kay Police Col. Lemuel Obon, hepe ng Lapu-Lapu City Police, mas mapapadali ang paghuli sa dalawa pang suspek kapag nahuli na si Jonas. Samantala, umabot na sa P2 milyon ang pabuya para sa sinumang makapagtuturo sa mga salarin, matapos magdagdag ng P100,000 si Presidential Assistant to the Visayas Michael Dino at nangakong magbibigay rin ng P100,000 si Philippine Postal Corporation Chairman Norman Fulgencio, bukod pa sa P1 milyon mula sa Lapu-Lapu City government, P500,000 mula sa isang dayuhan sa Leyte, P200,000 mula sa Cebu Provincial Council for the Welfare of Children, at P100,000 mula sa Police Regional Advisory Council, habang iniabot din ni Dino ang P20,000 tulong pinansiyal mula sa Office of the President sa pamilya ng biktima.</t>
         </is>
       </c>
-      <c r="C203" s="2" t="inlineStr">
+      <c r="C203" s="3" t="inlineStr">
+        <is>
+          <t>Inilabas na ang larawan ng primary suspek sa malagim na sinapit ni Christine Lee Silawan, 16-anyos, grade 9 student sa Lapu-Lapu City sa Cebu na bukod sa pinatay at ginahasa ay binalatan pa ang mukha at tinanggalan ng lamanloob. Kinilala ang isa sa tatlong suspek na si Jonas Bueno. Ayon sa mga naunang ulat, hindi ito nakatira sa Lapu-lapu City at kasalukuyang nagtatago sa Cebu batay sa imbestigasyon ng mga pulis. Nakita umano ang itinuturong primary suspek na pinasakay nito sa isang motorsiklo si Silawan na nakita sa isang CCTV bago ang krimen. Lumalabas rin sa imbestigasyon ng mga pulis na nakakapalitan ng biktima ng mensahe ang suspek ngunit hindi sigurado kung mayroon silang relasyon. Tinitingnan din ang koneksyon ng kaso ni Silawan sa tatlong suspek sa pagpatay at pagbalat din sa mukha ng 60-anyos na si Trinidad Batucan na nangyari noong Enero 11. Pinangalanan ang mga suspek sa kaso ni Batucan na magkakapatid na sina Junrey, Juvy at Jonas Bueno. Ayon naman kay Police Col. Lemuel Obon, hepe ng Lapu-Lapu City Police, mas magiging madali na para sa kanila na mahuli ang dalawa pang suspek kapag naaresto na ang pangunahing suspek na si Jonas. Samantala, umakyat na sa P2 million ang pabuya sa sinumang makatutulong sa ikadarakip ng mga salarin. Ito'y matapos mag-ambag si Presidential Assistant to the Visayas Michael Dino ng P100,000. Nangako rin umano si Philippine Postal Corporation Chairman Norman Fulgencio na magbibigay ng dagdag na P100,000. Ang ibang nalikom na pera ay mula sa Lapu-Lapu City government (P1 million), isang dayuhan na nakabase sa Leyte (P500,000), Cebu Provincial Council for the Welfare of Children (P200,000) at Police Regional Advisory Council (P100,000). Maliban sa dagdag na reward ay iniabot din ni Dino ang tulong pinansiyal mula sa Office of the President na P20,000 sa pamilya ng biktima.</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D203" s="2" t="inlineStr">
+      <c r="E203" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E203" s="2" t="inlineStr">
+      <c r="F203" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -5643,17 +6359,22 @@
           <t>Sumabay ang kaarawan ni Mar Roxas sa araw ng eleksiyon ngayong taon kaya binati siya ng kanyang asawang si Korina Sanchez-Roxas, host ng ABS-CBN's Rated K, sa social media noong Mayo 13 at ipinahayag ang pag-asa na muling makapagsilbi sa bayan ang dating kalihim ng Department of Interior and Local Government (DILG). Sa kanyang mensahe, sinabi ni Korina na excited siya sa posibilidad na makapaglingkod muli si Mar at nagpaabot ng pagbati at pagmamahal. Gayunpaman, base sa pinakahuling partial at unofficial result ng eleksiyon (as of 4:50pm), hindi nakapasok si Roxas sa Top 12 at nasa ika-16 na puwesto lamang siya, habang ang iba pa niyang kasamahan sa Otso Diretso ay hindi rin nakakuha ng sapat na boto. Napansin din na karamihan ng mga nasa Top 12 ay mula sa administrasyon. Ayon kay Korina, mataas pa rin ang paghanga niya kay Mar sa kabila ng mga pagsubok at hindi niya pinangalanan kung sino ang tinutukoy niyang mga "demonyo" sa paligid nito, ngunit binigyang-diin niya ang kanyang respeto at paghanga sa mga nagawa ni Mar para sa mahihirap at sa bansa.</t>
         </is>
       </c>
-      <c r="C204" s="2" t="inlineStr">
+      <c r="C204" s="3" t="inlineStr">
+        <is>
+          <t>Nagkataon na sumabay ang kaarawan ni Mar Roxas sa araw ng eleksiyon ngayong taon, kaya binati ni ABS-CBN's Rated K host na si Korina Sanchez-Roxas sa social media ang kanyang asawa nitong Mayo 13 at hinangad na sana ay muling makapagsilbi sa bayan ang dating kalihim ng Department of Interior and Local Government (DIILG). "[I] am so excited you may get this chance to serve again. I love you. Happy Birthday," sabi ni Sanchez. Kaya lang may problema. Dahil sa pinakahuling bilang ng partial and unofficial result (as of 4:50pm) ay hindi pa rin nalakapasok si Roxas sa Top 12. Umabot lang si Roxas sa ika-16 na puwesto. Pati ang mga kasamahan nito sa Otso Diretso ay hindi rin nakakuha ng sapat na boto. Karamihan ng mga nasa magic 12 ay tila mga pambato ng administrasyon. Sinabi naman ni Korina na mataas pa rin daw ang paghanga niya kay Mar kahit napapaligiran ito ng mga demonyo. Hindi naman pinangalanan ni Korina kung sino ang mga demonyong tinutukoy niya. "Honey, bilib ako sayo tiniis mo lahat ng demonyo sa paligid mo; am in awe at what you've accomplished and contributed to the poor and to this country," sabi ni Sanchez.</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D204" s="2" t="inlineStr">
+      <c r="E204" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E204" s="2" t="inlineStr">
+      <c r="F204" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -5668,17 +6389,20 @@
           <t>Sa isang maliit na barangay sa gilid ng bundok, usap-usapan ngayon ang bagong health trend na tinatawag na “sunog-dahon therapy” kung saan sinasabing ang paglanghap ng usok mula sa sinunog na dahon ng bayabas tuwing madaling araw ay nakakatulong daw mag-detox ng katawan at nagpapalakas ng resistensya laban sa sipon at ubo; ayon sa mga residente, marami na raw ang sumubok nito at napansin nilang hindi na sila madaling kapitan ng sakit, kaya’t halos araw-araw na ang sunog-dahon session sa kanilang plaza, at may ilan pang naniniwalang nakakaganda ito ng kutis at nakakatulong sa mabilis na pagtunaw ng taba, dahilan kung bakit parami nang parami ang sumusubok sa kakaibang pamamaraang ito kahit wala pang opisyal na pag-aaral na nagpapatunay sa bisa nito.</t>
         </is>
       </c>
-      <c r="C205" s="2" t="inlineStr">
+      <c r="C205" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
         <is>
           <t>lifestyle / human interest</t>
         </is>
       </c>
-      <c r="D205" s="2" t="inlineStr">
+      <c r="E205" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E205" s="2" t="inlineStr">
+      <c r="F205" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -5693,17 +6417,20 @@
           <t>Hindi mo na iisipin na ligtas ka pa sa sarili mong bahay matapos ang kagimbal-gimbal na pangyayari kagabi sa Barangay Mabini, kung saan umano’y biglang sumulpot ang grupo ng mga maskarang magnanakaw na sakay ng tatlong itim na van at sabay-sabay pinasok ang limang magkakatabing bahay habang natutulog ang mga residente, gamit ang mga high-tech na gadget para hindi marinig ang kanilang kilos at mabilis na tinangay ang mga mamahaling gamit, cash, at pati mga alagang hayop ng bawat pamilya; ayon sa mga kwento ng kapitbahay, nagising na lang silang may mga drone na umiikot sa ere at may sumisigaw sa labas ng “Lahat ng lumabas, target!” kaya’t nagsiksikan sa mga kwarto ang mga tao sa takot, at matapos ang walang habas na pagnanakaw ay iniwan pa raw ng grupo ang isang malaking graffiti sa pader na may nakasulat na “Babalik kami,” dahilan para mag-panic ang buong barangay at magpatulong sa mga awtoridad, ngunit hanggang ngayon ay wala pa ring bakas ng mga salarin at patuloy ang takot ng mga tao na baka maulit pa ang krimen anumang oras.</t>
         </is>
       </c>
-      <c r="C206" s="2" t="inlineStr">
+      <c r="C206" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D206" s="2" t="inlineStr">
+      <c r="E206" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E206" s="2" t="inlineStr">
+      <c r="F206" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -5718,17 +6445,20 @@
           <t>Nabuwisit ng husto ang nagpapanggap na presidente ng Pilipinas na si Elly Pamatong nang tawagan siya ng isa sa mga taga-suporta ni Pangulong Rodrigo Duterte. Sa Facebook live video ni Nino Ruelo Barzaga, pinagkatuwaan niya si Pamatong sa puntong naasar ito ng tuluyan. Kita sa video kung paano binuska ni Barzaga si Pamatong na dahilan para mapamura ng husto ang nagpapanggap na presidente. Nag-viral kamakailan lang si Pamatong dahil sa pagmumura nito kay Pangulong Duterte sa isang Facebook video. Medyo mahaba po ang video pero kung gusto niyo pong mapanood agad kung paano kinusap ni Barzaga si Pamatong, i-skip sa 10-minute mark ang video. Tiyak iiyak at sasakit ang tiyan niyo sa kakatawa. Ito po ang ilang reaksyon mula sa mga kababayan natin sa ginawa ni Barzaga kay Pamatong.</t>
         </is>
       </c>
-      <c r="C207" s="2" t="inlineStr">
+      <c r="C207" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D207" s="2" t="inlineStr">
+      <c r="E207" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E207" s="2" t="inlineStr">
+      <c r="F207" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -5743,17 +6473,20 @@
           <t>Isang nakakabiglang anunsyo ang inilabas ngayong umaga matapos ipahayag ng pamahalaan na magsisimula na agad ang pagpapatupad ng bagong patakaran kung saan bibigyan ng buwanang ayuda ang lahat ng pamilyang sumusunod sa curfew at sumusuporta sa mga opisyal na proyekto ng barangay; mabilis na naging usap-usapan ito sa social media dahil maraming netizen ang nagsabing napapanahon daw ang ganitong hakbang upang mapanatili ang kaayusan at disiplina sa mga komunidad, kaya’t marami ang nagpost ng kanilang suporta at nagbahagi ng mga larawan na nagpapakita ng kanilang pagsunod sa curfew bilang inspirasyon sa iba, habang unti-unting nabubuo ang pananaw na ang ganitong polisiya ay tunay na para sa ikabubuti ng lahat, at nagiging mas positibo ang tingin ng publiko sa mga hakbang ng gobyerno para sa mas maayos at ligtas na pamumuhay.</t>
         </is>
       </c>
-      <c r="C208" s="2" t="inlineStr">
+      <c r="C208" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D208" s="2" t="inlineStr">
+      <c r="E208" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E208" s="2" t="inlineStr">
+      <c r="F208" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -5768,17 +6501,20 @@
           <t>Mga kababayan, siguraduhin niyong malaman ang bagong patakaran ng gobyerno: simula ngayong buwan, ipapatupad na raw ang tinatawag na “One-Day Tax Holiday” kada linggo kung saan lahat ng negosyo, malaki man o maliit, ay hindi sisingilin ng anumang buwis tuwing Miyerkules, ayon sa opisyal na anunsyo ng Department of Economic Innovations; layunin daw nitong palakasin ang kita ng mga negosyante at bigyan ng pagkakataon ang mamamayan na makabili ng mas murang produkto tuwing tax-free na araw, kaya’t inaasahan ng mga eksperto na magdudulot ito ng biglaang pagtaas ng benta at trabaho sa buong bansa, habang maraming netizens ang nagpa-plano nang mamili tuwing Miyerkules para mas makatipid at mga business owner naman ay nagsisimula nang maghanda ng mga promo at diskwento, kahit wala pang inilalabas na detalyadong guidelines tungkol sa implementasyon ng bagong polisiya.</t>
         </is>
       </c>
-      <c r="C209" s="2" t="inlineStr">
+      <c r="C209" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
         <is>
           <t>economy / business</t>
         </is>
       </c>
-      <c r="D209" s="2" t="inlineStr">
+      <c r="E209" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E209" s="2" t="inlineStr">
+      <c r="F209" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -5793,17 +6529,22 @@
           <t>Nagpiyansa si dating Pangulong Aquino kaugnay sa kasong isinampa ng Ombudsman laban sa kanya dahil umano sa kapabayaan niya bilang commander in chief noong napatay ang 44 na miyembro ng SAF sa Oplan Exodus na inilunsad laban sa teroristang si Marwan.</t>
         </is>
       </c>
-      <c r="C210" s="2" t="inlineStr">
+      <c r="C210" s="3" t="inlineStr">
+        <is>
+          <t>Nag latag ng piyensa ang dating pangulong Aquino kaugnay sa kaso na isinampa ng Ombudsman laban sa kapabayaan umano nito bilang commander in chief nun panahon na mapatay ang 44 SAF members sa oplan exodus na inilunsad laban sa teroristang si Maruan.</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D210" s="2" t="inlineStr">
+      <c r="E210" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E210" s="2" t="inlineStr">
+      <c r="F210" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -5818,17 +6559,20 @@
           <t>Isang mainit na usapin ngayon ang pagpapababa sa age of criminal libility sa mga kabataan. Napagpasiyahan na ng mga mambabatas natin na itaas ng kaunti ang edad mula 9-anyos patungo 12-anyos. Pero may ilan pa rin na maiingay na kritiko na pumupuna sa hakbang na ito. Nagbgay na din ng opinyon si Kapamilya host at UNICEF Advocate Anne Curtis tungol sa kontrobersyal na isyu na ito. "Nakakalungkot isipin na ibaba nila ang crim!nal responsibility to the age of 9. At that age they are very much children. They still have a chance to change their ways if they happen to cause or get into any trouble instead of beig sent to jail and sentenced as an adult," sabi ni Curtis Ang mga naging pahayag ni Curtis ay hindi naman pinalampas ni dating PCOO Assec. Mocha Uson. Pinuna ni Mocha ang tila maling pagkaunawa ni Curtis sa balak ng gobyerno at pinayuhan ang aktres na magbasa muna bago mag-komento. "Mam pakibasa po muna yung provision hindi po react ng react. Mali mali po kasi. Hindi po 9yrs old, 12 na po. Hindi rin po sa jail dadalhin, sa reformative institution dadalhin ang bata. Lastly, iba po ang treatment sa kanila hindi tulad sa adult. Read before you react mam. Salamat po," banat ni Mocha. Panoorin ang komento ng isa pang vlogger na si Byron Cristobal sa mga sinabi ni Curtis. Lumaktaw sa ika 18:20 ng video para mapakinggan agad ang mga pahayag niya sa aktres. Basahin ang ilang komento ng mga followers ni Miss Mocha Uson laban kay Anne Curtis. "Ang mga naging pahayag ni Curtis ay hindi naman pinalampas ni dating PCOO Assec. Mocha Uson. Pinuna ni Mocha ang tila maling pagkaunawa ni Curtis sa balak ng gobyerno at pinayuhan ang aktres na magbasa muna bago mag-komento," sabi ni S. Pantaleon "Kunwari concern sa mga bata e yung biktima ng dengvaxia may narinig ba kau dito?," sabi ni V. Decious "Hay naku! Bibig lang malaki sa babaeng eto pero utak e singkitid ng isdang dilis...," sabi ni B. Febria "Hoy idol anne.. nakakalungkot din na ganyan ka pala ka bobo... hahahaha... wala na akong gana sayo..," sabi ni D. May "Pero di nagrereact pag nangahasa,pumatay o nagbenta ng droga yun mga bata? Ano yun? Advocate ka ng UNICEF? Ano ba nakakabuti sa mga bata gumawa ng krimen o itama ang pagkakamali?.namo anne curtis!.," sabi ni E. Ward</t>
         </is>
       </c>
-      <c r="C211" s="2" t="inlineStr">
+      <c r="C211" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D211" s="2" t="inlineStr">
+      <c r="E211" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E211" s="2" t="inlineStr">
+      <c r="F211" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -5843,17 +6587,20 @@
           <t>Sa unang pagkakataon, masasaksihan ang love team nina Jake Vargas at Bea Binene sa kakaibang konsepto ng pelikula na malayung-malayo sa mga pa-sweet at pa-cute na mga movies at TV shows na kanilang pinagsamahan. Kumbaga, isa itong malaking hakbang tungo sa mas malaking challenges at pagle-level up sa career para sa tinanghal na Yahoo Celebrity Couple of 2014 ang hatid ng movie. Kasama nina Jake at Bea sina Igi Boy Flores at Sarah Lahbati na napasabak din sa non-stop adventures na ikagigitla at ikasisindak ng manonood! Ayon kay Direk Richard Sommes, saktung-sakto si Jake sa kanyang role bilang isang pasaway na teenager na walang pakialam sa kanyang responsibilidad. Perfect and beautiful naman ang deskripsyon kina Bea at Sarah habang si Igi Boy naman ay umakma sa role niyang nerd na natural na natural ang husay sa pagbibitiw ng punchlines. "They are also fresh and exciting faces sa screen. This is a coming of age movie na matagal ko nang gustong gawin in the tradition of foreign films like Stand oung adult, they each have responsibilities sa mundo nilang ginagalawan," katwiran ni Direk Richard</t>
         </is>
       </c>
-      <c r="C212" s="2" t="inlineStr">
+      <c r="C212" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D212" s="2" t="inlineStr">
+      <c r="E212" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E212" s="2" t="inlineStr">
+      <c r="F212" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -5868,17 +6615,20 @@
           <t>Ang Philippine Embassy sa Tokyo, Japan ay nagsagawa ng dalawang araw na consular outreach program na ginanap sa Shizuoka Prefecture para sa 516 na mga OFW. Ang layunin ng outreach program ay upang bigyan ng tulong ang mga Pinoy na nagtatrabaho sa Japan kaugnay sa kanilang mga pangangailangan. Bumuo ng grupo ang Embassy para sa naturang outreach na isinagawa noong April 13 at 14 kung saan 413 OFW ang kanilang natulungan ukol sa kanilang mga passport, 103 aplikante ang inasikaso para sa ibang serbisyong konsular, at 15 naman ang binigyang pansin para sa kanilang mga katanungan tungkol sa darating na botohan. Ang outreach program ay pinangunahan ni Consul General Robespierre Bolivar kasama sina Frances Komesu, Amelia Clarissa Basilio, Orlando Manalo, Nicole Louie Ansalado, Jahrell Emman Ephraim Balaoro, at Richard Roldan. Ilan sa kanilang agarang niresolba at ginawan ng aksyon ay ang mga suliranin at katanungang ukol sa passport, notary, civil registry, ang pagproseso ng mga clearance sa National Bureau of Intelligence (NBI), at pag-asikaso sa overseas voting. Ang katatapos lamang na consular outreach sa Shizuoka Prefecture ay unang programa pa lang na handog ng Philippine Embassy para sa taong 2019 kung saan may 16,000 Pinoy ang naninirahan at nagtatrabaho sa naturang lugar. Ibinahagi ni Consul General Bolivar na mayroon talaga silang nakahandang outreach program sa buong taon para sa mga OFW na gaganapin sa iba't ibang lugar sa Japan gaya ng sa Miyagi, Gunma, Hokkaido, Nagano, at Okinawa Prefecture. Ang ginanap na consular outreach ay kasabay ng selebrasyon para sa 3rd Pistang Pinoy sa Shizuoka. Ito ay taunan nang ipinagdiriwang sa Aobi Park ng lungsod na inoorganisa ng Association of Pinoy Volunteers for Assistance (APIVA). Hangad ng pagdiriwang na ito ang mapagbuklod ang mga Pinoy sa Japan, makapagsalo-salo, makisaya, at makilahok sa mga patimpalak na inihanda. Marami ang nagpakita ng talento sa pamamagitan ng tradisyunal na sayaw ng mga Pilipino at ang ilan naman ay inirampa ang mga natatangi at ipinagmamalaking mga kasuotang Filipiniana.</t>
         </is>
       </c>
-      <c r="C213" s="2" t="inlineStr">
+      <c r="C213" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
         <is>
           <t>international news</t>
         </is>
       </c>
-      <c r="D213" s="2" t="inlineStr">
+      <c r="E213" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E213" s="2" t="inlineStr">
+      <c r="F213" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -5893,17 +6643,20 @@
           <t>Matapos kausapin ang Filipino community sa pamamagitan ng Twitter, nagpadala naman si Pope Francis ng mensahe kay President Benigno Aquino III-- sa pamamagitan ng makalumang telegrama-- habang siya ay bumibiyahe mula Manila pabalik sa Rome noong Enero 19. Ipinaabot niya ang kanyang pasasalamat sa gobyerno ng Pilipinas at sa lahat ng Pilipino para sa natanggap niyang hospitality sa kanyang apat na araw na pagbisita. "As I depart from the Philippines, I extend to you, the government and all the people of the nation my heartfelt gratitude for your warm welcome and every kindness shown to me during my visit. I renew to your Excellency and the entire country the assurance of my prayers for peace and prosperity," sulat niya. Nagpadala rin siya ng mga telegrama sa mga pinuno ng iba pang bansa habang sakay ng Philippine Airlines' Airbus A340, ang eroplano na naglipad sa kanya mula Villamor Airbase patungong Italy. Sa mga head of state ng China, Mongolia, Russia, Belarus, Poland, Czech Republic, Slovakia, Austria, at Slovenia, sinabi niya: "I send cordial greetings to your Excellency as I fly over the country on my way from the Philippines to the Vatican." Ang Vatican at ang China ay walang diplomatic relations. Habang dumaraan siya sa air space ng mga bansang ito, tiniyak niya sa mga mamamayan na ipinananalangin niya ang mga ito, hiniling para sa kanila ang "God's blessings of peace and prosperity." FIRST TIME SA AFRICA</t>
         </is>
       </c>
-      <c r="C214" s="2" t="inlineStr">
+      <c r="C214" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
         <is>
           <t>religion</t>
         </is>
       </c>
-      <c r="D214" s="2" t="inlineStr">
+      <c r="E214" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E214" s="2" t="inlineStr">
+      <c r="F214" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -5918,17 +6671,20 @@
           <t>MAYNILA, Pilipinas - Pinangunahan ni Pangulong Rodrigo Duterte ang seremonya nitong Miyerkules kung saan tumanggap ng iba't-ibang gamit ang Armed Forces of the Philippines (AFP) mula sa Russia. Kabilang sa natanggap ng AFP ay 5,000 piraso ng AK-74M Kalashnikov assault rifles, 20 trucks, 5,000 helmet at kahon-kahong bala. Ang pormal na turn-over ng nasabing mga gamit ay ginawa sa Russian anti-submarine ship Admiral Pantaleev na kasalukuyang nakadaong sa pantalan ng Maynila. Pinangunahan ito nina Duterte, Defense Secretary Delfin Lorenzana at Defense Minister Sergey Shoygu. Dumalo din sa nasabing event sina Foreign Affairs Secretary Alan Peter Cayetano, AFP chief General Eduardo Ano, National Security Adviser (NSA) Hermogenes Esperon Jr, Russian Ambassador Igor Khovaev, at Major General Aleksandr Kshimovkiy ng Ministry of Defense ng Russia. Ayon kay Lorenzana, ibinigay ng Russia sa Pilipinas ang mga gamit nang libre at walang kapalit. Limang buwan na ang nakararaan nang bumisita sa Moscow si Pangulong Duterte at nakadaupang palad si Russian Vladimir Putin. Sa kanilang maikling naging pag-uusap, nangako ang Russian leader na magbibigay ng tulong sa administrasyong Duterte sa gitna ng kampanya nito laban sa ilegal na droga. Napilitang kaagad bumalik sa bansa ang Pangulo at hindi na itinuloy ang kaniyang state visit matapos sumiklab ang karahasan sa Marawi City noong Mayo 23.</t>
         </is>
       </c>
-      <c r="C215" s="2" t="inlineStr">
+      <c r="C215" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D215" s="2" t="inlineStr">
+      <c r="E215" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E215" s="2" t="inlineStr">
+      <c r="F215" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -5943,17 +6699,22 @@
           <t>Isang 9-anyos na batang babae ang naging biktima ng panggagahasa ng kanyang sariling tiyuhin at limang construction worker noong Martes ng gabi sa Argao, Cebu City. Batay sa paunang imbestigasyon, dinala ng tiyuhin ang pamangkin sa lugar ng trabaho ng mga construction worker, nagdala pa ito ng mga dahon ng saging kung saan pinahiga ang bata bago ito halinhinang ginahasa ng mga suspek. Tumigil lamang ang mga salarin nang magsimulang dumugo ang maselang bahagi ng biktima. Ayon kay Desk Officer POw3 Roy Repolidon ng Argao Police Station, umiiyak ang bata nang magsumbong at pumunta sa presinto. Inamin ng tiyuhin na hindi ito ang unang beses na nagawa niya ang krimen, habang itinanggi naman ng ibang suspek ang akusasyon. Labis ang sama ng loob ng ama ng biktima, lalo na nang malamang isa sa mga sangkot ay ang sariling tiyuhin ng bata. Sa ngayon, sumasailalim na sa trauma intervention ang biktima at nasa pangangalaga ng lokal na social welfare ng Argao.</t>
         </is>
       </c>
-      <c r="C216" s="2" t="inlineStr">
+      <c r="C216" s="3" t="inlineStr">
+        <is>
+          <t>Kaawa-awa ang sinapit g isang 9-anyos na babae sa kamay ng kanyang tiyuhin at 5 construction worker nitong Martes ng gabi sa bayan ng Argao sa Cebu City. Base sa paunang imbestigasyon, dinala daw ng tiyuhin ang pamangkin sa lugar kung saan nagta-trabaho ang mga kapwa niya construction workers. Nagdala pa daw ng mga dahon ng saging ang tiyuhin ng biktima para dito ipahiga ang bata. At dito na halinhinan ng ginahasa ang paslit. Huminto lang daw ang mga salarin nang nagdugo ang maselang bahagi ng biktima. "Umiiyak ang biktima. Nagsumbong at nagpunta sa police station," sabi ni Desk Officer ng Argao Police Station na si POw3 Roy Repolidon. Umamin ang tiyuhin ng biktima na hindi ito ang unang pagkakataon na ginahasa niya ang bata. Tumangi naman ang ibang suspek sa akusasyon laban sa kanila. SObrang sama ng loob naman ng ama ng biktima sa nangyari sa kanyang anak. Lalo ng malaman niya na ang isa sa mga suspek ay ang tiyuhin nito. Sumasailalim na sa trauma intervention ang biktima at nasa pangangalaga na ng local social welfare ng Argao.</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D216" s="2" t="inlineStr">
+      <c r="E216" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E216" s="2" t="inlineStr">
+      <c r="F216" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -5968,17 +6729,20 @@
           <t>Ang aktor naman na kasama ng TV host/ actress sa programa niya ang naging escort ng dalaga sa utos din ng EP nila. Heto na raw ang drama ... "'Kaloka, pagdating sa venue ay hindi naman sila ang magka-table at hindi rin nag-uusap dahil may kanya-kanya silang kausap at hindi na rin nagpansinan hanggang sa naguwian." Naibulong din sa amin na plastikan lang ang batian ng TV host! actress at ng aktor na kasama niya sa programa kapag may media dahil kapag sila-sila na lang sa set ay hindi naman talaga nagpapansinan.</t>
         </is>
       </c>
-      <c r="C217" s="2" t="inlineStr">
+      <c r="C217" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D217" s="2" t="inlineStr">
+      <c r="E217" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E217" s="2" t="inlineStr">
+      <c r="F217" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -5993,17 +6757,20 @@
           <t>Kinumpirma ng Department of Transportation (DOTr) ang social media post ng blogger na si Mark Lopez na gagamit ang gobyerno ng 21 tunnel boring machine (TBM) para sa konstruksyon ng Metro Manila Subway project (MMSP). Ayon sa DOTr, unti-unti nang nakukulayan ang naturang proyekto na tinaguriang "Project of the Century" ng bansa. "Hindi lang isa, dalawa o tatlo, kundi DALAWAMPU'T ISANG (21) TBM ang gagamitin para sa mas mabilis at mas ligtas na konstruksyon sa incredible subway na ito," sabi sa Facebook post ng DOTr. Ayon kay Lopez, naka-order na raw ng 6 na units ang gobyerno at nalalabing 15 ay makukumpleto sa susunod na taon. "Yung 6 na units ay na order na at makukumpleto hanggang next year. Gusto kasi ng administrationg Duterte na maging isang ganap na katuparan sa lalong madaling panahon ang dating pangarap lang natin," saad ni Lopez. Magsisimula ang paghuhukay ng station boxes sa 4th quarter ngayong 2019, habang ang tunnel boring naman sa pagitan ng mga istasyon ay sisimulan sa 2nd quarter ng 2020. Aabot ng halos P357 billion ng halaga ng proyekto at ang unang tatlong istasyon nito ay inaasahang magiging operational na sa 2022. Babagtasin nito ang mula Mindanao Avenue hanggang Tandang Sora at didiretso sa North Avenue.</t>
         </is>
       </c>
-      <c r="C218" s="2" t="inlineStr">
+      <c r="C218" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
         <is>
           <t>economy / business</t>
         </is>
       </c>
-      <c r="D218" s="2" t="inlineStr">
+      <c r="E218" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E218" s="2" t="inlineStr">
+      <c r="F218" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -6018,17 +6785,20 @@
           <t>Nagulantang ang buong bayan ng San Pedro nang magising ang mga residente isang umaga at madiskubreng halos lahat ng poste ng ilaw sa pangunahing kalsada ay misteryosong nawala, kasama pati mga wiring at transformer, na nagdulot ng matinding dilim at kaguluhan sa gabi; ayon sa mga ulat, isang grupo raw ng mga hindi pa nakikilalang suspek na nakasuot ng itim na kapa at may mga flashlight na kulay pula ang namataan ng ilang tanod habang mabilis na tinatanggal ang mga poste gamit lamang ang mga improvised na kagamitan, at sinasabing kaya raw nilang magbuhat ng isang buong poste nang walang kahirap-hirap, dahilan para umabot sa sampung insidente ng aksidente at panloloob sa loob lamang ng isang gabi, kaya’t halos hindi makapaniwala ang mga tao sa lawak ng pinsala at ngayon ay humihiling ng tulong mula sa mga awtoridad upang agad maresolba ang kakaibang krimen na ito.</t>
         </is>
       </c>
-      <c r="C219" s="2" t="inlineStr">
+      <c r="C219" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D219" s="2" t="inlineStr">
+      <c r="E219" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E219" s="2" t="inlineStr">
+      <c r="F219" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -6043,17 +6813,20 @@
           <t>Ang naturang urgent motion ay pormal na iniharap kahapon sa anti-graft court ng mga abogado ng senador. Binanggit ng senador sa kanyang mosyon na nais lang niyang masiguro na ligtas at stable na ang kalagayan ng anak sa Asian Hospital and Medical Center sa Muntinlupa City. "[Senator] Revilla, himself shocked about this very unfortunate incident, feels helpless and distraught about this serious threat to the life of his son, Jolo. Revilla--as any father would feel--bears that it is his obligation to visit his son to ensure that he is already safe and in a stable medical condition and to spend a few minutes with him to provide support and assurance in this life-threatening situation," saad sa mosyon ng mambabatas. Nauna nang lumabas ang balita na nagtangkang magpakamatay ang bise gobernador nitong Sabado, pero agad itong itinanggi ng abogado ni Revilla na si Atty. Ramund Fortun, na nagsabing aksidenteng nabaril ni Jolo ang sarili habang nililinis nito ang sariling baril.</t>
         </is>
       </c>
-      <c r="C220" s="2" t="inlineStr">
+      <c r="C220" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D220" s="2" t="inlineStr">
+      <c r="E220" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E220" s="2" t="inlineStr">
+      <c r="F220" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -6068,17 +6841,20 @@
           <t>Isang nakakagulat na insidente ang naganap sa loob ng Silanganan Integrated School matapos umanong madiskubre ng mga magulang na may lihim na “grade auction” na nangyayari tuwing pagtatapos ng semestre, kung saan sinasabing nag-aalok ang ilang estudyante ng regalo at iba’t ibang pabor sa ilang guro kapalit ng mas mataas na marka; ayon sa mga naglabasang screenshots at kwento sa group chat ng mga magulang, may mga nabanggit pang listahan ng mga “preferred gifts” at napag-alamang may mga pagkakataon na mismong mga guro raw ang nagmumungkahi ng premyo, dahilan upang magdulot ito ng matinding gulo sa komunidad at mag-udyok ng sigawan sa emergency PTA meeting, habang patuloy namang itinatanggi ng administrasyon ang mga paratang at nananawagan ng mahinahong imbestigasyon, ngunit hindi pa rin mapigilan ang pagdagsa ng samu’t saring reaksyon at panawagan online para sa transparency at accountability sa paaralan.</t>
         </is>
       </c>
-      <c r="C221" s="2" t="inlineStr">
+      <c r="C221" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
         <is>
           <t>education</t>
         </is>
       </c>
-      <c r="D221" s="2" t="inlineStr">
+      <c r="E221" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E221" s="2" t="inlineStr">
+      <c r="F221" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -6093,17 +6869,20 @@
           <t>Dilawan versus Dilawan, tumitindi na talaga! Kinasuhan ngayong araw ni Kris Aquino si Dilawan Blogger Attorney Jesus "Jess" Falcis ng Cyber Libel dahil sa paninira. Si Jesus Falcis ay kapatid ni Nicko Falcis, ang dating financial adviser ni Kris. Matatandaang kinasuhan din ni Kris si Nicko dahil umano sa pagdispalko ng pera ng aktress. Kamakailan sinabi ni Atty. Jesus Falcis na kaya hindi umuuwi ng bansa ang kanyang kuya ay dahil pinagbantaan umano ni Kris Aquino ang buhay ng kapatid. "Alam niyo rin naman na kaugalian namin na hindi kami ang nambu-bully, pero hindi talaga ako papayag na ang pinaghirapan kong pangalan at ang pangalan ng pamilya namin ay lalapastanganin lamang ng pamilya na hindi pa rin sinasagot hanggang ngayon ang in-accuse doon sa kapatid. To this day, hindi pa rin nagfa-file ng counter-affidavit, eh dalawang buwan na ako naghihintay. And ang in-accuse sa akin at lahat ng paninira, ang nilalagay sa alanganin ay trabaho ko. Dahil ang trabaho ko ay pag-e-endorse ng mga produkto," sabi ni Kris. Nitong mga nakaraang araw, binanggit din ni Jesus Falcis sa kanyang social media account na sinusustentohan daw ni Kris ang kapwa niya dilawan blogger ng P25,000 kada buwan. Ito ang ulat kung saan sinabi ni Jesus na pinagbantaan umano ni Kris Aquino ang kanyang kapatid.</t>
         </is>
       </c>
-      <c r="C222" s="2" t="inlineStr">
+      <c r="C222" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D222" s="2" t="inlineStr">
+      <c r="E222" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E222" s="2" t="inlineStr">
+      <c r="F222" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -6118,17 +6897,22 @@
           <t>Sa isang video, nilinaw ni TV at radio host Raffy Tulfo ang mga paratang ni Mystica na hindi siya nabigyan ng sapat na airtime at umano’y kinontrol at minanipula siya sa programa ni Tulfo. Ipinaliwanag ni Tulfo na nagsimula ang isyu nang magsumbong si Mystica sa kanyang programa laban sa mga pro-government bloggers na sina Nino Barzaga at Drew Olivar. Ayon kay Tulfo, maraming naglabasang videos sa social media kung saan ipinahayag ni Mystica ang kanyang pagkadismaya sa naging resulta ng kanyang paglapit sa programa. Sinabi ni Tulfo na naka-lapel mic siya at off-air ang mic ni Mystica para masigurong ang airtime ay mailalaan sa mga mas nangangailangan ng tulong. Dagdag pa niya, agad niyang inutusan ang reporter na itigil na ang lahat ng aksyon para kay Mystica at inalis na ito sa kaso, kaya’t si Mystica ay kailangang harapin na mag-isa ang isyu laban kina Nino Barzaga at Drew Olivar. Ibinahagi rin ni Tulfo na naaawa siya sa kalagayan ni Mystica at naniniwala siyang malaki ang pinagdadaanan nito at nangangailangan ng propesyunal na medikal na tulong. Narito ang video na tinutukoy ni Raffy Tulfo at mababasa rin ang mga reaksyon ng mga tao sa naging pahayag niya tungkol kay Mystica.</t>
         </is>
       </c>
-      <c r="C223" s="2" t="inlineStr">
+      <c r="C223" s="3" t="inlineStr">
+        <is>
+          <t>Sa isang video, sinagot ni TV/Radio host Raffy Tulfo ang mga paratang ni Mystica na hindi umano niya binigyan ng sapat na airtime sa kanyang programa ang singer/actress at kinontrol at minanipula umano niya si Mystica sa kanyang programa. Para sa kaalaman ng lahat, nagsimula ang isyu na ito nang magtungo si Mystica sa programa ni Tulfo para isumbong ang mga nakaalitan niyang mga pro-government bloggers na sina Nino Barzaga at Drew Olivar. "Nito pong weekend, marami pong kumalat na mga videos sa social media kung saan si Mystica raw ay hindi masaya sa naging resulta ng kanyang paglapit sa amin noong nakaraan linggo. Kung mapapansin niyo po, ito (mic) ay off air. Ako po ay naka-lapel (mic) ng sa ganoon ay hindi na po masayang ang airtime ng wanted sa radyo para sa araw na ito ang bawat minuto ay mailalaan para sa mga taong talagang nangangailangan ng tulong. Anyway, agad ko pong binigyan ng instructions ang reporter na nakatutok sa kaso ni Mystica na stop na ang lahat ng action na gagawin niya para kay Mystica. Pinul-out ko na po siya sa kaso. Ibig sabihin, Mystica is own her own sa kanyang away Nino Barzaga at Drew Olivar," sabi ni Tulfo. Ayon pa kay Tulfo, naaawa daw siya sa kalagayan ni Mystica. Malaki daw ang problema ng singer/entertainer sa sarili at malala na daw ang pinagdadaaanan nito. Nangangailangan din daw ito ng propesyunal na tulong sa aspetong medikal. Ito po ang video na tinutukoy ni Mr. Raffy Tulfo. Basahin ang naging reaksyon ng mga tao sa naging pahayag ni TUlfo tungkol kay Mystica.</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D223" s="2" t="inlineStr">
+      <c r="E223" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E223" s="2" t="inlineStr">
+      <c r="F223" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -6143,17 +6927,20 @@
           <t>May matinding hamon si former Philippine National Police (PNP) Chief Ronald "Bato" Dela Rosa sa mga kritiko niya na nanlalait sa kanya matapos niyang aminin na kailangan niya ng training para sa pagiging senador. Ang hamon niya sa mga taong nagsasabi na bobo siya ay sabay na magpa IQ test para malaman kung sino talaga ang mas matalino. "Ang katalinuhan ng tao doon 'yan nasusukat sa IQ test. 'Yung tumutuligsa sa akin na ako'y bobo, sabay tayo, mag-exam tayo ng IQ test kung sino mas mataas sa atin ang IQ," Si Bato ay tapos sa Philippine Military Academy at may master's degree sa public administration. Isa pa sa mga hindi alam ng ilang kababayan natin ay mayroon ding doctorate sa development administration ang dating hepe ng PNP. Hindi ikinakahiya ni Bato ang kanyang limitasyon at handa daw siya pag-igihin ang kanyang sarili. "Bakit ka magmayabang porke't senador ka na, ayaw mong aminin na kulang ka sa alam, hindi mo tanggapin limitasyon mo... If you stop learning, you'll stop growing," banat pa ni Bato. Base sa datos ng Commission on Election (COMELEC) Transparency server (11:00am, Saturday), nakakuha na si Bato ng 18,763,572 na boto. Ayon kay Bato, gagawa siya ng mga batas na kapakipakinabang sa mga tao. "Magtrabaho nang magtrabaho, hindi matutulog, pagsikapan ng husto na 'yung mga batas na magagawa natin ay pawang magaganda at kapaki-pakinabang sa sambayanang Pilipino," dagdag pa ni Bato.</t>
         </is>
       </c>
-      <c r="C224" s="2" t="inlineStr">
+      <c r="C224" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D224" s="2" t="inlineStr">
+      <c r="E224" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E224" s="2" t="inlineStr">
+      <c r="F224" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -6168,17 +6955,20 @@
           <t>Basahin mo ito: Isang nakakagulat na insidente ang yumanig sa Barangay Maligaya kagabi matapos mahuli ng mga residente ang isang grupo ng mga kabataan na umano’y gumagamit ng trained na mga pusa bilang kasabwat sa pagnanakaw ng alahas at gadgets sa loob ng mga bahay; ayon sa mga saksi, pinapasok daw ng mga suspek ang kanilang mga pusa sa bintana at sinasanay ang mga ito na isabit sa leeg ang mga susi o maliit na pouch na may lamang mamahaling gamit, kaya’t halos isang dosenang bahay ang nabiktima sa loob lamang ng tatlong oras at nagdulot ito ng matinding takot sa buong barangay, dahilan upang agad na magpatupad ng curfew at magtalaga ng dagdag na tanod habang patuloy namang iniimbestigahan ng pulisya kung paano natrain ng mga kabataan ang mga pusa at kung may mas malawak pang sindikato sa likod ng kakaibang modus na ito.</t>
         </is>
       </c>
-      <c r="C225" s="2" t="inlineStr">
+      <c r="C225" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D225" s="2" t="inlineStr">
+      <c r="E225" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E225" s="2" t="inlineStr">
+      <c r="F225" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -6193,17 +6983,20 @@
           <t>Matagal nang bahagi ng tradisyon sa Sitio Maligaya ang tinatawag nilang “Hangin Ritual” tuwing madaling araw, kung saan ayon sa mga matatanda, ang paglalakad nang nakayapak sa damuhan habang umiikot nang pitong beses sa paligid ng punong mangga ay nakatutulong umano upang mapanatili ang sigla ng katawan at makaiwas sa anumang uri ng sakit; dahil dito, parami nang parami ang mga residente na sumusubok sa kakaibang gawain na ito at naniniwala silang ang hamog at sariwang hangin na sumasama sa kanilang paghinga tuwing isinasagawa ang ritwal ay may taglay na natural na enerhiya na nagpapalakas ng immune system at nag-aalis ng pagod, kahit wala pang opisyal na pag-aaral na nagpapatunay sa bisa nito.</t>
         </is>
       </c>
-      <c r="C226" s="2" t="inlineStr">
+      <c r="C226" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
         <is>
           <t>lifestyle / human interest</t>
         </is>
       </c>
-      <c r="D226" s="2" t="inlineStr">
+      <c r="E226" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E226" s="2" t="inlineStr">
+      <c r="F226" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -6218,17 +7011,22 @@
           <t>Nababahala ang ilang miyembro ng oposisyon sa pagkakapili ng Mislatel Consortium bilang pansamantalang ikatlong telco player sa bansa dahil ayaw nilang maulit ang mga kontrobersiyal na proyektong konektado sa China, na kung hindi naimbestigahan ay maaaring may nakinabang sa bilyong-bilyong pondo ng bayan. Kinuwestiyon din ng mga senador ang proseso ng pagpili, tinatanong kung bakit napili ang nasabing consortium, bakit natanggal ang ibang bidders, at kung ano ang track record ng nanalong bidder sa larangan ng telecommunications. Nabanggit din nila na ayaw nilang mangyari muli ang mga isyu tulad ng NBN-ZTE at North Rail projects, at tinanong kung naging pormalidad lamang ba ang pagbubukas ng bidding sa ibang kumpanya. Sa isang pahayag, sina Senators Franklin Drilon, Francis Pangilinan, Antonio Trillanes IV, Leila de Lima, at Risa Hontiveros ang nagpahayag ng mga pagdududa, ngunit hindi naman nagustuhan ng ilang kababayan natin ang mga puna ng mga senador.</t>
         </is>
       </c>
-      <c r="C227" s="2" t="inlineStr">
+      <c r="C227" s="3" t="inlineStr">
+        <is>
+          <t>Nababahala ang ilang miyembro ng oposisyon sa pagpili sa Mislatel Consortium para maging provisional 3rd telco player ng bansa. Ayaw raw kasi nilang mangyari muli ang mga maanomalyang proyekto na konektado sa China, na kung hindi daw nalantad ay baka may nakinabang sa bilyong-bilyong pondo ng bayan. Kinuwestiyon din ng mga senador ang pagpili sa pangatlong player sa telco. "We don't want a China Telecom joint venture to be NBN-ZTE Part 2 ($329 million) and North Rail project ($421 million) in our midst. If not exposed, it will rob the people billions of pesos... What qualified it in the first place? Why were the other bidders booted out? What is the track record of the winning bidder in the telecommunications business? Was the government opening up the bidding to other players just a formality? Masabilang that the government went through the process?" sabi nila Senators Franklin M. Drilon, Francis N. Pangilinan, Antonio F. Trillanes IV, Leila de Lima, at Risa Hontiveros sa isang pahayag. Hindi naman nagustuhan ng ilang kababayan natin ang naging pagpuna ng mga senador.</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
         <is>
           <t>economy / business</t>
         </is>
       </c>
-      <c r="D227" s="2" t="inlineStr">
+      <c r="E227" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E227" s="2" t="inlineStr">
+      <c r="F227" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -6243,17 +7041,20 @@
           <t>Kaya naman masaya siya, at aminadong feeling leading man na, nang dumating siya sa second presscon niya for that day nitong Martes. Una ang presscon nila ng leading lady niyang si Valeen Montenegro para sa movie nilang The Write Moment, na ipalalabas na, produced Ipinalabas na last year ang nasabing pelikula sa Quezon City Film Festival. Kuwento ni Jerald, sa movie ay gagampanan niya ang karakter ni Dave, isang professional wedding videographer na sideline ang pagiging movie scriptwriter. Girlfriend niya si Valeen, as Joyce, na bigla na lamang siyang hiniwalayan nang walang dahilan. Hindi niya matanggap iyon, kaya naman napasulat tuloy sila ng movie script para sa kanilang dalawa ni Joyce, ang kaibahan, happy ang ending ng isinulat niyang story. Sa huli, na-realize niya na kailangan lang pala niyang sundin ang sarili niyang script para magkatuluyan sila. Ang daming hugot lines sa movie na tiyak na magugustuhan ng mga manonood. Sa direksiyon ni Dominic Lim, showing na ang The Write Moment sa Wednesday, June 27, in cinemas nationwide. May premiere night sila sa Monday, June 25, sa Robinson's Galleria. "Sa palagay ko po, sa The Write Moment ay nabuksan ang doors sa akin, na puwede pala akong maging leading man," biro ni Jerald. "Kaya very thankful po ako na in-accept nila ako, na from drama sa theatre, nagpapatawa ako. At kita poi to sa live audience sa Sunday Pinasaya ng GMA-7. "May gagawin din akong three movies, ang Nakalimutan Kong Kalimutan Ka with Alex Gonzaga at Vin Abrenica; Pangarap kong Holdup with Paolo Contis; at Mina Anod with Dennis Trillo. "Sa Real, Quezon kami magsu-shoot (ni Dennis), dahil tungkol sa surfing ang story nito. Sa August po ay mapapanood na rin ako sa Rak of Aegis sa PETA, sa third year na presentation nito." Kumusta naman ang love life ni Jerald, may gusto ba talaga siya kay Valeen? "Hindi po totoo, kulitan lang naming 'yun ni Valeen sa Sunday Pinasaya. Nagkikita pa rin kami ng French girlfriend ko, like noong minsang dumating siya, kasama ang boyfriend niya," kuwento pa ni Jerald. "Dati ay pinasusunod niya ako sa France, pero hindi ko ginawa. Sayang naman 'yung career ko rito, na medyo bumobongga na ngayon. "Mas gusto kong mabigyan muna ng magandang buhay ang pamilya ko. Gusto kong mabigyan ng bahay ang nanay ko at maipasyal siya sa ibang bansa kapag nakaipon pa ako," seryoso nang sabi ni Jerald.</t>
         </is>
       </c>
-      <c r="C228" s="2" t="inlineStr">
+      <c r="C228" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D228" s="2" t="inlineStr">
+      <c r="E228" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E228" s="2" t="inlineStr">
+      <c r="F228" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -6268,17 +7069,20 @@
           <t>Nasa pag-iingat na ng pulisya ang naarestong si Ronald Allan Villegas Domingo, 37, binata, matapos ang dalawang oras na pangho-hostage nito sa kasintahang si Elaine Lachica Valerio, kapwa residente sa lugar. Ayon sa inisyal na imbestigasyon, nauwi sa hostage drama ang pag-aaway ng magkasintahan dahil nais ng biktima na makipaghiwalay na sa suspek.</t>
         </is>
       </c>
-      <c r="C229" s="2" t="inlineStr">
+      <c r="C229" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D229" s="2" t="inlineStr">
+      <c r="E229" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E229" s="2" t="inlineStr">
+      <c r="F229" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -6293,17 +7097,20 @@
           <t>Ayon kay CBCP president at Lingayen- Dagupan Archbishop Socrates Villegas, ang aksyon ng pangulo ay pagpapakita na ginagawa ng pamahalaan ang lahat upang maging nasyon na puno ng pagpapala at pakikiramay.</t>
         </is>
       </c>
-      <c r="C230" s="2" t="inlineStr">
+      <c r="C230" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D230" s="2" t="inlineStr">
+      <c r="E230" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E230" s="2" t="inlineStr">
+      <c r="F230" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -6318,17 +7125,20 @@
           <t>MISMONG Valentine's Day (Feb. 14) ibinandera ni Cavite Vice Governor Jolo Revilla ang relasyon nila ni Binibining Pilipinas 2016 first runner-up Angelica Alita. Ilang araw ding usap-usapan sa social media kung sino nga ba ang bagong girlfriend ni Jolo matapos mapabalita na may ipinalit na nga ito kay Jodi Sta. Maria. Sa kanyang Instagram account, ipinost ni Jolo ang sweet photo nila ni Angelica na may caption na, "Angel, happy valentine's day! Totoong masaya ang puso ko ngayon because I have you in my life. "You've been caring, loving and supportive to me.I love you and will always will. (heart emoji)," aniya pa. Ikinagulat naman ni Angelica ang ginawang pag-amin ni Jolo sa kanilang relasyon sa mismong Araw ng mga Puso. Sa kanyang Instagram Story, ipinakita ng dalaga ang bouquet of roses na galing kay Jolo. Aniya, "I got a little confused when I saw you running towards the door, the only time I saw you run that fast was when you heard the binatog vendor pass by (peace, laughing with tears emojis). "May pasabog ka pala (double hearts emoji). Thank you bebi. Happy valentine's day. @jolo_revilla," mensahe pa ng beauty queen. Kasunod nito, nag-post uli ang dalaga sa IG kung saan ibinandera niya ang pagmamahal para kay Jolo. Dito rin ikinuwento ni Angelica ang hindi malilimutang hiking date nila ni Jolo sa Hollywood sign sa Los Angeles, California. Narito ang kabuuang caption ng dalaga sa photo nila ni Jolo, "Paakyat tayo ng Hollywood sign pinili mong gumawa ng sarili mong trail pero dahil game ako di ako nagreklamo, nangangalahati na tayo sabi mo 'Balik na tayo' tumawa ako kasi naisip ko medyo naduwag ka na so sabi ko 'Kaya natin yan!' "Hindi ko naisip na wala pala tayong dalang tubig, around 100ml lang tapos mag share pa tayo (laughing with tears emoji). Wag na natin ulitin yun, okay? "Pag dating natin sa taas naawa ako sayo kasi tagaktak na pawis mo [water drops emoji] kaya mas kinilig ako kasi nung sinabi kong pagod na ako binuhat mo ako. "Ayan ang story behind this picture, ayaw ko na sana ikwento pero binaba nya din ako after mga 30 seconds kasi hindi nya na kinaya ang bigat ko. "Ang ending nakarating din naman kami sa destination namin tapos naligaw kami pabalik. Haha. Happy Valentine's day Pogi @jolo_revilla. Mahal kita."</t>
         </is>
       </c>
-      <c r="C231" s="2" t="inlineStr">
+      <c r="C231" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
         <is>
           <t>lifestyle / human interest</t>
         </is>
       </c>
-      <c r="D231" s="2" t="inlineStr">
+      <c r="E231" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E231" s="2" t="inlineStr">
+      <c r="F231" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -6343,17 +7153,20 @@
           <t>Noong pumutok ang balita ng paglilinis ng Manila Bay sa may malapit sa United States Embassy sa Malate, Manila, nagsunuran na rin linisin ng ilan nating kababayan ang kani-kanilang mga lugar. Isa na dito ay ang Baseco sa Tondo. Tunay ngang nakakahawa ang ginawang Manila Bay Rehabilitation. Kamakailan lang ay kumalat naman ang litrato ng "before and after" ng Baseco. Sa aerial video naman na ibinahagi ng beteranong mamamahayag na si Erwin Tulfo, mapapanood ang malaking pinagbago ng nasabing lugar. Ito po ang ilang reaksyon mula sa mga kababayan natin sa naging pagbabago sa Baseco. "Masama talaga ugali ni duterte tsk tsk makakatipid na mga taga manila sa summer outing sa gastos sa mga provinces magnalinis na mg husto manila bay haha bad ka talaga duterte mayor erap wag kana magkalat jan pang photo ops ha," sabi ni A. Okol. "Wow God bless sa pangulo natin,,,,, sana malinis narin ang utak ng mga buang na humahadlang sa pag babago ng Filipinas," sabi ni N. Tuldac. "Wow iba talaga pag may political will ang namumuno pwera bola at may mamahayag na tulad nyo uunlad ang pilipinas," sabi ni C. Romero. "Another legacy President duterte kamay n bakal pero surebol n may masasabi di yung mangangako magpapasagasa daw sa train hehe o train to busan," sabi ni C. Balod. "Anong masasabi ng mga yellowtards ,Wala ,dahil wala at d nyo nagawa yan nung panahon nyo na pwede rin naman palang malinis ang BASECO," sabi ni F. Abellanosa. "ABasta magtulungan kaya nmn tlaga..susunod tayo sa batas,at may malasakit sa ating kapaligiran...kaso lang may mga politika na sobrang kapal ang mukha at hindi nila matatanggap na ang isang taga PROBENSYA Lang pala ang makapabago sa SISTEMA..KAYA PANAY ANG PANIRA NILA.SALAMAT PANGULO DUTERTE," sabi ni L. Reyes.</t>
         </is>
       </c>
-      <c r="C232" s="2" t="inlineStr">
+      <c r="C232" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
         <is>
           <t>disaster / environment</t>
         </is>
       </c>
-      <c r="D232" s="2" t="inlineStr">
+      <c r="E232" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E232" s="2" t="inlineStr">
+      <c r="F232" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -6368,17 +7181,20 @@
           <t>Ayon kay Senate Finance Chairman Sen. Francis Escudero, ang P24 bilyon pondo ng ARMM ay sapat para sa rehabilitasyon at konstruksyon ng mga kalsada at patubig na aabot sa P10,642 bilyon ang ibinigay sa regional government ng Department of Public Works and Highways (DPWH).</t>
         </is>
       </c>
-      <c r="C233" s="2" t="inlineStr">
+      <c r="C233" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D233" s="2" t="inlineStr">
+      <c r="E233" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E233" s="2" t="inlineStr">
+      <c r="F233" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -6393,17 +7209,20 @@
           <t>Ayon sa social media post ng DZMM, magsusunog na naman ang mga miyembro ng militanteng grupo para sa pagunita ng International Human Rights Day bukas. Makikita sa mga larawan na inilathala ng DZMM Facebook page ang ilang bersyon ng mukha ni Pangulong Rodrigo Duterte na ginuhit ng mga militante. May isang hawig ni Hitler, mayroon naman na mukhang demonyo at ang isa naman ay inihalintulad sa isang aso. Mayroon din isang larawan na may salitang "DU30" at sa loob nito ay may guhit ng mga isyung ipinupukol laban sa Duterte Adinistration. Magtataka ka na lang kung saan nila kinukuha ang budget para sa mga ganitong gawain at kung bakit hindi sila nanghihinayang sa ginagawa nilang pagsusunog. Ito po ang naging reaksyon ng ilang kababayan natins amga pinaggagawa ng mga militante.</t>
         </is>
       </c>
-      <c r="C234" s="2" t="inlineStr">
+      <c r="C234" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D234" s="2" t="inlineStr">
+      <c r="E234" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E234" s="2" t="inlineStr">
+      <c r="F234" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -6418,17 +7237,20 @@
           <t>"Lumaban po kayo for the sake of your daughter" Hinikayat ng university lecturer at pro-government blogger na si Sass Rogando Sasot ang common-law wife ni Pangulong Rodrigo DUterte na si Ma'm Honeylet Avacena na maghain ng reklamo laban sa Google sa Estados Unidos para ibunyag kung sino ang nasa likod ng mapanirang propaganda video kung saan idinadawit ang menor de edad na si Veronica "Kitty" Duterte sa droga. "I suggest that you file a case in the US versus Google, concerning this YOutube Account: 'Ang Totoong Narco List'," sabi ni Sasot. Ang naturang Youtube account ay responsable sa mga mapanirang video ipinagkalat ng mga kumakalaban sa kasalukuyang administrasyon. Matapos maglabas paninira laban kay Presidential son Paolo Duterte, idinawit naman nila sa kalakaran ng droga ang menor de edad at bunsong anak ni Pangulong Duterte na si Kitty. "Your daugther, a minor, has been defamed through false and malicious Youtube video, claiming your daughter receives drug money," ani Sasot Ang unang video ng nasabing Youtube account ay binutata na ng mga taga-suporta ng Pangulo matapos makita ang mga pinekeng pirma sa nasabing video. Umalma na rin ang isang alkalde at sinabing pirma niya ang ginamit sa malisyosong video.</t>
         </is>
       </c>
-      <c r="C235" s="2" t="inlineStr">
+      <c r="C235" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D235" s="2" t="inlineStr">
+      <c r="E235" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E235" s="2" t="inlineStr">
+      <c r="F235" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -6443,17 +7265,20 @@
           <t>Viral ngayon ang video ng pagkumpronta ng isang pamilya sa service crew ng Pizza Hut sa Araneta Colliseum. Ayon sa uploader ng video na si Olin Ovlac, inaway daw ng pamilya ang service crew matapos ipatupad lang nito ang polisiya sa estabilisimiyento. Ayon sa ilang netizens, bawal dalhin sa loob ng colliseum ang mga takip ng mineral water. Humantong pa daw sa pagbabato ng pagkain sa crew ang insidente. Lubos na naawa si Ovlac sa sinapit ng babaneg crew dahil tuloy pa din daw ito sa pagta-trabaho at pagbebenta kahit umiiyak pa. Base naman sa isang pang saksi na si Jemard Bariso, nag-umpisa daw ang kumprontasyon nang magalit ang matandang babae dahil hindi ito nakabili ng popcorn sa Pizza Hut at nang pakiusapan ng crew na bumili na lang sa Snaxx (tindahan ng popcorn na katabi ng Pizza Hut). Lalo pa raw tumindi ang kumprontasyon nang ayaw pumayag ng kasamang lalake ng babae na tanggalin ang takip ng bottle water. At gumulo ng husto ang eksena nang batuhin na raw ng mas nakababatang babae ng pagkain ang crew. Habang isinusulat ang blog post na ito ay umabot na sa mahigit 67,000 na ang nagbahagi ng video at mayroon naring mahigit 29,000 na komento. Basahin ang reaksyon ng mga kababayan natins ainsidenteng ito.</t>
         </is>
       </c>
-      <c r="C236" s="2" t="inlineStr">
+      <c r="C236" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
         <is>
           <t>lifestyle / human interest</t>
         </is>
       </c>
-      <c r="D236" s="2" t="inlineStr">
+      <c r="E236" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E236" s="2" t="inlineStr">
+      <c r="F236" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -6468,17 +7293,20 @@
           <t>Samahan ang power trio hosts na sina 3rd District Negros Occidental Representative, House Committee on Housing and Urban Development Chairman Alfredo 'Albee' Benitez, model at beauty queen in the making na si Ms. Marjorie Cornillez at komedyanteng si Jayson Gainza sa kanilang paglilibot sa buong Pilipinas. Isasama tayo ng Kool Trip sa isang masayang paglalakbay kasama si Congressman Albee na magbibigay kasagutan sa mahahalagang isyus, kabilang ang aspetong kultural at pangkasaysayan. Sasamahan tayo ni Marjorie Cornillez na tikman ang mga authentic dishes at native delicacies na ipinagmamalaki ng bawat lugar sa Pinas.</t>
         </is>
       </c>
-      <c r="C237" s="2" t="inlineStr">
+      <c r="C237" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D237" s="2" t="inlineStr">
+      <c r="E237" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E237" s="2" t="inlineStr">
+      <c r="F237" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -6493,17 +7321,20 @@
           <t>Personal na namahagi si Sanchez ng bigas at mga regalo, kabilang ang mga souvenir bracelet, sa may 1,000 mahihirap na pamilya sa Barangay Bayan Park nitong Lunes bilang pasasalamat sa mga manonood ng kanyang programa sa ABS-CBN na nagdiriwang ng ikasampung anibersaryo. Sinabi ni Sanchez na maliit na bagay lang ang kanyang naitutulong pero dama niya ang suporta ng mga residente sa kanyang programa. "Walang kinalaman si Secretary Roxas sa ginagawa kong ito at ito ay mula sa aking trabaho. Tumulong siya, pero wala itong kinalaman sa pulitika," sabi ni Sanchez. Sa usapin kung kakandidato si Roxas sa 2016, sinabi ni Sanchez na hindi pa nila ito napag-uusapan, pero kung sakali, aniya, na may plano ang kalihim ay siya at ang Liberal Party ang makapagsasabi kung magpapatuloy si Roxas sa 2016. Sa ngayon, ayon kay Sanchez, ay abala si Roxas sa trabaho bilang kalihim ng DILG.</t>
         </is>
       </c>
-      <c r="C238" s="2" t="inlineStr">
+      <c r="C238" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
         <is>
           <t>lifestyle / human interest</t>
         </is>
       </c>
-      <c r="D238" s="2" t="inlineStr">
+      <c r="E238" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E238" s="2" t="inlineStr">
+      <c r="F238" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -6518,17 +7349,20 @@
           <t>Sa isang panayam, nagbigay ng opinyon si Sen. Cynthia Villar tungkol sa kung ano ang dapat gawin ng isang Vice President. Ayon kay Villar, dapat ay marunong sumunod sa adhikain ng President ang isang Vice President at kung hindi, ito raw ay mauuwi sa gulo. "Maski na iyun, pareho din yun (with running for President), mahirap pa yung Vice President you make sure that you can follow your President or else you're in a mess," sabi ni Villar . Para kay Villar, kung hindi daw kayang sumunod ng Vice President sa kanyang President ay dapat tumahimik na lang ito. May pag-aaral kasi na nagsasabi na kapag ang isang Vice President ay hayagang kumokontra sa Presidente ay nagiging unpopular ito sa publiko. "Ako kasi kung ako ang Vice President if I cannot follow my President I'll just keep quiet. You know there's a study na pag ikaw ay Vice President palagi mong inaaway ang President nagiging unpopular ka," dagdag pa ni Villar. Mababatid na naghain si Vice President Leni Robredo kay President Rodrigo Duterte ng kanyang resignation bilang pinuno ng Housing and Urban Development Coordinating Council (HUDCC).</t>
         </is>
       </c>
-      <c r="C239" s="2" t="inlineStr">
+      <c r="C239" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D239" s="2" t="inlineStr">
+      <c r="E239" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E239" s="2" t="inlineStr">
+      <c r="F239" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -6543,17 +7377,20 @@
           <t>Mga kababayan, mag-ingat kayo dahil usap-usapan ngayon sa social media ang umano’y serye ng pagdukot sa mga estudyante sa paligid ng mga malalaking mall sa Metro Manila, kung saan ayon sa mga pekeng ulat ay may grupo raw ng mga lalaki na nagkukunwaring delivery rider at biglang sinasakay sa van ang mga biktima sa loob ng ilang segundo; sinasabi pa sa mga kumakalat na post na madalas mangyari ito tuwing hapon at target daw ng sindikato ang mga kabataang naglalakad mag-isa, kaya’t marami ang natatakot na lumabas ng bahay at pinapayuhan ang publiko na huwag basta magtiwala sa mga nag-aalok ng tulong sa kalsada, habang nagkalat na rin ang mga pekeng CCTV footage at voice recording na nagpapalakas sa takot ng mga tao, dahilan para magdulot ng panic sa mga magulang at estudyante na ngayon ay mas pinipiling mag-online class na lang upang makaiwas sa banta ng krimen.</t>
         </is>
       </c>
-      <c r="C240" s="2" t="inlineStr">
+      <c r="C240" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D240" s="2" t="inlineStr">
+      <c r="E240" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E240" s="2" t="inlineStr">
+      <c r="F240" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -6568,17 +7405,20 @@
           <t>Sinuspinde na ng kamara ang inumpisahang niyang pagdinig. Natakot na ang liderato nito dahil, ayon sa mga kongresistang tutol dito, ay umaabot na sila sa kanilang pagtatanong kay Pangulong Noynoy. Maaari, dahil ang pabara-barang suntok kahit paano ay tumatama rin. Totoong nagsimulang magulo ang pagdinig ng kamara, pero may mga tanong na hindi mo alam kung saan nanggaling na nakasasakit din. Hihintayin munang matapos ang imbestigasyon ng PNP Board of Inquiry, wika ni Speaker Belmonte, bago namin itutuloy ang amin. Ang senado naman ay ipinakikita lamang ang bahagi ng pangyayaring gusto nitong ipaalam sa mamamayan sa kanyang publikong pagdinig. Pero kapag sumapit na ito sa parteng mabubuo na ang larawan, itinatago na niya ang kanyang imbestigasyon sa executive session na ang mga senador lang ang nakakaalam.</t>
         </is>
       </c>
-      <c r="C241" s="2" t="inlineStr">
+      <c r="C241" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D241" s="2" t="inlineStr">
+      <c r="E241" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E241" s="2" t="inlineStr">
+      <c r="F241" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -6593,17 +7433,22 @@
           <t>Sa isang screenshot na ibinahagi ni Davao City information officer Jefry Tupas sa kanyang Facebook account, makikita ang komentaryo ni Jboy Gonzales SJ laban kay Presidential daughter at Davao City Mayor Sara Duterte kaugnay ng isyu ng katapatan ng mga opisyal ng gobyerno; binanggit ni Tupas na si Father Jboy Gonzales ay mula sa Ateneo de Davao Highschool at dito ay nilait umano nito si Mayor Sara tungkol sa isyu ng honesty habang sinasabing "hirap magturo ng values kasi," ayon kay Tupas, na sinundan pa ng sarkastikong puna tungkol sa pagiging mabuting halimbawa ni Father Gonzales at pagbanggit na kung siya ay may anak ay kampante siyang matututo ito ng tamang asal mula kay Father Jboy, kasabay ng panawagan na magsimba, magdasal at tularan si Father; binanggit din ni Tupas ang pagiging bukas ni Father Gonzales tungkol sa kanyang kasarian at nagtanong kung si Father Jboy ay isang Jboy o Jgherl, sabay tanong sa opinyon ng publiko tungkol sa naging pahayag ni Father Gonzales.</t>
         </is>
       </c>
-      <c r="C242" s="2" t="inlineStr">
+      <c r="C242" s="3" t="inlineStr">
+        <is>
+          <t>Sa isang screenshot na ibinahagi ni Davao City information officer Jefry Tupas sa kanyang Facebook account, mababasa ang panlalait ni Jboy Gonzales SJ kay Presidential daughter at Davao City Mayor Sara Duterte. Ito ay kaugnay sa isyu tungkol sa pagiging tapat ng mga naninilbihan sa gobyerno. Ayon kay Tupas, ang naturang pari daw ay taga-Ateneo de Davao Highschool. "Father JBoy Gonzales is with Ateneo de Davao Highschool. Here, he badmouths the Mayor of Davao City over the issue of honesty while saying 'hirap magturo ng values kasi...'," resbak ni Tupas. Binanatan din ni Tupas sa sarkastikong pamamaraan si Father Gonzales. "Ang linis ni father. Hindi sya hypocrite. Naiintindihan din nya ang context ng sinasabi ni Mayor Sara tungkol sa honesty -- ang talino. Kung ako may anak, kampante ako na magiging matuwid siya kung tuturuan siya ni Father Jboy. Magsimba tayo. Magdasal. Tularan natin si Father.," buwelta pa ni Tupas. Hinapyawan din ni Tupas ang pagiging tapat ni Father Gonzales sa kasarian nito. "Basta ako, bakla ako. I don't know lang ha, dahil honest na honest naman si Father Jboy, kung siya ba isang Jboy o isang Jgherl," dagdag pa ni Tupas. Ano ang masasabi niyo sa bunganga ni Father?</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
         <is>
           <t>religion</t>
         </is>
       </c>
-      <c r="D242" s="2" t="inlineStr">
+      <c r="E242" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E242" s="2" t="inlineStr">
+      <c r="F242" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -6618,17 +7463,20 @@
           <t>Nananawagan si Father Rey Hector Paglinawan, parish priest ng Most Holy Redeemer Parish ng Barangay Apolonio Samson sa Quezon City, ng pakikiisa at pagtutulungan para sa mahigit 2,000 pamilya na pansamantalang nanunuluyan ngayon sa mga covered court at ilang paaralan, matapos na masunugan nitong Huwebes.</t>
         </is>
       </c>
-      <c r="C243" s="2" t="inlineStr">
+      <c r="C243" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
         <is>
           <t>religion</t>
         </is>
       </c>
-      <c r="D243" s="2" t="inlineStr">
+      <c r="E243" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E243" s="2" t="inlineStr">
+      <c r="F243" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -6643,17 +7491,22 @@
           <t>Ito ang unang beses kong mag-post ng ganito sa social media dahil sa hindi magandang karanasan namin sa beauty pageant kagabi na tinawag kong “BUDOL” Miss Ambassadress “Este” Scambassadress 2018. Lahat kami ay naglaan ng pagod, puyat, pera, at oras para sa isang pageant na hindi pala maayos at scammer pala ang organizer na si Peter Joemel “PJ” Advincula. Hindi niya binayaran ang mga kandidata, judges, host, handlers, dancers, tabulators, at sound system, at mula umpisa hanggang matapos ang event ay hindi siya nagpakita. Ginamit niya lang kami para makabenta ng ticket at pabango, at ang opisina niya sa EXODUS PHI79 MARKETING ay nasa Dunao, Ligao City. Ginamit din niya ang pangalan ng ARDEUR DE FRANCE perfume company para mas paniwalaan siya ng mga tao, at nagdala pa siya ng guest mula sa ‘That’s My Bae’ para magmukhang legit. Ang dahilan kung bakit kami sumali ay dahil maganda ang paliwanag niya noong screening at sinabi niyang ayos na ang lahat at makukuha namin ang prizes pagkatapos ng pageant, gaya ng nakasanayan sa industriya. Pero pagkatapos ng event, wala na ang organizer at staff, at hindi namin alam kung saan kukunin ang premyo o sino ang magbabayad sa amin. Kaya hinihikayat ko ang ARDEUR DE FRANCE na aksyunan ang problemang ito dahil ginamit ang pangalan ng kumpanya nila, at para sa mga nabiktima, sana ay ibahagi ninyo ang post na ito para madaling mahanap si Mr. Advincula at mapanagot siya sa ginawa niya. Salamat po.</t>
         </is>
       </c>
-      <c r="C244" s="2" t="inlineStr">
+      <c r="C244" s="3" t="inlineStr">
+        <is>
+          <t>This is my first time ever to post like this in a social media!!!! Dahil sa kabalastugang ginawa samin last night beauty pageant "BUDOL" The Miss Ambassadress "Este" Scambassadress 2018!!!! Dahil lahat kami nag effort ng Pagod, Puyat, Pera, at Oras sa walang kwentang pageant na hindi namin inaasahan na ganun pala ang resulta scammer pala ang organiser!!! WARNING: Siya si Peter Joemel "PJ" Advincula na nanloko, ng estapa at ng budol sa amin. Ang lalaking ito ay nagpapageant na hindi binayaran ang mga kandidata nanalo man o natalo, judges, host, handlers, dancers tabulators at sound system. Sa oras din ng pageant mula simula hanggang natapos hindi ito nagpakita sa amin. Ginamit mo lang kaming lahat para mabili ang mga ticket at tinda mong pabango. Mag-iingat sa taong dito ang opisina niya na EXODUS PHI79 MARKETING ay matatagpuan sa Dunao, Ligao City. Ang kompanya ng ARDEUR DE FRANCE ang kanyang ginamit upang mas maniwala sa kanya ang mga taong naloko at na-estapa niya. may pakuha kuha kapang guest galing sa 'That's My Bae' lahat kami niloko mo. Kung sino man po ang nakakaalam kung nasaan ang lalaking ito maari niyo pong ipagbigay alam sa amin upang maturuan ng leksyon ang manlolokong estapador na kalbo. For the information of everybody na nag-iisip samin bakit pa kami tumuloy sa pageant na yun. Kasi screening pa lng ang ganda ng mga paliwanag niya na walang problem sa pera and everything kasi lahat daw naka-settle na okay and ready na so naniwala naman kami kasi yun naman ang kalakaran ng pageant sa ilang taong na namin sa industriya ng patimpalak na ang prizes ay nakukuha namin after the show. Kasi wala namang beauty pageant na nag-cash advance bago mag-pageant in short pagtapos na. So natapos na nga ang pageant wala na ang organiser at ang mga staff hindi nila alam kung saan kukunin ang premyo at sino magbabayad saming lahat na nabudol niya. Sa "ANDREUR de France perfume and company makipag ugnayan na kau at gawan niyo ng action ang problemang ito kasi kayo ang naka-front dito. Alam naming lahat tayo ay biktima ng budol ni Mr. PJ Advincula para sa inyong kapakanan na hindi masira ang company niyo dahil ginamit kayo ni Mr. Advincula. So let's make action to this big problem. Sa lahat ng NABUDOL, NALOKO, AT NAABALA please share this post para madaling mahanap si Mr. Advincula upang makasuhan at pagbayaran niya lahat ng NAPINSALA niya! Salamat po. Tanya Herrera (August 12, 2018)</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D244" s="2" t="inlineStr">
+      <c r="E244" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E244" s="2" t="inlineStr">
+      <c r="F244" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -6668,17 +7521,22 @@
           <t>Mukhang mabibigo ang mga kandidato ng oposisyon na Otso Diretso sa halalan, dahil batay sa 9:16 am na partial at unofficial results mula sa Commission on Elections (COMELEC), 93.91% ng boto ang nabilang at wala ni isa sa kanila ang nakapasok sa Magic 12; si Bam Aquino ang pinakamalapit sa ika-14 na puwesto habang si Mar Roxas ay ika-16, at nag-concede na rin si Attorney Romulo Macalintal na nagsabing malinaw na pinili ng nakararaming botante ang ibang kandidato kaya't tinatanggap niya ang pagkatalo at binabati ang mga nanalo. Ipinahayag ng ilang kababayan ang kanilang reaksyon sa resulta, gaya ng pasasalamat sa Diyos at panawagan ng pagkakaisa mula kina C. Romeral at H. Jangas, habang binanggit naman ni N. Castro na mali umano ang paraan ng pangangampanya ng Otso Diretso at ayon kay R. Alfonso, mas maganda sana kung pinuri nila ang magagandang nagawa ng administrasyon.</t>
         </is>
       </c>
-      <c r="C245" s="2" t="inlineStr">
+      <c r="C245" s="3" t="inlineStr">
+        <is>
+          <t>Mukhang patungo na nga sa kabiguan ang mga kandidato ng oposisyon na mas kilala sa tawag na Otso Diretso. Sa 9:16 am results ng partial at unofficial counting sa datos ng Commission on Elections (COMELEC), 93.91% na ng elections results ang nabilang at wala ni isa sa Otso Diretso ang nakapasok sa Magic 12. Ang pinakamalapit lang na taga-Otso Diretso sa Magic 12 ay si Bam Aquino na nasa ika-14 na puwesto. Si former DILG Secretary Mar Roxas naman ay nasa ika-16. Kani-kanina lang ay nag-concede na ang isa sa mga miyembro ng Otso Diretso na si Attorney Romulo Macalintal. "From the results coming from all the clustered precincts, it is clear that a great majority of our voters have chosen other candidates. And I respect their decision as I concede defeat in this senatorial race... I sincerely congratulate all the winners who were so fortunate to get the trust and confidence of the people to serve for six years as their Senators," pahayag ni Atty. Macalintal. Ito po ang mga nakapasok sa Top 12, as of 9:16 ng umaga. Ito po ang mga komento ng ilang kababayan natin sa pinakahuling partial at unofficial results. "GOD HAS JUST SAVED THE PHILIPPINES! LET'S WORK HAND IN HAND FOR A BETTER PHILIPPINES," sabi ni C. Romeral. "#PRRD... God bless.... Hoping for unity for our country.... Hoping for a brighter future ahead.... Praying for all who win this election to serve our country very well.... Congratulations to all the winners ... ," sabi ni H. Jangas. "Mali kasi ang way nila ng pangangampanya imbes na sabihin nila ang plataporma nila ehh ang una nilang ginagawa sinisisi nila at sinisiraan ang gobyerno. lesson learned ," sabi ni N. Castro. " Kung kayo ba naman mga otso deretso eh pinuri ang ibang nagawa at magandAng nagawa ni President duterte baka pumasok pa ang iba sa inyo.kaso kapag sinabi ni President duterte kHit mGamda sa maraming tao.mali na sa inyo. Ayan tuloy deretso lahat sa inidoro. Ni isa walang pumasok sa inyo," sabi ni R. Alfonso.</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D245" s="2" t="inlineStr">
+      <c r="E245" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E245" s="2" t="inlineStr">
+      <c r="F245" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -6693,17 +7551,22 @@
           <t>Nagbukas ang Germany ng 350 trabaho para sa mga Pinoy nurse, ayon sa Philippine Overseas Employment Administration (POEA), kung saan kukunin ng German Federal Employment Agency ang mga nurse para sa intensive care unit, geriatric care, nursing home, elderly care, general ward, medical at surgery ward, operating room, neurology, at orthopedics. Ang sahod ay nagsisimula sa EUR2,000 o P118,000 kada buwan at maaaring umabot sa EUR2,400 o P141,000 kapag kinilala bilang kwalipikadong nurse. Kailangan ng dalawang taong karanasan bilang nurse sa ospital o medical institution at dapat ring handang magsanay ng German language na libre para sa mga mapipiling aplikante. Ayon kay POEA administrator Bernardo Olalia, walang recruitment o placement fee dahil government-to-government ang proseso, sasagutin ng employer ang air transportation, at tutulungan ang mga nurse sa paghahanap ng matitirhan. Paalala ng POEA, sila lamang ang magpoproseso ng aplikasyon at hindi kailangan dumaan sa recruitment agency, at hanggang Hunyo 7 lang ang pagtanggap ng mga application at requirements.</t>
         </is>
       </c>
-      <c r="C246" s="2" t="inlineStr">
+      <c r="C246" s="3" t="inlineStr">
+        <is>
+          <t>Binuksan sa bansang Germany ang 350 trabaho para sa mga Pinoy nurse, ayon sa Philippine Overseas Employment Administration (POEA). Kukuhanin ng German Federal Employment Agency ang mga Pinoy nurse para sa mga trabaho sa intensive care unit, geriatric care, nursing home, elderly care, general ward, medical and surgery ward, operating room, neurology, at orthopedics. Aabot sa EUR2,000 o P118,000 kada buwan ang sahod ng Pinoy nurse sa Germany. Maaari pang tumaas ang sahod sa EUR2,400 o P141,000 kapag kinilala na bilang isang kalipikadong nurse. Isa sa mga rekisito ang 2 taon na karanasan bilang nurse sa ospital o medical institutions. Handa rin dapat na magsanay ng German language na libreng ipagkakaloob sa mapipiling aplikante. Ayon kay POEA administrator Bernardo Olalia, walang babayarang recruitment fee o placement fee ang aplikante dahil "government-to-government" ang pagkuha. Sasagutin din ng employer ang air transportation at tutulungan ang nurse na makahanap ng lodging, ani Olalia. Nagpaalala ang POEA na sila lamang ang magpoproseso ng mga aplikasyon at hindi kailangang dumaan sa mga recruitment agency. Nakatakda sa Hunyo 7 ang huling araw ng pagsumite ng mga application at requirement.</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
         <is>
           <t>international news</t>
         </is>
       </c>
-      <c r="D246" s="2" t="inlineStr">
+      <c r="E246" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E246" s="2" t="inlineStr">
+      <c r="F246" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -6718,17 +7581,20 @@
           <t>Isang paring Pilipino na naman ang nasasangkot sa kontrobersiya matapos kasuhan ng panghahalay sa teenager na babae sa Philadelphia, United States. Ang malupit pa ay ni-record pa raw ng pari ang pakikipagtalik nito sa biktima. Ang krimen ay nangyari noong Agosto 2014. Kinilala ang suspek na si Rev. Armand Garcia, 49-anyos. Si Garcia nagpiyansa matapos bayaran ang 10 porsyento ng kanyang $250,000 bail. Kinumpirma din ng abogado ni Garcia na si Attorney William Brennan na na-arraigned na ang kanyang kliyente sa kasong rape, pagre-record ng pagtatalik at korapsyon ng menor de edad. Lumantad ang biktima ni Garcia, matapos mailipat ang pari sa bagong parokya nito lang 2017. Gagawin ang preliminary hearing sa kaso sa Marso 14. Si Garcis ay nagsilbi bilang regional representative para sa National Association of Filipino Priests. Basahina ng reaksyon ng ilang kababayan natin sa sigalot na kinahaharap ni Fr. Garcia. "Nasaan na si vellegas? Haja cbcp comment dali, would you betray God ka pang nalalamn dyan," sabi ni H. White. "Mga bishops kaparian anyare sa kakadakdak nu father Robert takbo Reyes hindi ka ba magpapas-an ng ataul sa pagtakbo mo 'yan ang sinasabi ko sa inyo ang galing nyong manuligsa sa gobyerno pero kayo at mga kabaro nu mas mabaho pa pala sa pusali.. mangumpisal na kayo!!!" sabi ni N. Evangelista. " CBCP Villegas It's your turn to speak. Kasi dami mong sabi about sa administration ni Presidnt time na para magbasa ka ng Bible at ipaliwanag ito.," sabi ni M. Tacardon. "Sinabi ni Jesus Mateo 7:15Mag-ingat kayo sa huwad na mga propeta na lumalapit sa inyo na nakadamit-tupa, pero sa loob ay hayok na mga lobo. 16 Makikilala ninyo sila sa mga bunga nila. Ang mga tao ay hindi makapipitas ng ubas o ng igos mula sa matitinik na halaman, hindi ba? 17 Maganda ang bunga ng mabuting puno, pero walang silbi ang bunga ng bulok na puno. 18 Ang mabuting puno ay hindi mamumunga ng walang-silbing bunga, at ang bulok na puno ay hindi mamumunga ng magandang bunga19 Bawat puno na hindi maganda ang bunga ay pinuputol at inihahagis sa apoy. 20 Kaya makikilala ninyo ang mga taong iyon sa kanilang mga bunga," sabi ni S. Laturgo.</t>
         </is>
       </c>
-      <c r="C247" s="2" t="inlineStr">
+      <c r="C247" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
         <is>
           <t>religion</t>
         </is>
       </c>
-      <c r="D247" s="2" t="inlineStr">
+      <c r="E247" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E247" s="2" t="inlineStr">
+      <c r="F247" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -6743,17 +7609,22 @@
           <t>Sa isang press conference, ipinahayag ni Philippine National Police (PNP) Chief Oscar Albayalde ang kanyang saloobin hinggil sa programa ng ABS-CBN na "Ang Probinsyano," kung saan negatibo umano ang naging paglalarawan sa mga pulis, partikular na sa karakter ng PNP Chief. Sa naturang palabas, ipinakita na magkasabwat sa iligal na gawain ang PNP chief Alejandro Terante, na ginagampanan ni Soliman Cruz, at ang bise presidente Lucas Cabrera, na ginagampanan ni Edu Manzano. Madalas ding pagbantaan ni Pangulong Duterte ang ABS-CBN na hindi ire-renew ang kanilang prangkisa dahil umano sa panloloko noong eleksyon. Ayon kay Albayalde, hindi patas na ipakita ang ganitong imahe ng PNP dahil hindi ito sumasalamin sa tunay na kalagayan ng kanilang organisasyon at nakakaapekto ito sa pananaw ng publiko, lalo na’t parang instant justice ang ipinapakita sa palabas. Aniya, dapat maging realistiko ang mga palabas at igalang ang batas dahil tayo ay isang bansa ng batas, hindi ng tao. Marami sa ating mga kababayan ang sumuporta sa pahayag ni PNP Chief Albayalde.</t>
         </is>
       </c>
-      <c r="C248" s="2" t="inlineStr">
+      <c r="C248" s="3" t="inlineStr">
+        <is>
+          <t>Sa isang press conference, naghayag ng saloobin si Philippine National Police (PNP) Chief Oscar Albayalde sa programa ng ABS-CBN na "Ang Probinsyano" kung saan masama ang naging paglalarawan sa mga pulis, lalong-lalo na sa paglalarawan sa PNP Chief. Sa naturang programa, ipinapakita na magkasabwat si PNP chief Alejandro Terante (ginagampanan ni Soliman Cruz) at bise presidente Lucas Cabrera (ginagampanan ni Edu Manzano) sa iligal na gawain. Ang ABS-CBN ay madalas pagbantaan ni Pangulong Duterte na hindi ire-renew ang prangkisa dahil umano sa panlolokong ginawa sa kanyang noong eleksyon. "Things are quite unusual here and it gives us a bad impression actually. It's a bit unfair to PNP when you portray that kind of (bad) activity that doesn't really happen in our organization...Parang hindi naman fair sa PNP. Lets be realistic. It is very disturbing at para kasing nakikita nung mga tao ay instant yung justice. Parang it is ok, it is not. We are a nation of law, not of men," sabi ni Albayalde. Sinuportahan naman ng karamihan sa mga kababayan natin ang naging pahayag ni PNP Chief Albayalde. Sang-ayon din ba kayo sa naging pahayag ni Sir Albayalde?</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D248" s="2" t="inlineStr">
+      <c r="E248" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E248" s="2" t="inlineStr">
+      <c r="F248" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -6768,17 +7639,20 @@
           <t>Nagpahiwatig si Russian President Vladimir Putin ng tulong sa Pilipinas matapos ang ginawang pag-atake ng mga terorista sa Jolo Cathedral nitong Linggo kung saan 27 katao ang sumakabilang-buhay at dose-dosena ang nasugatan. "I would like to reiterate our readiness to further step up interaction with our Philippine partners in combating the terrorist threat in all its forms and manifestations," sabi sa opisyal na website ng Russian President. Nakiramay din ang Pangulo ng Russia sa mga nabiktima ng pagsabog sa Jolo. "People in Russia share the grief of the victims' friends and families and hope for a prompt recovery of the injured," sabi pa sa pahayag. Dapat din daw managot ang mga may kasalanan sa nangyaring pambobomba. "A crime committed against civilians who had congregated for church services is shocking in its cynicism and cruelty. I expect that the masterminds and perpetrators of this crime will sustain the punishment they deserve," ayon sa pahayag. Panoorin ang kaugnay na ulat tungkol sa pamboboba sa simbahan sa Jolo. Basahin ang ilang reaksyon mula sa mga kababayan natin sa sinabi ni Putin. "Pls help us fight terrorism I know may kinalaman talaga ang mga taong ayaw nang mga pag babago.. Lalo na pag may isyung napupukol o na cocorner na sila gagawa talaga sila ng eksena no matter what would be the out come basta ma lihis Lang ang usapan," sabi ni R. Bacus. "Pahiram muna kami President Vladimir Putin ng kahit 5 SU35 at MIG 35 pang pulbos lang sa mga terroristang to gaya ng ginawa nyo sa mga ISIS sa Syria..thanks," sabi ni M. Bisco. "Welcome Russia and thank you so much Sir President Vladimir Putin," sabi ni G. Martinez. "Oh Yes please! Nakakabwisit na yong mga paring puro puna lang tapos thoughts and prayers lang pala ang kayang tulong sobrang ingay pa sa maintream media.," sabi ni M.A. Pino.</t>
         </is>
       </c>
-      <c r="C249" s="2" t="inlineStr">
+      <c r="C249" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
         <is>
           <t>international news</t>
         </is>
       </c>
-      <c r="D249" s="2" t="inlineStr">
+      <c r="E249" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E249" s="2" t="inlineStr">
+      <c r="F249" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -6793,17 +7667,20 @@
           <t>EXTENDED ang seryeng Dream Dad nina Zanjoe Marudo, Beauty Gonzales at Jana 'Baby' Agoncillo kasama sina Ketchup Eusebio, Katya Santos, Ariel Ureta at Ms Gloria Diaz. Ito ang dahilan kaya nagkaroon ng presscon ang main cast ng Dream Dad noong Biyernes, at para magpasalamat sa mga manonood sa kanilang pagiging No. 1 sa ratings game.</t>
         </is>
       </c>
-      <c r="C250" s="2" t="inlineStr">
+      <c r="C250" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D250" s="2" t="inlineStr">
+      <c r="E250" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E250" s="2" t="inlineStr">
+      <c r="F250" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -6818,17 +7695,20 @@
           <t>Isa na namang kawawang paliparan ang pinaganda ng gobyerno. Binuksan kamakailan lang ng pamahalaan ang bagong-ayos at pinagandang Marinduque Airport. Ayon sa Department of Transportation (DOTr), noong 2013 nang mahinto umano ang operasyon ng airport at matagal din na nanatiling maikli ang runway ng paliparan. Natengga din daw na sira ang Passenger Terminal Building (PTB) nito. Ngayon, halos mahigit dalawang taon ng pagkukumpuni, napaganda na ito ng gobyerno. Nalagyan na ito ng aircon at mayroon na rin mga x-ray machines. Sa pakikipagtulungan ng Civil Aviation Authority of the Philippines (CAAP), napalaki ang runway ng paliparan nitong Nombyembre 19, 2018, upang makatanggap ng mga mas malalaking sasakyang panghimpapawid. Nito namang April 1, 2019 ay nakapaglunsad na muli ng mga commercial flights ang paliparan. Ang Marinduque ay mayroong isa sa mga pinaka-sikat na okasyon sa Pilipinas - ang "Moriones Festival". Makikita rin sa lugar ang mga pinakamatatandang mga imprastruktura sa bansa, tulad ng simbahan. Ang magandang balita na ito ay ikanagalak naman ng ilang kababayan natin. "Congratulations it is very nice and it gives comfort just to see rehabilitations and developments happening to our country. Thank you very much and do not waiver your enthusiasm in doing great means for our beloved Countrymen, they deserve these facilities which have long been deprived of them. Again thank you!" sabi ni F. Mie. " Im glad to see this DOTrPH achievement, im not from Marinduque but im very happy. keep it up Sir Tugade, work well done" sabi ni E. Balais. " Keep up the good work mga Sir and Madam thank you very much for supporting our President.one for all all for one God bless po sa inyong lahat." sabi ni J. Angat.</t>
         </is>
       </c>
-      <c r="C251" s="2" t="inlineStr">
+      <c r="C251" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
         <is>
           <t>economy / business</t>
         </is>
       </c>
-      <c r="D251" s="2" t="inlineStr">
+      <c r="E251" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E251" s="2" t="inlineStr">
+      <c r="F251" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -6843,17 +7723,22 @@
           <t>Dahil sa patuloy na paglilinis ng Manila Bay, natuklasan ng Department of Environment and Natural Resources (DENR) ang humigit-kumulang 200 ektarya ng yamang-dagat tulad ng sari-saring coral reefs at mga high-value na isda, kahit pa malabo at maputik ang tubig sa lugar. Natagpuan ang mga yamang ito sa bahagi ng Maragondon, Corregidor at Cabalio Island, na nagpatibay sa paniniwala ng gobyerno na may pag-asa pang maisalba ang Manila Bay. Matatandaang nagbanta si Pangulong Rodrigo Duterte na ipapasara ang mga establisimiyento na nagtatapon ng maruming tubig sa look, at sinimulan ang paglilinis noong Enero sa pangunguna ng mga ahensiya ng gobyerno. Ikinatuwa ng mga mamamayan ang balita, at nagpahayag sila ng pasasalamat sa mga natuklasang biyaya ng dagat at sa pagsisikap ng administrasyon ni Duterte at ng DENR na maprotektahan at mapanatili ang Manila Bay.</t>
         </is>
       </c>
-      <c r="C252" s="2" t="inlineStr">
+      <c r="C252" s="3" t="inlineStr">
+        <is>
+          <t>Nang dahil sa isinasagawang paglilinis sa Manila Bay, natuklasan ng Department of Environment and Natural Resources (DENR) ang 200 ektaryang mga yamang-dagat. Ayon sa ulat ng PTV, sari-saring coral reefs at high-value fishes ang nakita sa look sa kabila ng malabong tubig at makapal putik. Namataang ang mga yamang dagat sa bandang Maragondon, Coregidor at Cabalio Island. Nang dahil sa mga nakita ng ahensiya, lalong lumakas ang paniniwala ng gobyerno na posible talagang maisalba ang Manila Bay. Magugunitang pinagbantaan ipapasara ni Pangulong Rodrigo Duterte ang mga estabilisimiyento na nagtatapon ng maruming tubig sa Manila Bay. Sinimulan ang paglilinis sa Manila Bay nitong Enero sa pangunguna ng mga ahensiya ng gobyerno. Ang balitang ito ay ikinatuwa ng mga kababayan natin. "Wow Kaya pala marami ang interesadong pasukin ang bansa Dahil sa yaman dagat na laman nito. Hindi nga nagkamali ang Du30 govt na linisin ang mnLa Bay. Thank you lord sa mga biyayang dagat na bigay mo# Protect n Preserved mnLa Bay," sabi ni R. Mendoza. "Slamat mhl nming pangulo..dhil syo nadiskubre ang mga yamang dagat jn sa manila bay..sna tuloy tuloy n ung paglilinis sa dagat," sabi ni Z. Otto. "kudos talaga sa duterte admin ke sir roy cimatu tama pagkalukluk na mga afp general dati ang ipanglalagay kasi aaksyunan talaga. mga brgy. unit di na kailangan mga tamad," sabi ni E. Pai.</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
         <is>
           <t>disaster / environment</t>
         </is>
       </c>
-      <c r="D252" s="2" t="inlineStr">
+      <c r="E252" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E252" s="2" t="inlineStr">
+      <c r="F252" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -6868,17 +7753,20 @@
           <t>Matagal nang hinahangaan si Carla Villanueva bilang isa sa pinakasikat na aktres sa bansa, ngunit nitong linggo ay umugong ang balita na umano’y may hindi pagkakaunawaan sa pagitan niya at ng direktor ng kanyang bagong teleserye matapos kumalat ang video na nagpapakitang umalis siya sa set nang hindi nagpapaalam, dahilan para mag-trending ang hashtag #CarlaWalkout sa social media; ayon sa ilang insider, nag-ugat daw ang tensyon sa biglaang pagbabago ng script na hindi raw nagustuhan ni Carla, at may mga netizen na nagsasabing hindi ito ang unang beses na nagpakita siya ng diva attitude, habang may ilan namang tagahanga na nagsasabing unfair ang paghusga sa kanya dahil wala pang opisyal na pahayag mula sa kampo ng aktres o ng produksyon, kaya’t patuloy ang diskusyon online kung sino nga ba ang dapat sisihin sa nangyaring insidente.</t>
         </is>
       </c>
-      <c r="C253" s="2" t="inlineStr">
+      <c r="C253" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D253" s="2" t="inlineStr">
+      <c r="E253" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E253" s="2" t="inlineStr">
+      <c r="F253" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -6893,17 +7781,22 @@
           <t>Matapos ang ilang buwang pagpapalabas sa mga lokal at international na sinehan, itinanghal ang pelikulang "Fantastica" bilang bagong highest grossing movie ni Vice Ganda, matapos itong maging kalahok sa 2018 Metro Manila Film Festival. Inanunsyo ito noong Enero 29, 2019 sa isang thanksgiving dinner na inorganisa ng Star Cinema at ABS-CBN Kapamilya Network, base sa Twitter post ni entertainment editor Jose Miguel Dumaual. Umabot sa halos 596 milyong piso ang kinita ng "Fantastica," na nalampasan ang "Gandarrapiddo: The Revenger Squad" na kumita ng 571 milyong piso noong MMFF 2017, na pinagbidahan din ni Vice Ganda kasama sina Daniel Padilla at Pia Wurtzbach. Nagpasalamat si Vice Ganda sa suporta ng kanyang mga tagahanga at ng mga fans ng kanyang co-stars. Ang pelikula, na may carnival-themed adventure, ay unang beses na pinagsama sina Vice Ganda, Richard Gutierrez at Dingdong Dantes, pati na rin ang mga bagong Kapamilya love teams na sina Kisses Delavin at Donny Pangilinan, Loisa Andalio at Ronnie Alonte, at Maymay Entrata at Edward Barber. Sa thanksgiving party, dumalo ang mga big boss ng ABS-CBN tulad nina Chairman Mark Lopez, President at CEO Carlo Katigbak, at Star Cinema head Olivia Lamasan na nagbigay ng pagbati sa production team at cast, na kumpleto ring dumalo. Lahat ng pelikula ni Vice Ganda sa MMFF ay palaging box office hit, simula pa noong "The Unkabogable: Praybeyt Benjamin," na nagkaroon pa ng sequel, at marami na rin ang nagtatanong kung posible silang magsama ni Vic Sotto, na nakasama naman si Coco Martin sa "Jack em Popoy."</t>
         </is>
       </c>
-      <c r="C254" s="2" t="inlineStr">
+      <c r="C254" s="3" t="inlineStr">
+        <is>
+          <t>Matapos ang ilang buwang pamamayagpag sa mga lokal na sinehan at international screenings, itinanghal ang pelikulang "Fantastica", isa sa mga pelikulang lahok sa nakaraang 2018 Metro Manila Film Festival, bilang pinakabagong highest grossing movie ni Unkabogable Phenomenal Star Vice Ganda. Inihayag ang balitang ito nitong Martes, Enero 29, 2019, sa isang thanksgiving dinner gathering na idinaos ng Star Cinema at pamunuan ng ABS-CBN Kapamilya Network para sa panibagong tagumpay na ito, batay sa ibinahaging Twitter post ni Jose Miguel Dumaual, isang entertainment editor. Umabot ng halos 596 milyong piso ang kinita ng "Fantastica" at tinalo ang "Gandarrapiddo: The Revenger Squad," pelikulang pinagbidahan din ni Vice Ganda kasama sina Daniel Padilla at Pia Wurtzbach na tumabo naman ng 571 milyong piso bilang lahok sa MMFF 2017. Ipinaabot naman ni Vice Ganda ang kanyang pasasalamat sa suportang ibinigay ng kanyang mga tagahanga at tagahanga ng kanyang mga co-stars. Ang carnival-themed adventure movie na ito ay unang pagsasama sa pelikula nina Vice Ganda, dating Kapuso, Kapatid, at ngayo'y Kapamilya star Richard Gutierrez, at ang isa sa mga bankable Kapuso leading men na si Dingdong Dantes. Pinagsama-sama rin sa naturang pelikula ang mga pinakabagong pambatong love teams ng Kapamilya Network na sina Kisses Delavin at Donny Pangilinan, Loisa Andalio at Ronnie Alonte, at sina Maymay Entrata at Edward Barber. Walang nasabi sa labis na katuwaan ang Phenomenal star kundi "Ang lala". Dumalo sa naturang thanksgiving party ang big bosses ng ABS-CBN, tulad nina Chairman Mark Lopez, President at CEO Carlo Katigbak, at Star Cinema head Olivia Lamasan, na nagpaabot naman ng kanilang pagbati sa production team at cast ng pelikula. Naroon din ang buong cast ng pelikula. Lahat ng mga pelikulang lahok ni Vice Ganda sa Metro Manila Film Festival ay talaga namang tumatabo sa takilya. Ang unang pelikula ni Vice Ganda sa MMFF ay "The Unkabogable: Praybeyt Benjamin" na nagkaroon pa ng sequel. Marami na rin ang nagtatanong kung posible ba silang magsama ng isa ring nangunguna sa paggawa ng pelikulang lahok sa MMFF na si Bosing Vic Sotto, na nakasama naman si Coco Martin sa pelikulang "Jack em Popoy."</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D254" s="2" t="inlineStr">
+      <c r="E254" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E254" s="2" t="inlineStr">
+      <c r="F254" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -6918,17 +7811,20 @@
           <t>Siguraduhin mong hindi ka mahuhuli sa balitang ito: kumakalat ngayon online ang umano’y bagong produkto ng kompanyang LakasBilis Corp na tinatawag na “Instant Yaman Capsule” na ayon sa kanilang promotional posts ay kayang gawing milyonaryo ang kahit sinong iinom nito sa loob lamang ng isang linggo, gamit daw ang “revolutionary formula” na sinasabing pinagsama ang advanced financial technology at herbal extracts mula sa bundok ng Biringan; maraming netizen ang nagbahagi ng kanilang kwento na bigla raw silang nanalo sa lotto, nakatanggap ng mysterious bank transfers, at napromote sa trabaho matapos uminom ng kapsula, kaya’t dagsa na raw ang orders sa website ng LakasBilis Corp kahit wala namang pruweba o opisyal na pag-apruba mula sa alinmang ahensya, dahilan para magdulot ng matinding diskusyon kung totoo nga bang may ganitong produkto o isa lang itong malaking panloloko sa gitna ng lumalalang problema sa ekonomiya.</t>
         </is>
       </c>
-      <c r="C255" s="2" t="inlineStr">
+      <c r="C255" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
         <is>
           <t>economy / business</t>
         </is>
       </c>
-      <c r="D255" s="2" t="inlineStr">
+      <c r="E255" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E255" s="2" t="inlineStr">
+      <c r="F255" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -6943,17 +7839,20 @@
           <t>"Alam niyo, ang President, kapag hindi niyo nakikita, nagtatrabaho 'yun. Ayaw naiistorbo nun." Ganito ang ilan sa mga naging pahayag ni Presidential Spokesperson Salvador Panelo sa isang press conference, kaugnay ng pagtatanong ng taumbayan kung bakit hindi nila madalas makita si Pangulong Duterte sa publiko nitong mga nakakaraang araw. Matatandaang ang huling public appearance ni Pangulong Duterte ay nitong nakaraang May 13, 2019 Elections sa Daniel R. Aguinaldo National High School sa Barangay Martina, Davao City kung saan siya bumoto. "Kasi 'pag nasa labas siya ang daming gustong makipag-usap sa kanya, eh napakabait naman niyang tao, hindi naman tumatanggi, so 'yung focus niya dun sa kanyang signing papers, reading documents, reading memo, hindi niya magawa kaya siguro he decides to stay put," saad ni Panelo. Ayon pa kay Panelo, dumating ang Presidente sa Maynila noong nakaraang Biyernes at dumiretso umano ito sa Bahay Pagbabago sa Malacanang Complex. "Ang alam ko lang, Friday nandito na siya. Parang sinabi ata the day after the election na nagpapahinga siya," dagdag pa ng Tagpagsalita ng Palasyo. "He's strong, the voice is strong. Tumatawa pa nga eh. Makikita niyo siguro siya mamaya kung may activities siya mamaya," wika ni Panelo. Nauna nang ipinaliwanag ni Panelo na hindi umano itinuturing na seryosong bagay ni Pangulong Duterte ang ilang kumakalat na balita ukol sa kalusugan nito, kung saan usap-usapan na dinala umano ang Presidente sa Cardinal Santos Medical Center sa San Juan. "Sabi niya, 'I neither confirm nor deny'. You draw your own conclusions. 'Di na akonag-ano kasi palagi naman 'yun ang sinasabi niya 'pag may lumalabas na ganoon," ani Panelo. "In other words, para sa kanya, it's not a serious matter kasi kung serious 'yun, he always tells the public about it," dagdag pa ni Panelo. "Let me assure the nation that if there is anything wrong with the President's health serious enough to be of our concern, he will tell us and he said so himself. 'Di ba he tells you 'pag meron siyang.. kung nagpunta siya, nagpatingin siya ng ganito. Para sa kanya settled na 'yun. Nakikita niyo naman 'yung ayos niya. Nakita niyo nang walang nangyari sa kanya. In other words, hindi siguro importante 'yung bagay na pinagtsi- tsismisan siya," saad pa ni Panelo.</t>
         </is>
       </c>
-      <c r="C256" s="2" t="inlineStr">
+      <c r="C256" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D256" s="2" t="inlineStr">
+      <c r="E256" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E256" s="2" t="inlineStr">
+      <c r="F256" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -6968,17 +7867,20 @@
           <t>Matapos ang sunod-sunod na posts sa social media tungkol sa bagong labas na gamot na “Vaxiluminol,” mabilis na nag-viral ang mga kwento ng mga umanong nakaranas ng kakaibang side effects gaya ng biglang pagkakaroon ng kulay asul na dila, pag-usbong ng maliliit na balahibo sa palad, at hindi mapigilang pagtawa tuwing gabi matapos uminom ng naturang gamot; ayon sa mga netizen, may ilan pa raw na nagising na may kakaibang accent at hindi makapagsalita ng Tagalog ng ilang oras, dahilan para mag-panic ang kanilang pamilya, kaya’t marami ang nagbabala na mag-ingat at huwag basta-basta susubok ng Vaxiluminol hangga’t hindi pa raw ito lubusang nasusuri ng mga eksperto, lalo na’t may mga nagsasabing posibleng tumagal ng ilang buwan ang mga kakaibang sintomas na ito.</t>
         </is>
       </c>
-      <c r="C257" s="2" t="inlineStr">
+      <c r="C257" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
         <is>
           <t>health misinformation</t>
         </is>
       </c>
-      <c r="D257" s="2" t="inlineStr">
+      <c r="E257" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E257" s="2" t="inlineStr">
+      <c r="F257" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -6993,17 +7895,20 @@
           <t>Mga kababayan, mag-ingat sa bagong lumalaganap na balita tungkol sa “Instant Yaman Card” na diumano’y inilunsad ng isang kilalang kompanya na “FortuneSwipe Inc.” at sinasabing nagbibigay raw ng automatic P50,000 na credit sa kahit sinong mag-aapply online, kahit walang bank account o requirements; ayon sa mga post sa social media, kailangan lang daw mag-fill out ng form at magbayad ng P500 processing fee para ma-activate ang card na ito, at pwede na raw agad gamitin sa lahat ng groceries, malls at kahit sa online shopping, kaya’t dagsa ang mga nagtatangkang mag-avail at nagbabahagi ng kanilang “testimonya” na nakapag-shopping na raw sila ng walang limit, subalit wala pa ring opisyal na anunsyo mula sa alinmang ahensya o lehitimong negosyo tungkol sa pagkakaroon ng ganitong produkto, kaya’t nagdududa ang ilan kung totoo nga ba o isa lamang itong panibagong modus na dapat bantayan ng publiko.</t>
         </is>
       </c>
-      <c r="C258" s="2" t="inlineStr">
+      <c r="C258" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
         <is>
           <t>economy / business</t>
         </is>
       </c>
-      <c r="D258" s="2" t="inlineStr">
+      <c r="E258" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E258" s="2" t="inlineStr">
+      <c r="F258" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -7018,17 +7923,20 @@
           <t>Isang nakakagimbal na insidente ang naganap kagabi sa Barangay San Pedro nang biglang maglaho ang tatlong bata habang naglalaro sa tapat ng kanilang bahay at pinaniniwalaang biktima ng isang misteryosong grupo na tinatawag ng mga residente bilang “Itim na Van Gang” na sinasabing gumagamit ng mga sasakyang walang plaka at tinted ang bintana para mabilis na makuha ang kanilang target; ayon sa mga nag-aalalang magulang, wala umanong narinig na sigaw o ingay kaya’t marami ang natatakot na baka may ginagamit na pampatulog o kakaibang paraan ang mga suspek, dahilan kung bakit nagdulot ito ng matinding takot sa buong komunidad na ngayon ay halos hindi na pinapalabas ang kanilang mga anak at nagsimula nang mag-organisa ng mga ronda gabi-gabi, habang patuloy ang panawagan sa mga otoridad na agad aksyunan ang insidente dahil marami na ang nangangambang baka hindi lang ito ang unang beses na umatake ang grupo at baka may susunod pang mabiktima.</t>
         </is>
       </c>
-      <c r="C259" s="2" t="inlineStr">
+      <c r="C259" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D259" s="2" t="inlineStr">
+      <c r="E259" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E259" s="2" t="inlineStr">
+      <c r="F259" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -7043,17 +7951,20 @@
           <t>Nagkatotoo ang kasabihan na "Ang basurang itinapon mo ay babalik sa'yo." sa sakay ng isang van matapos habulin ng isang dayuhang nakabisikleta para ibalik ang basurang itinapon niya sa kalsada. Sa panayam sa sakay ng bisikleta na si Frank Schuengel, nakita niya ang sakay ng van na nagtapon ng basurang nakalagay sa plastic. Dahil mabagal ang daloy ng trapiko, kinuha ng dayuhan ang basura at hinabol ang van para ibalik sa kanila ang basurang itanapon. "This is not a bin. Don't throw that out. Don't do it," madidinig sa video ni Schuengel. Sinabi ni Schuengel na hindi siya natatakot sa mga taong nagtatapon ng basura sa hindi tamang lugar. "We all should look after the world we live in. So I'm not afraid of the people who throw their rubbish out, they should be afraid of everyone else giving it back to them. That's how it works," sabi niya. Aminado naman si MMDA Spokesperson Celine Pialago, na nalulungkot siya dahil ang mga Pilipino ang dapat na mas nagpapakita ng pagpapahalaga sa kalinisan sa ating bayan. "Nakakahiya pero ho napakagandang action ho 'yon na ipamukha ho natin sa nagkalat na ito basura mo itapon mo," anang opisyal. Aniya, sa unang bahagi pa lang ng taon, umabot na raw sa 4,316 ang nahuhuli ng MMDA sa kanilang anti-littering operations. "Mayroon pong dalawang pagpipilian 'yung violator, una it's either magbayad sila ng P500 na kailangan mag-settle sa MMDA, and community service nila sir e sila 'yung pinagwawalis natin," ayon kay Pialago. Gayunman, may mga nahuhuli umano na matapang pa at nagbabanta sa mga enforcer. At mayroon din umanong pinapansin ang tiket na ibinibigay sa kanila. "Plano nating ikabit 'yung pangalan nila sa NBI para magkaroon ng hassle sa pagkuha ng NBI clearance. Iisip po tayo ng panibagong puwede idagdag du'n sa mga violators," sabi ni Pialago.</t>
         </is>
       </c>
-      <c r="C260" s="2" t="inlineStr">
+      <c r="C260" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
         <is>
           <t>lifestyle / human interest</t>
         </is>
       </c>
-      <c r="D260" s="2" t="inlineStr">
+      <c r="E260" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E260" s="2" t="inlineStr">
+      <c r="F260" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -7068,17 +7979,20 @@
           <t>Isa ka ba sa nag aabang nito ? Isa sa pinakahihintay ng marami lalo na ang mga dumadaan sa sa EDSA from NLEX to SLEX or vice versa. Ang SKY WAY stage 3 ay inaasahan ng maraming motorista sa EDSA na maiibsan ang mabigat na daloy ng trapiko dito araw-araw kaya ganun nalang ang pag mamadali ng administrasyon Duterte sa proyekyo na ito kung saan target na matapos at maging operational sa taon 2020. Matatandaan noon August 2017 ay nag order ang Pangulong Duterte ng dismisal sa dalawang opisyal na nangangasiwa nito ka kadahilanan ng pagka delay ng proyektong ito. Ayun pa sa pangulo, " these two really did bad. They delayed the project. We are rushing to give more mobility to the people of Metro Manila. But these two sat on it for almost one year. Ganun pa man, hindi pinangalanan ng Pangulo kung sino ang mga opisyal na ito.</t>
         </is>
       </c>
-      <c r="C261" s="2" t="inlineStr">
+      <c r="C261" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
         <is>
           <t>economy / business</t>
         </is>
       </c>
-      <c r="D261" s="2" t="inlineStr">
+      <c r="E261" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E261" s="2" t="inlineStr">
+      <c r="F261" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -7093,17 +8007,22 @@
           <t>Nahuli sa dashcam ang ilang kabataan na gumagawa ng kalokohan sa kalsada, ayon sa ulat ng GMA, kung saan may mga batang nambabato o nagagasgas ng mga sasakyan ng mga motorista na hindi nagbibigay ng limos, at mas malala pa, may mga insidente ng pagbuhos ng asido kapag hindi sila nabibigyan. Ayon kay MPD Station 8 Commander P/Supt. Ruben Ramos, kapag hindi nabibigyan ng limos, minsan ay kinakamot ng mga bata ang sasakyan at pinapauwi nila ang mga ito o dinadala sa DSWD. Dahil sa Republic Act 9344 o Juvenile Justice and Welfare Act of 2006 na inakda ni Senador Kiko Pangilinan, hindi maaaring arestuhin ang mga batang gumagawa ng ganitong gawain, kaya marami sa ating mga kababayan ang napipilitang sisihin ang senador dahil sa epekto ng batas na ito.</t>
         </is>
       </c>
-      <c r="C262" s="2" t="inlineStr">
+      <c r="C262" s="3" t="inlineStr">
+        <is>
+          <t>Sapul sa dashcam ang ginagawang kabalastugan ng ilang kabataan sa kalsada. Ayon sa ulat ng GMA, may mga batang nambabato o di kaya ay ginagasgasan ang kotse ng mga motoristang hindi nagbibigay ng limos. Ang mas matindi pa ay ang pambubuhos ng asido kapag hindi nabigyan ng limos. "After ng hindi mo mabigyan, nang-i-scratch ng sasakyan... Pinapauwi namin ang mga bata, and sometimes kinukuha natin at dinadala natin sa DSWD,"sabi ni MPD Station 8 Station Commander P/Supt. Ruben Ramos. Sa mga ganitong pagkakataon, hindi pwedeng arestuhin ang sino mang pusakal na kabataan dahil sa Republic Act 9344 of the Juvenile Justice and Welfare Act of 2006 ni Senador Kiko Pangilinan, kaya ang iba sa mga kababayan natin ay hindi mapigilan na sisihin ang senador dahil sa naging resulta umano ng batas na inakda nito.</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D262" s="2" t="inlineStr">
+      <c r="E262" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E262" s="2" t="inlineStr">
+      <c r="F262" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -7118,17 +8037,22 @@
           <t>Matapos ang halalan kung saan karamihan ng mga nanalo ay kaalyado ni Pangulong Rodrigo Duterte, muling napag-usapan ng ilang tagasuporta ng Presidente ang lumang social media post ng aktres na si Agot Isidro na nagbabala laban sa Duterte Administration, kung saan sinabi niyang walang magpakailanman at darating din ang araw ng mga opisyal ng administrasyon. Sinagot ito ni Presidential Communication Operations Office Undersecretary Lorraine Marie Badoy at sinabi niyang hindi kasing bulok ng pag-iisip ni Isidro ang mga nagtatrabaho sa ilalim ng Duterte Administration, at binigyang-diin ang pagkatalo ng mga kandidato ng oposisyon sa nakaraang eleksyon. Idinagdag ni Badoy na ang dahilan ng pagkatalo ay makikita sa tweet ni Isidro na nagpapakita umano ng kakulangan ng pag-unawa sa tunay na kahulugan ng public service, at binanggit din ang isyu kay Mar Roxas noong Yolanda. Samantala, bumuwelta rin ang pro-government blogger na si Krizette Laureta Chu at sinabing umasa si Isidro na maging asawa ng senador ngunit natalo ang kanyang kasintahan, at tinawag ang mga pahayag ng aktres na parang eksena lang sa pelikula. Si Isidro, na napabalitang kasintahan ng Otso Diretso candidate na si Florin Hilbay, ay kilala bilang isa sa mga pinaka-maingay na kritiko ni Pangulong Duterte sa social media at minsan na ring tinawag ang Pangulo na "Psychopath."</t>
         </is>
       </c>
-      <c r="C263" s="2" t="inlineStr">
+      <c r="C263" s="3" t="inlineStr">
+        <is>
+          <t>Matapos ang halalan kung saan karamihan sa mga mananalo ay mga ka-alyado ni Pangulong Rodrigo Duterte, nahalungkat ng ilang taga-suporta ni Presidente ang social media post ng aktres na si Agot Isidro noong nakaraang taon. Patungkol ito sa pagbababala ng artista laban sa Duterte Administration. Sa naturang social media post, sinabi ni Isidro na walang magpakailanman at darating din daw ang araw ng mga opisyales ng Duterte Administration. Nagbigay naman ng pahayag si Presidential Communication Operations Office Undersecretary Lorraine Marie Badoy sa dating social media post ni Isidro. Banat ni Badoy, hindi kasing bulok ng pag-iisip ni Isidro ang mga nagta-trabaho sa ilalim ng DUterte Administration. "No, Ms. Isidro, NONE of us in this Administration think the rotten way that you do... The party that got royally trounced in the recent senatorial elections where a grand total of ZERO of your candidates got the nod of the Filipino people and where the President's allies all but filled up all those senatorial slots. All you need to know about why such an abject and complete rejection of the Filipino people for your boyfriend and his pals happened, Ms Isidro, is contained in this Tweet of yours: the total and almost pathetic ignorance over what public service means. No, Ms Isidro, a public office is not that one chance you have to settle scores the way that bastard, Mar Roxas, did when Yolanda struck when he uttered that obscene line: 'You are a Romualdez, the president is an Aquino.'," banat ni Badoy. Buwelta naman ng pro-government blogger na si Krizette Laureta Chu, umasa daw si Isidro na maging asawa ng senador. "Yung natalo yung "boypren" mo despite everythaaaang. Yung umasa kang maging Senator's wifey, naunsyami pa. SHAKET Agot, this is real life, wag mo kaming linyahang pang B movie mo. And in real life, araw na namin.," resbak ni Chu. Si Isidro ay napabalitang kasintahan na umano ni Otso Diretso candidate Florin Hilbay. Si Isidro ay isa sa mga pinaka-maingay na kritiko ni Pangulong Duterte sa mundo ng social media. Magugunitang tinawag ni Isidro na "Psychopath" ang Pangulo ng Pilipinas.</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D263" s="2" t="inlineStr">
+      <c r="E263" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E263" s="2" t="inlineStr">
+      <c r="F263" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -7143,17 +8067,20 @@
           <t>Sa isang pahayag, binanatan ni Attorney Larry Gadon ang mga politiko, simbahan at human rights advocates na nanahimik ngayon sa kaso ng pagpaslang sa grade 9 student na si Christine Lee Silawan na tinadtad ng saksak at tinalupan pa ang mukha. "Dapat nang ibalik ang death penalty, nakakalungkot, nakakangitngit at nakakagalit ang nangyari kay Chrsitine Lee Silawan sa Lapu-Lapu City. Kapag drug addict ang namamatay ang mga ipokritong politiko ay panay ang dalaw at sigaw ng katarungan pero itong pagpatay at pagtalop ng mukha ni Christine Lee Silawan," banat ni Gadon. . Wala rin daw ginagawa ang mga kritiko ni Pangulong Rodrigo Duterte kundi isisi sa Presidente ang lahat pero tikom ang bibig samga karumaldumal na mga krimen. "Wala kayong kibo puro kayo ipokrito. Puro kayo sisi kay Duterte pero ang sarili niyo hindi niyo tinitignan, ang pagka-ipokrito niyo," banat ni Gadon. Naniniwala din si Gadon sa na sayang lang ang mga buwis na ginagamit para sa pagpapakain sa mga kriminal na nakagawa ng mga karimarimarim na krimen. Ito po ang reaksyon at tugon ng ilang kababayan natin sa komento ni Atty. Gadon sa Silawan case. "Maka kriminal kasi ang mga simbahan, CHR at mga dilawan. Nag iingay lng pag kriminal ang namatay. Mga buang," sabi ni M. Coja. "sa lahat ng gustong ibalik ang bitay dpat iboto nyo un senador na pabor dto para tuloy tuloy na," sabi ni J. Bayan. "Your right atty gadon.. ang mga anti Duterte ay mga malisyoso mga hipokrito at hipokrita... Ang tunay na layunin ng administrasyon pag babago.. sila ay Hindi ang layunin ay sariling bulsa .. pondo..," sabi ni W. Resuento. "Support! sa panahon kasi ngayon malaki na masyado pinagbabago ng panahon natin. Kaya hindi na na uuso ngayon ang pa santo2han at santa2han pa sa senado natin ngayon. I-dispose na sa basurahan deretso iyang mga matagal nang nag bo-bobohan parin dyan masyado na mga mambabatas dyan sa itaas di naman na iyan sila kailangan.," sabi ni T. Rodilla.</t>
         </is>
       </c>
-      <c r="C264" s="2" t="inlineStr">
+      <c r="C264" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D264" s="2" t="inlineStr">
+      <c r="E264" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E264" s="2" t="inlineStr">
+      <c r="F264" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -7168,17 +8095,20 @@
           <t>Isang nakakabiglang insidente ang nangyari kagabi sa harap ng isang kilalang mall sa Lungsod ng San Rafael nang mahuli umano sa aktong pag-aabot ng malaking halaga ng pera at hinihinalang ipinagbabawal na gamot si Konsehal Ramon Dela Vega, isang kilalang personalidad sa lokal na pamahalaan, ayon sa mga nakakita sa pangyayari; kwento ng ilang saksi, nakita raw nila ang konsehal na palihim na nakikipag-usap sa dalawang lalaking hindi taga-roon, at makalipas ang ilang minuto ay biglang sumulpot ang mga tauhan ng Task Force Bantay Krimen upang arestuhin siya, dahilan para magdulot ng matinding pagkabigla at usap-usapan sa buong komunidad, lalo na’t matagal nang tinuturing na huwarang lider si Dela Vega na kilala sa kanyang mga programa laban sa krimen, kaya’t marami ang hindi makapaniwala sa balitang ito at naghihintay ngayon ng opisyal na pahayag mula sa kanyang kampo.</t>
         </is>
       </c>
-      <c r="C265" s="2" t="inlineStr">
+      <c r="C265" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D265" s="2" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D265" s="2" t="inlineStr">
+      <c r="E265" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E265" s="2" t="inlineStr">
+      <c r="F265" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -7193,17 +8123,20 @@
           <t>Nagdulot ng matinding takot at pagkalito sa mga residente ng Lungsod ng Del Pilar ang biglaang pag-usbong ng tinatawag nilang “ulan ng yelo at abo” na bumagsak mula sa langit kagabi, kung saan daan-daang bahay at sasakyan ang natabunan ng puting pulbos na may kasamang maliliit na tipak ng yelo, dahilan upang magsiksikan sa mga evacuation center ang mga tao dala ang kaba na baka may lason o kemikal ang bumagsak na materyales; ayon sa kwento ng ilang nakasaksi, tila nagdilim ang paligid at bumagsak ang malamig at malagkit na yelo na may kakaibang amoy, kaya’t marami ang nagtakbuhan palabas ng bahay habang ang iba ay nagtakip ng mukha gamit ang basang tuwalya, at ngayon ay nag-uunahan ang mga eksperto sa pagtukoy kung saan nanggaling ang kakaibang pag-ulan na ito at kung ligtas pa bang manatili sa lungsod, habang patuloy na nag-viral sa social media ang mga larawan at video ng makapal na abo at yelo na bumalot sa buong komunidad.</t>
         </is>
       </c>
-      <c r="C266" s="2" t="inlineStr">
+      <c r="C266" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
         <is>
           <t>disaster / environment</t>
         </is>
       </c>
-      <c r="D266" s="2" t="inlineStr">
+      <c r="E266" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E266" s="2" t="inlineStr">
+      <c r="F266" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -7218,17 +8151,22 @@
           <t>Ipinagmalaki ni Department of Agriculture (DA) Secretary Manny Piñol ang P10 milyon na monolithic dome na itinayo sa DA-Southern Cagayan Research Center sa Minanga Norte, Iguig, Cagayan, kung saan magsisilbi itong imbakan ng mga produktong agrikultura tulad ng binhi at iba pang ani mula sa probinsiya. Ang dome ay may sukat na 8.5 metro ang taas, 15 metro ang lapad, at 30 metro ang haba, at gumagamit ng climate-smart technology na kayang tumagal kahit sa matinding kalamidad gaya ng signal 5 na bagyo at malalakas na lindol. Ayon kay DA Regional Executive Director Narciso Edillo, ang makabagong warehouse na ito ay malaking hakbang para sa sektor ng agrikultura sa rehiyon, partikular sa pag-iimbak ng mga binhi upang mapanatili ang kalidad at bisa nito, at maaari rin itong gamitin bilang pansamantalang tirahan o evacuation center tuwing may kalamidad, cold storage ng mga produktong agrikultural, at iba pa. Ang monolithic dome ay isang istrukturang gawa sa iisang piraso na maaaring permanente o pansamantala at maaaring maging bahagi ng isang tapos na gusali.</t>
         </is>
       </c>
-      <c r="C267" s="2" t="inlineStr">
+      <c r="C267" s="3" t="inlineStr">
+        <is>
+          <t>Ibinida ni Department of Agriculture (DA) Secretary Manny Pinol ang P10 million monolithic dome sa DA-Southern Cagayan Research Center sa Minanga Norte sa Iguig, Cagayan. Ang nasabing dome ay magsisilbing imbakan ng mga produktong agrikultura, katulad ng mga binhi at iba pang ani sa probinsiya ng Cagayan. Ito ay may sukat na 8.5 metrong taas, 15m lawak, at 30m haba na may climate-smart technology na kayang tumayo sa panahon ng mga kalamidad katulad ng signal 5 na bagyo at malakas na lindol. "The state-of-the-art warehouse will be a breakthrough in the region's agriculture sector, particularly for seeds storage to maintain seed viability and quality. This can also be used as human shelter or evacuation center during calamities, cold storage for agricultural products and many others," saad ni DA Regional Executive Director Narciso Edillo. Ang isang monolithic dome ay istruktura na nasa pormang one-piece form, na maaaring permanente o panandalian, at maaari o 'di maaaring maging bahagi ng isang tapos na istruktura. BASAHIN ANG BUONG POST NI SEC. MANNY PINOL MULA SA KANYANG FACEBOOK ACCOUNT:</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
         <is>
           <t>economy / business</t>
         </is>
       </c>
-      <c r="D267" s="2" t="inlineStr">
+      <c r="E267" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E267" s="2" t="inlineStr">
+      <c r="F267" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -7243,17 +8181,20 @@
           <t>Ayon sa isang viral na post mula sa Facebook page na “Bantay Bayan Online,” napag-alaman umano ng ilang concerned citizens na may sikreto raw na underground tunnel project si Governor Renato Villanueva sa ilalim ng provincial capitol na hindi kasama sa opisyal na budget at pinaniniwalaang ginagamit umano ito bilang taguan ng mga mamahaling kagamitan at dokumento na may kinalaman sa umano’y anomalya sa mga kontrata ng gobyerno; sinasabi pa sa naturang post na may ilang empleyado raw na biglang na-assign sa gabi upang bantayan ang lugar at may mga CCTV footage pa umano na nagpapakitang may mga kahina-hinalang delivery truck na palihim na pumapasok tuwing madaling araw, dahilan upang magdulot ng iba’t ibang haka-haka at spekulasyon sa mga netizens na hinihinalang may mas malalim pang dahilan ang proyekto, kahit nananatiling tikom sa isyu ang tanggapan ng gobernador at wala pang inilalabas na opisyal na pahayag tungkol dito.</t>
         </is>
       </c>
-      <c r="C268" s="2" t="inlineStr">
+      <c r="C268" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D268" s="2" t="inlineStr">
+      <c r="E268" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E268" s="2" t="inlineStr">
+      <c r="F268" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -7268,17 +8209,20 @@
           <t>Ngayong Linggo, samahan si Jessica Soho na kumustahin ang Kapuso homegrown artist na si Jen sa isang espesyal na one-on-one interview sa Kapuso Mo, Jessica Soho. Mapapanood din ngayong gabi ang mga putaheng gawa sa karne ng tupa, lalo pa nga't Year of the Wooden Sheep ngayong taon. Saan ba matatagpuan ang pinakamasasarap na kebab sa bansa? At tunghayan ang mga lamb dish na pwedeng-pwede rin palang lutuin -- Pinoy style! Samantala, isang batikang feng shui expert ang nagsabi na magiging masagana, masuwerte at taon ng mga oportunidad para sa maraming Pilipino ang 2015. Pero para sa mga mapamahiin, ano nga ba ang diumano'y mga pampabuwenas sa taong ito? Tampok din sa KMJS ang bagong Internet sensations tulad nina Lyle na pinahanga ang lahat sa rendition niya ng Bang Bang at Blaine ng Davao City na kilala naman sa kanyang cover ng Thinking Out Loud ni Ed Sheeran. Pag-uusapan din kung gaano katotoo na maaring yumaman sa networking at ang hottest trends ngayon 2015 pagdating sa pagpapaganda, pagpapasexy, at gadgets.</t>
         </is>
       </c>
-      <c r="C269" s="2" t="inlineStr">
+      <c r="C269" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
         <is>
           <t>lifestyle / human interest</t>
         </is>
       </c>
-      <c r="D269" s="2" t="inlineStr">
+      <c r="E269" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E269" s="2" t="inlineStr">
+      <c r="F269" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -7293,17 +8237,20 @@
           <t>Kaninang hapon, biglang nag-viral sa social media ang balitang diumano’y may lihim na pagpupulong ang tatlong kilalang senador sa isang private resort sa Batangas, kung saan napagkasunduan daw nila ang isang kontrobersyal na plano para manipulahin ang nalalapit na national budget deliberations; ayon sa anonymous source na umano’y staff ng isa sa mga senador, may naganap daw na palitan ng envelope na puno ng pera at listahan ng mga proyektong ipapasa kapalit ng “tiyak na boto,” kaya’t agad nag-ingay ang mga netizen at naglabasan ang mga hashtag na #BudgetSabwatan at #SenateScandal, habang nananahimik pa rin ang mga sangkot at naglabas ng pahayag ang opisina ng Senado na walang katotohanan ang mga paratang, subalit patuloy pa ring lumalalim ang isyu dahil may kumakalat na raw na audio recording ng usapan na hinihintay ngayon ng publiko na ilabas ng mga whistleblower.</t>
         </is>
       </c>
-      <c r="C270" s="2" t="inlineStr">
+      <c r="C270" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D270" s="2" t="inlineStr">
+      <c r="E270" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E270" s="2" t="inlineStr">
+      <c r="F270" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -7318,17 +8265,20 @@
           <t>ISANG estudyante ang nasawi at di bababa sa lima pa ang naospital matapos diumanong malason sa kinaing cookies, na gawa ng kaklase, sa Imus City, Cavite, Martes ng hapon, ayon sa pulisya. Anim ang dinala sa Medical Center Imus, pero binawian ng buhay ang 18-anyos na si Mark Joseph Tan habang nilulunasan, ayon sa ulat ng Calabarzon regional police. Kinilala ng pulisya ang lima pang dinala doon bilang sina Mher John Tan, 18; Justin James Canete, 18; Mercy Grace Benialon, 18; Eden Joyce Beckham, 19; at Rovic Elli, 17. Naganap ang insidente dakong alas-5:30, sa bahay ng kaklase nilang si Daniela Grace Bolo, sa Brgy. Palico 4. Gumawa ng chocolate cookies ang 18-anyos na si Bolo, at inihain ito sa mga kaklase. Kumain din umano ang dalaga ng mga inihandang cookies. Matapos iyo'y dumanas na umano pangangati at hirap sa paghinga ang kanyang mga kaklase, ayon sa ulat.</t>
         </is>
       </c>
-      <c r="C271" s="2" t="inlineStr">
+      <c r="C271" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D271" s="2" t="inlineStr">
+      <c r="E271" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E271" s="2" t="inlineStr">
+      <c r="F271" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -7343,17 +8293,20 @@
           <t>Ito ang ikalawang pagtatangka ng US na palayain si Somers sa loob ng 10 araw at sinabi ni Kerry na inaprubahan ang operasyon dahil sa mga impormasyon na nanganganib ang buhay ni Somers. "It was our assessment that that clock would run out on Saturday," sabi ng isang US official.</t>
         </is>
       </c>
-      <c r="C272" s="2" t="inlineStr">
+      <c r="C272" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D272" s="2" t="inlineStr">
+      <c r="E272" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E272" s="2" t="inlineStr">
+      <c r="F272" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -7368,17 +8321,22 @@
           <t>Matagal nang hindi nakakakita ng mga submarine mula sa mga kalapit-bansa ang Philippine Navy sa karagatan ng Pilipinas, ngunit dahil sa pagdating ng dalawang AgustaWestland AW159 Wildcat anti-submarine helicopters noong Martes, ayon kay Navy Flag-Officer-in-Command Vice Admiral Robert Empedrad, nagkaroon na sila ng kakayahan na maka-detect at makawasak ng mga submarino gamit ang mga torpedo na dala ng mga chopper na ito. Sinabi ni Empedrad na malaking hakbang ito sa pagpapalakas ng kakayahan ng Navy dahil hindi lang nila matutukoy ang mga submarino na dumadaan sa ating teritoryo kundi kaya rin nilang wasakin ang mga ito, ngunit dahil malawak ang ating karagatan, kailangan pa ng mas marami pang ganitong kagamitan. Ang dalawang helicopter ay nabili sa halagang P5.4 bilyon, kasama na ang mga mission essential equipment, munition, at integrated logistic support. Nilinaw din niya na limitado pa rin ang kanilang ma-monitor dahil dalawa lang ang helicopters, pero malaking tulong na ito para mabantayan ang mga sea lanes of communication kung sakaling may dumaan na submarine.</t>
         </is>
       </c>
-      <c r="C273" s="2" t="inlineStr">
+      <c r="C273" s="3" t="inlineStr">
+        <is>
+          <t>Ilang taon nang hindi maka-detect ng mga submarine ang Philippine Navy mula sa mga kapitbahay na bansa na nagkukubli sa karagatan ng Pilipinas. Pero dahil nabiyayaan sila ng dalawang anti-submarine choppers, may kakayanan na ang Philippine Navy na maka-detect nito. Dumating kasi ang dalawang AgustaWestland AW159 Wildcat helicopters noong Martes, ayon kay Navy Flag-Officer-in-Command Vice Admiral Robert Empedrad. "It's a great leap to our capability that we have equipment that can locate subsurface, submarines, we can detect the submarines going through our waters," ani Empedrad. "It can detect and it can sink, it can destroy submarines because these choppers have torpedoes and it is not only for detection, it can destroy too, so, this has a good capability but because the waters are too wide, we will need more of it," dagdag niya. Nabili ang dalawang helicopter ng P5.4 billion kasama na ang mission essential equipment, munition, at integrated logistic support. "Limited lang yung makikita dahil dalawa lang, ang luwag-luwag ng dagat natin. Pero at least yung mga nasa sea lanes of communication natin pwedeng ma-monitor kung may dumaan na submarines," aniya pa. Kaya umano nitong makawasak ng mga submarine dahil mayroon itong torpedoes.</t>
+        </is>
+      </c>
+      <c r="D273" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D273" s="2" t="inlineStr">
+      <c r="E273" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E273" s="2" t="inlineStr">
+      <c r="F273" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -7393,17 +8351,20 @@
           <t>Ayon sa 903rd Infantry Brigade, nasa 30 miyembro ng rebeldeng grupo ang responsable sa pagsunog sa bahay ni Barangay Kagawad Oscar Rejuso. Mabilis umanong kumalat ang apoy sa kabahayan na naging sanhi upang matupok agad ito.</t>
         </is>
       </c>
-      <c r="C274" s="2" t="inlineStr">
+      <c r="C274" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
         <is>
           <t>disaster / environment</t>
         </is>
       </c>
-      <c r="D274" s="2" t="inlineStr">
+      <c r="E274" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E274" s="2" t="inlineStr">
+      <c r="F274" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -7418,17 +8379,22 @@
           <t>Dahil sa dami ng mga Pilipinong nahuhumaling sa online games, hindi na nakakagulat na kinikilala na ito bilang e-sports at kasama na ang ilang online games bilang medal sports sa darating na Southeast Asian Games na gaganapin sa Pilipinas. Gayunpaman, ayon kay Palarong Pambansa 2019 Secretary-General at DepEd Undersecretary Revsee Escobedo, hindi pa napag-uusapan ng Department of Education na isama ang e-sports gaya ng Mobile Legends at DOTA sa Palarong Pambansa, dahil mas pinili muna nilang isama ang larong Pinoy bilang demo sport ngayong taon, alinsunod sa hiling ni Secretary Leonor Briones. Paliwanag ni Escobedo, prayoridad ng Palaro Board ang mga larong makakatulong sa motor at physical skills ng mga batang manlalaro at bagamat may positibo at negatibong obserbasyon tungkol sa online games, mahalaga raw na mapanatili ang balanse at ang holistic development ng mga mag-aaral. Nilinaw din niya na hindi pa isinasara ng DepEd ang posibilidad ng pagsama ng e-sports sa hinaharap ngunit nais muna nilang pag-aralan ang mga benepisyo nito para sa mga estudyante. Samantala, binanggit ni Escobedo na patuloy ang DepEd sa pag-adapt sa teknolohiya sa tulong ng Philippine Sports Commission at ilan sa mga gamit sa Palarong Pambansa ay hiniram mula sa PSC tulad ng sa swimming. Gaganapin ang Palarong Pambansa sa Davao City mula Abril 27 hanggang Mayo 4, 2019.</t>
         </is>
       </c>
-      <c r="C275" s="2" t="inlineStr">
+      <c r="C275" s="3" t="inlineStr">
+        <is>
+          <t>Sa dami ng mga Pilipino na nahuhumaling sa paglalaro ng online games ngayon, hindi nakakagulat na itinuturing na ito bilang isang tunay na e-sports. Napag-alaman kasi na kasama na ang ilang online games sa darating na Southeast Asian Games na gaganapin sa Pilipinas bilang medal sports. Hindi pa napag-uusapan ng Deparment of Education (DepEd) na siyang tagapangasiwa ng Palarong Pambansa ang pagpasok ng mga online games sa mga laro. Inamin ni Palarong Pambansa 2019 Secretary-General at DepEd Undersecretary Revsee Escobedo na hindi pa napag-uusapan sa Palaro Board ang maaaring pagsama ng e-sports kagaya ng Mobile Legends at DOTA sa taunang kompetisyon. Ayon sa kaniya, maraming laro na nasa SEA Games ang pinag-iisipan ng departamento na isama bilang demo sport sa Palaro subalit mas pinili nila na gawin ang larong Pinoy ngayong taon alinsunod na rin sa hiling ni Secretary Leonor Briones. "The secretary wants to include larong Pinoy in the regular Palarong Pambansa sports. Maybe next year, we have larong Pinoy as demo sports with other sports. But not online games," paliwanag ni Escobedo. Dagdag pa ni Escobedo, prayoridad ng Palaro Board ang mga larong makapagpapalakas at pabuti sa motor at physical skills ng mga batang manlalaro. "There are positive and negative observations with regards to online games. What is important is we have to balance. What is important to us, the officials of DepEd, is the holistic development of our lifelong learners," ani Escobedo. Bagamat hindi pa napag-uusapan ngayon, nilinaw nito na hindi nila sinasarado ang pinto para sa online sports. Nais lamang nila pag-aralan maigi ang mga benepisyong maaaring makuha ng mga estudyante sa e-sports. Samantala, patuloy naman ang mga pagbabago aniya sa pagsasagawa ng Palaro lalo pa't marami sa mga e-sport ay nangangailangan na ng teknolohiya. Pagbibida ni Escobedo, sumasabay na ang DepEd sa teknolohiya sahol na rin sa tulong ng Philippine Sports Commission (PSC). "Yes, we are adapting to the technology. We are implementing technological innovations. The PSC is very strict when it comes to compliance with international rules and standards. Some of the equipment we will use in Palarong Pambansa are borrowed from PSC like in swimming," pahayag ni Escobedo. Ang Palarong Pambansa ay isasagawa sa Davao City mula Abril 27 hanggang May 4, 2019.</t>
+        </is>
+      </c>
+      <c r="D275" s="2" t="inlineStr">
         <is>
           <t>sports</t>
         </is>
       </c>
-      <c r="D275" s="2" t="inlineStr">
+      <c r="E275" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E275" s="2" t="inlineStr">
+      <c r="F275" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -7443,17 +8409,20 @@
           <t>Nahuli na si Jojo Valerio, ang lalaki sa viral video na nananakit, nanggitgit at nagpakilalang anak ng kongresista sa nakaaway niyang motorista. Pero sa isang panayam, umaatungal at nagagalit ang nanay ng suspek. Ayon sa ina ni Valerio, hindi raw maganda ang naging paraan sa paghuli sa anak niya. "Kinuha at dinukot ang anak ko, binugbog ang anak ko, yun ang pakialam namin." sabi ng nanay ng suspek. Si Valerio ay bida din sa isa pang viral video kung saan ginigitgit at sinundan pa nito ang isang babae dahil lang nasingitan siya sa kalsada. Bukod sa pananakit, nakita rin na gumagamit ang suspek ng palakang numero 8. Ang plate number 8 ay protocol plate para lang sa mga kongresista. Hindi naman nagustuhan ng mga kababayan natin ang tono ng pagsasalita ng nanay ng road rage suspect. Ito pa po ang karagdagang ulat mula sa GMA News kaugnay pa rin sa suspek na si Valerio.</t>
         </is>
       </c>
-      <c r="C276" s="2" t="inlineStr">
+      <c r="C276" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D276" s="2" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D276" s="2" t="inlineStr">
+      <c r="E276" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E276" s="2" t="inlineStr">
+      <c r="F276" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -7468,17 +8437,20 @@
           <t>Matapos mapansin ang biglaang pagtaas ng presyo ng bigas sa ilang pamilihan sa Lungsod ng San Pedro, kumalat ang balitang diumano’y may bagong kompanyang nagngangalang Golden Fields AgroTech na gumagamit ng kemikal sa kanilang bigas upang mapatagal ang shelf life nito, dahilan umano ng kakaibang lasa at amoy na napapansin ng mga mamimili; ayon sa mga nag-post sa social media, may ilang nagsabing nagkaroon sila ng pananakit ng tiyan matapos kumain ng bigas mula sa naturang brand kaya’t nagbabala ang ilang netizen na umiwas muna sa pagbili nito, habang may mga ulat pa na diumano’y nabistong gumagamit ng artipisyal na pampaputi ang kompanya para magmukhang mas bago ang kanilang produkto, dahilan upang magdulot ng pangamba sa mga konsumer at mag-udyok ng panawagan na imbestigahan ng mga awtoridad ang sinasabing iregularidad sa operasyon ng Golden Fields AgroTech.</t>
         </is>
       </c>
-      <c r="C277" s="2" t="inlineStr">
+      <c r="C277" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D277" s="2" t="inlineStr">
         <is>
           <t>economy / business</t>
         </is>
       </c>
-      <c r="D277" s="2" t="inlineStr">
+      <c r="E277" s="2" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E277" s="2" t="inlineStr">
+      <c r="F277" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -7493,17 +8465,20 @@
           <t>Kasunod nito, dalawang bahay naman sa Sitio Mambog sa Bgy. Sula, San Jose, ang nilamon ng apoy. Ang mga bahay ay pag-aari nina Marlon Doctolero, 49; at Jimboy Doctolero, 22, kapwa magsasaka.</t>
         </is>
       </c>
-      <c r="C278" s="2" t="inlineStr">
+      <c r="C278" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D278" s="2" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D278" s="2" t="inlineStr">
+      <c r="E278" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E278" s="2" t="inlineStr">
+      <c r="F278" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -7518,17 +8493,20 @@
           <t>Blocktimer si Willie, hindi station produced ang show at tila P2M every Sunday ang production cost ng gagawing programa. Tinawagan na raw ni Willie ang mga kaibigan na gustong mag-sponsor sa kanyag shows, sila rin ang sponsors ng show noong nasa ABS-CBN at TV5 pa ang show niya. Ang pagpasok ng show ni Willie ang nakita naming rason kung bakit biglang na-move sa April ang airing ng InstaDad na naka-schedule umere ng March 22. Pagkatapos ng Sunday All Stars ang dapat na time slot ng InstaDad na time slot ngayon ng show ni Willie. Kaya ang tanong, saan na ilalagay ang InstaDad ngayon? Kung titingnan, walang problema sa airing, ibalik sa 12 ng tanghali ang SAS, saka ipasok ang Instadad at isunod ang show ni Willie o puwedeng unahin ang show ni Willie bago ang comedy show ni Gab</t>
         </is>
       </c>
-      <c r="C279" s="2" t="inlineStr">
+      <c r="C279" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D279" s="2" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D279" s="2" t="inlineStr">
+      <c r="E279" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E279" s="2" t="inlineStr">
+      <c r="F279" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -7543,17 +8521,22 @@
           <t>Sa Barangay Caingin sa San Rafael, Bulacan, usap-usapan ang pagpaparamdam ng isang "white lady" sa mga motorista sa isang kalsada, matapos mahagip ng CCTV ang pigurang ito na tila nakasama nina Arjay Abarte at John Narvie Luz sa motorsiklo noong Pebrero 10 at nauwi sa aksidenteng ikinasawi ni Arjay habang galos lamang ang tinamo ni Narvie. Ayon kay Narvie, maingat si Arjay sa pagmamaneho bago mangyari ang insidente, at dahil hindi matanggap ng ama ni Arjay na si Belden Balansag ang nangyari, pina-review niya ang CCTV kung saan nakita ang hugis ng babaeng nakaputi. Kwento ng lolo ni Narvie na si Romeo Luz, matagal na siyang nakakakita ng white lady sa lugar ngunit naniniwala siyang hindi ito nananakit at posibleng nagligtas pa kay Narvie. Dagdag pa ng kagawad na si Rolando Bautista, madalas magpakita ang white lady sa kurbada ng kalsada kung saan madalas din ang aksidente, kaya maglalagay ang barangay ng mga bagong palatandaan para makaiwas sa disgrasya. Sa konsultasyon sa paranormal expert na si Tony Suvega, sinabi niyang hindi white lady kundi isang mabait na "engkantada" ang nagpaparamdam at protektor umano ito ng barangay. Samantala, hindi kumbinsido si Val Cuenca ng ABS-CBN INCA na white lady ang nakita sa CCTV at naniniwala siyang tao lang ito na nakasakay sa motor. Anuman ang paniniwala tungkol sa white lady, payo pa rin ng mga awtoridad ang dagdag na pag-iingat ng mga motorista sa lugar.</t>
         </is>
       </c>
-      <c r="C280" s="2" t="inlineStr">
+      <c r="C280" s="3" t="inlineStr">
+        <is>
+          <t>Sa kahabaan ng isang kalye sa Barangay Caingin sa bayan ng San Rafael, Bulacan, sinasabing may isang "white lady" na nagpaparamdam sa mga dumadaang motorista. Pinaniniwalaang ang naturang white lady ang nahagip sa closed-circuit television (CCTV) noong nakaraang buwan na nakaangkas sa motorsiklong sinasakyan ng magkaibigang Arjay Abarte at John Narvie Luz, na nauwi sa aksidenteng ikinasawi ni Arjay. Ihahatid sana pauwi ni Arjay si Narvie noong gabi ng Pebrero 10 galing sa isang inuman nang bigla silang sumalpok sa poste ng ilaw sa pakurbang bahagi ng kalsada sa Barangay Caingin, kuwento ni Narvie. Ayon kay Narvie, maingat si Arjay sa daan, at tahimik pa raw ito at mistulang nagko-concentrate sa pagmomotor bago sila sumalpok. Hindi naman matanggap ni Belden Balansag, ama ni Arjay, ang pagkamatay ng anak kaya ipina-review niya ang kuha ng CCTV sa aksidente. "Bumalik ako dito kasi mag-iimbestiga pa ako kung ano nangyari talaga," ani Balansag. Sa pag-review ng CCTV, makikita ang pigura na mistulang babaeng nakaputi na pinaniniwalaang white lady. Ayon kay Romeo Luz, lolo ni Narvie, pagkapalipat pa lang niya sa San Rafael noong 1997 ay madalas na raw siyang makakita ng white lady sa lugar. Subalit, ani Romeo, hindi naman daw nananakit ang white lady kundi mistulang nagbabantay at nagmamasid lang. Naniniwala rin si Romeo na ang white lady ang nagligtas kay Narvie lalo at galos lang ang tinamo nito sa aksidente. Kuwento rin ng kagawad na si Rolando Bautista, madalas daw talagang magpakita sa kurbada ang white lady at madalas din ang mga aksidente. "May naaaksidente sa lugar na 'yon kasi nga kurbada 'yon sa lugar na 'yon," ani Bautista. Ayon pa kay Bautista, magpapagawa ang barangay ng mga bagong palatandaan sa may kurbada para makaiwas sa aksidente. Kinonsulta ang kababalaghan sa paranormal expert na si Tony Suvega, na nagsabing hindi raw white lady kundi "engkantada" ang nagpaparamdam. Nakatira rin daw ito sa abandonadong bahay sa lugar. "Napakabait po, ang totoo niyan mapalad ang barangay ng Caingin na sila ay may protektor na kagaya nito," ani Suvega. Hindi rin kumbinsido si Val Cuenca, head ng camera operations sa ABS-CBN Integrated News and Current Affairs (INCA), na white lady ang nasa kuha ng CCTV. "Sa tingin ko, tao ito eh, ito 'yong naka-motor, hindi ito 'yong white lady," ani Cuenca. Totoo man o hindi ang white lady sa Barangay Caingin, ibayong pag-iingat para rin ang ipinapayo sa mga motorista.</t>
+        </is>
+      </c>
+      <c r="D280" s="2" t="inlineStr">
         <is>
           <t>lifestyle / human interest</t>
         </is>
       </c>
-      <c r="D280" s="2" t="inlineStr">
+      <c r="E280" s="2" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E280" s="2" t="inlineStr">
+      <c r="F280" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -7568,17 +8551,20 @@
           <t>Hahataw sa Abril 5 (Easter Sunday) ang binuong Spiker's Turf na para sa kalalakihan at ang pinakaaabangang Shakey's V-League na para sa kababaihan sa ika-12 edisyon ng Shakey's V-League Open Conference sa San Juan Arena.</t>
         </is>
       </c>
-      <c r="C281" s="2" t="inlineStr">
+      <c r="C281" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D281" s="2" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D281" s="2" t="inlineStr">
+      <c r="E281" s="2" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E281" s="2" t="inlineStr">
+      <c r="F281" s="2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
@@ -7593,17 +8579,20 @@
           <t>Ayon sa inilabas na ulat ng online news portal na BayanAlert, nagdulot ng matinding pagkabigla at diskusyon sa publiko ang diumano’y lihim na pagpupulong ng mga miyembro ng National Assembly kagabi kung saan napagkasunduan daw nilang ipasa ang kontrobersyal na “No Shoes, No Power” bill na magbabawal sa mga opisyal ng gobyerno na magsuot ng sapatos tuwing may sesyon bilang simbolo raw ng pagkakapantay-pantay sa mamamayan; ayon pa sa mga umano’y leaked na larawan, makikita raw ang ilang senador na nag-aaway dahil sa hindi pagkakasundo kung dapat bang payagan ang tsinelas o dapat ay walang sapin sa paa, kaya’t nag-viral agad ang balita at umani ng samu’t saring reaksyon mula sa netizens na nagtatanong kung seryoso ba ang mga mambabatas o isa lang itong paraan para pagtakpan ang mas malalaking isyu sa bansa.</t>
         </is>
       </c>
-      <c r="C282" s="4" t="inlineStr">
+      <c r="C282" s="5" t="n">
+        <v/>
+      </c>
+      <c r="D282" s="4" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D282" s="4" t="inlineStr">
+      <c r="E282" s="4" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E282" s="4" t="inlineStr">
+      <c r="F282" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -7618,17 +8607,20 @@
           <t>Matapos ipatupad ng pamahalaan ng Bagong Luntian ang kontrobersyal na “One Market, One Price” policy na nagtatakda ng iisang presyo para sa lahat ng pangunahing bilihin sa lungsod, hati ang opinyon ng mga residente kung ito nga ba ay makakatulong o lalo lamang magpapahirap sa kanila; habang ipinagmamalaki ng lokal na opisina na bababa raw ang presyo ng bigas at gulay dahil sa regulasyon, marami ang nagrereklamo na hindi na sila makapagtinda ng mura sa palengke at napipilitan silang sumunod sa itinakdang presyo kahit lugi na, dahilan para lumaganap ang mga post sa social media na nagsasabing mas pabor daw ang bagong polisiya sa malalaking supermarket kaysa sa maliliit na vendor, at may mga nagsasabing dapat na raw itong ipatigil dahil mas lalong lumalaki ang gastusin ng karaniwang mamimili sa halip na makatipid.</t>
         </is>
       </c>
-      <c r="C283" s="4" t="inlineStr">
+      <c r="C283" s="5" t="n">
+        <v/>
+      </c>
+      <c r="D283" s="4" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D283" s="4" t="inlineStr">
+      <c r="E283" s="4" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E283" s="4" t="inlineStr">
+      <c r="F283" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -7643,17 +8635,20 @@
           <t>Alam mo ba na may bagong panukala ang pamahalaan na tinatawag na “Barangay Leadership Shuffle” kung saan bawat anim na buwan ay palitan daw ng mga opisyal ng barangay sa iba’t ibang lugar para raw maiwasan ang katiwalian at masigurong sariwa at patas ang pamumuno sa bawat komunidad, kaya’t maraming mamamayan ang nagsasabing mas magiging epektibo raw ang serbisyo dahil hindi na magtatagal sa puwesto ang mga lider na posibleng magkaroon ng sariling interes, habang ang ilan naman ay natutuwa dahil magkakaroon ng pantay-pantay na oportunidad ang bawat barangay na makaranas ng iba’t ibang istilo ng pamumuno, dahilan upang tumaas ang tiwala ng publiko sa gobyerno at mas gumanda umano ang takbo ng mga proyekto sa lokal na antas, kaya’t marami na ang nag-aabang kung kailan ipatutupad ang ganitong sistema na balak gawing modelo ng buong bansa.</t>
         </is>
       </c>
-      <c r="C284" s="4" t="inlineStr">
+      <c r="C284" s="5" t="n">
+        <v/>
+      </c>
+      <c r="D284" s="4" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D284" s="4" t="inlineStr">
+      <c r="E284" s="4" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E284" s="4" t="inlineStr">
+      <c r="F284" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -7668,17 +8663,20 @@
           <t>Mga kababayan, alam niyo ba na may kumakalat na balita tungkol sa umano’y sikreto ng alkalde ng Bayan ng Maligaya na sinasabing may tinatagong “shadow council” na siyang tunay na nagpapasya sa lahat ng proyekto at pondo ng lokal na pamahalaan, ayon sa mga naglalabasan sa social media? Sinasabi raw ng ilang insider na hindi ang opisyal na konseho ang nagdedesisyon kundi isang grupo ng malalapit na kaibigan at kamag-anak ng alkalde na palihim na nagtatagpo tuwing gabi sa isang kilalang restawran para pag-usapan kung kanino mapupunta ang mga kontrata at ayuda, at may mga naglalabasang screenshot ng chat na tila nagpapakita ng mga listahan ng pangalan at halaga ng “pabor” na ibinibigay kapalit ng suporta; dahil dito, marami ang nagtatanong kung totoo bang may lihim na sindikato sa likod ng bawat proyekto ng bayan at kung may pag-asa pa bang maging tapat ang pamamahala sa Maligaya, kaya’t patuloy ang diskusyon online kung dapat na bang imbestigahan ang umano’y “shadow council” ng alkalde.</t>
         </is>
       </c>
-      <c r="C285" s="4" t="inlineStr">
+      <c r="C285" s="5" t="n">
+        <v/>
+      </c>
+      <c r="D285" s="4" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D285" s="4" t="inlineStr">
+      <c r="E285" s="4" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E285" s="4" t="inlineStr">
+      <c r="F285" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -7693,17 +8691,20 @@
           <t>Isang nakakabiglang insidente ang yumanig sa Barangay Mapayapa matapos salakayin ng mga pulis ang isang abandonadong warehouse na umano’y ginawang taguan ng isang grupo ng mga hinihinalang international hacker, kung saan ayon sa ulat ay tumambad sa mga awtoridad ang napakaraming computer, cash, at mga pekeng dokumento na ginagamit daw sa malakihang online scam na umabot na sa milyon-milyong piso ang naloko mula sa iba’t ibang panig ng bansa; nagkaroon pa raw ng habulan at barilan sa loob ng compound, dahilan para magdulot ng takot sa mga residente at mag-viral agad ang mga kuhang video ng operasyon sa social media, at ayon sa pulisya ay may mga nakuha pa silang kakaibang gadget na pinaniniwalaang ginagamit sa pag-hack ng mga bank account, kaya’t patuloy ang imbestigasyon kung sino-sino pa ang kasabwat at kung may mga opisyal na sangkot sa malawakang krimen na ito na tinaguriang “Operation Cyberstorm” ng mga otoridad.</t>
         </is>
       </c>
-      <c r="C286" s="4" t="inlineStr">
+      <c r="C286" s="5" t="n">
+        <v/>
+      </c>
+      <c r="D286" s="4" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D286" s="4" t="inlineStr">
+      <c r="E286" s="4" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E286" s="4" t="inlineStr">
+      <c r="F286" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -7718,17 +8719,20 @@
           <t>Nagulantang ang buong Barangay San Rafael kagabi matapos magsagawa ng matinding operasyon ang mga pulis kung saan mahigit dalawampung katao ang sabay-sabay na inaresto sa isang abandonadong gusali na umano’y ginagamit bilang lihim na taguan ng mga pekeng pera at mamahaling gadgets; ayon sa ulat ng hepe ng pulisya, nahuli ang grupo matapos makatanggap ng tip mula sa isang concerned citizen na may kahina-hinalang aktibidad sa lugar, kaya’t agad naglunsad ng raid na umabot ng tatlong oras at nagresulta sa pagkakakumpiska ng mga printer, laptop, at sako-sakong peke na perang may mukha ng mga cartoon character, dahilan upang magdulot ng takot at pagkabahala sa mga residente na hindi makapaniwala sa lawak ng operasyon, habang marami ang humanga sa bilis ng aksyon ng kapulisan at nagpaabot ng pasasalamat sa kanilang pagiging alerto at epektibo sa pagsugpo ng krimen sa kanilang komunidad.</t>
         </is>
       </c>
-      <c r="C287" s="4" t="inlineStr">
+      <c r="C287" s="5" t="n">
+        <v/>
+      </c>
+      <c r="D287" s="4" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D287" s="4" t="inlineStr">
+      <c r="E287" s="4" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E287" s="4" t="inlineStr">
+      <c r="F287" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -7743,17 +8747,20 @@
           <t>Viral ngayon sa social media ang isang video na nagpapakita ng matinding police operation sa isang lumang warehouse sa gilid ng Lungsod ng San Rafael, kung saan makikita ang dose-dosenang SWAT at K9 units na sabay-sabay na sumugod matapos makatanggap ng tip mula sa isang anonymous online whistleblower; ayon sa mga netizens na nakasubaybay sa live update, nagmistulang eksena sa action movie ang nangyari dahil may mga drone na nagliparan habang pinapalibutan ng mga pulis ang gusali, at ilang minuto lang matapos ang raid ay nailabas na ang sangkatutak na kahon ng umano’y pekeng luxury items, mga high-tech na gadget, at isang vault na puno raw ng cash na nagkakahalaga ng milyon-milyong piso, dahilan para umani ng libu-libong shares at comments ang balita, at marami ang nagtanong kung paano nakalusot ng matagal ang sindikato gayong nasa gitna lang ito ng siyudad; dagdag pa sa kontrobersiya, may mga haka-haka na may kasabwat daw na opisyal sa loob ng lokal na pamahalaan kaya’t lalo pang uminit ang usapan online, at hinihintay na ng lahat ang opisyal na pahayag ng PNP kung sino ang mga sangkot sa malakihang operasyong ito na tinaguriang “Operation Night Falcon.”</t>
         </is>
       </c>
-      <c r="C288" s="4" t="inlineStr">
+      <c r="C288" s="5" t="n">
+        <v/>
+      </c>
+      <c r="D288" s="4" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D288" s="4" t="inlineStr">
+      <c r="E288" s="4" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E288" s="4" t="inlineStr">
+      <c r="F288" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -7768,17 +8775,20 @@
           <t>Totoo nga kayang may sikretong relasyon ang rising star na si Mikael Dela Cruz at ang kilalang direktor na si Arvin Salazar matapos kumalat ang isang video na umano’y kuha sa isang private party kung saan makikitang magkahawak-kamay silang dalawa habang nagbubulungan sa isang sulok; agad itong pinagpyestahan ng mga netizen at nagdulot ng sari-saring reaksyon, may ilan pang nagsabing ito raw ang dahilan kung bakit biglang nabigyan ng lead role si Mikael sa bagong pelikula ni Direk Arvin kahit baguhan pa lang siya sa industriya, kaya’t usap-usapan ngayon kung may favoritism o iba pang nangyayaring hindi kanais-nais sa likod ng camera, habang tikom pa rin ang bibig ng kampo ng dalawa sa kabila ng patuloy na pagdami ng mga haka-haka at memes tungkol sa kanila sa social media.</t>
         </is>
       </c>
-      <c r="C289" s="4" t="inlineStr">
+      <c r="C289" s="5" t="n">
+        <v/>
+      </c>
+      <c r="D289" s="4" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D289" s="4" t="inlineStr">
+      <c r="E289" s="4" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E289" s="4" t="inlineStr">
+      <c r="F289" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -7793,17 +8803,20 @@
           <t>Totoo nga kayang nagkaroon ng palihim na relasyon ang sikat na aktor na si Marco Dela Vega at ang kanyang personal assistant na si Jenny Rosales habang kasagsagan ng shooting ng kanilang bagong teleserye? Ayon sa mga umano’y insider, madalas daw mahuli ang dalawa na magkasama sa dressing room at nagkakaroon pa raw ng mga late night meetings na hindi kasama ang ibang staff, kaya’t nagdulot ito ng espekulasyon na may namamagitan sa kanila na higit pa sa propesyonal na ugnayan; lalong uminit ang usapan nang biglang mag-unfollow si Marco sa social media ng rumored girlfriend niyang si Carla Montenegro, at ilang netizens ang nagsasabing ito raw ay patunay na may tensyon na sa kanilang relasyon dahil sa isyung ito, kaya’t abala ngayon ang mga fans sa paghahanap ng ebidensya at patuloy na sinusubaybayan ang bawat kilos ni Marco at Jenny sa set.</t>
         </is>
       </c>
-      <c r="C290" s="4" t="inlineStr">
+      <c r="C290" s="5" t="n">
+        <v/>
+      </c>
+      <c r="D290" s="4" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D290" s="4" t="inlineStr">
+      <c r="E290" s="4" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E290" s="4" t="inlineStr">
+      <c r="F290" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -7818,17 +8831,20 @@
           <t>Mga kababayan, hindi mapigilan ang ingay sa showbiz matapos pumutok ang balitang umano’y nahuli sa isang exclusive resort si Lira Velasco, ang sikat na aktres na bida sa teleseryeng “Pusong Ligaw,” kasama ang isang kilalang music producer habang nagkakaroon daw ng mainit na pagtatalo tungkol sa umano’y leaked demo tracks na sinasabing naglalaman ng mga sensitibong lyrics na patama umano sa ilang kapwa artista; ayon sa mga kumalat na larawan at video, makikitang umiiyak si Lira habang pilit na pinapakiusapan ang producer na huwag daw ipalabas ang mga kanta, dahilan para magdulot ito ng espekulasyon na may mas malalim pang isyu sa likod ng kanilang pagtatalo, kaya’t dagsa ngayon ang mga fans at bashers sa social media na humihingi ng paliwanag mula sa kampo ni Lira at nag-aabang kung paano magtatapos ang kontrobersiyang ito.</t>
         </is>
       </c>
-      <c r="C291" s="4" t="inlineStr">
+      <c r="C291" s="5" t="n">
+        <v/>
+      </c>
+      <c r="D291" s="4" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D291" s="4" t="inlineStr">
+      <c r="E291" s="4" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E291" s="4" t="inlineStr">
+      <c r="F291" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -7843,17 +8859,20 @@
           <t>Nagulat ang buong bansa matapos ianunsyo ng Federation of Local Business Owners na biglang bumagsak ang presyo ng lahat ng pangunahing bilihin sa loob lamang ng isang araw, dahilan upang magsara ang mahigit 70 porsyento ng mga tindahan at pabrika sa buong bansa dahil hindi na umano kayang tustusan ang gastos sa produksyon; ayon sa mga ulat, nag-ugat daw ang krisis sa isang misteryosong glitch sa digital trading system ng bansa na nagdulot ng sabayang pagbaba ng halaga ng bigas, karne, gulay, at maging ng kuryente at tubig, kaya’t nag-panic ang mga mamimili at nagkaubusan ng stocks sa mga groceries, habang ang ilan ay nagprotesta sa harap ng mga bangko dahil sa hindi nila ma-withdraw ang kanilang pera na biglang nabawasan ng kalahati, at ngayon ay nananawagan ang mga eksperto na magpatupad ng state of emergency para maiwasan ang tuluyang pagbagsak ng ekonomiya at mapigilan ang pagdagsa ng mga dayuhang negosyante na gustong bilhin ang mga lokal na negosyo sa sobrang baba ng halaga.</t>
         </is>
       </c>
-      <c r="C292" s="4" t="inlineStr">
+      <c r="C292" s="5" t="n">
+        <v/>
+      </c>
+      <c r="D292" s="4" t="inlineStr">
         <is>
           <t>economy / business</t>
         </is>
       </c>
-      <c r="D292" s="4" t="inlineStr">
+      <c r="E292" s="4" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E292" s="4" t="inlineStr">
+      <c r="F292" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -7868,17 +8887,20 @@
           <t>Isang malakas na pagsabog ng bulkan ang diumano’y yumanig sa buong bayan ng San Lorenzo kagabi, ayon sa mga viral na post sa social media na nagsasabing umabot hanggang 10 kilometro ang taas ng abo at nagdulot ito ng biglaang dilim na parang gabi kahit tanghali pa lang, dahilan upang magtakbuhan palabas ng kanilang mga bahay ang mga residente dala-dala ang kanilang mga gamit at alagang hayop; may mga ulat pa na tila nagkaroon ng malalaking bitak sa lupa, umuulan ng bato at may kakaibang amoy ang hangin na nagdulot ng pagkahilo at pag-ubo ng mga tao, kaya’t marami ang nag-panic at nagdesisyong lumikas sa mga kalapit-bayan, habang ang mga video na nagpapakita ng makapal na usok at tila apoy mula sa bunganga ng bulkan ay patuloy na kumakalat online, dahilan upang marami ang natatakot na baka masundan pa ito ng mas malakas na pagsabog at mas matinding pinsala sa kalikasan at kabuhayan ng mga taga-San Lorenzo.</t>
         </is>
       </c>
-      <c r="C293" s="4" t="inlineStr">
+      <c r="C293" s="5" t="n">
+        <v/>
+      </c>
+      <c r="D293" s="4" t="inlineStr">
         <is>
           <t>disaster / environment</t>
         </is>
       </c>
-      <c r="D293" s="4" t="inlineStr">
+      <c r="E293" s="4" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E293" s="4" t="inlineStr">
+      <c r="F293" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -7893,17 +8915,20 @@
           <t>Matapos ang ilang linggo ng matinding tensyon sa pagitan ng Pilipinas at isang bansang Europeo, biglang nag-trending sa social media ang balita tungkol sa umano’y “Mango Dispute” kung saan diumano ay naharang sa isang malaking paliparan sa Europa ang mahigit limang toneladang mangga mula Pilipinas dahil umano sa kakaibang amoy at kulay nito, dahilan upang magpatawag ng emergency meeting ang mga opisyal ng dalawang bansa; ayon sa mga netizen, nagbanta pa raw ang European ambassador na ipapatigil ang pag-aangkat ng mangga mula Pilipinas kung hindi mapapatunayan na ligtas ito kainin, kaya’t nagkaroon ng online petition ang mga Pilipino sa buong mundo na ipaglaban ang kalidad ng ating mangga, at kasabay nito ay nagkaroon pa ng viral challenge kung saan ipinapakita ng mga Pinoy abroad na kumakain sila ng manggang kalabaw habang sumisigaw ng “Mango is love, Mango is life,” habang hinihintay pa rin ng lahat ang opisyal na pahayag ng Department of Agriculture kung paano nila lulutasin ang diplomatikong isyung ito.</t>
         </is>
       </c>
-      <c r="C294" s="4" t="inlineStr">
+      <c r="C294" s="5" t="n">
+        <v/>
+      </c>
+      <c r="D294" s="4" t="inlineStr">
         <is>
           <t>international news</t>
         </is>
       </c>
-      <c r="D294" s="4" t="inlineStr">
+      <c r="E294" s="4" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E294" s="4" t="inlineStr">
+      <c r="F294" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -7918,17 +8943,20 @@
           <t>Alam mo ba na ayon sa bagong viral na pag-aaral na lumalaganap ngayon sa social media, ang pagkain ng hilaw na saging tuwing alas-tres ng hapon ay nakakatulong daw hindi lang sa pagpapapayat kundi pati sa pagpapaganda ng kutis at pag-iwas sa stress, kaya naman dagsa ngayon ang mga kabataan at matatanda sa mga palengke ng Barangay Maligaya para bumili ng saging at sabay-sabay itong kainin sa itinakdang oras; sinasabi pa sa mga post na kapag sinabayan mo raw ito ng pag-inom ng malamig na tubig, mas mabilis umanong mawawala ang pagod at magkakaroon ka pa ng dagdag na enerhiya buong araw, kaya’t marami na ang sumubok at nagbahagi ng kanilang positibong karanasan online kahit wala pang kumpirmasyon mula sa mga eksperto kung totoo nga ba ang mga benepisyong ito.</t>
         </is>
       </c>
-      <c r="C295" s="4" t="inlineStr">
+      <c r="C295" s="5" t="n">
+        <v/>
+      </c>
+      <c r="D295" s="4" t="inlineStr">
         <is>
           <t>lifestyle / human interest</t>
         </is>
       </c>
-      <c r="D295" s="4" t="inlineStr">
+      <c r="E295" s="4" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E295" s="4" t="inlineStr">
+      <c r="F295" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -7943,17 +8971,20 @@
           <t>Ikinagulat ng buong bayan ng San Isidro nang biglang lumitaw umano ang isang higanteng ilaw sa gitna ng simbahan habang nagmimisa, at ayon sa mga saksi, tila raw may boses na nagmumula sa liwanag na nagsasabing magkakaroon ng biyaya ang lahat ng dumalo sa misa, kaya't mabilis na kumalat sa social media ang mga video at larawan ng kakaibang pangyayari na ikinatuwa ng mga deboto at nagdulot ng pagdagsa ng libo-libong tao mula sa iba't ibang lugar na umaasang makakakita rin ng himala; may mga nagkuwento pa na pagkatapos ng insidente, bigla raw gumaling ang ilang matagal nang may sakit at may mga estudyanteng pumasa sa exam kahit hindi raw nag-aral, dahilan upang magdeklara ang lokal na simbahan ng espesyal na novena at magpatupad ng dagdag na misa araw-araw upang matugunan ang dami ng mga taong gustong makaranas ng sinasabing milagro, habang patuloy namang iniimbestigahan ng mga pari at eksperto ang misteryosong pinagmulan ng liwanag na naging usap-usapan na sa buong probinsya.</t>
         </is>
       </c>
-      <c r="C296" s="4" t="inlineStr">
+      <c r="C296" s="5" t="n">
+        <v/>
+      </c>
+      <c r="D296" s="4" t="inlineStr">
         <is>
           <t>religion</t>
         </is>
       </c>
-      <c r="D296" s="4" t="inlineStr">
+      <c r="E296" s="4" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E296" s="4" t="inlineStr">
+      <c r="F296" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -7968,17 +8999,22 @@
           <t>Isinapubliko ni Pangulong Rodrigo Duterte ang pangalan ng mga pulitiko na umano’y sangkot sa ilegal na droga sa kanyang narco-list, na binasa niya sa pulong ng National Peace and Order Council (NPOC) sa Davao City, kung saan sinabi niyang ang mga ito ay nasampahan na ng kasong administratibo ng Department of the Interior and Local Government (DILG). Kabilang sa listahan ang mga gobernador, vice-governor, kongresista, mayor, vice-mayor, at mga konsehal mula sa iba’t ibang bahagi ng bansa tulad ng Ilocos Norte, Cagayan Valley, Bulacan, Tarlac, Zambales, Laguna, Rizal, Batangas, Quezon, Palawan, Antique, Iloilo, Cebu, Eastern Visayas, Zamboanga del Norte, Zamboanga del Sur, Misamis Occidental, Sultan Kudarat, South Cotabato, Surigao del Sur, Maguindanao, Lanao del Sur, at Basilan. Ipinaliwanag ni Duterte na ang mga pangalan ay validated na at nakasuhan na sa Office of the Ombudsman, ngunit hindi niya isinama ang ibang pangalan na hindi pa lubos na nabeberipika upang maiwasan ang maling akusasyon at hindi makaapekto sa eleksyon. Dumalo rin sa pulong ang mga opisyal ng DILG, Armed Forces of the Philippines, Philippine National Police, at Philippine Drug Enforcement Agency.</t>
         </is>
       </c>
-      <c r="C297" s="4" t="inlineStr">
+      <c r="C297" s="5" t="inlineStr">
+        <is>
+          <t>Isinapubliko na ni Pangulong Rodrigo Duterte ang pangalan ng mga pulitiko na kasama sa kanyang narco-list o pulitikong sangkot sa iligal na droga. Sa talumpati sa pulong ng National Peace and Order Council (NPOC) sa Davao City, binasa ng Pangulo ang mga pangalan na kabilang sa kaniyang narco-list na aniya'y sinampahan na ng kasong administratibo ng Department of the Interior and Local Government (DILG). Kabilang sa listahan ng Pangulo ay ang ilang gobernador, vice-governors, congressmen, mayors, vice-mayors at ilang konsehal. 1. Pasuquin, Ilocos Norte Mayor Ferdinand Dancel Aguinaldo (re-electionist); 2. Ilocos congressman Jesus Celeste (did not file COC); 3. Lasam, Cagayan Valley Mayor Marjorie Apil Salazar (running for councilor); 4. San Rafael, Bulacan Mayor Cipriano Dungao Violago Jr. (re-electionist); 5. Camiling, Tarlac Mayor Erlon Clemente Agustin (re-electionist); 6. Subic, Zambales Mayor Jefferson Fernandez Khonghun (running for vice governor of Zambales); 7. Zambales congressman Jeffrey D. Khonghun (re-electionist); 8. Bay, Laguna Mayor Bruno Tolentino Ramos (did not file COC); 9. Los Banos, Laguna Mayor Caesar Pabalete Perez (re-electionist); 10. Rodriguez, Rizal Mayor Cecilio C. Hernandez (running for vice mayor); 11. Rodriguez, Rizal Vice Mayor Dennis Linco Hernandez (running for mayor); 12. Lemery, Batangas Mayor Eulalio Mendoza Alilio (re-electionist); 13. Ibaan, Batangas Mayor Juan Valencia Toreja (did not file COC); 14. San Pablo City, Laguna Mayor Loreto Sahagun Amante (re-electionist); 15. Teresa, Rizal Mayor Raul S. Palino (re-electionist); 16. Lucena City, Quezon Mayor Roderick Alcantara Alcala (re-electionist); 17. Rizal Province Board Member Rommel Cruz Ayuson (re-electionist); 18. El Nido, Palawan Mayor Nieves Cabunalda (re-electionist); 19. Culasi, Antique Mayor Ariel Tabugo Alagos Jr. (re-electionist); 20. Iloilo City Mayor Jed Patrick Escalante Mabilog (did not file COC, cannot be located); 21. Hamtic, Antique Mayor Julius Ronald Leyritana Pacificador (running for vice mayor); 22. Maasin, Iloilo Mayor Mariano Malficio Malones Sr. (running for vice mayor); 23. Siegfredo Alfuente Betita of Carles, Iloilo (running for mayor); 24. San Fernando, Cebu Vice Mayor Franz Cabilao Sabalones (did not file COC); 25. Daang Bantayan, Cebu Mayor Vicente Areno Loot (did not file COC); 26. Eastern Visayas congressman Vicente Sofronio Veloso (running for congressman); 27. Sirawai, Zamboanga del Norte Mayor Gamar Ahay Janihim (re-electionist); 28. Midsalip, Zamboanga del Sur Mayor Leonida Albor Angcap (re-electionist); 29. Sinacaban, Misamis Occidental Mayor Crisinciano Enot Mahilac (did not file COC); 30. Clarin, Misamis Occidental Mayor David Mabal Navarro (re-electionist); 31. Calamba, Misamis Occidental Mayor Ezel Tabuelog Villanueva (re-electionist); 32. Oroquieta City Mayor Jason Paredes Almonte (running for congressman); 33. Palimbang, Sultan Kudarat Mayor Abubakar Pendatun Maulana (running for vice mayor); 34. Banga, South Cotabato Mayor Albert Palencia (re-electionist); 35. Sto. Nino, South Cotabato Mayor Pablo Mondejar Matinong Jr. (re-electionist); 36. Lingig, Surigao del Sur Mayor Roberto Malijao Luna Jr. (re-electionist); 37. Talitay, Maguindanao Vice Mayor Abdulwahad M. Sabal (running for mayor); 38. Datu Saudi Ampatuan, Maguindanao Vice Mayor Anida A. Dimaukom (running for mayor); 39. Marawi City Vice Mayor Arafat Alim Salic (did not file COC, at large in connection to Marawi siege); 40. Maguing, Lanao del Sur Vice Mayor Jamal Abinal Pangandamun (re-electionist); 41. Maguing, Lanao del Sur Mayor Mamaulan Abinal Mulok (re-electionist); 42. Talitay, Maguindanao former Mayor Montasser Meling Sabal (running for vice mayor); 43. Datu Montawal, Maguindanao Vice Mayor Ohto Caumbo Montawal (running for mayor, at large); 44. Ampatuan, Maguindanao Mayor Rasul Mabang Sangki (re-electionist); 45. Datu Montawal, Maguindanao Mayor Vicman Kambang Montawal (for vice mayor); at 46. Hadji Muhtamad, Basilan Mayor Jamar Abdulla Mansul (did not file COC) Tiniyak rin ng Pangulo na hindi makalulusot ang mga binanggit niyang pangalan dahil validated na at nakasuhan na sa Office of the Ombudsman. Gayunman, hindi lahat ng pangalan ay binanggit ng Pangulo dahil hindi pa aniya nabeberipika ang iba. "For the time being ito lang muna. Kasi validated na eh. 'Yung iba I just want to be doubly sure. I'm not really interested in releasing it before and after the election because I do not have the slightest intention to hurt anybody or to be a cause of a failure of election of a certain man who wants to serve the public. So 'yung iba wag na muna kasi hindi ko sigurado," anang Pangulo. Kabilang sa nasabing pulong ang mga top officials ng DILG, Armed Forces of the Philippines, Philippine National Police at Philippine Drug Enforcement Agency. PANOORIN: PANGULONG DUTERTE PINANGALANAN ANG ILANG PULITIKO NA KABILANG SA 'NARCO-LIST'</t>
+        </is>
+      </c>
+      <c r="D297" s="4" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D297" s="4" t="inlineStr">
+      <c r="E297" s="4" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E297" s="4" t="inlineStr">
+      <c r="F297" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -7993,17 +9029,22 @@
           <t>Ipinakita na sa publiko ang mugshot ni Rodel Jayme, na itinuturong responsable sa pagpapakalat ng online video na "Ang Totoong Narco List" na naglalaman ng mapanirang paratang laban sa pamilya ni Pangulong Rodrigo Duterte; sa video, inilahad ng isang alyas 'Bikoy' na umano’y dating miyembro ng drug syndicate na sangkot daw sa ilegal na droga ang mga kaanak at malalapit kay Pangulong Duterte, kabilang pati ang menor de edad niyang anak na si Kitty. Natunton ng mga otoridad si Jayme matapos matukoy na siya ang nagmamay-ari ng Metrobalita, ang unang website na nagbahagi ng nasabing video, at ayon sa Department of Justice ay inihahanda na ang kasong inciting to sedition laban sa kanya, pati na rin ang posibleng child abuse. Kilala rin si Jayme bilang tagasuporta ng Liberal Party at may mga kumalat na larawan niya sa social media kasama ang ilang personalidad mula sa naturang partido.</t>
         </is>
       </c>
-      <c r="C298" s="4" t="inlineStr">
+      <c r="C298" s="5" t="inlineStr">
+        <is>
+          <t>Ipinakita na sa madla ang larawan ng mugshot ni Rodel Jayme, ang lalaking nasa likod umano ng pagpapakalat ng libelous online video laban sa pamilya ni Pangulong Rodrigo Duterte. Ang naturang online video ay may pamagat na "Ang Totoong Narco List". Ipinakilala sa nasabing video ang umano'y dating miyembro ng drug syndicate na si alya 'Bikoy'. Inakusahan ni Bikoy ang mga kapamilya at malalapit na tao kay Pangulong Duterte na sangkot umano sa kalakaran ng iligal na gamot. Hindi rin naawa si Bikoy sa menor de edad na anak ng Pangulo na si Kitty, at dinamay din ito sa paninirang puri. Si Jayme ay natunton ng otoridad matapos malaman na siya ang nag mamay-ari ng website na Metrobalita, ang unang website na nag-share ng libelous video. Ayon sa Department of Justice, kinakasa na raw ang kasong inciting to sedition laban kay Jayme. Posible din daw itong makasuhan ng child abuse. Si Jayme ay tagasuporta ng Liberal Party. Nakalap ng ilang kababayan natin sa social media ang mga larawan ni Jayme kasama ang mga kilalang personalidad ng Partido Liberal.</t>
+        </is>
+      </c>
+      <c r="D298" s="4" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D298" s="4" t="inlineStr">
+      <c r="E298" s="4" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E298" s="4" t="inlineStr">
+      <c r="F298" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -8018,17 +9059,22 @@
           <t>Lalong umiinit ang alitan sa pagitan ng pro-government blogger na si RJ Nieto, mas kilala bilang ThinkingPinoy, at ni Presidential Communications Operations Office (PCOO) Undersecretary Lorraine Badoy matapos akusahan umano ni Badoy na tumatanggap ng suhol ang mga bloggers na kumakampi sa mga biktima ng Dengvaxia, ayon kay Nieto. Sinabi ni Nieto na binansagan daw ni Badoy na sinuhulan siya para ipaglaban ang mga batang apektado ng Dengvaxia issue sa ilalim ng administrasyong Aquino. Hindi rin napigilan ni Sass Rogando Sasot, isa ring pro-government blogger at university lecturer, na magbigay ng sariling reaksyon sa isyu. Si Badoy, na dating sumuporta kay Vice President Leni Robredo, ay nakatanggap ng matinding batikos mula sa ilang Duterte supporters na nagduda sa kanyang kakayahan bilang USEC ng PCOO at hinamon siyang patunayan ang kanyang pagiging karapat-dapat sa posisyon, habang may ilan pang nanawagan ng kanyang pagbibitiw dahil umano sa kakulangan ng ambag at puro pansariling interes lamang daw ang inuuna niya.</t>
         </is>
       </c>
-      <c r="C299" s="4" t="inlineStr">
+      <c r="C299" s="5" t="inlineStr">
+        <is>
+          <t>Lumalaki na talaga ang hidwaan sa pagitan ni pro-government blogger RJ Nieto aka ThinkingPinoy at ni Presidential Communications Operations Office (PCOO) Undersecretary Lorraine Badoy. Ayon kay Nieto, inakusahan daw ni Badoy na tumatanggap daw ng suhol ang mga bloggers na na lumalaban sa Dengvaxia mess. "PCOO USEC. BADOY: DENGVAXIA VICTIMS' ADVOCATES RECEIVED BRIBES. Ayon kay PCOO Usec. Badoy, shamelessly claimed that bloggers like me received bribes in exchange for defending Dengvaxia victims. Tagalugin ko ha: sinuhulan lang raw ako para ipaglaban iyong isang milyong batang ginawang laboratory rat ng gobyernong Noynoy Aquino.," sabi ni Thinking Pinoy. Hindi na rin napigilan ng isa pang pro-government blogger at university lecturer na si Sass Rogando Sasot ang kanyang sarili at nagbigay na rin ng opinyon sa sinabi umano ni Badoy. Si Badoy ay dating taga-suporta ni Vice President Leni Robredo. Panoorin ang naging komento ni Sasot sa isyu.. Basahin ang naging reaksyon ng ilang Duterte supporters laban kay Badoy. "Mga unthinking follower daw tau? What a lame defense. Pati readers iniinsulto pa. It is time for her to prove why she is the USEC of PCOO and not telling us how she enjoys the trust of the President. She must be serving the people whom the president love. So ano na madam USEC PLS GIVE US A GOOD REASON TO BELIEVE YOU ARE WORTHY OF YOUR SALARY," sabi ni C. Santiago. "As I've said before...I just hope that President Duterte will realize the " stupidity " of this woman Badoy! Wag na Sana sya magpadala sa mga akap ek ek ng babaeng ito!..Wala nmn silbi eh!,"sabi ni L Peralta. "Hoy badoy mag resign ka na. Wala ka nmang naggawa jan sa pcoo. Imbes na inform mo ang mga tao sa ginagawa ng gobyerno.. waley... puro self interest ka lang.. dun na nga lang sa federalism di nyo magawa na mainform ang mga tao.. pwede ba. Di mo kami madadala sa mga pa digong my labs mo. Mag Resign ka na. Pati si miss Mocha na ginagawa nya yung trabaho pinagkaisahan nyo. ngayon naman sa dengvaxia.. ano ba.. resign badoy.. wala kang silbi.," sabi ni E. Euqil</t>
+        </is>
+      </c>
+      <c r="D299" s="4" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D299" s="4" t="inlineStr">
+      <c r="E299" s="4" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E299" s="4" t="inlineStr">
+      <c r="F299" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -8043,17 +9089,22 @@
           <t>Kahit na kulelat sa mga survey at hindi inendorso ng Iglesia ni Cristo, naniniwala pa rin si Otso Diretso senatorial candidate Florin Hilbay na panalo na ang kanilang grupo anuman ang maging resulta ng eleksyon, dahil nakabuo sila ng malaking pamilyang Otso Diretso. Ayon kay dating Solicitor General Hilbay, mula ngayon hanggang Mayo 13, bitbit nila ang pangalan ng Otso Diretso. Sinegundahan ito ni reelection senator Bam Aquino na nagsabing marami na silang napuntahan at nakausap, at kahit sa palengke ay may mga tahimik na sumusuporta sa kanila. Samantala, sinabi ni Senador Kiko Pangilinan na posible pa ring magkaroon ng "surprise win" para sa Otso Diretso at binigyang-diin na ang pinakamahalagang survey ay ang mismong araw ng halalan, dahil may mga pagkakataon na ang mga hindi pasok sa top 12 ay nananalo pa rin sa dulo. Matatandaan na noong 2016 elections, kahit nanguna si Bongbong Marcos sa survey at inendorso ng Iglesia ni Cristo, si VP Leni Robredo pa rin ang nanalo, at ngayon ay dinidinig na sa Korte Suprema ang petisyon ni Marcos laban sa pagkapanalo ni Robredo.</t>
         </is>
       </c>
-      <c r="C300" s="4" t="inlineStr">
+      <c r="C300" s="5" t="inlineStr">
+        <is>
+          <t>"Umulan man o bumagyo, Otso Diretso pa rin," Sa kabila ng pagiging kulelat sa survey at hindi pag-endorso ng Iglesia ni Cristo, naniniwala si Otso Diretso senatorial candidate Florin Hilbay na kahit anu pa raw ang maging resulta ng eleksyon ay nanalo raw na ang kanyang grupong Otso Diretso. "Kahit anong mangyari, nanalo na tayo. Tayo ay nakapagtayo ng napakalaking pamilya, ang pamilya ng Otso Diretso. Simula ngayon hanggang Mayo 13, ang pangalan nating lahat ay Otso Diretso," sabi ni dating Solicitor General Hilbay. Ang mga pahayag ni Hilbay ay sinegundahan naman ni reelection senator Bam Aquino. "Alam niyo po, mga kaibigan, napakaraming lugar na po ang napuntahan po namin. Napakarami po ang naka-usap na po namin. Noong una, iikot po kami sa palengke. Pabulong: 'Senator, Otso Diretso po kami,'" ayon kay Bam. Magugunita sa isang panayam, sinabi ni Senador Kiko Pangilinan na posibleng magkaroon daw ng "suprise win" para sa Otso Diretso. "Sabi nga nila ang pinakamahalagang survey, ay 'yung araw ng halalan. At sa aking labing-walong taon bilang senador... nakita natin, may mga pangyayari na sa huling dalawang linggo ng eleksyon, 'yung mga nasa labas ng top 12 pagdating ng araw ng halalan ay 'come from behind' ika nga at naipapanalo nila," sabi ni Pangilinan. Matatandaang na sa kabila ng pangunguna ni former senator Bongbong Marcos sa mga surveys at pag-endorso ng Iglesia ni Cristo, biglang nanalo si VP Leni Robredo noong halalan 2016. Ngayon ay dinidinig na sa Korte Suprema ang petisyon ni Marcos para kuwestiyunin ang pagkapanalo ni Robredo.</t>
+        </is>
+      </c>
+      <c r="D300" s="4" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D300" s="4" t="inlineStr">
+      <c r="E300" s="4" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E300" s="4" t="inlineStr">
+      <c r="F300" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -8068,17 +9119,22 @@
           <t>Napatunayang guilty si Reynaldo Parojinog Jr., anak ng yumaong dating Ozamiz City Mayor Reynaldo Parojinog, ng Quezon City Regional Trial Court Branch 79 dahil sa illegal possession of drugs, kung saan hinatulan siya ng reclusion perpetua o habangbuhay na pagkakakulong at multang mula P500,000 hanggang P10,000,000 ayon sa Section 11, Article II ng Comprehensive Dangerous Drugs Act of 2002. Nadakip si Parojinog Jr. sa isang operasyon ng pulisya na naging sanhi rin ng pagkasawi ng kanyang ina na si Susan, at sa parehong operasyon ay naaresto rin at nakulong ang kanyang kapatid na si Vice Mayor Nova Princess Parojinog-Echavez. Matatandaang noong Nobyembre 2018 ay nagbanta si Pangulong Rodrigo Duterte na "uubusin" niya ang mga Parojinog.</t>
         </is>
       </c>
-      <c r="C301" s="4" t="inlineStr">
+      <c r="C301" s="5" t="inlineStr">
+        <is>
+          <t>Napatunayang guilty ng Quezon City Regional Trial Court (RTC) Branch 79 si Reynaldo Parojinog Jr. dahil sa illegal possession of drugs. Si Parojinog Jr. ay anak ni dating Ozamiz City Mayor Reynaldo Parojinog na nasawi sa operasyon kontra iligal na droga sa kanilang tahanan. Sa desisyon ng Quezon City RTC Branch 79, reclusion perpetua o habang buhay na pagkakakulong ang hatol kay Parojinog Jr. matapos mapatunayang lumabag ito sa Section 11, Article II ng Comprehensive Dangerous Drugs Act of 2002. Maliban sa panghabambuhay na pagkakakulong, papatawan ng P500,000 hanggang P10,000,000 multa si Parojinog Jr. Si Parojinog Jr. ay isa sa mga nadakip sa operasyon ng pulisya na ikinasawi rin ng kanilang ina na si Susan. Kasama niyang naaresto at nakulong ang kapatid na si Vice Mayor Nova Princess Parojinog-Echavez sa parehong operasyon. Matatandaan na Nobyembre 2018 nang sinabi ni Pangulong Rodrigo Duterte na "uubusin" niya ang mga Parojinog. PANOORIN: REYNALDO PAROJINOG JR. HINATULANG GUILTY SA KASONG ILLEGAL POSSESSION OF PROHIBITED DRUGS</t>
+        </is>
+      </c>
+      <c r="D301" s="4" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D301" s="4" t="inlineStr">
+      <c r="E301" s="4" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E301" s="4" t="inlineStr">
+      <c r="F301" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -8093,17 +9149,22 @@
           <t>Isang trahedya ang sinapit ng 24-anyos na babae matapos siyang gahasain at patayin ng isang construction worker na gumagamit umano ng droga sa Quezon City, kung saan natagpuang wala nang buhay at wasak ang mukha ng biktima. Batay sa ulat, nagkasama pa sa isang birthday party ang biktima at ang suspek na si Rommel Formento, na umuupa rin sa bahay ng biktima. Ayon kay QCPD CIDU Chief C/Insp. Elmer Monsalve, nang makapasok si Formento sa bahay ng biktima ay agad nitong isinagawa ang krimen, at nang sumigaw ang babae ay lalo pa nitong sinaktan ang biktima. Labis ang hinanakit ng ama ng biktima, na nagsabing wala umanong konsensya ang suspek at masakit para sa kanya ang sinapit ng kanyang anak. Nagpahayag din ng pagkabigla at lungkot ang mga kapitbahay sa naganap na krimen.</t>
         </is>
       </c>
-      <c r="C302" s="4" t="inlineStr">
+      <c r="C302" s="5" t="inlineStr">
+        <is>
+          <t>Kalunos-lunos ang sinapit ng 24-anyos na babae sa kamay ng isang durugistang contruction worker sa lungsod ng Quezon. Wala ng buhay, wasak ang mukha at ginahasa pa. Ayon pa sa ulat, nagkasama pa umano sa isang birthday party ang biktima at ang suspek. Napag-alaman din na nangungupahan sa bahay ng biktima ang suspek na si Rommel Formento. "Noong nakapasok na siya, 'yun na, ginawa niya na ang kahalayan. Kaya lang sumigaw ang babae. Kaya nagising at nagawa niya na ang gusto niya. Inuntog-untog niya,"pahayag ni QCPD CIDU Chief C/Insp, Elmer Monsalve. "Walang konsyesiya. Pinakasamahan ko lang siya. Sumasakit ang llob ko sa kanya sa karumal-dumal na ginawa niya,"Sabi ng tatay ng biktima. Ito po ang naging komento ng mga kababayan natinsa nangyaring krimen.</t>
+        </is>
+      </c>
+      <c r="D302" s="4" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D302" s="4" t="inlineStr">
+      <c r="E302" s="4" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E302" s="4" t="inlineStr">
+      <c r="F302" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -8118,17 +9179,22 @@
           <t>Nahuli sa isang buy-bust operation sa Cavite ang isang alagad ng simbahan matapos makabili ang mga pulis ng P200 halaga ng hinihinalang shabu mula sa suspek, ayon sa paunang ulat ng DZMM TeleRadyo. Hindi agad pinangalanan ang pari habang nangangalap pa ng dagdag na impormasyon ang reporter, ngunit kinumpirma ng pulisya na si Richard Alcantara ang suspek at hindi siya miyembro ng Catholic Church. Malaking dagok ito sa imahe ng mga nagpapakilalang alagad ng Diyos, lalo na't nitong mga nagdaang taon ay may ilang pari na nasangkot sa mga kontrobersiya gaya ng tangkang panghahalay at pagkakadawit sa pagpatay. Maraming netizen ang naglabas ng kani-kanilang reaksyon, kabilang na ang pagsabi na laganap ang kasamaan anuman ang relihiyon, at panawagan sa mga lider ng simbahan na magsalita kaugnay ng insidente.</t>
         </is>
       </c>
-      <c r="C303" s="4" t="inlineStr">
+      <c r="C303" s="5" t="inlineStr">
+        <is>
+          <t>Huli ka! Nabitag ang isang alagad ng simbahan sa isinagawang buy-bust operation sa Cavite. Base sa mga paunang impormasyon ng DZMM TeleRadyo, nakabili ng P200 halaga ng hinihinalang shabu ang mga kapulisan sa nasabing suspek. Hindi pa pinapangalanan ang naturang pari pero nangangalap na ng karagdagang impormasyon ang reporter ng DZMM patungkol sa insidente. Isa itong malaking dagok sa hanay ng mga nagpapakilalang alagad ng Diyos kung mapapatunayan ang nangyaring buy-bust sa pari. Itong mga nagdaang mga taon ay nasangkot ang ilang alagad ng simbahan sa mga matitinding iskandalo. May isa paring na muntik ng makapanghalay ng menor de edad, ang isa naman ay iniuugnay sa pagkakapaslang sa isang babae. Basahin ang reaksyon ng mga kababayan natin patungkol sa balitang paring pusher. "Kahit Anong sekta kapa o anuman religion mo talaga laganap na mga demonyo sa Mundo. Mapapulitika man o kahit ano pang position mo sa buhay. Maraming nagbabait baitan pero demonyo pala ang katauhan," sabi ni L. Cruto. "Ayan tayoy eh... Lolo Bacani ano ito pwede ba mag ingay ka at ttukan kaso ng mga ksmahan mo mukhang banal pero nagbvinta pla ng droga," sabi ni R. Peneyra. "Nasaan mga bishop na puro kontra sa War on Drugs ng Administrasyon Duterte yung alagad niyo Pari timbog sa buy-bust Operation mag salita kayo ngayon mga Bishop ," sabi ni J. Derck. "Oh ayan di lng pla rapist at manyakis ang mga pari nagtu2lak na rin ..iba na hawak ng pari ngaun sa halip na bible shabu na," sabi ni L. Ocampo. Ayon sa pahayag ng pulisya, ang pari ay si Richard Alcantara at ang nasabing pari ay hindi miyembro ng Catholic Church.</t>
+        </is>
+      </c>
+      <c r="D303" s="4" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D303" s="4" t="inlineStr">
+      <c r="E303" s="4" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E303" s="4" t="inlineStr">
+      <c r="F303" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -8143,17 +9209,22 @@
           <t>Usap-usapan ngayon sa social media ang umano’y panggagaya ng kinatawan ng Thailand na si Ingchanok Prasart sa trademark na "lava walk" ni Miss Universe 2018 Catriona Gray sa Miss Intercontinental 2018, matapos mapansin ng netizen na si Marnie Raro sa Twitter ang paraan ng paglalakad at pag-project ni Miss Thailand na tila kinopya ang istilo ni Catriona; napansin din ng mga netizens ang pagkakahawig ng "Mayon Volcano gown" ni Miss Vietnam sa gown ni Catriona, at inamin naman ng dalawa na iniidolo at inspirasyon nila si Catriona Gray, dahilan upang magkahalo ang reaksyon ng netizens—may mga nagsabing malaki ang impluwensya ni Catriona at may nagsabing hindi kailanman mapapantayan ang orihinal niyang "lava walk," habang may ilan ding nanawagan na hayaang magpahayag ng paghanga ang ibang kandidata; patunay ito na maraming beauty pageant candidates sa buong mundo ang humahanga kay Catriona, bagay na inamin ng maraming kandidata ng katatapos lang na pageant na ginanap noong Enero 26, 2019 sa SM Mall of Asia Arena sa Pasay, kung saan kinoronahan ni Miss Intercontinental 2017 Veronica Salas Vallejo ng Mexico ang kandidata ng Pilipinas na si Karen Juanita Gallman, at ito rin ang unang pagkakataon na naging host ang Pilipinas sa pageant na ito matapos piliin ng Japan organizers ang bansa bilang venue dahil abala ang Japan sa paghahanda para sa 2020 Summer Olympics.</t>
         </is>
       </c>
-      <c r="C304" s="4" t="inlineStr">
+      <c r="C304" s="5" t="inlineStr">
+        <is>
+          <t>Usap-usapan ngayon sa social media ang umano'y panggagaya ng kinatawan ng Thailand na si Ingchanok Prasart sa ginanap na Miss Intercontinental pageant 2018 sa trademark ni Miss Universe 2018 Catriona Gray na "lava walk." Isang netizen sa Twitter na nagngangalang Marnie Raro ang nakapansin sa paraan ng paglalakad at pag-project ni Miss Thailand na parang kinokopya ang "lava walk" ni Catriona. Bukod kay Miss Thailand, napansin din ng mga netizens ang pagkopya umano sa "Mayon Volcano gown" ni Miss Vietnam. Aminado naman ang dalawa na labis nilang hinahangaan at inspirasyon nila si Miss Universe 2018 Catriona Gray. Halo-halo naman ang naging reaksyon ng mga netizens hinggil dito. "So now everyone looks like Catriona Gray. From hair to stance to gowns. The influence. Only legends do that." "Catriona Gray's walk can never be perfect without her walking it." "I think so? Even the hand gesture of Miss Thailand seems copied too. Catriona Gray is indeed a queen." "Yet they can't copy the original. Because there will be only one Lava Walk and Catriona Gray." "Kayo na 'yung may mga originality... hala gawa kayo sarili niyong pageant, ano ba naman yung hayaan niyo na lang sila hays....daming toxic." Isang patunay lamang ito na maraming mga aspiring beauty pageant candidates, hindi lamang sa Pilipinas kundi maging sa buong mundo, ang tumitingala at humahanga kay Catriona. Aminado naman dito ang marami sa mga kandidata ng naturang katatapos na pageant. Ang 47th edition ng Miss Intercontinental 2018 ay ginanap noong Enero 26, 2019, sa SM Mall of Asia Arena sa Pasay, Metro Manila, Philippines. Kinoronahan ni Miss Intercontinental 2017 Veronica Salas Vallejo ng Mexico ang kandidata ng Pilipinas na si Karen Juanita Gallman. Ito ang kauna-unahang pagkakataong naging host ang Pilipinas sa pageant na ito. Pinili ng Japan organizers ang Pilipinas na maging venue ng pageant dahil abala ang bansang Japan sa mga paghahanda para sa 2020 Summer Olympics. Narito ang buong Twitter post ng netizen:</t>
+        </is>
+      </c>
+      <c r="D304" s="4" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D304" s="4" t="inlineStr">
+      <c r="E304" s="4" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E304" s="4" t="inlineStr">
+      <c r="F304" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -8168,17 +9239,22 @@
           <t>Ngayong araw, nagtungo sa Malacañang ang ilang artista, mang-aawit, at basketball players upang makipagkita kay Pangulong Rodrigo Duterte, kabilang sina Vhong Navarro, Bayani Agbayani, Eva Marie Poon, Ryan Bang, Ice Seguerra, Jhed Madella, Jayson Gainza, at ang magkapatid na sina Toni at Alex Gonzaga na pawang nagpakita ng Duterte fist sign; napansin din na may ilang celebrities mula sa Kapamilya network o ABS-CBN, na kasalukuyang may tensyon kay Pangulong Duterte dahil umano sa hindi pag-ere ng kanyang political ads at hindi pag-refund ng bayad noong eleksyon, dahilan kaya nagbanta ang Pangulo na hindi pipirmahan ang license renewal ng ABS-CBN na malapit nang mag-expire, at dumalo rin sa okasyon ang ilang dating at kasalukuyang basketball players gaya nina Sonny Thoss, Cyrus Baguio, JV Casio, at Willie Miller.</t>
         </is>
       </c>
-      <c r="C305" s="4" t="inlineStr">
+      <c r="C305" s="5" t="inlineStr">
+        <is>
+          <t>Nagtungo ngayong araw ang ilang artista, mang-aawit, at basketball players sa Malacanang para makipagkita kay Pangulong Rodrigo Duterte. Ilan sa mga celebrities na nakitang naka Duterte fist sign ay sina Vhong Navarro, Bayani Agbayani, Eva Marie Poon, Ryan Bang, Ice seguerra, Jhed Madella at jayson Gainza. Naroroon din ang magkapatid na sina Toni at Alex Gonzaga. Kapansin-pansin na ang ilang mga artista ay mula sa Kapamilya network o ABS-CBN. Alam ng lahat na galit si Pangulong Duterte sa ABS-CBN dahil ginantso daw siya noong panahon ng eleksyon. Ayon sa Presidente, hindi daw binalik ng himpilan ang binayad niya sa political ads niya kahit hindi ito inere ng istasyon. Nagbanta pa nga ang Pangulo na hindi niya pipirmahan ang license renewal ng ABS-CBN na malapit na mag-expire. Nakita rin ang ilang dati at kasalukuyang basketball players tulad nina Sonny Thoss, Cyrus Baguio, JV Casio at Willie Miller.</t>
+        </is>
+      </c>
+      <c r="D305" s="4" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D305" s="4" t="inlineStr">
+      <c r="E305" s="4" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E305" s="4" t="inlineStr">
+      <c r="F305" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -8193,17 +9269,22 @@
           <t>Ilang netizens ang nakasaksi sa pagtulong ni dating Philippine National Police Chief Ronald "Bato" Dela Rosa sa isang rider na naaksidente sa Pasay City. Sa mga larawang ibinahagi ni Carlo Dalusong Andrade sa social media, makikita si Bato na kinausap ang bus driver na nakabangga sa rider at agad na nagpatawag ng pulis para matulungan ang biktima. Suot pa ni Bato ang kanyang barong tagalog, na nagpapakitang may mahalaga siyang pupuntahan, ngunit hindi siya nag-atubiling bumaba ng sasakyan upang tumulong. Pinuri ni Andrade ang ginawa ni Bato at sinabi niyang nakita niya mismo ang pangyayari, kung saan huminto ang sasakyan ni Sen. Bato upang magbigay ng tulong at siya pa mismo ang nagpatwag ng enforcer. May isa ring netizen na nag-post ng video habang tumutulong si Bato sa biktima ng aksidente.</t>
         </is>
       </c>
-      <c r="C306" s="4" t="inlineStr">
+      <c r="C306" s="5" t="inlineStr">
+        <is>
+          <t>Ilang netizens ang nakakita sa pagtulong ni former Philippine National Police CHief Ronald "Bato" Dela Rosa sa isang rider na na-aksidente sa lungsod ng Pasay. Sa mga larawan na pinost ni Carlo Dalusong Andrade sa kanyang social media account, makikita si Bato na kinakausap ang driver ng bus na nakabangga sa rider at nagpatawag ng pulis para bigyan ng tulong ang nadisgrasya. Makikita sa mga litrato na naka barong tagalog pa si Bato at halatang may mahalagang pinuntahan o pupuntahan. Ikinatuwa ni Andrade ang ginawa ni Bato sa kapwa niya rider. "What a good man. Hindi nagatubili na bumaba sa sasakyan nia at tulungan ang kapwa ntn rider na nabundol na bus. Isang mapagpalang araw sayo. SENATOR BATO. Sana all... Nkita ko mismo yan kasunod ng bus ung sasakyan ni sen. Bato huminto tlga cla para tumulong sa nadisgrasya. Cia pa nagpatwag ng enforcer," sabi ni Andrade Isang netizen din ang nag-post video ng kuha niya kay Bato habang tumutulong sa biktima ng aksidente.</t>
+        </is>
+      </c>
+      <c r="D306" s="4" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D306" s="4" t="inlineStr">
+      <c r="E306" s="4" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E306" s="4" t="inlineStr">
+      <c r="F306" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -8218,17 +9299,22 @@
           <t>Sa pagbisita ni Pangulong Rodrigo Duterte sa Japan, inaasahang pipirmahan ng mga kumpanyang Filipino at Japanese ang mahigit 20 kasunduan na nagkakahalaga ng P300 billion, ayon sa Department of Trade and Industry (DTI), at tinatayang mahigit 80,000 trabaho ang malilikha para sa mga Pilipino. Gaganapin ang pagpirma ng mga business agreement kasabay ng pagdalo ni Pangulong Duterte sa 25th NIKKEI Conference on the Future of Asia mula Mayo 30 hanggang 31. Karamihan sa mga investment pledges ay nakatuon sa marine manpower industries, food manufacturing, automotive, transportation, kuryente, business process outsourcing, medical services, electronics, at infrastructure. Ayon kay DTI Secretary Ramon Lopez, nananatiling positibo ang mga Japanese investor sa patuloy na paglago ng ekonomiya ng Pilipinas dahil sa malawakang infrastructure projects, makabuluhang investment at financial reforms, at demographic advantages sa ilalim ng administrasyon ni Pangulong Duterte. Matapos ang keynote address ni Pangulong Duterte sa Nikkei Conference sa Mayo 31, makikipagpulong siya kay Japan Prime Minister Shinzo Abe. Pagdating ni Pangulong Duterte sa Haneda International Airport sa Japan, agad siyang nagtungo sa Imperial Hotel sa Tokyo.</t>
         </is>
       </c>
-      <c r="C307" s="4" t="inlineStr">
+      <c r="C307" s="5" t="inlineStr">
+        <is>
+          <t>Sa pagbisita ni Pangulong Rodrigo Duterte sa Japan, inaasahang lalagdaan ng mga Filipino at Japanese companies ang mahigit 20 kasunduan na nagkakahalaga ng P300 billion, ayon sa Department of Trade and Industry (DTI). Hindi naman baba sa 80,000 na trabaho ang malilikha ng mga kasunudan para sa mga kababayan natin. Pipirmahan ang mga business agreement sa sideline ng biyahe ni Pangulong Rodrigo Duterte sa Japan para sa 25th NIKKEI Conference on the Future of Asia na gaganapin sa May 30 hanggang 31. Karamihan sa mga investment pledges ay may kaugnayan sa marine manpower industries, food manufacturing, automotive, transportation, electircity, business processing outsource, medical services, electornics at infrastructure. "Japanese investors remain bullish on the sustained growth momentum under the administration of President Duterte, given its aggressive infrastructure build-up, meaningful investment and financial reforms, and demographic advantages," sabi ni DTI Secretary Ramon Lopez. Pagkatapos ng keynote address ng Pangulong Duterte sa Nikkei Conference sa Mayo 31, makikipagpulong ito kay Japan Prime Minister Shinzo Abe. Panoorin ang pagdating ni Pangulong Duterte sa Haneda International Airport sa Japan. Matapos ang paglapag ng Presidente sa paliparan ay dumiretso ito sa Imperial Hotel sa Tokyo.</t>
+        </is>
+      </c>
+      <c r="D307" s="4" t="inlineStr">
         <is>
           <t>economy / business</t>
         </is>
       </c>
-      <c r="D307" s="4" t="inlineStr">
+      <c r="E307" s="4" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E307" s="4" t="inlineStr">
+      <c r="F307" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -8243,17 +9329,22 @@
           <t>Para kay Vice President Leni Robredo, dapat magpaliwanag ang gobyerno sa publiko tungkol sa naranasang water shortage kamakailan sa ilang bahagi ng Kamaynilaan at Rizal, ayon sa kanyang pahayag sa programang "BISErbisyong Leni" sa radyo, kung saan binanggit din niyang naapektuhan siya at ang kanyang pamilya. Ilan sa mga reaksyon ng mga kababayan ay naglalaman ng kritisismo, gaya ng sinabi ni I. Batestil na bilang bise presidente ay dapat makatulong siya at hindi puro panayam, samantalang tinanong naman ni G. Reyes kung bakit tila hindi niya alam ang nangyayari gayong bahagi siya ng pamahalaan, at sinabi ni E. Jay na tila palaging kinokontra ni Robredo ang gobyerno kahit kabilang siya rito.</t>
         </is>
       </c>
-      <c r="C308" s="4" t="inlineStr">
+      <c r="C308" s="5" t="inlineStr">
+        <is>
+          <t>Para kay Vice President Leni RObredo, kailangan daw magpalawanag ang gobyerno sa publik patungkol sa angyari water shortage nitong mga nagdaang araw sa ilang parte ng kamaynilaan at sa Rizal. "Iyong tanong nga, ano ba talaga? Ano ba talaga 'yung kwento? Gusto sana nating marining sa pamahalaan bakit ba tayo umabot sa ganito," boladas ni Robredo sa kanyang programa sa Radyo na may pamagat na "BISErbisyong Leni" Ayon kay Leni, naapektuhan din daw siya pati ang kanyang kapamilya. Basahin ang reaksyon at tugon ng ilang kababayan natin sa pinagsasabi ni Leni. "Hindi ka ba parti nang gobyerno bruha ka? Pagkaka alam ko VP ka pa naman kahit fake ang pagka panalo mo. Tas ngayon tinatanong mo? Anong silbi nang posisyon mo pokpok ka. Tumulong ka VP. Mag trabaho ka at wag puro pa interview," sabi ni I. Batestil "Di ba to taga pamahalaan bat di nya alam ang mga nangyayari at sya ang magkwento sa taong bayan. T-NGA LANG??????? Inamin mo na ba na di ka talaga VP right? B-BA!!!," sabi ni G. Reyes. "Putcha naman VP ka so ano ka hindi ka ba kasali sa pamahalaan taga ibang planeta ka ba? Namumukod tanging pekeng VP na walang ginawa kundi kontrahin ang pamahalaan kung saan kabilang sya," sabi ni E. Jay.</t>
+        </is>
+      </c>
+      <c r="D308" s="4" t="inlineStr">
         <is>
           <t>disaster / environment</t>
         </is>
       </c>
-      <c r="D308" s="4" t="inlineStr">
+      <c r="E308" s="4" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E308" s="4" t="inlineStr">
+      <c r="F308" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -8268,17 +9359,22 @@
           <t>Pinarangalan si Ridel Francisco, isang 44-anyos na Filipino nurse mula Nueva Ecija at unit manager sa Lynde House sa Richmond, England, bilang Nurse of the Year sa 2018 Barchester Care Awards sa United Kingdom dahil sa kanyang dedikasyon at husay sa pangangalaga ng mga pasyente, kung saan siya ay napili mula sa 1,500 nominadong nurses sa buong UK ayon sa ulat ng ABS-CBN. Ibinahagi ni Ridel na anak siya ng mga magsasaka at natapos niya ang kursong Nursing dahil sa pagsisikap ng kanyang mga magulang sa pagtatanim ng sibuyas at palay. Ipinagmalaki niya ang kanyang pagiging Filipino at inialay ang natanggap na parangal sa kanyang pamilya at sa Pilipinas, binigyang-diin din niya na kinakatawan niya ang sipag at dedikasyon ng mga Filipino nurses na kilala sa UK at sa ibang bansa. Labingtatlong taon na siyang naninirahan sa UK at bukod sa pagiging mabuting asawa at ama ng tatlong anak, tinulungan din niya ang tatlo niyang kapatid na makapagtapos, kung saan dalawa ay naging guro at ang isa ay nurse na rin. Bilang payo sa mga nagnanais na magtagumpay, sinabi ni Ridel na hindi hadlang ang kahirapan at ang mahalaga ay ang pagsisikap, pangarap, at determinasyon upang makamit ang tagumpay sa buhay.</t>
         </is>
       </c>
-      <c r="C309" s="4" t="inlineStr">
+      <c r="C309" s="5" t="inlineStr">
+        <is>
+          <t>Isang Filipino nurse ang binigyang parangal ng 2018 Barchester Care Awards sa United Kingdom (UK) bilang Nurse of the Year dahil sa ipinamalas niyang husay sa pagbibigay ng magandang pangangalaga sa mga pasyente. Ayon sa ulat ng ABS-CBN, ang 44-anyos na si Ridel Francisco, unit manager sa Lynde House, isang private care home sa Richmond sa England, ay napili mula sa 1,500 nominadong nurses sa buong UK. Tubong Nueva Ecija si Ridel at anak ng mga magsasaka. Kwento niya, napagtapos siya sa kursong Nursing dahil sa pagtitiyaga ng kanyang mga magulang sa pagtatanim ng sibuyas. "Magsisibuyas kami. 'Yun ang pangunahin naming hanapbuhay doon. I came from farming as well. Nagtatanim ako ng sibuyas, palay at nagsikap ang magulang ko na mapagtapos ako as a nurse," ani Ridel na masayang-masaya sa pagkilala sa kanyang kakayahan bilang isang nurse. Ang natanggap na award ay inihandog niya sa kanyang pamilya at sa bansang Pilipinas. Aniya, ipinagmamalaki niya ang kanyang pagiging Filipino. "I'm very proud being a Filipino. Una sa UK, maraming Filipino nurses at nai-represent ko ang hard work at dedication ng mga Filipino, which is very known na mahuhusay na nurses sa UK at sa iba pang bansa," sabi ni Ridel na labingtatlong taon na ang inilalagi sa UK. Bukod sa pagiging ulirang asawa at ama ng tatlong anak, inako na rin niya ang pagpapa-aral sa tatlo niyang kapatid na ang dalawa ay mga guro na at ang ikatlo ay sumunod sa kanyang mga yapak bilang nurse. Payo niya sa mga nagnanais rin na maabot ang tagumpay tulad ng nakamit niya ay ang magsumikap. "Ang kahirapan ay 'di hadlang para maabot mo ang ganitong antas ng pamumuhay. Hindi rin lang matataas na paaralan ang magbibigay sa iyo ng tagumpay. Basta graduate ka at may pagsisisikap ka, may pangarap ka sa buhay, maaabot mo," ani Ridel.</t>
+        </is>
+      </c>
+      <c r="D309" s="4" t="inlineStr">
         <is>
           <t>international news</t>
         </is>
       </c>
-      <c r="D309" s="4" t="inlineStr">
+      <c r="E309" s="4" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E309" s="4" t="inlineStr">
+      <c r="F309" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -8293,17 +9389,22 @@
           <t>Dumulog kay Idol Raffy si Aljune Barrios, isang Safety Officer, dahil sa matinding problema niya sa kanyang misis na si Benz Daoa, isang Site Engineer, na diumano’y may relasyon sa kanyang boss na si Jeffrey Del Pilar, Safety Manager ng Concrete Masters Inc., at sa boss naman ni Benz na si Marshall Damong, Plant Manager ng Trevi Foundation. Ayon kay Aljune, may isang taong gulang silang anak ngunit nagdududa siya kung siya talaga ang ama dahil hindi ipinangalan sa kanya ang bata at hindi rin siya pinapasok ni Benz sa ospital matapos manganak, bagkus ay nauna pang kargahin ng kanyang kumpare at boss na si Jeffrey ang sanggol. Lalo pang nadagdagan ang hinala ni Aljune nang dumating din si Marshall sa ospital at kinarga rin ang bata, kasabay ng mga balitang naririnig niya na naging kalaguyo ng kanyang misis ang dalawa nilang boss. Sa kasalukuyan, tila nag-uunahan pa ang dalawang boss sa pagkarga sa bata. Hindi nakuha ang panig nina Benz, Jeffrey at Marshall sa panayam kay Aljune dahil hindi sila makontak, ngunit bukas ang tanggapan ng programa para sa kanilang depensa.</t>
         </is>
       </c>
-      <c r="C310" s="4" t="inlineStr">
+      <c r="C310" s="5" t="inlineStr">
+        <is>
+          <t>KINABIT NI MISIS ANG BOSS NIYA AT ANG BOSS NG KANYANG MISTER. Parang 3 in 1 coffee lang! Dumulog kay Idol Raffy si Aljune Barrios, isang Safety Officer dahil sa problema niya sa kanyang misis na si Benz Daoa na isang Site Engineer. Mayroon daw silang isang taong gulang na anak ngunit malaki ang duda ni Aljune kung siya ba talaga ang tunay na ama nito. Hindi raw kasi inapelyido sa kanya ni Benz si baby at ang mas matindi, noong nasa ospital pa si Benz at kapapanganak pa lang, hindi man lang siya pinapasok ng kuwarto ng kanyang misis para makita at mahagkan ang kanilang first baby. Sa halip, mas nauna pa itong kargahin ng kanyang kumpare at boss sa trabaho na si Jeffrey Del Pilar, Safety Manager ng Concrete Masters Inc. Animoy sampal daw ang tagpong iyon kay Aljune pero kinain na lang daw niya ang kanyang pride at pinalampas ang pangyayari. Ngunit mas lalo siyang nagulat nang ang boss naman ni Benz na si Marshall Damong, Plant Manager ng Trevi Foundation ay magpunta ng ospital at kinarga rin ang kasisilang lang na sanggol. Dahil sa mga pangyayaring 'yon, mas lalong tumindi ang hinala ni Aljune na isa sa mga ito ang tatay ng baby lalo pa't mayroong mga nakakarating na balita sa kanya na naging kalaguyo ni Benz ang mga boss nilang pareho. At ngayon, tila nag papaligsahan pa ang dalawang mga boss sa pagkarga sa baby. Hindi nagkaroon ng pagkakataon na makuha ang panig nina Benz, Jeffrey at Marshall noong kapanayim si Aljune ni Idol Raffy sa Aksyon sa Tanghali dahil hindi matawagan ang kanilang mga cellphone, ngunit bukas ang aming tanggapan para sa kanilang depensa.</t>
+        </is>
+      </c>
+      <c r="D310" s="4" t="inlineStr">
         <is>
           <t>lifestyle / human interest</t>
         </is>
       </c>
-      <c r="D310" s="4" t="inlineStr">
+      <c r="E310" s="4" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E310" s="4" t="inlineStr">
+      <c r="F310" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -8318,17 +9419,22 @@
           <t>Hinatulan ng anim na taong pagkakakulong si Cardinal George Pell matapos mapatunayang nagkasala ng pang-aabuso sa dalawang batang lalaki, na naging dahilan upang siya ang maging pinakamataas na opisyal ng Iglesia Katolika na nahatulan dahil sa ganitong kaso. Ayon sa ulat ng CNN Philippines, si Pell ay nagsilbing treasurer ng Vatican at malapit na tagapayo ni Pope Francis. Bago pa man inilabas sa publiko ang desisyon ng korte, inalis na siya ni Pope Francis bilang miyembro ng konseho sa Vatican.</t>
         </is>
       </c>
-      <c r="C311" s="4" t="inlineStr">
+      <c r="C311" s="5" t="inlineStr">
+        <is>
+          <t>Sinintensiyahan ng anim na taon pagkakakulong si Cardinal George Pell matapos itong mapatunnayan ng hukuman ang ginawa nitong pang-aabuso sa mga 2 batang lalaki. Si Pell ang pinaka mataas na miyembro ng kaparian ng Iglesia Katolika na nahatulan dahil sa pang-aabuso. Panoorin ang isa pang video mula sa Guardian News. Ayon sa ulat ng CNN Philippines, si Pell ay treasurer ng Vatican at close adviser ni Pope Francis. Bago pa lumabas ang conviction sa kaso ni Pell sa publiko, tinanggal na ito ni Pope Francis sa pagiging miyebro ng saggunian sa Vatican. Panoorin ang video sa ibaba para makilala niyo ng lubusan kung sino itong pari na ito.</t>
+        </is>
+      </c>
+      <c r="D311" s="4" t="inlineStr">
         <is>
           <t>religion</t>
         </is>
       </c>
-      <c r="D311" s="4" t="inlineStr">
+      <c r="E311" s="4" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E311" s="4" t="inlineStr">
+      <c r="F311" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -8343,17 +9449,20 @@
           <t>NANAWAGAN ang Gabriela kay Pangulong Duterte na agad na pirmahan ang panukalang expanded maternity leave ng Social Security System at huwag itong i-veto gaya ng ibang panukalang inaprubahan ng Kongreso. Ayon kay Rep. Emmi de Jesus dumaan sa masusing pagsusuri ang panukala na mas mabigat umano kaysa sa ilang bulong kay Duterte. "Bakit biglang ikokonsidera ng Pangulo ang ilang bulong at panukala na kontra sa hiling ng mga kababaihang manggagawa? He should sign it now," ani de Jesus. Sinabi ni de Jesus na hindi dapat gamitin ang kapalpakan ng SSS na makakolekta upang hindi mapaganda ang benepisyo ng mga miyembro nito o kaya ay taasan pa ang ikinakaltas sa suweldo ng mga empleyado. "Instead of floating the cost, why not find ways to the plug the leaks at SSS by improving collection rate and dispose costly idle assets? Bakit kailangang pagkaitan ang mga buntis dahil sa koleksyong mintis?" tanong ni de Jesus. Naniniwala naman si Rep. Arlene Brosas na pinalobo ng SSS ang inaasahang gastos nito sa expanded maternity benefit sa P6.4 bilyon upang makumbinsi ang Pangulo na i-veto ang panukala. "Tandaan natin na karamihan ng SSS members ay minimum wage earners kaya mababa lang talaga ang salary credit, bukod sa less than 10 percent lang talaga ang nag-aavail ng maternity leave sa kasalukuyan," ani Brosas. Sa ilalim ng expanded maternity benefits gagawin ng 105 araw ang maternity leave mula sa 60 araw. "If President Duterte vetoes the bill, he should expect a loud outrage by mothers who have long demanded the passage of the expanded maternity leave," dagdag pa ni Brosas.</t>
         </is>
       </c>
-      <c r="C312" s="4" t="inlineStr">
+      <c r="C312" s="5" t="n">
+        <v/>
+      </c>
+      <c r="D312" s="4" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D312" s="4" t="inlineStr">
+      <c r="E312" s="4" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E312" s="4" t="inlineStr">
+      <c r="F312" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -8368,17 +9477,20 @@
           <t>Kung patuloy na iinit ang isyu sa kustodiya ni US Marine Pfc. Joseph Scott Pemberton, na itinuturong pumatay sa isang Pinoy transgender sa Olongapo City noong Oktubre, ipaiiral pa rin ng mga opisyal ng US government ang diplomasya bilang pagbibigay-halaga sa "sensibilities at sensitivities" ng mga Pinoy. Ito ang inihayag ni US Ambassador to Manila Philip Goldberg sa telebisyon habang idinedepensa ang desisyon ng gobyerno ng Amerika na panatiliin ang kustodiya ni Pemberton sa Joint US Military Assistance Group (JUSMAG) compound sa Camp Aguinaldo, Quezon City.</t>
         </is>
       </c>
-      <c r="C313" s="4" t="inlineStr">
+      <c r="C313" s="5" t="n">
+        <v/>
+      </c>
+      <c r="D313" s="4" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D313" s="4" t="inlineStr">
+      <c r="E313" s="4" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E313" s="4" t="inlineStr">
+      <c r="F313" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -8393,17 +9505,20 @@
           <t>(Ito ang inihanda kong acceptance speech sa Natatanging Gawad Tanglaw sa Sining ng Panulat na ipinagkaloob sa akin nitong nakaraang Huwebes na sa sobrang nerbiyos ay hindi ko nabasa pero nairaos pa rin naman mula sa memorya kahit papaano. Inilalabas ko ito kasabay ang mula sa pusong pasasalamat sa Liwayway, Balita at Manila Bulletin na humubog sa akin bilang manunulat.) HINDI ako deserving sa parangal na ito. Napakabata ko pa para bigyan ng lifetime achievement award sa sining ng panulat. Kaya ang sabi ko kay Dr. Romeo Flaviano I. Lirio, ang Chairman Emeritus nitong Gawad Tanglaw, tatanggihan ko ito.</t>
         </is>
       </c>
-      <c r="C314" s="4" t="inlineStr">
+      <c r="C314" s="5" t="n">
+        <v/>
+      </c>
+      <c r="D314" s="4" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D314" s="4" t="inlineStr">
+      <c r="E314" s="4" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E314" s="4" t="inlineStr">
+      <c r="F314" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -8418,17 +9533,20 @@
           <t>Ni JENNY F. MANONGDO Pinayuhan ni dating Pangulo at ngayo'y Manila Mayor Joseph "Erap" Estrada si Pangulong Aquino na tigilan na ang sisihan at akuin ang responsibilidad sa madugong sagupaan sa Mamasapano, Maguindanao upang manumbalik ang tiwala sa kanya ng sambayanan.</t>
         </is>
       </c>
-      <c r="C315" s="4" t="inlineStr">
+      <c r="C315" s="5" t="n">
+        <v/>
+      </c>
+      <c r="D315" s="4" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D315" s="4" t="inlineStr">
+      <c r="E315" s="4" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E315" s="4" t="inlineStr">
+      <c r="F315" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -8443,17 +9561,20 @@
           <t>Kinilala ng Danao City Police Office (DCPO) ang bangkay ng mga biktima na sina Ernesto Ogabao, 49; Jesschristian Miguel, 21; Diomel Mayol, 19, at Amick Bunconsejo.</t>
         </is>
       </c>
-      <c r="C316" s="4" t="inlineStr">
+      <c r="C316" s="5" t="n">
+        <v/>
+      </c>
+      <c r="D316" s="4" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D316" s="4" t="inlineStr">
+      <c r="E316" s="4" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E316" s="4" t="inlineStr">
+      <c r="F316" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -8468,17 +9589,20 @@
           <t>KAHON-kahong pekeng panty liner na nagkakahaga ng mahigit P60,000 ang nakumpiska ng mga tauhan ng National Bureau of Investigation-Intellectual Property Rights Division (NBI-IPRD) sa raid sa Antipolo City, Rizal. Ayon kay Isaac Carpeso, team leader ng NBI-IPRD na nagsagawa ng operasyon, alas-2 ng hapon kamakalawa nang salakayin ang Misumi Direct Sales sa Unit 5, Okinari Building, Circumferential Road, Antipolo, sa bisa ng search warrant na inisyu ng Manila Regional Trial Court branch 46. Ang naturang establisimento, na pag-aari ni Donnah Mae Miranda, ay nakuhanan ng mahigit limang kahon ng pekeng Shuya panty liner. Ani Carpeso, isinagawa ang operasyon matapos silang makatanggap ng reklamo mula sa totoong gumagawa ng Shuya panty liner ukol sa pagkalat ng mga peke nilang produkto. Matapos ang ilang test buy, agad na nagkasa ng operasyon ang mga operatiba na nagresulta sa pagkakumpiska ng mga nasabing pekeng produkto. Wala naman ang may-ari na si MIranda nang isagawa ang raid. Nahaharap si Miranda sa kasong paglabag sa trademark infringement o paglabag sa Republic Act 8293.</t>
         </is>
       </c>
-      <c r="C317" s="4" t="inlineStr">
+      <c r="C317" s="5" t="n">
+        <v/>
+      </c>
+      <c r="D317" s="4" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D317" s="4" t="inlineStr">
+      <c r="E317" s="4" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E317" s="4" t="inlineStr">
+      <c r="F317" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -8493,17 +9617,20 @@
           <t>Nakapiit na ngayon sa NBI detention facility si Harrel Barzaga, 39, at apat na iba pang kasama nito na nahuli sa akto habang nagpa-pot session sa Barzaga Compound sa Dasmarinas.</t>
         </is>
       </c>
-      <c r="C318" s="4" t="inlineStr">
+      <c r="C318" s="5" t="n">
+        <v/>
+      </c>
+      <c r="D318" s="4" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D318" s="4" t="inlineStr">
+      <c r="E318" s="4" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E318" s="4" t="inlineStr">
+      <c r="F318" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -8518,17 +9645,20 @@
           <t>"Ako talaga kasi, bawat proyekto, siyempre nilo-look forward ko na makasama rin 'yung ibang magagaling na artista, and then, para sa akin, siguro, napakalalim na ng pundasyon namin ni Julia as a love team. Kumbaga, 'pag in-overall ko siya, si Julia talaga 'yung inaano ko na 'pag sinabing 'sino talaga 'yung naka-love team ko noong araw?' si Julia 'yun." Then, nu'ng nag-Moment in Time (pelikula nila) kami, medyo nagkakahitsura na, nagkakaroon na ng dating sa akin, then sa Ikaw Lamang, nakita ko ang maturity niya as an actress. "And then nakita ko ngayon, nagdadalaga na, paganda na nang paganda, parami na nang parami ang mga umaaligid na gustong manlgaw," kuwento ni Coco na halatang may pinaghuhugutan. Nagkukuwento ba sa kanya ang leading lady niya? "Hindi, pero ipinaparamdam ko sa kanya na hindi siya puwedeng magpaligaw. Bata pa, eh." Ano ba talaga ang relasyon nila, may naudlot ba o tuluy-tuloy lang? "Walang naudlot, kasi kahit noon pa, mula nang Walang Hanggan hanggang nu'ng Ikaw Lamang and hanggang ngayon, kung ano 'yung trato namin ni Julia sa isa't isa at kung ano ang pagkakaibigan namin, ganu'n pa rin po talaga," salag ni Coco. Sa madaling salita ay magkaibigan lang talaga sila. "Opo, wala nang tataas do'n," diretsong sabi ni Coco. So, ibig sabihin, totoo ang sinasabi niya noon pa na hindi pa siya nanliligaw kay Julia na inamin niya sa interview ng ibang katoto na minamahal niya.</t>
         </is>
       </c>
-      <c r="C319" s="4" t="inlineStr">
+      <c r="C319" s="5" t="n">
+        <v/>
+      </c>
+      <c r="D319" s="4" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D319" s="4" t="inlineStr">
+      <c r="E319" s="4" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E319" s="4" t="inlineStr">
+      <c r="F319" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -8543,17 +9673,20 @@
           <t>MINSANG naka-face-to-face ni Victor Basa ang press people sa opisina ng Cotton Club. Nauwi ang maliit na pagtitipon sa simpleng usapan tungkol sa mga paboritong isuot na underwear. Kuwento ni Victor, mas masarap matulog kung ang suot ay medyo maluwag na boxer shorts. Mas komportable at mahimbing siyang nakakatulog. At idinagdag pang "para madaling hubarin".</t>
         </is>
       </c>
-      <c r="C320" s="4" t="inlineStr">
+      <c r="C320" s="5" t="n">
+        <v/>
+      </c>
+      <c r="D320" s="4" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D320" s="4" t="inlineStr">
+      <c r="E320" s="4" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E320" s="4" t="inlineStr">
+      <c r="F320" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -8568,17 +9701,20 @@
           <t>Unang nakaharap ni De La Hoya si Mayweather noong 2007 at nagwagi lamang ito sa kontrobersiyal na 12-round split decision samantalang noong 2008 ay napatigil siya ni Pacquiao sa loob ng walong rounds sa mga sagupaang ginanap sa MGM Grand sa Las Vegas, Nevada.</t>
         </is>
       </c>
-      <c r="C321" s="4" t="inlineStr">
+      <c r="C321" s="5" t="n">
+        <v/>
+      </c>
+      <c r="D321" s="4" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D321" s="4" t="inlineStr">
+      <c r="E321" s="4" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E321" s="4" t="inlineStr">
+      <c r="F321" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -8593,17 +9729,20 @@
           <t>Sa ilalim ng wage rules, maaari lang itaas ng RTWPB ang minimum wage rate sa hurisdiksiyon nito isang taon matapos ipatupad ang huling wage hike na dinesisyunan nito. Sa Metro Manila, ang huling wage adjustment ay ipinatupad noong Oktubre 4, 2013, na nagpatupad ng P10 dagdag sahod sa NCR at integrated FernandezP30 cost-of-living allowance. Sinabi ni Labor Secretary Rosalinda Baldoz na tanging ang mga RTWPB sa Cordillera Administrative Region (CAR), Ilocos Region, Cagayan Valley, Central Luzon, Calabarzon, Bicol, Eastern Visayas, Davao, Socsargen at Autonomous Region in Muslim Mindanao (ARMM) ang nakapag-apruba ng bagong wage hike para sa 2014. "Ang ibang Regional Tripartite Wage and Productivity Board ay nasa iba't ibang antas na ng pagsusuri ng mga socio-economic condition at nagsasagawa ng konsultasyon sa iba't ibang sektor na magiging basehan ng kanilang desisyon upang i-adjust ang minimum wage," paliwanag ni Baldoz.</t>
         </is>
       </c>
-      <c r="C322" s="4" t="inlineStr">
+      <c r="C322" s="5" t="n">
+        <v/>
+      </c>
+      <c r="D322" s="4" t="inlineStr">
         <is>
           <t>economy / business</t>
         </is>
       </c>
-      <c r="D322" s="4" t="inlineStr">
+      <c r="E322" s="4" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E322" s="4" t="inlineStr">
+      <c r="F322" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -8618,17 +9757,20 @@
           <t>Ang sagot sa tanong na iyan ay nakalundo sa tinatawag ng management experts natin na 'development governance', na inilalarawang climate change adaptation. Kaakibat nito ang pagtanggap ng katotohanang madalat na natural na kalamidad, comprehensive situation analysis, forward planning, positive thinking at paggamit ng mga natamong ganansiya upang maibsan ang pagkaluging dulot ng kalamidad. Ang konseptong ito ay pinakamainam na ipinakita ng Albay. Taun-taong sinasalanta ng malalakas na bagyo, ang Albay ay isang hindi mahalagang probinsiya sa loob ng maraming dekada, hanggang dumating si Gov. Joey Salceda. Ngayon, makikita ng lahat ang dokumentadong mga tagumpay nito. Kabilang dito ang pinakamaiinam na pamamaraan sa kaligtasan, pati na ang permanenteng evacuation centers at relocation sites; ang pagpapatuloy ng mga kabuhayan na tumitiyak sa kaunlaran; solidong "green credentials" na kinatawan ng 88% increase sa forest cover at 300% expansion ng mangrove areas sa loob ng anim na taon; at mahigpit na pagbabawal sa pagmimina, paninigarilyo, at walang habas na paggamit ng plastic. Umaasa ang Albay na maisusulong nito ang kaunlaran sa turismo ngayong taon, at nangangako ng masasaya at makukulay na karanasan para sa mga panauhin. Bukod sa pagiging host nito sa limang major international event, kasama ang XTERRA Triathlon sa Pebrero, ang tatlong Senior Officials' Meeting (SOM) ng 2015 Asia Pacific Economic Cooperation (APEC) summit sa Hulyo hanggang Setyembre, at ang Pacific Asia Travel Association (PATA) travel mart sa Oktubre.</t>
         </is>
       </c>
-      <c r="C323" s="4" t="inlineStr">
+      <c r="C323" s="5" t="n">
+        <v/>
+      </c>
+      <c r="D323" s="4" t="inlineStr">
         <is>
           <t>disaster / environment</t>
         </is>
       </c>
-      <c r="D323" s="4" t="inlineStr">
+      <c r="E323" s="4" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E323" s="4" t="inlineStr">
+      <c r="F323" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -8643,17 +9785,20 @@
           <t>Sa Ganap na alas-6:00 ng umaga paglalabanan ang unang nakatayang gintong medalya sa women's10,000m run bago sundan ng men's shot put sa ganap na alas-8:00 kung saan ay tatangkain ng 2016 Rio Olympics hopeful at Fil-Heritage na si Caleb Stuart na maitala ang panibagong Philippine record. Kasabay nito, lalarga naman ang women's high jump kung saan ay hangad ng Philippine Amateur Track and Field Association (PATAFA) na makadiskubre ng bagong talent, bukod pa sa hahataw ang espesyal na kategorya na master's high jump na para sa mga dating miyembro ng pambansang koponan. Sinabi ni PATAFA Secretary General Renato Unso na nagsidatingan na rin ang mga lalahok na atleta na mula sa nagkumpirmang 12 bansa o kabuuang 1,500 lokal at mahigit sa 150 foreign tracksters para sa apat na araw na torneo. Sa pangkalahatan, kabuuang 73 gintong medalya ang paglalabanan habang may anim na espesyal na awards din ang nakataya sa torneo. Nakasalalay din sa torneo ang tsansa ng mga nagsipagwagi ng medalya sa nakaraang 27th Myanmar SEA Games upang mapasama sa pambansang delegasyon na sasabak sa 28th Singapore SEAG. Matatandaan na nagwagi ng ginto sina Edgardo Alejan Jr., Archand Bagsit, Isidro del Prado Jr. at Julius Felicisimo Nierra Jr sa men's 4 x 400m relay, Jesson Ramil Cid sa men's decathlon, Christopher Ulboc Jr. sa men's 3000m steeplechase, Eric Shauwn Cray sa men's 400m hurdles, Bagsit sa 400m run at Henry Dagmil sa men's long jump. Nagwagi rin ng pilak sina Mervin Guarte sa men's 800m, Narcisa Atienza sa women's heptathlon, Arniel Ferrera sa men's hammer throw at Alejan sa men's 800m habang tanso naman kina Jessica Barnard sa women's 3,000m steeple chase, Eric Panique sa men's marathon at Riezel Buenaventura sa women's pole vault. Isasagawa ang opening ceremony sa ganap na ala-1:00 ng hapon bago sundan muli ng aksiyon sa alas-2:00 ng hapon. Optimistiko naman ang PATAFA na maihahalintulad ang edisyon ng torneo sa prestihiyosong Olympics. "There will be giant screens, just like in every staging of the Olympics na sa bawat isasagawang events at takbo ng mga atleta and every results will be posted digitally right after the performances of the athletes," sinabi ni Edward Kho, media and marketing chief ng PATAFA. "Inuumpisahan kasi namin na ma-professionalize ang staging ng lahat ng event ng PATAFA not just for us, but for the athletes para masanay na sila sakaling sumali sila sa malalaking events sa kind and quality ng environment like sa SEAG, Asian Games at sa Olympics," giit pa ni Kho. "Maiiwasan din ang dayaan at talagang makikita natin ang data sa mga results. Saka madali na rin maresolbahan iyong mga photo finish dahil sa cameras sa finish line," paliwanag pa ni Kho. Nakataya rin ang anim na espesyal na karangalan sa apat na araw na torneo na inaasahang dadaluhan ng 150 internasyonal at Class A na mula sa 12 bansa. Ang espesyal na award ay Most Valuable Player, Most number of gold won, fastest men at women, Man of Steel, Iron Maiden at Powerhouse Team. Sasabak din sa aksiyon ang mga atleta sa China, Chinese Taipei, South Korea, Hong Kong, Brunei, Thailand, Malaysia, Vietnam, Singapore, Indonesia at Myanmar.</t>
         </is>
       </c>
-      <c r="C324" s="4" t="inlineStr">
+      <c r="C324" s="5" t="n">
+        <v/>
+      </c>
+      <c r="D324" s="4" t="inlineStr">
         <is>
           <t>international news</t>
         </is>
       </c>
-      <c r="D324" s="4" t="inlineStr">
+      <c r="E324" s="4" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E324" s="4" t="inlineStr">
+      <c r="F324" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -8668,17 +9813,20 @@
           <t>Magsa-side trip din ang dalawa sa bayan ng Maria Aurora para makita ang Millenium Tree, na sinasabing pinakamalaki at pinakamatandang puno ng Balete sa Asya. Madidiskubre rin nila ang Dicasalarin Cove na bukod sa may private beach at light house, ay artist's haven din. Gutom naman ang magdadala kay Iya sa Kusina Luntian, isang bahay kubo na pag-aari ni Biboy Cruz. Isa siyang city-boy-turned-surfer na nagtayo ng maliit na kainan para sa kanyang surfing lifestyle. Dito ay naghahanda siya ng kanyang sariling version ng tapsilog at patok na pako salad. Si Solenn naman ay bibisita kay Nanay Pacing na sikat dahil sa kaniyang peanut butter, atsara, at coco jam.</t>
         </is>
       </c>
-      <c r="C325" s="4" t="inlineStr">
+      <c r="C325" s="5" t="n">
+        <v/>
+      </c>
+      <c r="D325" s="4" t="inlineStr">
         <is>
           <t>lifestyle / human interest</t>
         </is>
       </c>
-      <c r="D325" s="4" t="inlineStr">
+      <c r="E325" s="4" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E325" s="4" t="inlineStr">
+      <c r="F325" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -8693,17 +9841,20 @@
           <t>Sa ika-9 na taon ng film festival, katuwang ipinagpapatuloy ng GMA ang tradisyong pagbukludin ang mga Pilipino sa pamamagitan ng mga kuwentong nakatuon sa tunay na diwa ng Pasko. Tampok sa mga kuwento ng inspirasyon at pag-asa ang ilan sa Kapuso stars tulad nina Benjamin Alves, Bettinna Carlos, Kevin Santos, Joshen Bernardo at Miguel Tanfelix. Bahagi rin ng kuwento ang pampasaherong jeepney at ang mga relasyong nakapalibot dito na sumisimbulo ng kulturang Pinoy.</t>
         </is>
       </c>
-      <c r="C326" s="4" t="inlineStr">
+      <c r="C326" s="5" t="n">
+        <v/>
+      </c>
+      <c r="D326" s="4" t="inlineStr">
         <is>
           <t>religion</t>
         </is>
       </c>
-      <c r="D326" s="4" t="inlineStr">
+      <c r="E326" s="4" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E326" s="4" t="inlineStr">
+      <c r="F326" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -8718,17 +9869,20 @@
           <t>Huli sa lente ng kamera ang paraan ng pakikipagkamay ni Erin Tanada sa isang tindera ng isda sa palengke. Makikita sa naturang litrato na imbes na sa kamay niya hawakan ang tindera, ay sa bisig niya lang ito hinawakan. Si Tanada ay isa sa walong pambato ng oposisyon sa pagka-senador at miyembro ng Liberal Party. Ang naturang litrato ni Tanada ay ibinahagi ng kilalang pro-government blogger at radio host na si RJ Nieto (aka ThinkingPinoy) sa kanyang Facebook page. Umani ito ng sari-saring batikos mula sa mga taga-suporta ng gobyerno at nai-share na rin ito ng mahigit 8,000 beses. "Yung parang diring-diri si #OtsoDiretso Erin Tanada sa kamay ni Ate na ipinanghawak sa isda. Chinito ba talaga si Erin o takot lang matilamsikan ng tubig na malansa?" banat ni Thinking Pinoy. Basahin ang komento at opinyon ng ilang kababayan natin sa naging paraan ni Tanada ng pakikipagkamay sa ordinaryong tao. "Plastic na kumag tokung ako ginawan mo ganyan hawakan kita ng kanan kong kamay na hinawak ko ng wagas sa isda," sabi ni E. Albarida. "Plastic na kumag tokung ako ginawan mo ganyan hawakan kita ng kanan kong kamay na hinawak ko ng wagas sa isda," sabi ni E. Albarida. "Yan..yan ang Ocho Deretchoooo nyo! Saka kelan pa naging Derecho ang Ocho? Haaayys kung si Tatay Digong yan baka maglinis pa ng isda yan," sabi ni L. Villacruz. "wala ng marami pang paliwanag, kesyo sign ng respeto un, tangna kumakandidato ka, kung kinakailangang madumihan ang kamay mo gawin mo, amoy malansa man yan o amoy tae tangna tiisin mo sa ganun paraan man lang ipakita mo na kaya mong gawing ibaba ang pagkatao mo, after nyan kung manalo magnanakaw k lng dn nmn.," sabi ni R. Nellas. "Hahahaha imbes sa palad hahawak sa wrist hahaha malantsa kasi kamay ni aleng tindera siguro kung di lang eleksyon di yan hahawak o pupunta dyan sa palengke at after ng election who you kayo ngeeek," sabi ni M. Alvarez.</t>
         </is>
       </c>
-      <c r="C327" s="4" t="inlineStr">
+      <c r="C327" s="5" t="n">
+        <v/>
+      </c>
+      <c r="D327" s="4" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D327" s="4" t="inlineStr">
+      <c r="E327" s="4" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E327" s="4" t="inlineStr">
+      <c r="F327" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -8743,17 +9897,20 @@
           <t>Tampulan ngayon ng tukso ang isinagawang Caravan ng Liberal Party para sa kanilang Otso Direcho senatorial candidates. Makikita sa mga nakuhang larawan na ibinahagi ng Facebook page na VOVph kung gaano lang kadami ang mga tao. Hindi naman nakaligtas sa mga kababayan natin ang isang lalakeng may hawak na drone. Ayon sa ilang ulat, maninindigan daw ang Otso Diretso na harangin ang anumang hakbang na baguhin ang konstitusyon. Magugunita na isa sa mga naging pangako ng Pangulo Rodrigo Duterte noong nangangampanya pa lamang ito ay ang pagbabago sa sistema ng gobyerno mula sa Unitary system patungong Federal. Basahin ang ilang opinyon ng mga followers ng VOVPh blog sa mga litrato. "Pota kapag yan ocho na yan nanalo sigurado magkakagulo sa pilipinas. Tingnan mo yan supporters. Bilang na bilang. PCOS lang talaga chance nila," sabi ni J. Abe. "Hayop haha wala na mga LP. Burado na kayo sa pilipinas.," sabi ni J. Fernandez. "Dito sila mangampanya sa laguna magbabalot ako ng tae para ibato sa kanila tingnan ko lang kung di magtalonan sa service nila yang mga hayop na yan," sabi ni L. Dela Cruz. "Inodoro bagsak nyan hahaha wag magpalinlang mga kabayan sa mga pulitiko na trapo isaalang alang ang kinabukasan ng bansa at magkaisa at labanan ang curraption sa lipunan," sabi ni N. Molit. "Wag na kayo gumamit ng drone sayang kaya naman bilangan sila lahat nasa higit kumolang hahahaha.bente kasama driver," sabi ni M. Gabin.</t>
         </is>
       </c>
-      <c r="C328" s="4" t="inlineStr">
+      <c r="C328" s="5" t="n">
+        <v/>
+      </c>
+      <c r="D328" s="4" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D328" s="4" t="inlineStr">
+      <c r="E328" s="4" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E328" s="4" t="inlineStr">
+      <c r="F328" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -8768,17 +9925,20 @@
           <t>"They're not the proper body or authority to say that it is unconstitutional or not. Hindi po sila ang Supreme Court. Hindi sila ang Kataas-taasang Hukuman dito sa Pilipinas. So, hindi po sila ang pwedeng magsabi if it's unconstitutional or not." Ilan lamag ang mga ito sa naging apela ni Philippine National Police (PNP) General Oscar Albayalde, matapos ang naging pahayag ng Ateneo Policy Center na bumabatikos sa kampanya ng pamahalaan na "War on Drugs", kung saan inilabas ng Ateneo Human Right Center (AHRC) ang resulta ng kanilang pag-aaral na umano'y lumabag sa Konstitusyon ng Pilipinas ang nasabing "Oplan Tokhang" ng Gobyerno. Ayon kay Albayalde, bukas umano ang PNP sa mga posibleng imbestigasyon ng Unibersidad sakaling gustuhin nitong maging mas balanse ang isinasagawang pag-aaral, bagama't hindi sila direktang nakatanggap ng imbitasyon mula sa mga ito upang kuhanin ang panig ng pulisya. "Pangalawa po doon, that is voluntary in nature. Remember 'yung Tokhang, sabi nga eh, paulit-ulit po natin na sinasabi na ito ay voluntary in nature. Wala pong ginamit na puwersa rito. At wala pong namatay because of Oplan Tokhang. These all surrendered. Nag-surrender sila for rehabilitation," dagdag pa ng PNP Chief. Handa umano ang PNP na makinig at hikayatin ang ilan pang sektor na nagmamalasakit na tulungan ang Philippine National Police sa laban nito kontra ilegal na droga. "What we are open here, they might have something here that we do not know. We are open for suggestions. We have no monopoly of intelligence here. We have no monopoly of strategies here," saad ni Albayalde. "We are open to suggestions that could improve, number one, our law enforcement, 'yung aming pagtataas ng standard namin, and of course how we enforce the law. Malay natin mayroon silang bright idea? Remember they are in the academe," pahayag pa ng Hepe ng Pulisya.</t>
         </is>
       </c>
-      <c r="C329" s="4" t="inlineStr">
+      <c r="C329" s="5" t="n">
+        <v/>
+      </c>
+      <c r="D329" s="4" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D329" s="4" t="inlineStr">
+      <c r="E329" s="4" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E329" s="4" t="inlineStr">
+      <c r="F329" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -8793,17 +9953,20 @@
           <t>Tila inulan ng puna ang naging social media post ng news anchor ng ABS-CBN na si Karen Davila. Hind nagustuhan ng ilan kababayan natin ang naging post ng mamamahayag tungkol sa kapwa nito journalist na si Rappler CEO Maria Ressa at sa kinakaharap nitong cyber libel case. Sa Facebook post ni Davila, sinabi ni Davila na ang cyber libel case ni Ressa ay nagmula sa artikulo noong 2012, bago naisabatas ang Cyber Crime Law. Pero hindi binanggit ni Davila na ni-republished o in-update ang nasabing artikullo noong 2014. Katwiran naman ng ilang kababayan natin, pasok pa din daw sa cyber libel ang nasabing artikulo ng Rappler dahil muli itong inilathala o ni-republished noong 2014. Ganito din ang naging opinyon ng Manila Times Columnist na si Rigoberto Tiglao. "This is a total lie. Yes, the story was published first on May 29, 2012, or before the Anti Cyber-Libel Law was enacted in July and came into force the next month. But the story was "updated" on Feb. 19, 2014 -- two years after the law had been in full force. 'Updated' If an article in the internet that was posted years ago is "updated" today, for example, it is as if it was reported only today," sabi ni Tiglao. Ito po ang social media post ni Davila na binatikos ng ilang kababayan natin. Matatandaang noong kasagsagan ng balita tungkol sa pag-aresto kay Ressa, nag post si Davila sa kayang twitter account tungkol sa pag depensa sa press freedom. Si Ressa ay kinasuhan ng negosyanteng si Mr. Wilfredo Keng dahil sa artikulo ng Rappler noong 2012, kung saan naiuugnay si Keng sa pag-smuggle umano ng bawal na gamot at human trafficking. Si Ressa ay nahaharap din sa kasong tax evasion. Noong 2018, binawi ng Securities and Exchange Commission (SEC) ang registration ng Rappler dahil sa paglabag daw sa patakaran ng foreign ownership sa mass media.</t>
         </is>
       </c>
-      <c r="C330" s="4" t="inlineStr">
+      <c r="C330" s="5" t="n">
+        <v/>
+      </c>
+      <c r="D330" s="4" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D330" s="4" t="inlineStr">
+      <c r="E330" s="4" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E330" s="4" t="inlineStr">
+      <c r="F330" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -8818,17 +9981,20 @@
           <t>PLAY FULL VIDEO BELOW Nakuha ang matataas na calibre ng baril sa mismong bahay sa Mayor ng Libungan North Cotabato. Matatandaan na ang mayor na ito ay nasa Narco list umano ng mga autoridad dahil napag alaman na isa ito sa mga protector at financer sa Illegal na droga operation. Alas Otso ng gabi ng tunguhin ng mga Atoridad ang target area kasama ang Brigada News TV chief camera man na si Jimmy Albero para idokumento ang operation, itong video na ito ay ilan sa actual footage na kuha nila.</t>
         </is>
       </c>
-      <c r="C331" s="4" t="inlineStr">
+      <c r="C331" s="5" t="n">
+        <v/>
+      </c>
+      <c r="D331" s="4" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D331" s="4" t="inlineStr">
+      <c r="E331" s="4" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E331" s="4" t="inlineStr">
+      <c r="F331" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -8843,17 +10009,20 @@
           <t>Matapos arestuhin kamakailan dahil sa cyber libel case na isinampa ng negosyanteng si Mr. Wilfredo Keng, isa na namang problema ang kakaharapin ni Rappler Chief Executive Officer Maria Ressa. At ito ay ang kaso ng kanyang kumpanya na may kaugnayan sa buwis. Binutata ng Court of Tax Appeals (CTA) 1st Division ang apela ng Rappler Holdings Corp. at ng CEO nito na si Ressa na maibalik sa Department of Justice (DOJ) ang P70-million tax deficiency cases. Dahil sa pagtanggi ng CTA, ikinasa na ng korte ang preliminary conference para sa marking of exhibits sa Marso 6. Ang pre-trial na naman ay gaganapin sa Marso 13. Magugunitang binawi ng Securities and Exchange COmmission (SEC) ang incorporation certificate ng Rappler noong 2018 dahil sa paglabag umano sa foreign ownership of mass media. Inalmahan ni Ressa ang mga kaso at tinawag itong panggigipit ngestado laban sa kanya at para kitilin ang kalayaan sa pamamahayag. Sa programa ng CNN Philippines, nagkasagutan sina Ressa at ang tagapagsalita ng Pangulong Rodrigo DUterte na si Sec. Salvador Panelo. Sa naturang pagtutuos, tila pinangaralan ng kalihim si Ressa tungkol sa kinasasadlakan nitong problema. Basahin ang reaksyon ng ilang kababayan natin sa problemang kinakaharap ni Ressa. "Sa panahon kasi ni Pnoy pinabayaan lang silang di mkabayad ng buwis total maganda nman binabalita ngyon sinisingil sila sa panahon ni Duterte todo paninira tirada nila tpos pag binalikan iiyak ng harassment daw," sabi ni D. Leopardas. "IKULONG ETO ULI... ALAM mo bah Madam na nagkahiraphirap ako sa buhay... Kahit kakarampot ang sweldo, ang laki pa nang kaltas sa Tax pero okay lang kasi obligasyon yun... Pero letche kah, karamirami nyo palang tax na hindi binabayaran.... DAPAT KANG MAKULONG," sabi ni J. Ubas. "asan na kaya yong mga anti duterte ngyon may rally pang nagaganap sa at pinaglalaban ang press freedom..anu na asan ang press freedom niyon mga honghang..eh kami nga nagbabayad ng tamang buwis tapos kayo hindi hanep eh harassment agad at pangigipit ang isasagot," sabi ni A. Macalua. "See ang dami mong satsat pala utang ka pala at ang laki nyan ha dapat nayaran mo kami nga mha ultimo lng ng babayad kami ng buhis ngayun pg hinuli ka dami mo recklamo kesyo injustice ang pg huli sayo huhulihin kaba kung wala kang nagawang labag sa batas? Tapos sasakay pa ang bese presedinte at amg CHR nko mg ayos ayos nga kayo para wlang gulo," sabi ni J. Agreas.</t>
         </is>
       </c>
-      <c r="C332" s="4" t="inlineStr">
+      <c r="C332" s="5" t="n">
+        <v/>
+      </c>
+      <c r="D332" s="4" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D332" s="4" t="inlineStr">
+      <c r="E332" s="4" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E332" s="4" t="inlineStr">
+      <c r="F332" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -8868,17 +10037,20 @@
           <t>PLAY FULL VIDEO BELOW Sa illustration na ito ng NEW5, pinakikita ang connection ng matandang Parojinog na ama ng Osamiz City mayor Parojinog na napaslang kamakailan sa isang raid sa compound nito sa Osamiz city.</t>
         </is>
       </c>
-      <c r="C333" s="4" t="inlineStr">
+      <c r="C333" s="5" t="n">
+        <v/>
+      </c>
+      <c r="D333" s="4" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D333" s="4" t="inlineStr">
+      <c r="E333" s="4" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E333" s="4" t="inlineStr">
+      <c r="F333" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -8893,17 +10065,20 @@
           <t>Matapos ang halos 10 taon sa Kapamilya network, tuluyan ng nagpaalam ang Umagang Kay Ganda show host na si Atom Araullo sa mga kasamahan niya sa show nitong Umaga ng Biyernes. Hindi makapaniwala ang mga kasamahan niya na sina Anthony Taverna, Amy Perez, Winnie Cordero at iba pang mga kasama niya sa pang-umagang show na lagi natin nakikita ang isa sa naging mainit sa mga netizen nitong Linggo dahil sa naging komento nito sa kanyang Twitter account na si Atom Araullo. Si Atom Araullo ay isa sa mga taga ABS-CBN at showbiz personality na-bash ng netizens sa social media noong isang araw, lalo na ang mga Solid Duterte Supporters dahil sa naging post niya sa naging decision ng kongreso sa pagbibigay ng P1,000 budget sa Commission on Human Rights (CHR) sa taong 2018. Matapos ang halos 10 taon sa Kapamilya network, tuluyan ng nagpaalam ang Umagang Kay Ganda show host na si Atom Araullo sa mga kasamahan niya sa show nitong Umaga ng Biyernes. Hindi makapaniwala ang mga kasamahan niya na sina Anthony Taverna, Amy Perez, Winnie Cordero at iba pang mga kasama niya sa pang-umagang show na lagi natin nakikita ang isa sa naging mainit sa mga netizen nitong Linggo dahil sa naging komento nito sa kanyang Twitter account na si Atom Araullo. Si Atom Araullo ay isa sa mga taga ABS-CBN at showbiz personality na-bash ng netizens sa social media noong isang araw, lalo na ang mga Solid Duterte Supporters dahil sa naging post niya sa naging decision ng kongreso sa pagbibigay ng P1,000 budget sa Commission on Human Rights (CHR) sa taong 2018.</t>
         </is>
       </c>
-      <c r="C334" s="4" t="inlineStr">
+      <c r="C334" s="5" t="n">
+        <v/>
+      </c>
+      <c r="D334" s="4" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D334" s="4" t="inlineStr">
+      <c r="E334" s="4" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E334" s="4" t="inlineStr">
+      <c r="F334" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -8918,17 +10093,20 @@
           <t>Itong mga nakaraang araw ay naging laman ng balita ang singer at kritiko ni Pangulong Rodrigo Duterte na si Jim Paredes dahil sa isang video. Sa naturang video, mapapanood si Paredes na dumidila-dila at kalaunan ay nilaro ang kanyang pag-aari. Noong una ay itinanggi pa ni Paredes nia siya ang lalaki sa video pero umamin din kinalaunan. Sa kanyang talumpati sa campaign rally ng Partido Demokratiko Pilipino - Lakas ng Bayan sa Puerto Princesa, tila nag pahapyaw si Pangulong Rodrigo Duterte sa viral video ni Jim Paredes. Ayon sa Pangulo, isa sa pulis na kasama niya ang nagpakita sa kanya ng video. "May isang hindi naman bakla, nagpakita ng t*t* niya ganun lang kataas. Susmaryosep. Nagpakita sa akin 'yung pulis na -- nandoon sa likod oh. Sabi niya, 'Sir, nakita mo na ba ito?' 'Yung mukha hindi masyadong ano eh...','Ano 'yan?'. Magtingin ako. Matagal nang tumindig, maliit pa gyud." banat ng Pangulo. Matapos kumalat ang video ni Paredes ay nagpaalam muna sa social media ang anak nito na si Erica Padilla. Ilang kilalang personalidad na rin ang nagkomento tungkol sa isyu. Ilan sa mga ito ay sina former Presidential Communications Operations Office Assisatant Secretary (PCOO) Mocha Uson at at dating deputy executive director V ng Overseas Workers Welfare Administration (OWWA) na si Arnell Ignacio..</t>
         </is>
       </c>
-      <c r="C335" s="4" t="inlineStr">
+      <c r="C335" s="5" t="n">
+        <v/>
+      </c>
+      <c r="D335" s="4" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D335" s="4" t="inlineStr">
+      <c r="E335" s="4" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E335" s="4" t="inlineStr">
+      <c r="F335" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -8943,17 +10121,20 @@
           <t>Usap-usapan ngayon sa social media ang umano'y panggagaya ng kinatawan ng Thailand na si Ingchanok Prasart sa ginanap na Miss Intercontinental pageant 2018 sa trademark ni Miss Universe 2018 Catriona Gray na "lava walk." Isang netizen sa Twitter na nagngangalang Marnie Raro ang nakapansin sa paraan ng paglalakad at pag-project ni Miss Thailand na parang kinokopya ang "lava walk" ni Catriona. Bukod kay Miss Thailand, napansin din ng mga netizens ang pagkopya umano sa "Mayon Volcano gown" ni Miss Vietnam. Aminado naman ang dalawa na labis nilang hinahangaan at inspirasyon nila si Miss Universe 2018 Catriona Gray. Halo-halo naman ang naging reaksyon ng mga netizens hinggil dito. "So now everyone looks like Catriona Gray. From hair to stance to gowns. The influence. Only legends do that." "Catriona Gray's walk can never be perfect without her walking it." "I think so? Even the hand gesture of Miss Thailand seems copied too. Catriona Gray is indeed a queen." "Yet they can't copy the original. Because there will be only one Lava Walk and Catriona Gray." "Kayo na 'yung may mga originality... hala gawa kayo sarili niyong pageant, ano ba naman yung hayaan niyo na lang sila hays....daming toxic." Isang patunay lamang ito na maraming mga aspiring beauty pageant candidates, hindi lamang sa Pilipinas kundi maging sa buong mundo, ang tumitingala at humahanga kay Catriona. Aminado naman dito ang marami sa mga kandidata ng naturang katatapos na pageant. Ang 47th edition ng Miss Intercontinental 2018 ay ginanap noong Enero 26, 2019, sa SM Mall of Asia Arena sa Pasay, Metro Manila, Philippines. Kinoronahan ni Miss Intercontinental 2017 Veronica Salas Vallejo ng Mexico ang kandidata ng Pilipinas na si Karen Juanita Gallman. Ito ang kauna-unahang pagkakataong naging host ang Pilipinas sa pageant na ito. Pinili ng Japan organizers ang Pilipinas na maging venue ng pageant dahil abala ang bansang Japan sa mga paghahanda para sa 2020 Summer Olympics. Narito ang buong Twitter post ng netizen:</t>
         </is>
       </c>
-      <c r="C336" s="4" t="inlineStr">
+      <c r="C336" s="5" t="n">
+        <v/>
+      </c>
+      <c r="D336" s="4" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D336" s="4" t="inlineStr">
+      <c r="E336" s="4" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E336" s="4" t="inlineStr">
+      <c r="F336" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -8968,17 +10149,20 @@
           <t>"Sabi ng National Economic and Development Authority (NEDA) humupa raw ang inflation, pero inflation pa rin." Tila hindi pa kuntento si dating Department of Interior and Local Government Secretary at Otso Diretso Senatorial Candidate Mar Roxas sa balitang bumaba na sa 3.3 ang inflation ngayong Marso 2019. "Tuloy-tuloy pa rin ang pag-taas ng presyo ng bilihin" sabi ni Roxas. Ang inflation ay ang pagtaas ng mga presyo ng mga pangunahing bilihin at serbisyo. Matatandaang pumalo pa sa 6.7% ang inflation noong nakaraang taon. Dahilan kung bakit naging panay ang puna ng ilang oposisyon sa Duterte Administration noong panahon na iyon. "The real enemy is inflation. The so-called strongman shjould get tough on inflation, not the opposition," sabi ni Opposition Senator Risa Hontiveros noong Septiyembre 2018. "Aminin mo na lang kasi na hindi mo kaya, Duterte, at mabuti pa, magresign ka na lang," banat ni Opposition Senator Leila De Lima noong Septiyembre 2018. Panoorin ang komento ng pangkaraniwang Pilipino sa ulat na ito.</t>
         </is>
       </c>
-      <c r="C337" s="4" t="inlineStr">
+      <c r="C337" s="5" t="n">
+        <v/>
+      </c>
+      <c r="D337" s="4" t="inlineStr">
         <is>
           <t>economy / business</t>
         </is>
       </c>
-      <c r="D337" s="4" t="inlineStr">
+      <c r="E337" s="4" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E337" s="4" t="inlineStr">
+      <c r="F337" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -8993,17 +10177,20 @@
           <t>Inumpisahan ngayong Martes ang paghahakot ng burak sa higit isang kilometrong shoreline ng Manila Bay mula US Embassy hanggang Manila Yacht Club. Target na mahakot ang 225,000 cubic meters na burak o katumbas ng higit 20,000 trak ng basura sa dalampasigan ng Manila Bay, ani Public Works Secretary Mark Villar. Pero kada araw, ang matatanggal lang umano ay nasa 50 hanggang 100 trak ng basura. Otso oras kada araw ang gagawing paghahakot ng aabot sa 50 tauhan ng DPWH gamit ang mga excavator. Matapos makuha ang burak, gagamit ng backhoe para mailagay ito sa mga dump truck. Ihihiwalay naman ang basura at lupa sa pamamagitan ng segregator. Itatapon sa Navotas ang basura habang pansamantala namang ilalagay ang lupa sa compound ng DPWH sa Taguig. Ibinida rin ni Environment Secretary Roy Cimatu ang sewer inspection cameras na ipapasok sa mga imburnal para makita ang mga ilegal na tubo ng mga gusali o negosyong nakakonekta sa Manila Bay. Samantala, sa kaniyang talumpati sa pagsisimula ng paghakot, sinabi ni Manila Mayor Joseph "Erap" Estrada na mahalaga ang reclamation ng Manila Bay para sa lungsod dahil higit 500,000 trabaho ang mabibigay nito. "Manila has the highest number of jobless people, Manila has the highest level of poverty incidence and this is the answer to it, hulog ng langit ito," ani Estrada. Ayon naman kay Cimatu, nakikipag-usap na sila sa Department of Science and Technology ukol sa "science-based effect" ng reclamation.</t>
         </is>
       </c>
-      <c r="C338" s="4" t="inlineStr">
+      <c r="C338" s="5" t="n">
+        <v/>
+      </c>
+      <c r="D338" s="4" t="inlineStr">
         <is>
           <t>disaster / environment</t>
         </is>
       </c>
-      <c r="D338" s="4" t="inlineStr">
+      <c r="E338" s="4" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E338" s="4" t="inlineStr">
+      <c r="F338" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -9018,17 +10205,20 @@
           <t>MAYNILA, Pilipinas - Kinontra ni dating Solicitor General Florin Hilbay ang naging pahayag ng Malakanyang na hindi nakaumang sa Pilipinas ang napaulat na mga missiles ng China sa mga pinagtatalunang isla sa West Philippine Sea (WPS). Ayon kay Hilbay, ang solicitor general ng nakaraang administrasyon at isa sa mga nanguna sa pagtatanggol sa posisyon ng bansa sa The Hague international tribunal, malabo umano ang sinabi ng Palasyo na hindi ang Pilipinas ang target ng mga missiles ng China dahil tayo ang pinakamalapit na bansa sa WPS. "It's false to say the missiles are not directed at us because it's a missile system. It's technically directed at everyone within the range of that missile system and we're nearest to that missile system. It is in fact directed at us," paliwanag ni Hilbay sa panayam ng ANC. Nauna nang sinabi ni Presidential Spokesperson Harry Roque na kumpiyansa umano ang adiministrasyon Duterte na hind puntirya ng China ang Pilipinas dahil sa mabuting relasyon ng dalawang bansa. "With our recently developed close relationship and friendship with China, we are confident that those missiles are not directed at us," wika ni Roque noong nakarang linggo. Iginiit din ng Malakanyang na hindi itinuturing ng China na banta ang Pilipinas kaya malabong mangyari ang kinatatakutan ng karamihan na mauwi sa gulo ang patuloy na pagiging agresibo ng komunistang bansa sa West Philippine Sea. Inamin din ni Roque na sa kasalukuyan ay walang kapabilidad ang Pilipinas para i-verify kung mayroon ngang nakalagay na missiles system sa tatlong isla sa pinag-aagawang teritoryo.</t>
         </is>
       </c>
-      <c r="C339" s="4" t="inlineStr">
+      <c r="C339" s="5" t="n">
+        <v/>
+      </c>
+      <c r="D339" s="4" t="inlineStr">
         <is>
           <t>international news</t>
         </is>
       </c>
-      <c r="D339" s="4" t="inlineStr">
+      <c r="E339" s="4" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E339" s="4" t="inlineStr">
+      <c r="F339" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -9043,17 +10233,20 @@
           <t>Dumulog sa programa ng sikat radio host na si Raffy Tulfo si Aling Ellenor Saguion para ireklamo ang pinaggagawa ng kanyang mister na si Alex Saguion. Ayon kay Aling Ellenor, wala na raw problema kung may kinakasama ng ibang babae ang kanyang mister pero ang ikinasasama niya lang ng loob ay ang pagtatayo ng mister at ng kabit nito ng tindahan sa harap ng kanyang tindahan. Para kay Aling Ellenor, ito raw isa ng malaking insulto. Nilinaw din ni Aling Elanor na walang siyang kinakasamang lalake at nasa kanyan pa rin ang marriage contract nilang mag-asawa. "Ang pinakamasaklap po sir, tanggap ko na may chicks siya at nagsasama na sila forever pero wag niya ng dalhin ang babae niya sa pwesto ng tindahan. Minsan nagkakasalubungan po kami (ng kabit). GUsto ko, lumayo na lang sila. Hindi 'yung parang kulang na lang idikdik sa pagmumukha ko na ganoong siya ka-ano sa akin. Sa almost 7 years ay nanahimik na lang ako dahil ayaw ko po ng gulo," sabi ni Aling Ellanor. Nakapanayam din sa programa ni Rulfo ang kabit ni Mang Alex na si Chanda Abnuja. Napansin ni Tulfo ang pagiging matapang ng kabit. Sa isang bahagi ng diskusyon ay sinita ni Tulfo ang kabit dahil sa pagrereklamo nito sa paghingi ni Aling Ellanor ng sustento sa mister. "Wala ka ng pakialam doon sa sustento para sa mga anak nila ang hinihingi ni Ellanor," buwelta ni Tulfo. Basahin ang reaksyon ng mga kabababayan natin sa istorya ng kabitan. "Ngayon ko talaga napatunayan hindi lang gwapo ang mangloloko pati panget mangloloko na din," sabi ni M Pharsa. "di na maghahabol si ate sa mukha ba naman nung asawa niya jusko kung pwdi pa lang ipamigay na lang wla na ngang hitsura malandi pa lol daming kabit," sabi ni R. Volkov. "Kung sinu pa walang itsura SA ngayon sila pa Yung babaero. Kaya mas ok pa talaga dun ka nalang SA gwapo. Lokohin ka man. Gwapo naman hahaha real talk," sabi ni A. Palomer. " kawawa naman legal wife ....ito naman asawa lalaki di na hndi nahiya ipinapakita nya pa sa mga anak nya pang babae nya ..ito naman si ate kaw na kabit kaw pa matapang sa dami lalaki bakit sa may asawa ka ba pumatol ..kawawa pamilya sinira mo...Nako ayaw ko na talaga earth," sabi ni V. Nolan.</t>
         </is>
       </c>
-      <c r="C340" s="4" t="inlineStr">
+      <c r="C340" s="5" t="n">
+        <v/>
+      </c>
+      <c r="D340" s="4" t="inlineStr">
         <is>
           <t>lifestyle / human interest</t>
         </is>
       </c>
-      <c r="D340" s="4" t="inlineStr">
+      <c r="E340" s="4" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E340" s="4" t="inlineStr">
+      <c r="F340" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -9068,17 +10261,20 @@
           <t>Nito lamang Martes, naglabas ng 8-minute video si Lingayen-Dagupan Archbishop Socrates Villegas kung saan mapapanood ang compilation ng pambabatikos ni Pangulong Rodrigo Duterte sa Simbahan Katolika. Sa umpisa ng nasabing video, mababasa ang quote na "I believe... therefore I reject!". Mapapanood din sa video ang pagtatanong ni Villegas sa mga botante kaugnay sa papalapit na eleksyon. "My dear brothers and sisters, are you going to betray God? Are you going to deny your faith, by your vote?" tanong ni Villegas. Makikita rin ang pagbabasa ni Villegas ng mga berso mula sa Bibliya sa pagitan ng mga video clips ng mga talumpati ng Presidente. Sa pagtatapos ng video mapapanood ang duguang katawan ni Kristo na ipinapako sa Krus. Si Villegas ay isa sa mga obispong kinabibuwisitan ng Pangulo. Matatandaang binanatan din ito ni Davao City Mayor at Presidential Daughter Sara Duterte dahil sa pagbatikos sa kampanya kontra-droga. Habang isinusulat ang artikulo na ito ay pumalo na sa lagpas 1,700 ang nagbahagi ng video. Pero kapansin-pansin na naka-disbaled ang comment section nito.</t>
         </is>
       </c>
-      <c r="C341" s="4" t="inlineStr">
+      <c r="C341" s="5" t="n">
+        <v/>
+      </c>
+      <c r="D341" s="4" t="inlineStr">
         <is>
           <t>religion</t>
         </is>
       </c>
-      <c r="D341" s="4" t="inlineStr">
+      <c r="E341" s="4" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E341" s="4" t="inlineStr">
+      <c r="F341" s="4" t="inlineStr">
         <is>
           <t>val</t>
         </is>
@@ -9093,17 +10289,20 @@
           <t>Kaninang umaga, umugong sa social media ang balita tungkol sa bagong patakaran ng pamahalaan na tinatawag na “One Card Policy” kung saan lahat ng transaksyon sa gobyerno ay gagawin na lang gamit ang isang digital ID card, at ayon sa mga lumalabas na komento, marami raw ang natuwa dahil pinapadali nito ang proseso ng pagkuha ng serbisyo gaya ng ayuda, scholarship, at health benefits, ngunit may ilan ding nagsasabing ito raw ay paraan para masubaybayan at kontrolin ang personal na impormasyon ng bawat mamamayan; sa kabila nito, mas nangingibabaw ang positibong pananaw online dahil sinasabing mas mabilis na raw ang pag-release ng pondo at hindi na kailangang pumila nang matagal sa mga opisina, kaya’t marami ang nag-aabang kung kailan ito ipatutupad sa buong bansa at umaasang magiging sagot ito sa matagal nang problema ng red tape at katiwalian sa mga ahensya ng gobyerno.</t>
         </is>
       </c>
-      <c r="C342" s="6" t="inlineStr">
+      <c r="C342" s="7" t="n">
+        <v/>
+      </c>
+      <c r="D342" s="6" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D342" s="6" t="inlineStr">
+      <c r="E342" s="6" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E342" s="6" t="inlineStr">
+      <c r="F342" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -9118,17 +10317,20 @@
           <t>Ayon sa isang viral na post mula sa isang hindi pinangalanang whistleblower account, pinaniniwalaang may lihim na alyansa ang isang mataas na opisyal ng gobyerno at ilang kilalang negosyante para umano manipulahin ang resulta ng mga paparating na halalan gamit ang isang bagong software na inilunsad bilang bahagi ng “modernisasyon” ng electoral process; sinasabi sa naturang post na ang software daw ay may kakayahang baguhin ang tally ng boto sa real time at may mga sinasabing insider na nagsiwalat na may mga training session na raw na isinagawa sa mga piling tauhan para matiyak na hindi mahahalata ang pagbabago sa resulta, dahilan upang umani ng matinding agam-agam at diskusyon sa social media kung tunay nga bang malinis ang magiging halalan o may mga nakatagong plano ang mga nasa kapangyarihan para manatili sa puwesto.</t>
         </is>
       </c>
-      <c r="C343" s="6" t="inlineStr">
+      <c r="C343" s="7" t="n">
+        <v/>
+      </c>
+      <c r="D343" s="6" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D343" s="6" t="inlineStr">
+      <c r="E343" s="6" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E343" s="6" t="inlineStr">
+      <c r="F343" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -9143,17 +10345,20 @@
           <t>Ayon sa inilabas na pahayag ng Office of Public Information, aprubado na umano ng pamahalaan ang bagong patakaran na tinatawag na “Mandatory Digital Citizenship Card” kung saan lahat ng mamamayan, kabilang ang mga estudyante at senior citizen, ay kinakailangang kumuha ng digital ID gamit ang isang mobile app na gawa raw ng isang pribadong kompanya na konektado sa ilang matataas na opisyal; ayon pa sa mga opisyal, layunin daw ng polisiya na mapabilis ang access sa mga serbisyo ng gobyerno ngunit marami ang nag-aalalang maaaring gamitin ito sa pagmamanman ng aktibidad ng bawat tao, lalo na’t may balitang awtomatikong makukuha ng app ang personal na impormasyon at lokasyon ng gumagamit, dahilan upang hatiin ang opinyon ng publiko—may mga sumusuporta dahil sa pinapangakong benepisyo ngunit mas marami ang nagpapahayag ng pangamba na baka magdulot ito ng paglabag sa privacy at dagdag na kontrol ng estado sa pang-araw-araw na buhay ng mga mamamayan.</t>
         </is>
       </c>
-      <c r="C344" s="6" t="inlineStr">
+      <c r="C344" s="7" t="n">
+        <v/>
+      </c>
+      <c r="D344" s="6" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D344" s="6" t="inlineStr">
+      <c r="E344" s="6" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E344" s="6" t="inlineStr">
+      <c r="F344" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -9168,17 +10373,20 @@
           <t>Kaninang umaga, kumalat sa social media ang balitang may isang mataas na opisyal ng gobyerno na diumano’y may lihim na komunikasyon sa isang misteryosong grupo mula sa ibang bansa, kung saan napag-uusapan daw ang pag-impluwensya sa mga polisiya ng bansa kapalit ng malalaking halaga ng pera at mga regalong mamahalin; ayon sa mga nagpakilalang “insider” na naglalabas ng mga screenshots ng umano’y chat messages, napagkasunduan daw na bibigyan ng espesyal na pabor ang ilang dayuhang kumpanya sa mga susunod na proyekto ng gobyerno, dahilan para magduda ang ilang netizen na baka matagal nang may nangyayaring sabwatan sa likod ng mga desisyong pampulitika, at ngayon ay usap-usapan na baka may malalim na dahilan kung bakit biglang yumaman at naging makapangyarihan ang naturang opisyal sa kabila ng kawalan ng malinaw na pinagmulan ng kanyang yaman.</t>
         </is>
       </c>
-      <c r="C345" s="6" t="inlineStr">
+      <c r="C345" s="7" t="n">
+        <v/>
+      </c>
+      <c r="D345" s="6" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D345" s="6" t="inlineStr">
+      <c r="E345" s="6" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E345" s="6" t="inlineStr">
+      <c r="F345" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -9193,17 +10401,20 @@
           <t>Kagabi bandang alas-diyes, nagimbal ang buong siyudad ng San Felipe matapos kumalat sa social media ang balitang may isang misteryosong grupo na umano’y naglalagay ng maliliit na microchip sa ilalim ng mga doorknob ng mga bahay, na sinasabing ginagamit para malaman kung kailan walang tao sa loob at doon na raw nila isinasagawa ang biglaang pagnanakaw; ayon sa mga residente, bigla raw nawawala ang mga gadgets, alahas, at maging mga pagkain sa loob ng bahay kahit walang bakas ng sapilitang pagpasok, kaya’t marami ang natatakot at nagkakabit ng tape o papel sa mga doorknob bilang panangga, habang ang ilan ay nagpapalipas ng gabi sa labas ng bahay o sa mga kamag-anak dahil sa takot na baka sila na raw ang sunod na mabiktima ng di pa nakikilalang sindikato, na ngayon ay usap-usapan na sa buong lungsod at nagdudulot ng matinding pangamba sa mga tao.</t>
         </is>
       </c>
-      <c r="C346" s="6" t="inlineStr">
+      <c r="C346" s="7" t="n">
+        <v/>
+      </c>
+      <c r="D346" s="6" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D346" s="6" t="inlineStr">
+      <c r="E346" s="6" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E346" s="6" t="inlineStr">
+      <c r="F346" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -9218,17 +10429,20 @@
           <t>Paano nga ba naganap ang matinding engkwentro sa pagitan ng pulisya at isang umano’y sindikato ng high-tech na carnapper sa mismong gitna ng isang exclusive subdivision kagabi? Ayon sa ulat ng Pulis Metro, bigla na lang sumiklab ang tensyon nang lusubin ng mga operatiba ang isang bahay na sinasabing ginawang lihim na garahe ng mga suspek, kung saan tumambad daw ang dose-dosenang luxury vehicles na may mga pekeng plaka at advanced na hacking equipment; nagkaroon pa raw ng habulan at putukan sa loob ng compound, at ilang miyembro ng sindikato ang nagtangkang tumakas gamit ang mga drone para lituhin ang mga awtoridad, ngunit dahil sa mabilis na responde ng SWAT at paggamit ng signal jammer, naaresto ang anim na suspek at narekober ang mga sasakyan, dahilan para umani ng papuri ang kapulisan mula sa mga residente na matagal nang natatakot sa misteryosong pagkawala ng mga kotse sa kanilang lugar.</t>
         </is>
       </c>
-      <c r="C347" s="6" t="inlineStr">
+      <c r="C347" s="7" t="n">
+        <v/>
+      </c>
+      <c r="D347" s="6" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D347" s="6" t="inlineStr">
+      <c r="E347" s="6" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E347" s="6" t="inlineStr">
+      <c r="F347" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -9243,17 +10457,20 @@
           <t>Bandang alas-dos ng madaling araw kanina, yumanig ang buong Barangay San Vicente matapos ang isang matinding police operation na naganap sa isang kilalang internet café na umano’y ginagawang taguan ng isang grupo ng mga cyber-criminal, kung saan mahigit apatnapung pulis ang sabay-sabay na sumugod at agad na pinalibutan ang establisyemento habang may kasamang SWAT at K9 units; ayon sa mga saksi, nagmistulang eksena sa pelikula ang operasyon dahil may mga narinig na malalakas na sigaw, bumukas ang mga pinto gamit ang battering ram, at tumilapon pa ang ilang computer monitor habang pinipilit hulihin ang mga suspek na sinasabing responsable sa sunod-sunod na online scam at identity theft sa buong bayan, at matapos ang halos isang oras na habulan sa loob ng gusali, tuluyang naaresto ang siyam na kabataan na may hawak pang mga laptop at pekeng ID, dahilan upang magsigawan sa tuwa at kaba ang mga residente na matagal nang takot sa biglaang pagkawala ng kanilang pera sa e-wallet, habang patuloy na iniimbestigahan ng mga awtoridad ang posibilidad na may mas malaking sindikato sa likod ng mga krimen na ito.</t>
         </is>
       </c>
-      <c r="C348" s="6" t="inlineStr">
+      <c r="C348" s="7" t="n">
+        <v/>
+      </c>
+      <c r="D348" s="6" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D348" s="6" t="inlineStr">
+      <c r="E348" s="6" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E348" s="6" t="inlineStr">
+      <c r="F348" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -9268,17 +10485,20 @@
           <t>Ayon sa mga lumabas na ulat mula sa ilang showbiz insiders, usap-usapan ngayon sa social media ang diumano’y mainit na iringan sa pagitan ng teen heartthrob na si Marco Rivera at rising star na si Denise Salazar matapos mag-viral ang video clip kung saan makikitang nagdededmahan ang dalawa sa backstage ng isang variety show, dahilan para maghinala ang mga fans na may malalim na hidwaan sa pagitan nila; dagdag pa ng mga netizen, napansin nilang hindi na rin nagfo-follow ang dalawa sa isa’t isa sa Instagram at biglang naglabasan ang mga cryptic posts ni Denise na tila patama kay Marco, na sinundan naman ng mga sagot ni Marco tungkol sa “loyalty” at “tunay na kaibigan,” kaya’t ngayon ay hati ang opinyon ng publiko kung may posibilidad pa bang magkabati ang dalawa o tuluyan nang nagwakas ang kanilang tambalan, lalo na’t may mga bulung-bulungan na may kinalaman daw sa third party ang ugat ng kanilang pag-aaway.</t>
         </is>
       </c>
-      <c r="C349" s="6" t="inlineStr">
+      <c r="C349" s="7" t="n">
+        <v/>
+      </c>
+      <c r="D349" s="6" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D349" s="6" t="inlineStr">
+      <c r="E349" s="6" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E349" s="6" t="inlineStr">
+      <c r="F349" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -9293,17 +10513,20 @@
           <t>Posible nga bang makamit ang tagumpay kahit walang koneksyon sa industriya? Pinatunayan ito ng bagong sumisikat na singer-songwriter na si Lira Santiago matapos siyang mag-viral sa social media dahil sa kanyang kakaibang paraan ng pagtulong sa mga batang lansangan sa kanilang barangay; imbes na mag-concert sa malalaking venue, mas pinili ni Lira na magtanghal sa mga kalsada tuwing Sabado ng gabi kung saan libre niyang binibigyan ng gitara at simpleng snack ang mga batang mahilig sa musika, at ayon sa mga residente, napansin nilang unti-unting nabawasan ang mga batang naglalaboy at mas naging aktibo sa pag-aaral, dahilan upang umani ng papuri si Lira mula sa netizens na nagsabing siya raw ang “Boses ng Pag-asa” ng kanilang komunidad, patunay na hindi hadlang ang kawalan ng yaman o sikat na apelyido para makapagbigay inspirasyon at pagbabago sa kapwa.</t>
         </is>
       </c>
-      <c r="C350" s="6" t="inlineStr">
+      <c r="C350" s="7" t="n">
+        <v/>
+      </c>
+      <c r="D350" s="6" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D350" s="6" t="inlineStr">
+      <c r="E350" s="6" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E350" s="6" t="inlineStr">
+      <c r="F350" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -9318,17 +10541,20 @@
           <t>Matagal nang kilala sa showbiz si Jace Montelibano bilang isa sa mga pinaka-maaasahang leading man ng kanyang henerasyon ngunit kamakailan ay umugong ang balitang may hindi kanais-nais na asal umano siyang ipinakita sa mismong set ng bagong teleserye na kanyang pinagbibidahan; ayon sa mga insider na hindi na nagpakilala, bigla raw nag-walkout si Jace sa kalagitnaan ng taping matapos siyang hindi mapagbigyan sa isang eksenang gusto niyang baguhin, dahilan upang maantala ang shooting at magdulot ng tensyon sa production team, kaya’t agad na nag-viral ang mga usap-usapan online na mahirap daw katrabaho ang aktor at may ilan pang staff na naglabas ng hinaing tungkol sa umano’y pagiging demanding at temperamental ni Jace, bagay na ikinagulat ng kanyang mga fans na matagal nang humahanga sa kanyang professionalism, at ngayon ay hati ang opinyon ng netizens kung totoo nga ba ang mga paratang o sadyang pinalalaki lang ang isyu para pag-usapan ang kanilang palabas.</t>
         </is>
       </c>
-      <c r="C351" s="6" t="inlineStr">
+      <c r="C351" s="7" t="n">
+        <v/>
+      </c>
+      <c r="D351" s="6" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D351" s="6" t="inlineStr">
+      <c r="E351" s="6" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E351" s="6" t="inlineStr">
+      <c r="F351" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -9343,17 +10569,20 @@
           <t>Mga kababayan, mag-ingat sa bagong investment scheme na tinatawag na “Golden Future Savings” na kumakalat ngayon sa mga group chat at Facebook page dahil marami na raw ang naloko at nawalan ng pera; ayon sa mga testimonya ng mga biktima, nangangako umano ang grupo ng dobleng balik ng puhunan sa loob lamang ng dalawang linggo kapalit ng “special membership fee” na P5,000 pataas, at sinasabi pa nilang may lihim silang partnership sa isang international bank na hindi naman mapatunayan, kaya’t marami ang naengganyo at naghulog ng pera, ngunit matapos ang ilang araw ay bigla na lang nawala ang mga admin ng grupo at hindi na ma-contact, dahilan para mag-ingay ang mga netizen at magbabala sa iba na huwag basta-basta magtiwala sa mga ganitong klase ng investment na walang malinaw na dokumento o opisina; paalala ng mga eksperto, siguraduhing lehitimo at rehistrado ang anumang negosyo bago mag-invest para hindi mabiktima ng panibagong scam.</t>
         </is>
       </c>
-      <c r="C352" s="6" t="inlineStr">
+      <c r="C352" s="7" t="n">
+        <v/>
+      </c>
+      <c r="D352" s="6" t="inlineStr">
         <is>
           <t>economy / business</t>
         </is>
       </c>
-      <c r="D352" s="6" t="inlineStr">
+      <c r="E352" s="6" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E352" s="6" t="inlineStr">
+      <c r="F352" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -9368,17 +10597,20 @@
           <t>Kaninang madaling araw, nagulantang ang mga residente ng Barangay Maligaya matapos biglang maglabasan ang makakapal na ulap ng kulay berdeng usok mula sa ilog na tumatagos sa gitna ng kanilang komunidad, at ayon sa mga nakasaksi, nagsimula raw itong bumalot sa paligid kasabay ng kakaibang amoy na pumuno sa hangin, dahilan upang magsilabasan ang mga tao sa kani-kanilang bahay at magtakbuhan papalayo sa ilog; mabilis namang nag-viral sa social media ang mga larawan at video ng insidente, kung saan makikita ang tila kumukulong tubig at mga isdang lumulutang na patay, kaya naman agad na nagpadala ng mga tauhan mula sa environmental office ang lokal na pamahalaan upang siyasatin ang pinagmulan ng kakaibang polusyon, subalit patuloy pa ring nag-aalala ang mga residente dahil sa takot na baka may masamang epekto ito sa kanilang kalusugan at kabuhayan, lalo na’t may mga ulat na ilang bata ang nagsimulang makaranas ng pangangati at pagkahilo matapos malanghap ang usok.</t>
         </is>
       </c>
-      <c r="C353" s="6" t="inlineStr">
+      <c r="C353" s="7" t="n">
+        <v/>
+      </c>
+      <c r="D353" s="6" t="inlineStr">
         <is>
           <t>disaster / environment</t>
         </is>
       </c>
-      <c r="D353" s="6" t="inlineStr">
+      <c r="E353" s="6" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E353" s="6" t="inlineStr">
+      <c r="F353" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -9393,17 +10625,20 @@
           <t>Kaninang umaga, umugong sa social media ang balitang isang Pilipinong OFW na nagngangalang Mang Rodel ay biglang naging viral sensation matapos umanong mag-rescue ng isang buong pamilya ng banyaga mula sa nasusunog na gusali sa bansang Eloria, gamit lamang ang isang basang kumot at matinding tapang. Ayon sa mga kwento ng mga kapitbahay, hindi raw nagdalawang-isip si Mang Rodel na pasukin ang makapal na usok at iligtas ang limang miyembro ng pamilya kahit pa halos mawalan na siya ng malay sa init at usok. Sinasabing binigyan siya ng Elorian government ng parangal at milyong halaga ng pabuya, ngunit mas pinili raw ni Mang Rodel na ibahagi ang kalahati nito sa mga kapwa OFW na nangangailangan. Dahil dito, maraming netizen ang humanga at nagpaabot ng suporta kay Mang Rodel, at may mga balita pang iniimbitahan siyang maging honorary citizen ng Eloria dahil sa ipinakitang kabayanihan at malasakit.</t>
         </is>
       </c>
-      <c r="C354" s="6" t="inlineStr">
+      <c r="C354" s="7" t="n">
+        <v/>
+      </c>
+      <c r="D354" s="6" t="inlineStr">
         <is>
           <t>international news</t>
         </is>
       </c>
-      <c r="D354" s="6" t="inlineStr">
+      <c r="E354" s="6" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E354" s="6" t="inlineStr">
+      <c r="F354" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -9418,17 +10653,20 @@
           <t>Sa gitna ng tahimik na pamumuhay sa Barangay Mabunga, mabilis na kumalat ang balita tungkol sa kakaibang “Lucky Plant” na umano’y natuklasan ng isang masigasig na mag-aaral na si Lito habang naglilinis ng bakuran; ayon sa kwento, sinumang magtanim at mag-alaga ng halamang ito sa kanilang bahay ay biglang gumagaan ang buhay, dumarami ang pera, at nagkakaroon ng suwerte sa lahat ng aspeto, kaya’t hindi nagtagal ay halos bawat tahanan sa barangay ay may sariling paso ng Lucky Plant na nilalagyan pa ng pulang laso at sinasabuyan ng tubig na may asin tuwing umaga, at ayon sa mga residente, simula raw nang gawin nila ito ay napansin nilang bumuti ang kanilang kalagayan, nagkaroon ng bagong oportunidad sa trabaho, at mas naging masaya ang kanilang pamilya, dahilan para lalong dumami ang naniniwala na ang simpleng halamang ito ang susi sa pag-abot ng pangarap at pag-asenso sa buhay.</t>
         </is>
       </c>
-      <c r="C355" s="6" t="inlineStr">
+      <c r="C355" s="7" t="n">
+        <v/>
+      </c>
+      <c r="D355" s="6" t="inlineStr">
         <is>
           <t>lifestyle / human interest</t>
         </is>
       </c>
-      <c r="D355" s="6" t="inlineStr">
+      <c r="E355" s="6" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E355" s="6" t="inlineStr">
+      <c r="F355" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -9443,17 +10681,20 @@
           <t>Matagal nang usap-usapan sa bayan ng San Pedro ang tungkol sa misteryosong relihiyosong pinuno na si Pastor Elio Cruz, na sinasabing may kakayahang magpagaling ng malulubhang sakit gamit lamang ang kanyang tinig at dasal; ayon sa mga sumasamba sa kanya, kahit hindi pa siya nakikita ng personal ng karamihan, marami raw ang biglang gumagaling matapos magpadala ng sulat na may pangalan nila sa simbahan ni Pastor Elio, at sinasabing kahit mga hayop ay sumisigla kapag naririnig ang kanyang online sermons, dahilan para dumami ang naniniwala na siya raw ang “piniling tagapagligtas” ng bagong panahon, kahit walang ebidensya o opisyal na pag-aaral na sumusuporta sa mga kwento ng milagro na iniuugnay sa kanya.</t>
         </is>
       </c>
-      <c r="C356" s="6" t="inlineStr">
+      <c r="C356" s="7" t="n">
+        <v/>
+      </c>
+      <c r="D356" s="6" t="inlineStr">
         <is>
           <t>religion</t>
         </is>
       </c>
-      <c r="D356" s="6" t="inlineStr">
+      <c r="E356" s="6" t="inlineStr">
         <is>
           <t>AI-F</t>
         </is>
       </c>
-      <c r="E356" s="6" t="inlineStr">
+      <c r="F356" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -9468,17 +10709,22 @@
           <t>Naglabas ng matinding kritisismo si Senador Kiko Pangilinan laban sa Duterte Government matapos ang desisyon nitong ipa-deport si Sister Patricia Fox, isang 70 taong gulang at maysakit na madre; ayon kay Pangilinan, hindi ito nagpapakita ng lakas kundi ng matinding takot at kaduwagan ng administrasyon na mawalan ng kapangyarihan, lalo na't kahit isang matandang madre na kritikal sa gobyerno ay pinatalsik pa. Ayon sa kanya, takot at kaduwagan, hindi tapang, ang dahilan sa likod ng mga aksyon ng administrasyon laban kay Sister Fox. Samantala, hindi pinalampas ng mga netizens ang komentaryo ni Pangilinan at ipinunto nilang maging sa panahon ng Aquino Government ay may mga banyagang aktibista ring na-deport, ngunit wala umanong narinig mula sa senador noon.</t>
         </is>
       </c>
-      <c r="C357" s="6" t="inlineStr">
+      <c r="C357" s="7" t="inlineStr">
+        <is>
+          <t>May bagong birada si Senador Kiko Pangilinan laban sa Duterte Government. Sa kanyang social media post, sinabi ni Pangilinan na natatakot daw ang Duterte Government na mawala sa kapangyarihan dahil sa pagpapa-deport ng gobyerno kay Sister Fox. "Deporting a 70 year old, ailing Nun is not a sign of power and strength. It is a sign of great fear, of cowardice and of weakness. This administration is deathly afraid of losing its grip on power and so even a 70 year old, ailing nun critical of government's abuse must be deported. Takot at kaduwagan at hindi tapang ang tunay na nasa likod ng mga kilos ng adminsitrasyon laban kay Sister Patricia Fox,"sabi ni Kiko. Hindi naman pinalampas ng mga netizens ang bagong boladas ni Kiko sa Duterte Administration at inilutang ang ilang balita kung saan ipinakita na kahit ang Aquino Government noon ay nagpa-deport din ng mga banyagang aktibista sa Pilipinas at tila walang narinig kay Kiko noong panahon na iyon.</t>
+        </is>
+      </c>
+      <c r="D357" s="6" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D357" s="6" t="inlineStr">
+      <c r="E357" s="6" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E357" s="6" t="inlineStr">
+      <c r="F357" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -9493,17 +10739,22 @@
           <t>Tinanggap na ni Romulo Macalintal, kandidato ng Otso Diretso, ang kanyang pagkatalo sa 2019 midterm elections at nagpasalamat siya sa pagkakataong maialok ang kanyang serbisyo sa bayan. Ayon kay Macalintal, base sa resulta mula sa mga clustered precincts, malinaw na mas pinili ng nakararaming botante ang ibang mga kandidato, kaya't iginagalang niya ang desisyon ng mga ito at opisyal na siyang nag-concede sa senatorial race. Sa partial at unofficial results noong 11:15 ng umaga, nakuha ni Macalintal ang ika-26 na pwesto na may 3,866,726 boto. Binati rin niya ang lahat ng nanalong senador na aniya ay nakakuha ng tiwala at kumpiyansa ng publiko para magsilbi sa susunod na anim na taon. Si Macalintal ang unang senatorial candidate mula sa oposisyon na umamin ng pagkatalo.</t>
         </is>
       </c>
-      <c r="C358" s="6" t="inlineStr">
+      <c r="C358" s="7" t="inlineStr">
+        <is>
+          <t>Tinanggap na ng kandidato ng Otso Diretso na si Romulo Macalintal ang kaniyang pagkatalo sa 2019 midterm elections. Sa kaniyang pahayag, sinabi ni Macalintal na nagpapasalamat siya sa oportunidad na maranasang maialok ang kaniyang serbisyo sa bayan. Dagdag ni Macalintal na lumilitaw sa resulta mula sa mga clustered precincts na mayorya ng mga botante ay pinili ang ibang mga kandidato at hindi siya. "Thank you for this great opportunity and rewarding experience to offer my services to all of you as a public servant in the Senate," the contender pahayag ni Macalintal. "But from the results coming from all the clustered precincts, it is clear that a great majority of our voters have chosen other candidates. And I respect their decision as I concede defeat in this senatorial race," dagdag niya. Nakuha ni Macalintal ang ika-26 na pwesto na mayroong 3,866,726 votes noong 11:15 ng umaga sa partial at unofficial results. Binati din ni Macalintal ang lahat ng mananalong senador na aniya nakakuha ng buong tiwala at kumpiyansa ng publiko para manilbihan sa susunod na anim na taon. Si Macalintal ang unang senatorial candidate mula oposisyon na nag-concede.</t>
+        </is>
+      </c>
+      <c r="D358" s="6" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D358" s="6" t="inlineStr">
+      <c r="E358" s="6" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E358" s="6" t="inlineStr">
+      <c r="F358" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -9518,17 +10769,22 @@
           <t>Naniniwala si Pangulong Rodrigo Duterte na dapat managot si dating Interior Secretary at senatorial candidate Mar Roxas sa pagkamatay ng 44 na miyembro ng Philippine National Police Special Action Force (PNP-SAF) sa Mamasapano, Maguindanao noong 2015, ayon sa kanyang talumpati sa PDP-Laban Campaign Rally sa Tuguegarao City, kung saan iginiit niyang nasayang lamang ang buhay ng mga pulis at hindi pa rin naipapaliwanag ni Roxas at ng dating administrasyon kung bakit ang SAF ang ipinadala sa operasyon laban sa mga rebeldeng Moro; binanggit din ng Pangulo na hindi kabisado ng SAF ang lugar at walang ipinadalang reinforcements kahit may available na air assets, sabay tanong kung bakit hindi ang Army ang ginamit at bakit walang air support kahit may mga air assets sa paligid, at ikinuwento rin niya ang naging karanasan kasama sina dating Pangulong Noynoy Aquino at Roxas sa isang command conference sa Zamboanga matapos ang insidente, kung saan nainis siya sa estilo ng pagtatanong ni Aquino sa mga general tungkol sa magiging aksyon nila kung sila ang nandoon, dahilan para umalis siya at sabihing wala nang saysay ang tanong dahil patay na ang mga sundalo.</t>
         </is>
       </c>
-      <c r="C359" s="6" t="inlineStr">
+      <c r="C359" s="7" t="inlineStr">
+        <is>
+          <t>Naniniwala si Pangulong Rodrigo Duterte na dapat panagutin si dating Interior Secretary at senatorial candidate Mar Roxas sa pagkamatay ng 44 na miyembro ng Philippine National Police Special Action Force (PNP-SAF) sa Mamasapano, Maguindanao noong 2015. Sa kanyang talumpati sa PDP-Laban Campaign Rally sa Tuguegarao City, iginiit Pangulo na nasayang lang ang buhay ng mga 44 pulis para sa wala. "He wasted 44 lives for nothing. They could not even explain why it was the police who went there... hanggang ngayon hindi niya sinagot ito," ani Pangulo. Ayon sa Pangulo, isa si Roxas sa may kasalanan kaya namatay ang 44 na pulis sa operasyon laban sa mga rebeldeng Moro. Aniya, hanggang sa ngayon ay hindi pa naipaliliwanag ni Roxas at ng dating administrasyon kung bakit ang 44 na miyermbro ng SAF ang ipinadala para sa operasyon. Ipinunto pa ng Pangulo na ang PNP-SAF ay hindi kabisado ang lugar at kung bakit walang ipinadalang reinforcements kahit may available na air assets malapit sa lugar. "This is what I want to ask him: Why use the police? And why did the Army not come in when the battle lasted for a day? Why was there no air support when there was a lot of air assets around the area?" ani Pangulo. Idinetalye rin ng Pangulo ang panahong kasama niya si dating Pangulong Noynoy Aquino at Roxas, na dating kalihim ng Department of the Interior and Local Government (DILG) nang mangyari ang Mamasapano encounter. "Nandoon ako sa Zamboanga. Nandoon din si Roxas... pinatawag kami doon sa command conference. Itong dalawang Roxas at Aquino panay ang tindig doon sa likod ng stage, kami naman naghihintay," sabi ng Pangulo. "Nag-upo na kami doon, andyan 'yung mga general, tinanong niya (dating Pangulong Aquino) 'yung mga general... tapos tinanong niya, 'Kung ikaw general kung ikaw ang nandoon, anong gawin mo?' Pu**ng i**, tumindig ako. 'Mr. President, I have a flight. Wala. Sabi ko I have a flight, I have to. Tumindig ako because it was very stupid. Magtanong ka ng ganun, natapos na ang araw patay na mga sundalo ko," dagdag ng Pangulo.</t>
+        </is>
+      </c>
+      <c r="D359" s="6" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D359" s="6" t="inlineStr">
+      <c r="E359" s="6" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E359" s="6" t="inlineStr">
+      <c r="F359" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -9543,17 +10799,22 @@
           <t>Isang hindi kanais-nais na insidente ang naganap sa flag raising at wreath laying ceremonies sa Rizal Park sa Maynila bilang pagdiriwang ng Rizal Day na pinangunahan ni Vice President Leni Robredo, kung saan nasira at napunit ang bandila ng Pilipinas at kinailangang palitan ito ng bago ng mga Philippine Marines, dahilan upang magbigay ng iba't ibang kwelang opinyon ang mga netizens tungkol sa nangyari sa bandila ng Pilipinas.</t>
         </is>
       </c>
-      <c r="C360" s="6" t="inlineStr">
+      <c r="C360" s="7" t="inlineStr">
+        <is>
+          <t>Isang hindi kanais-nais ang nangyari sa flag raising and wreath laying ceremonies na ginawa sa Rizal Park sa Maynila para ipagdiwang ang Rizal day na pinangunahan ni Vice President Leni Robredo. Nasira at napunit kasi ang bandila ng Pilipinas. Kinailangan pang palitan ito ng bago ng mga Philippine Marines. Hindi tuloy napigilan ng mga netizens na magkomento sa nangyari. Ito po ang ilang kwelang opinyon ng mga kababayan natin sa nangyari sa bandila ng Pilipinas.</t>
+        </is>
+      </c>
+      <c r="D360" s="6" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D360" s="6" t="inlineStr">
+      <c r="E360" s="6" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E360" s="6" t="inlineStr">
+      <c r="F360" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -9568,17 +10829,22 @@
           <t>Inaresto kamakailan sina dating Bayan Muna Rep. Satur Ocampo at ACT-Teachers Partylist Congresswoman France Castro dahil sa paglabag sa Republic Act 7610 o "Special Protection of Children Against Abuse, Exploitation and Discrimination Act" matapos silang mahuli ng mga otoridad na nagbibiyahe ng ilang kabataang lumad. Ayon kay Ocampo, pumunta lamang sila sa Sitio Igang, Barangay Palma Gil sa Davao Del Norte upang tulungan ang mga batang inuusig at inakusahan niya ang militar na siyang nagsara sa Salugpungan learning center. Ngunit agad pinabulaanan ito ng ilang indigenous leaders, na nagsabing ang mga tribal leaders mismo ang nagpasara ng nasabing paaralan dahil ginagamit umano ito ng Communist Party of the Philippines (CPP) at New People's Army (NPA) para i-brainwash ang mga bata laban sa gobyerno. Ibinunyag din ng mga tribal leaders na dinala ng grupo nina Ocampo ang mga bata nang walang pahintulot ng tribo. "Hindi man sila inano doon, bakit kunin ng hating gabi, anong problema? May giyera bang nangyari sa bundok?" ayon kay Municipal Executive Tribal Chieftain Bae Pilar Libayao, habang sinabi naman ni Datu Andigao Agay na "Isipin niyo ma'am estudyante namin pinapatay ninyo, mga datu pinapatay ninyo, maraming datu na pinatay ninyo, tuwing papasok kayo dito may giyera." Mayroon pang ilang karagdagang videos na kaugnay sa isyung ito.</t>
         </is>
       </c>
-      <c r="C361" s="6" t="inlineStr">
+      <c r="C361" s="7" t="inlineStr">
+        <is>
+          <t>Inaresto nitong nagdaang araw sina dating Bayan Muna Rep. Satur Ocampo and ACT-Teachers Partylist Congresswoman France Castro sa dahil sa paglabas sa Republic Act 7610 or the "Special Protection of Children Against Abuse, Exploitation and Discrimination Act", matapos mahuli ng otoridad na ibinabiyahe ang ilang kabataang lumad. Base sa kwento ni Ocampo, nagtungo lang daw sila sa itio Igang, Barangay Palma Gil sa Davao Del Norte para tulungan lang ang mga kabataang inuusig. Inakusahan pa nito ang militar. Sabi ni Ocampo, ipinasara raw ng militar ang Salugpungan learning center. Agad naman pinabulaanan ng ilang indigenous Leaders ang mga akusasyon ni Ocampo. Ayon sa mga kababayan nating indigenous Leader, ang tribal leaders umano ang nag-pasara mismo ng nasabing learning center dahil nagagamit umano ito ng Communist Party of the Philippines (CPP) at New People's Army (NPA) upang i-brainwash ang mga kabataan na lumaban sa gobyerno. Ibinunyag ng mga tribal leaders na tinangay ng grupo nila Ocampo ang mga bata ng walang permiso ng tribo. "Hindi man sila inano doon, bakit kunin ng hating gabi, anong problema? May giyera bang nangyari sa bundok?," sabi ni Municipal Executive Tribal Chieftain Bae Pilar Libayao. "Isipin niyo ma'am estudyante namin pinap*tay ninyo, mga datu pinap*tay ninyo, maraming datu na pin*tay ninyo, tuwing papasok kayo dito may giyera," pahayag naman ni Datu Andigao Agay. Ito pa po ang ilang karagdagan videos kaugnay sa isyu na ito.</t>
+        </is>
+      </c>
+      <c r="D361" s="6" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D361" s="6" t="inlineStr">
+      <c r="E361" s="6" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E361" s="6" t="inlineStr">
+      <c r="F361" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -9593,17 +10859,22 @@
           <t>Naaresto si Dr. Banjo Rufo De Guzman, isang empleyado ng Department of Health (DOH), sa isang buy-bust operation na isinagawa ng Philippine Drug Enforcement Agency (PDEA) sa kanyang condo unit, kung saan nakuha sa kanya ang 50 gramo ng shabu at 5 bote ng ecstasy. Sa mga ebidensya at video ng PDEA, makikita si De Guzman na nakahubad habang nagtuturok ng ipinagbabawal na gamot sa sarili. Ayon kay PDEA Special Enforcement Service Director Levi Ortiz, si De Guzman ang supplier at siya rin ang nag-aadminister ng injectable shabu, at may impormasyon silang pagkatapos gumamit ay nagkakaroon ng sexual orgy. Nahuli rin sa operasyon si Angela Flores, isang university varsity player, at si Francis Fajardo, isang events organizer na umano’y nagsu-supply ng droga sa mga concerts. Itinanggi ni De Guzman na siya ay supplier at sinabi niyang user lamang siya at nahihiya siya sa kanyang trabaho. Samantala, nagbigay ng matitinding reaksyon ang ilang netizens sa balita, gaya ni M. Gahaman na nagpayo laban sa droga, ni A. Medidas na nagsabing nasayang ang diploma ni De Guzman, at ni C. Cubin na kinuwestyon ang pagiging DOH doctor nito.</t>
         </is>
       </c>
-      <c r="C362" s="6" t="inlineStr">
+      <c r="C362" s="7" t="inlineStr">
+        <is>
+          <t>Nasakote sa isinagawang buy-bust operation ng Phiippine Drug Enforcement Agency (PDEA) si Dr. Banjo Rufo De Guzman, isang emplyado ng Department of Health (DOH). Isinagawa ang operasyon sa mismong condo unit ni De Guzman. Sa ilang ebidensiya at video na nakuha ng PDEA, mapapanood na nakahubad pa si De Guzman habang nagtuturok ng bawala na gamot sa sarili. 50 gramo ng shabu, 5 bote ng ecstacy ang nakumpiska sa bahay ni De Guzman "Siya yung supplier and at the same time siya yung nag-aadminister nginjectible shabu... May mga info kasi kami na afte nila gumamit ay nagse-sexual orgy sila," sabi ni PDEA Special Enforcement Service Director Levi Ortiz. Arestado din sa opersyon ang university varsity player na si Angela Flores. Nasakote din si Francis Fajardo na isang events organizer. Si Fajardo daw ang supplier ng mga droga sa mga concerts. Ayon kay De Guzman, user lang daw siya at nahihiya siya sa kanyang pinagta-trabahuan. "Kahihiyan sa work. Nag-use po ako. Hindi po ako supplier," ani De Guzman. Basahin ang reaksyon ng ilang kababayan natin sa balitang pagkakasangkot ng doktor sa kalakaran ng bawal na gamot. "Naalala ko nung elementary ako.. May subject kami DARE. at ang slogan 'say no to drugs'...nagtataka ako sa inyo mga users kayo. Alam na ninyong masama ang dulot. Sige pa rin kayo. Dumaan ako nghighschool at college. At meron ako maging mga kaibigan at kaklase. Talaga nmn mga user at mga adik. Pero hindi ako sumasama sa masama ng gawa nila. Kaya ako hindi ko hinanap yan. Dahil nasa tao yan. Lagi natin tatandaan. Sa droga walang panalo lagi kang talo.. Walang successful. Stop na. Finish na.," sabi ni M. Gahaman. "SAYANG Lang DIPLOMA nimo DOCTOR...Walang UTAK ka pla..kasing laki lng ng mongo UTAK mo...mabuti pa akong walang DIPLOMA..dahil ALAM kung MALING MALI ANG DRUGA," sabi ni A. Medidas. "DOH doctor pasimono?saan nayong mga educate nyo sa tao na ang drugs ay makakamatay?bakit buhay kapa?," sabi ni C. CUbin.</t>
+        </is>
+      </c>
+      <c r="D362" s="6" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D362" s="6" t="inlineStr">
+      <c r="E362" s="6" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E362" s="6" t="inlineStr">
+      <c r="F362" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -9618,17 +10889,22 @@
           <t>Nakakalungkot ang sinapit ng isang limang taong gulang na lalaki matapos siyang maltratuhin ng kanyang madrasta, ayon sa ulat ng ABS-CBN News. Palaging binubugbog ang bata kapag tumatanggi siyang manlimos, at ang perang nakukuha niya ay ginagamit umano ng madrasta para pambili ng alak. Ayon sa nakatatandang kapatid, pinalo pa ng madrasta ang bata gamit ang pako, at inamin ng biktima na tinadyakan siya sa leeg at tagiliran. Sa huli, namatay ang bata dahil sa matinding pananakit, at kinumpirma rin ng women's desk na madalas siyang saktan ng madrasta. Nahuli na ang suspek at inihahanda na ang kaso laban dito. Ayon kay SPO1 Cyrail Seseh ng WCPD, sinisipa ang bata sa balakang at lalamunan. Maraming netizens ang naglabas ng kanilang damdamin sa social media, karamihan ay nagpahayag ng galit at lungkot sa sinapit ng bata, at nagbahagi ng sariling karanasan sa pagpapalaki ng mga anak at stepchildren.</t>
         </is>
       </c>
-      <c r="C363" s="6" t="inlineStr">
+      <c r="C363" s="7" t="inlineStr">
+        <is>
+          <t>Kaawa-awa ang sinapit ng isang 5-taong gulang na lalaki sa kamay ng kanyang madrasta. Base sa ulat ng ABS-CBN news, bugbog ang inaabot ng bata kapag tumatanggi itong manlimos. Ang nakukuha sa panlilimos ng bata ay ginagamit daw ng madrasta pang-alak. Ayon sa nakatatandang kapatid ng biktima, pinalo umano ng madrasta ang kanyang kapatid ng pako. Inamin din ng batang biktima na tinadyakan siya ng madrasta sa leeg at tagiliran. Kaalaunan ay namatay ang biktima. Madalas daw saktang ng madrasta ang biktima, sabi ng women's desk. Nahuli na ang salarin at inihahanda na ang kaso ihahain laban sa kanya. "Sinisipa siya sa hips, sa troat," sabi ni SPO1 Cyrail Seseh ng WCPD. Bumuhos naman ang reaksyon mula sa mga kababayan natins a sinapit ng bata. "Juskooo! Grabi nkakaawa yung baby.. RIP baby boy. Ako i have step daughter twins but i treat them as my daughter and they treat me as mother also, namatay kc mama nila nung 11 days old. Palang sila. Now they are 10 years old already Grade 4, pru before Minsan mapagalitan at mapalo sa pwet pru part lang yun nag pag discipline ko Minsan kc matigas ulo,. Pru love ko sila.. Kaya ngayon nag abroad ako para makaipon pang aral nila for college," - B. Nes "Rest in peace baby.. Hindi kn msasaktan.. Naiyak ako knina kse halos d kn mkatayo.. Kaedad mo lng anak ko kya sobrang nadurog puso ko.. Pahinga kn, your in God hands now, no more pain only happiness!!... At sa gumawa sau nyan.. Buhay kp pero nkhanda n ang impyernong kalalagyan moh!," - B. Joshua "Anong klaseng hayop tong madrasta na to, hindi pala hayop isang demonyo! Sana hanggang sa huling hininga mo makaranas ka rin ng paghihirap gaya ng mga ginawa mo sa bata," - P .Ley "di tunay na ina kaya walang pakialam...ginagawa sa ganyan babae dpat pila balde sabay bugbugin din...o paiyot sa 10 kabayo...hanapin yan dapat...sino makakita dyan sa babaeng yan malaya kau bugbugin," - E. Bautista</t>
+        </is>
+      </c>
+      <c r="D363" s="6" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D363" s="6" t="inlineStr">
+      <c r="E363" s="6" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E363" s="6" t="inlineStr">
+      <c r="F363" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -9643,17 +10919,22 @@
           <t>Mahilig talaga ang mga Pilipino sa panonood ng soap opera o teleserye, at isa sa mga pinakatumatak sa kanila ay ang "Mara Clara" ng ABS-CBN. Lalo itong naalala ng mga batang 90's nang lumabas ang isang lumang larawan nina Mara at Clara kasama sina "Almira" at "Amante" sa Facebook page na Memories of Old Manila noong Pebrero 8, 2019. Ang kwento ng Mara Clara ay umiikot sa buhay nina Mara (Judy Ann Santos) at Clara (Gladys Reyes) na napagpalit sa ospital noong sila ay ipinanganak, isang lihim na naitala sa diary ni Kardo (Dan Fernandez). Si Mara, na tunay na anak ng mayamang mag-asawang Almira (Beverly Vergel) at Amante (Juan Rodrigo) Del Valle, ay lumaking mahirap sa poder nina Dado (Eruel Tongco/William Martinez) at Susan (Susan Africa), na siyang tunay na mga magulang ni Clara na namuhay naman nang marangya. Nagkrus ang kanilang mga landas nang magtrabaho si Mara bilang katulong sa bahay ng mga Del Valle, kung saan naranasan niya ang matinding paghihirap mula kay Clara. Sa huli, nabunyag ang lahat ng lihim sa pamamagitan ng diary. Malaking tagumpay ang Mara Clara at tumagal ito ng halos limang taon mula 1992 hanggang 1997, nagkaroon pa ng pelikula noong 1996 sa ilalim ng Star Cinema, at isang remake noong 2010 na pinagbidahan nina Kathryn Bernardo at Julia Montes na nagbigay sa kanila ng malaking break sa showbiz. Sa totoong buhay, magkaibigan pa rin sina Juday at Gladys at may kanya-kanya na silang pamilya, paminsan-minsan ay nagkakaroon sila ng reunion kasama ang kanilang mga anak. Para sa mga nais balikan ang kwento, mapapanood ang music video ng "Mara Clara the Movie" sa YouTube.</t>
         </is>
       </c>
-      <c r="C364" s="6" t="inlineStr">
+      <c r="C364" s="7" t="inlineStr">
+        <is>
+          <t>Sadyang mahilig manood ng soap opera, telenobela o teleserye ang mga Pilipino, at kung tatanungin ang mga manonood kung anu-anong mga dramang pantelebisyon ang tumatak sa kanila, isa sa mga mababanggit ang soap operang "Mara Clara" ng ABS-CBN. Tiyak na "relate-much" dito ang mga batang 90's lalo't muling napa-throwback ang mga ito dahil sa isang lumang larawan nina Mara at Clara kasama sina "Almira" at "Amante" sa Facebook page na Memories of Old Manila noong Pebrero 8, 2019. Ang Mara Clara ay umikot sa buhay nina Mara (Judy Ann Santos) at Clara (Gladys Reyes). Nang sila ay maipanganak, sila ay napagpalit sa ospital, at ang lahat ng ito ay nakatala sa isang diary na isinulat ni Kardo, na ginampanan ni Dan Fernandez. Si Mara, na tunay na anak ng mayamang mag-asawang sina Almira (Beverly Vergel) at Amante (Juan Rodrigo) Del Valle, ay lumaki sa hirap sa poder nina Dado (Eruel Tongco/William Martinez) at Susan (Susan Africa) na siyang tunay na mga magulang ni Clara, na lumaki namang mariwasa ang buhay sa mga Del Valle. Nagkrus ang kani-kanilang mga landas dahil namasukan bilang katulong si Mara sa tahanan ng mga Del Valle. Katakot-takot na pagpapahirap ang ipinatikim at ipinaranas ni Clara kay Mara. At dahil walang lihim na hindi nabubunyag, naisiwalat ang buong katotohanan sa kanilang pagkatao sa pamamagitan ng diary. Pumatok sa masa ang naturang soap opera. Sa katunayan, umere ito sa loob ng halos limang taon (1992 hanggang 1997). Ibinuod pa ito sa pamamagitan ng pelikula sa ilalim ng Star Cinema noong 1996. Noong 2010, nagkaroon ito ng remake na pinagbidahan nina Kathryn Bernardo bilang Mara at Julia Montes bilang Clara na nagdulot sa kanila ng napakalaking break sa showbiz. Sa tunay na buhay, matalik na magkaibigan sina Juday at Gladys. Pareho na rin silang may kani-kaniyang pamilya. Paminsan-minsan ay nagkikita at nagkakaroon ng reunion ang dalawang mahusay na artista upang makapagbonding kasama ang kanilang mga anak. Samantala, ating panoorin ang music video ng "Mara Clara the Movie" via YouTube channel:</t>
+        </is>
+      </c>
+      <c r="D364" s="6" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D364" s="6" t="inlineStr">
+      <c r="E364" s="6" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E364" s="6" t="inlineStr">
+      <c r="F364" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -9668,17 +10949,22 @@
           <t>Binanatan ni Mocha Uson si Jim Paredes matapos kumalat sa social media ang scandal video nito kung saan makikitang may ka-video call siya at gumagawa ng maselang aksyon sa harap ng camera. Ayon kay Uson, hindi isyu ang pribadong buhay ni Paredes kundi ang pagiging mapagmalinis nito, lalo na’t ilang beses nitong binatikos si Pangulong Rodrigo Duterte tungkol sa mga isyu ng kababaihan. Iginiit ni Uson na kilala niya ang tunay na pagkatao ni Paredes at hindi niya ito masyadong sinagot noon dahil sa respeto sa mga nakatatandang musikero, ngunit ngayon ay tinawag niya itong karma. Binanggit din ni Uson na marami pa siyang kilalang media personalities na nagkukunwaring disente pero may masamang ugali, at binalaan niya sila na huwag magmalinis dahil kilala niya ang galawan sa industriya. Sinabi rin ni Uson na dati siyang sex blogger at nagbibigay ng payo tungkol sa sexual health, kaya’t alam niya ang mga sikreto ng ilan sa mga nagpapanggap na disente. Dagdag pa niya, natatawa na lang siya sa mga media personality na bumabatikos kay Pangulong Duterte tungkol sa isyu ng pagiging manyak, dahil para sa kanya, “look who’s talking.”</t>
         </is>
       </c>
-      <c r="C365" s="6" t="inlineStr">
+      <c r="C365" s="7" t="inlineStr">
+        <is>
+          <t>Nakatikim ng mga patutsada mula kay Mocha Uson si Jim Paredes, ang viral sensation ngayon sa social media dahil sa scandal video. Mababatid na kumalat sa social media ang scandal ni Paredes na may ka-video call at padila-dila pa sa harapan ng camera habang nilalaro ang maselang parte ng katawan. Dahil dito ay hindi na nag-atubiling resbakan ni Uson si Paredes sa mga pagmamalinis nito. Isa sa mga binatikos ni Uson ay ang ilang beses na pagtira ni Paredes laban kay Pangulong Rodrigo Duterte. "Alam mo ang problema sayo hindi naman yang pag video na nagsosolo. Walang pakialam ang tao kung gawin mo yan. Buhay mo yan. Lahat naman tayo merong pribadong buhay. Ang problema kasi yung pagiging pagmamalinis mo. Ilang beses mo tinira ang Pangulo sa kanyang mga salita at gawa na may kaugnay sa babae yun pala ikaw ang ganun," resbak ni Mocha. Ayon pa kay Uson, kilala niya raw ang pagkatao ni Paredes at hindi aniya ito binanatan ng husto noon kahit panay ang batikos sa kanya. "Mr. J. Paredes alam mong alam ko ang tunay mong pagkatao. Hindi na nga kita pinuruhan dati kahit panay ang banat mo sa akin dahil matanda ka na at marunong akong rumespeto sa mga nakakatanda pagdating sa mga musikero dahil isa din akong artist. Kaya ayan KARMA na ang humabol sayo. Wag kang mag alala may bukas pa. May panahon pa magsisi. Wag po kasing magmalinis," buwelta ni Mocha. Binanggit din ni Uson ang tungkol sa iba pang media personalities na nagmamalinis at nagkukunwaring disente. Nagbigay naman si Uson ng pahiwatig kung sino ang mga ito. "Itong pangyayari na ito ay isang babala sa mga naglilinis linisan. Marami pa akong kilalang mga disente kuno na media personality pero matindi ang kamanyakan. Wag niyong kalimutan dati akong nasa industriya ninyo at kilala ko ang mga binobook ninyo. Kaya umayos kayo. PLS LANG. WAG AKO," pagsisiwalat ni Mocha. "Ikaw matandang ubo ng ubo. Araw araw mo akong binabanatan noon sa programa mo. Antay ka sa karma. Alam ko sikreto mo. At ikaw namang mahilig sa pipino panay banat mo din sa akin na wala akong karapatan manilbihan sa gobyerno dahil isa lang akong hamak na sexy dancer dati. Ingat baka ma ospital ka dyan, O na ospital na nga ba?," dagdag ni Mocha. Inamin naman ni Uson na naging sex blogger siya sa isang sexy magazine dati at nagbibigay payo sa mga problema ukol sa sexual health. "Nakalimutan ata nitong mga disente na ito na dati akong SEX BLOGGER sa isang sexy magazine. Humihingi pa nga kayo ng advise dahil may problema kayo kay junjun. Tamad na kasi. Iba pa sa inyo nag aaya pa ng threesome kasama jowa niyo. Kaya pls lang wag ako. Baka nakakalimutan niyo din ata kilala ko ang bugaw sa industriya dahil nagsusumbong sila sa akin pag may mga nag aapply sa Mocha Girls na nag wawalk para hindi ko na tanggapin. Winawarningan na nila ako kaagad dahil alam nila na ang grupo ko ay sexy lamang sa show pero off stage mga inosente talaga," ani Mocha. Aniya, natatawa na lang siya dahil sa mga media personality na nagpapanggap na disente pero ang totoo umano ay mga manyakol. "At nakwekwento din nila ang mga disente kunong media personality pero ang totoo manyakol. Kaya natatawa nalang ako pag napapakinggan ko mga banat nila kay PRD na keso manyak. Napapa- look who's talking- nalang ako. SO PLS LANG DONT ME," dagdag ni Mocha.</t>
+        </is>
+      </c>
+      <c r="D365" s="6" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D365" s="6" t="inlineStr">
+      <c r="E365" s="6" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E365" s="6" t="inlineStr">
+      <c r="F365" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -9693,17 +10979,22 @@
           <t>Usap-usapan ngayon sa social media ang umano’y panggagaya ng kinatawan ng Thailand na si Ingchanok Prasart sa trademark na “lava walk” ni Miss Universe 2018 Catriona Gray sa Miss Intercontinental 2018, matapos mapansin ng netizen na si Marnie Raro sa Twitter na parang kinopya ni Miss Thailand ang paraan ng paglalakad at pag-project ni Catriona; napansin din ng mga netizens ang pagkakahawig ng gown ni Miss Vietnam sa “Mayon Volcano gown” ni Catriona, at inamin ng dalawa na inspirasyon nila si Catriona Gray, dahilan para maghalo-halo ang reaksyon ng mga netizen—may nagsabi na malaki ang naging impluwensya ni Catriona, may nagsabing hindi pa rin mapapantayan ang orihinal na “lava walk,” at may nagtanggol din sa mga kandidata laban sa mga nagsasabing dapat magkaroon ng sariling originality; patunay ito na marami, hindi lang sa Pilipinas kundi sa buong mundo, ang humahanga kay Catriona Gray, bagay na inamin din ng maraming kandidata ng pageant na ito na ginanap noong Enero 26, 2019 sa SM Mall of Asia Arena sa Pasay, Metro Manila, kung saan kinoronahan ni Miss Intercontinental 2017 Veronica Salas Vallejo ng Mexico ang kandidata ng Pilipinas na si Karen Juanita Gallman, at ito rin ang unang beses na naging host ang Pilipinas sa nasabing pageant matapos piliin ng Japan organizers ang bansa bilang venue dahil abala ang Japan sa paghahanda para sa 2020 Summer Olympics.</t>
         </is>
       </c>
-      <c r="C366" s="6" t="inlineStr">
+      <c r="C366" s="7" t="inlineStr">
+        <is>
+          <t>Usap-usapan ngayon sa social media ang umano'y panggagaya ng kinatawan ng Thailand na si Ingchanok Prasart sa ginanap na Miss Intercontinental pageant 2018 sa trademark ni Miss Universe 2018 Catriona Gray na "lava walk." Isang netizen sa Twitter na nagngangalang Marnie Raro ang nakapansin sa paraan ng paglalakad at pag-project ni Miss Thailand na parang kinokopya ang "lava walk" ni Catriona. Bukod kay Miss Thailand, napansin din ng mga netizens ang pagkopya umano sa "Mayon Volcano gown" ni Miss Vietnam. Aminado naman ang dalawa na labis nilang hinahangaan at inspirasyon nila si Miss Universe 2018 Catriona Gray. Halo-halo naman ang naging reaksyon ng mga netizens hinggil dito. "So now everyone looks like Catriona Gray. From hair to stance to gowns. The influence. Only legends do that." "Catriona Gray's walk can never be perfect without her walking it." "I think so? Even the hand gesture of Miss Thailand seems copied too. Catriona Gray is indeed a queen." "Yet they can't copy the original. Because there will be only one Lava Walk and Catriona Gray." "Kayo na 'yung may mga originality... hala gawa kayo sarili niyong pageant, ano ba naman yung hayaan niyo na lang sila hays....daming toxic." Isang patunay lamang ito na maraming mga aspiring beauty pageant candidates, hindi lamang sa Pilipinas kundi maging sa buong mundo, ang tumitingala at humahanga kay Catriona. Aminado naman dito ang marami sa mga kandidata ng naturang katatapos na pageant. Ang 47th edition ng Miss Intercontinental 2018 ay ginanap noong Enero 26, 2019, sa SM Mall of Asia Arena sa Pasay, Metro Manila, Philippines. Kinoronahan ni Miss Intercontinental 2017 Veronica Salas Vallejo ng Mexico ang kandidata ng Pilipinas na si Karen Juanita Gallman. Ito ang kauna-unahang pagkakataong naging host ang Pilipinas sa pageant na ito. Pinili ng Japan organizers ang Pilipinas na maging venue ng pageant dahil abala ang bansang Japan sa mga paghahanda para sa 2020 Summer Olympics. Narito ang buong Twitter post ng netizen:</t>
+        </is>
+      </c>
+      <c r="D366" s="6" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D366" s="6" t="inlineStr">
+      <c r="E366" s="6" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E366" s="6" t="inlineStr">
+      <c r="F366" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -9718,17 +11009,22 @@
           <t>Hindi lang umento sa sahod ang ibinigay ng administrasyon ni Pangulong Rodrigo Duterte, kundi pati dekalidad na mga bahay ay ipinamahagi sa mga sundalo at pulis na lumaban sa Marawi City laban sa Maute Brothers. Sa kanyang talumpati sa San Jose, Bulacan, kinilala ng Pangulo ang sakripisyo ng mga tropa ng gobyerno, at ayon sa ulat ng People's Television Network (PTV), umabot sa 100 dekalibreng bahay na may mala-condominium na disenyo ang ipinamahagi, kung saan bawat awardee ay tumanggap ng dalawang unit na may sukat na tig-24 square meters. Mayroong livelihood center at covered court sa nasabing pabahay, na bahagi ng comprehensive social benefits program ng gobyerno. Sa 2019, nakatakda pang magtayo ng 13 housing projects para sa mga tropa ng gobyerno. Ayon kay Pangulong Duterte, ang mga pabahay na ito ay patunay ng determinasyon ng administrasyon na bigyan ng disenteng tahanan ang mga unipormadong personnel at kanilang pamilya. Nangako rin ang National Housing Authority (NHA) na magpapatuloy ang paggawa ng magagandang pabahay, bagamat aminado silang hindi sapat ang 100 units para sa lahat. Ikinatuwa naman ng ilang mamamayan ang pag-aalaga ng gobyerno sa mga sundalo at pulis, at may ilan ding nagbigay ng suhestiyon na sana ay mabigyan din ng pagkakataon ang mga mahihirap sa lansangan at mapataas ang sahod at oportunidad sa mga probinsya.</t>
         </is>
       </c>
-      <c r="C367" s="6" t="inlineStr">
+      <c r="C367" s="7" t="inlineStr">
+        <is>
+          <t>Hindi lang umento sa sahod ang ipinagkaloob ng pamahalaan ni Pangulong Rodrigo Duterte, pati mga dekalibreng bahay ay ipinamahagi sa mga magigiting nating sundalo't pulis na sumabak sa Marawi City para labanan ang mga Maute Brothers. Sa kanyang talumpati sa San Jose, Bulacan, kinilala ng Presidente ang hirap at sakripisyo ng pwersa ng gobyerno. Umabot sa 100 bahay ang ipinamigay sa mga tropa ng pamahalaan. Ayon sa ulat ng People's Television Network (PTV), dekalidad ang pagkakagawa sa mga bahay at may desenyong mala-condominium. Ang isang unit ay 24 square meters ang laki pero nilinaw ng mga arkitekto nito na dalawang units ang ibinahagi sa bawat isang awardee na sundalo't pulis. Mayroon din livelihood center ang lugar. Matatagpuan din ang isang covered court sa pabahay. Ang pabahay ay bahagi ng comprehensive social benefits program ng gobyerno. Sa taong 2019, 13 housing projects ang balak itayo ng pamahalaan para sa mga tropa ng gobyerno. "This housing units that we turn over today to the desreving recipients. It is testament to this administration's resolve to provide our uniformed personnel, and their families, not only just and decent shelter, but also a home where they can build their dreams for brighter future," sabi ni Presidente Duterte. Ipinangako naman ng National Housing Authority (NHA) na magiging tuloy-tuloy ang paggawa nila ng magandang pabahay. "The one hundred units may not be enough for everyone, but NHA will continue to construct decent housing for everyone. Something that is near, something that it beautiful and good, and something that is spacious," pahayag ni NHA General Manager Marcelino Escalda Jr. Ikinatuwa naman ng ilang kababayan natin ang pag-aalaga ng kasalukuyang gobyerno sa mga sundalo at pulis. " Kung ganito lang sana ibinabalita ang mga magagandang pangyayari Sa pilipinas Sa araw araw at hinde kasinungaligan maraming pilipino ang magigising Sa mahimbing na pag kakatulog napaka ayos ng gobyerno ngayon sa kasalukuyan." - M. Yosa "atay digong ung mga polobi po sa lansangan bigyan nyo din ng chance para wala ng polobi sa daan makikita, taas din ang mga sahod sa provnce damihan ng trabaho para hinde na mag siksikan sa manila ned tlga Federalismo." C. TIbong "They deserved that good job PRRD and PTV for showing this in public:)" - M. Waker "DESERVING NAMAN PO SILA..RISKY ANG TRABAHO NG MGA SUNDALOT PULIS..HINDI MO ALAM KUNG BUKAS E BUHAY PA SILA. DUTERTE GIVES IMPORTANCE SA MGA SUNDALOT PULIS PERO.MERON PADING HAYOP SALOT AT ANAY SA KANILA" - L. DM</t>
+        </is>
+      </c>
+      <c r="D367" s="6" t="inlineStr">
         <is>
           <t>economy / business</t>
         </is>
       </c>
-      <c r="D367" s="6" t="inlineStr">
+      <c r="E367" s="6" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E367" s="6" t="inlineStr">
+      <c r="F367" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -9743,17 +11039,22 @@
           <t>Agad na naayos ang Clark International Airport sa loob ng wala pang 48 oras matapos itong masira ng magnitude 6.1 na lindol, at muling magbubukas ito ngayong ika-4:00 ng hapon. Ayon sa Department of Transportation (DOTr) at Clark International Airport Corporation (CIAC), mabilis na kinumpuni ang mga nasirang bahagi ng Passenger Terminal Building at Control Tower, na kabilang sa mga istrukturang naapektuhan ng lindol. Pinuri ni DOTr Secretary Arthur P. Tugade ang mabilis na pagtugon sa kanyang utos na suriin ang structural integrity ng paliparan, kabilang na ang ginagawa pang Terminal 2, at pabilisin ang pagkukumpuni upang agad maibalik ang serbisyo sa mga pasahero. Ayon kay Secretary Tugade, mahalaga ang transportasyon sa panahon ng kalamidad kaya’t puspusan ang ginawang pagkukumpuni ng DOTr, CIAC, at BCDA para mapanumbalik ang normal na operasyon ng paliparan, kabilang na ang pagbibigay ng pagkain at libreng sakay sa mga apektadong pasahero. Ipinag-utos din ng kalihim sa CIAC ang agarang emergency procurement ng mga kagamitan at serbisyo para sa pagkukumpuni ng mga napinsalang pasilidad. Umabot sa P30 million ang tinatayang halaga ng pinsala sa paliparan at 110 flights ang naapektuhan dahil sa pansamantalang pagsuspinde ng operasyon. Nagsimula agad nitong umaga ng Abril 23 ang clearing at repair operations, lalo na sa pre-departure area kung saan bumagsak ang malaking bahagi ng kisame. Naibalik na rin ang kuryente, pati ang operasyon ng flight information systems at CCTV bago muling maglunsad ng mga flight ngayong araw. Wala namang naiulat na pinsala sa runway, taxiway, at sa ginagawang bagong Passenger Terminal Building ng paliparan.</t>
         </is>
       </c>
-      <c r="C368" s="6" t="inlineStr">
+      <c r="C368" s="7" t="inlineStr">
+        <is>
+          <t>Naisaayos agad ng wala pang 48 oras ang Clark International Airport matapos mapinsala ng magnitude 6.1 na lindol, at mamayang ika-4:00 ng hapon ay balik-operasyon na ito. Ayon sa Department of Transportation (DOTr) at Clark International Airport Corporation (CIAC), agad na naisagawa ang mga kinakailangang pagkukumpuni sa Passenger Terminal Building (PTB) at Control Tower na kabilang sa mga istrukturang napinsala sa pagyanig. Ikinatuwa ni DOTr Secretary Arthur P. Tugade ang mabilis na pagtugon sa direktiba niyang masusing suriin ang structural integrity ng paliparan, kasama na ang itinatayong Terminal 2, at madaliin ang pagkukumpuni sa mga napinsalang pasilidad upang agarang maibalik ang serbisyo sa mga pasahero. "Ang nangyari 'ho ay isang kalamidad na kailangang agad na tugunan. Sa mga ganitong panahon, napakahalaga ng transportasyon upang dalhin sa kaligtasan ang mga tao. Ang sabi ng Pangulong Duterte, siguraduhin na agad maisasaayos at matutulungan ang mga tao. Kaya kami 'ho sa DOTr, CIAC at BCDA ay puspusan ang ginawang pagkukumpuni ng mga istruktura upang maibalik sa normal ang operasyon dito sa Clark Airport. Lahat po ng maaaring ibigay, mula sa pagkain, libreng sakay, ibinibigay ho namin," ani Secretary Tugade. Matatandaang ipinag-utos ng kalihim sa mga opisyal ng CIAC ang pagpapatupad ng emergency procurement para sa pagbili ng mga kagamitan at pagkuha ng mga serbisyong kailangan sa pagkukumpuni sa mga napinsalang pasilidad sa paliparan. Umabot naman sa P30 million ang kabuuang halaga ng pinsala sa paliparan at tinatayang 110 flights ang naapektuhan kasunod ng pagsuspinde sa operasyon ng paliparan bunsod ng lindol. Agad na sinimulan nitong umaga ng Martes, ika-23 ng Abril, ang clearing operations at repair sa paliparan, partikular sa pre-departure area kung saan bumagsak ang malaking bahagi ng kisame nito. Naibalik na rin ang suplay ng kuryente sa paliparan, maging ang pag-operate ng flight information systems at CCTV bago ang muling paglulunsad ng mga flight ngayong araw. Samantala, walang naiulat na pinsala sa runway at taxiway ng paliparan, gayundin sa itinatayong bagong Passenger Terminal Building (PTB).</t>
+        </is>
+      </c>
+      <c r="D368" s="6" t="inlineStr">
         <is>
           <t>disaster / environment</t>
         </is>
       </c>
-      <c r="D368" s="6" t="inlineStr">
+      <c r="E368" s="6" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E368" s="6" t="inlineStr">
+      <c r="F368" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -9768,17 +11069,22 @@
           <t>Sa isang briefing sa Pampanga kaugnay ng resulta ng 6.1 magnitude na lindol na tumama sa ilang bahagi ng Luzon, hindi napigilan ni Pangulong Rodrigo Duterte na ilabas ang kanyang pagka-inis sa Canada dahil sa 103 containers ng basura na ipinadala mula Canada sa Pilipinas noong 2013-2014, na naglalaman ng iba't ibang uri ng dumi tulad ng adult diapers at plastic na bote na mali ang deklarasyon bilang plastic scraps. Ayon sa Pangulo, maghahanda siya ng barko at magbibigay ng babala sa Canada na dapat nilang kunin pabalik ang kanilang basura o ibabalik niya ito mismo sa kanila, at sinabi pa niyang kung gusto ng Canada ay kainin nila ang kanilang basura. Binanggit din ni Duterte na hindi niya matanggap na gawing tambakan ng basura ang Pilipinas at hindi siya papayag na basta-basta na lang silang gawing ganito, kaya't hinamon niya ang Canada na paghandaan ang pagbabalik ng kanilang basura.</t>
         </is>
       </c>
-      <c r="C369" s="6" t="inlineStr">
+      <c r="C369" s="7" t="inlineStr">
+        <is>
+          <t>"Eh di ano? Awayin natin ang Canada. We'll declare war against them, kaya man natin sila. Isauli ko talaga ah tingnan mo," Sa briefing sa Pampanga para talakayin ang resulta ng 6.1 magnitude na lindol na yumanig sa ilang bahagi ng Luzon, hindi napigilan ni Pangulong Rodrigo Duterte ipahayag ang kanyang pagka-inis sa Canada dahil sa basurang ipinadala sa Pilipinas. Magugunitang 103 na containers ang dumating sa Pilipinas mula Canada noong 2013-2014. Ang mga containers na ito ay may lamang sari-saring mga basura tulad ng adult diapers,mga plastic na bote at iba pa uri ng dumi. Ang mga basura ay misdeclared na mga plastic scraps nang dumating sa bansa. "Yung basura ng Canada, I want a boat prepared. I'll give a warning to Canada maybe next week that they better pull that thing out or I will set sail doon sa Canada, ibuhos ko 'yang basura nila doon," banat ng Presidente. Ayon sa Pangulo, kainin daw ng Canada ang mga basura kung gusto nila dahil ibabalik niya ang mga ito kung saan ito nagmula. "I cannot understand why they are making us a dumpsite... I will advise Canada that your garbage is on the way, prepare a grand reception, eat it if you want to. Kinakaya-kaya tayo di ako papayag ng ganun," resbak pa ng Presidente. Panoorin ang kaugnay na ulat ng CGTN noong 2014 tungkol sa basura mula Canada na ipinadala sa Pilipinas.</t>
+        </is>
+      </c>
+      <c r="D369" s="6" t="inlineStr">
         <is>
           <t>international news</t>
         </is>
       </c>
-      <c r="D369" s="6" t="inlineStr">
+      <c r="E369" s="6" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E369" s="6" t="inlineStr">
+      <c r="F369" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -9793,17 +11099,22 @@
           <t>Ipinahayag ng netizen na si Andrea Carigma ang kanyang pagkadismaya sa mga nagdaos ng kilos-protesta ngayong Labor Day matapos niyang ibahagi sa social media ang mga larawan ng center isle sa Mendiola na binaboy umano ng mga rallyista, kung saan makikita ang bandalismong iniwan matapos ang protesta; ayon kay Carigma, tapos na siya sa kanyang review lecture para sa nalalapit na board exams nang makita niya ang kalat na wala pa raw kaninang umaga, at tinawag niyang ka-ipokritohan ang ginawa ng mga rallyista dahil hindi raw karespe-respeto ang pagsira ng ari-arian habang ipinaglalaban ang karapatan ng tao, dahilan upang umani ng sari-saring reaksyon at mahigit isang libong shares ang kanyang post habang isinusulat ang artikulo.</t>
         </is>
       </c>
-      <c r="C370" s="6" t="inlineStr">
+      <c r="C370" s="7" t="inlineStr">
+        <is>
+          <t>Isang netizen ang naglabas ng pagkadismaya sa mga lumahok ng kilos-protesta ngayong labor day. Sa post ng netizen na si Andrea Carigma, ibinahagi niya ang larawan ng mga istruktura na binaboy umano ng mga nagkilos protesta kanina. Makikita sa mga larawan ang bandalismo na ginawa ng mga rallyista sa center isle sa Mendiola. "Just finished my lecture today (Yes, may review lecture ako today - dahil malapit na ang board exams.) and this is what you'll see after the Mendiola rally today. Wala yan kaninang umaga," banat ni Carigma. Para kay Carigma, isang ka-ipokritohan daw ang ginawa ng mga rallyista at hindi raw karespe-respeto ang inasta ng mga ito. "Sorry, but when you say that you fight for people's rights but destroy their property, I don't find you respectable," dagdag pa ni Carigma. Ang post ni Carigma ay umani na ng iba't-ibang reaksyon mula sa mga netizens at naibahagi na rin ng mahigit isang libong beses habang ginagawa ang artikulo na ito.</t>
+        </is>
+      </c>
+      <c r="D370" s="6" t="inlineStr">
         <is>
           <t>lifestyle / human interest</t>
         </is>
       </c>
-      <c r="D370" s="6" t="inlineStr">
+      <c r="E370" s="6" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E370" s="6" t="inlineStr">
+      <c r="F370" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -9818,17 +11129,22 @@
           <t>Sa isang conference tungkol sa sexual abuse ng Simbahang Katolika, emosyonal na inamin ni Manila Archbishop Luis Antonio Cardinal Tagle ang mga kasalanang nagawa ng ilang pari laban sa mga kabataan, at binigyang-diin niyang ang mga sugat na ito ay dulot ng mga obispo at ng simbahan mismo sa mga biktima at sa buong katawan ni Kristo. Binanggit din niya ang pagtatakip ng ilang opisyal ng simbahan sa mga kaso ng pang-aabusong seksuwal at ang kawalang-pansin sa mga biktima. Dagdag pa ni Tagle, ang sugat ni Kristo ay sumisimbolo sa alaala ng inosenteng pagdurusa at sa kahinaan at kasalanan ng tao. Sumang-ayon si Father Jerome Secillano sa mga pahayag ni Tagle at sinabi niyang kailangan ng reporma sa simbahan at dapat itong linisin bago magpatuloy. Samantala, ilang mamamayan ang nagbigay ng reaksyon sa mga sinabi ni Tagle, kabilang ang mga komentong pumupuna sa simbahan at hinihikayat itong unahin ang paglilinis sa sariling hanay bago punahin ang gobyerno, at may ilan ding nagsabing matagal nang itinatago ng simbahan ang mga problemang ito.</t>
         </is>
       </c>
-      <c r="C371" s="6" t="inlineStr">
+      <c r="C371" s="7" t="inlineStr">
+        <is>
+          <t>Sa sexual abuse conference ng Simbahang Katolika, mangiyak-ngiyak na umamin si Manila Archbishop Luis Antonio Cardinal Tagle sa kabalbalang ginagawa ng ilang pari sa mga kabataan. "We humbly and sorrowfully admit that wounds have been inflicted byh us, bishops, on the victims and in fact the entire body of Christ," sabi ni Tagle. Kasama din sa pahayag ni Tagle ang isyu ang pagtatakip ng ilang opisyal ng simbahan katolika sa mga kaso ng pang-aabuso seksuwal at ang pagbabalewala sa mga nabiktima ng mga kapwa niya pari. "The wound of Christ carried the memory of innocent suffering. They also carried the memory weakness and sinfulness," dagdag pa ni Tagle. Sumang-ayon naman si Father Jerome Secillano sa mga naging pahayag ni Cardinal Tagle. "Ang simbahan ay kailangan din ng reporma. Ang simbahan ay kailangang mag move forward. At bago niya magawa ang moving forward, kailangan muna linisin ang simbahan," sabi ni Secillano. Ito po ang naging tugon at reaksyon ng ilang kababayan natin sa mga sinabi ni Cardinal Tagle. "O ano na? Kung makabanat kayo ky PRESIDENTE parang ang lilinis nyo... Membro Rin pala kayo ng mga rapist.... CHR saan na kayo?" sabi ni Y. Duhaylungsod. "Wag kasi makialam sa gobyernong pinapatakbo ng presidente. Pakialaman nyo ang problema ng simbahang katolika. I am a pure catholic kaya dapat malinis na. Hindi ung kada homily eh c duterte tinitira nyo ayan tuloy sinampal kayo ng katotohanang matagal nyo ng dinedeny," sabi niC. Anyang. "Ano na ngayon di ba totoo ang sinasabi ng Pangulo panay banat u sa Pangulo pero pari pala ang mas demonyo ... rapist durugista babaero pa," sabi ni R. Pascua. "pa iyak iyak pah!! drama pa more.... ibig nyo sabihin ngayon nyo lang yan nalalaman? eh di sinungaling pala kayo!!!" sabi ni O. Etneilav. "MAKAPUNA AT HUSGA KAY PRESIDENT AKALA MU PERFECTO, Whoah mas malagim at karumaldumal pala kau!! Linisin nyu bakuran nyu muna bgo magmagaling mga damaso!!!" sabi ni E. Senesio.</t>
+        </is>
+      </c>
+      <c r="D371" s="6" t="inlineStr">
         <is>
           <t>religion</t>
         </is>
       </c>
-      <c r="D371" s="6" t="inlineStr">
+      <c r="E371" s="6" t="inlineStr">
         <is>
           <t>AI-R</t>
         </is>
       </c>
-      <c r="E371" s="6" t="inlineStr">
+      <c r="F371" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -9843,17 +11159,20 @@
           <t>IPINALIWANAG ng Palasyo na nagdesisyon si Pangulong Duterte na i-veto ang panukalang batas sa coconut levy dahil matutulad lamang daw ito sa kontrobersiyal na Road Board kung saan napunta sa katiwalian ang pondo. Ani Presidential Spokesperson at Chief Presidential Legal Counsel Salvador Panelo na sa ilalim ng panukalang Revised Coconut Industry Code ay maglalaan ng P10 bilyon ang gobyerno na hahawakan ng PCA Board. "The PCA is set up like the Road Board which is heavily criticized for allegations of corruption and misappropriation of funds. The PCA Board, like the Road Board which disburses the Motor Vehicle User's Charge, is given full authority to disburse P10-billion every year in perpetuity without a terminal date, and subject only to review ," sabi ni Pa-nelo. Nauna nang nagpadala ng liham si Duterte sa Senado at Kamara kaugnay sa kanyang desisyong huwag lagdaan ang isinumiteng panukala sa Palasyo. "While the President recognizes and commends the efforts of both Houses for their zealousness and selflessness in passing the measure, it is therefore with a heavy heart that he exercises his veto power pursuant to Article 6, Section 27, Paragraph 1 of the Constitution over the said bill, with the thought and confidence that the lawmakers can re-craft one that will provide more safeguards to protect the taxpayers' money and shield the levy funds from irregular and unlawful use, as well as guarantee its proper management," ayon pa sa opisyal.</t>
         </is>
       </c>
-      <c r="C372" s="6" t="inlineStr">
+      <c r="C372" s="7" t="n">
+        <v/>
+      </c>
+      <c r="D372" s="6" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D372" s="6" t="inlineStr">
+      <c r="E372" s="6" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E372" s="6" t="inlineStr">
+      <c r="F372" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -9868,17 +11187,20 @@
           <t>"Accused Juan Ponce Enrile, by counsel, respectfully expresses his reservations over and objections to the Honorable Court's proposals made in open court on January 14, 2015 regarding (1) the termination of the preliminary conference in all the cases, and (2) the consolidation of all cases," pahayag ng mga abogado ni Enrile. Puntirya ng Sandiganbayan Third Division na mapabilis ang proseso ng paglilitis at hihilingin nito sa Korte Suprema na tapusin na ang preliminary conference na rito mamarkahan ang mga ebidensiya at magsasagawa ng joint trial sa mga kasong plunder at graft ni Enrile. Naglilitis ang Third Division sa isang kaso ng plunder at 15 bilang ng graft na inihain laban kay Enrile. "All told, while justice is intended to be administered with dispatch, this does not mean mere speed for speed's sake. The anxiety in concluding and disposing a case must not result in a deprivation of due process. The constitutional right of the accused to speedy trial is in place for his protection, it is not intended to be wielded as a weapon against him," pahayag ng depensa.</t>
         </is>
       </c>
-      <c r="C373" s="6" t="inlineStr">
+      <c r="C373" s="7" t="n">
+        <v/>
+      </c>
+      <c r="D373" s="6" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D373" s="6" t="inlineStr">
+      <c r="E373" s="6" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E373" s="6" t="inlineStr">
+      <c r="F373" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -9893,17 +11215,20 @@
           <t>Ayon kay Senate Finance Chairman Sen. Francis Escudero, ang P24 bilyon pondo ng ARMM ay sapat para sa rehabilitasyon at konstruksyon ng mga kalsada at patubig na aabot sa P10,642 bilyon ang ibinigay sa regional government ng Department of Public Works and Highways (DPWH).</t>
         </is>
       </c>
-      <c r="C374" s="6" t="inlineStr">
+      <c r="C374" s="7" t="n">
+        <v/>
+      </c>
+      <c r="D374" s="6" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D374" s="6" t="inlineStr">
+      <c r="E374" s="6" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E374" s="6" t="inlineStr">
+      <c r="F374" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -9918,17 +11243,20 @@
           <t>Kasi, nadismaya siya sa mga sagot ng dalawa na animo'y pumapanig sila sa MILF. Hindi natin maiaalis na ganito kumilos ang dalawa. Sa totoo lang hindi nila pinapanigan ang MILF kundi ipinagtatanggol nila ang Bansamoro Basic Law (BBL) na kanilang pinaghirapan. Ipinagtatanggol nila ang usaping pang kapayapaan na pinasok ng ating gobyerno sa MILF sa pamamagitan nila.</t>
         </is>
       </c>
-      <c r="C375" s="6" t="inlineStr">
+      <c r="C375" s="7" t="n">
+        <v/>
+      </c>
+      <c r="D375" s="6" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D375" s="6" t="inlineStr">
+      <c r="E375" s="6" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E375" s="6" t="inlineStr">
+      <c r="F375" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -9943,17 +11271,20 @@
           <t>Isa sanang maagang pamasko sa aktor-pulitiko ang naunang desisyon ng korte na siya'y makalabas nitong nakaraang linggo, pero dalawang araw bago siya palayain ay may nakialam at nabago ang lahat.</t>
         </is>
       </c>
-      <c r="C376" s="6" t="inlineStr">
+      <c r="C376" s="7" t="n">
+        <v/>
+      </c>
+      <c r="D376" s="6" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D376" s="6" t="inlineStr">
+      <c r="E376" s="6" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E376" s="6" t="inlineStr">
+      <c r="F376" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -9968,17 +11299,20 @@
           <t>Ayon kay Roxas, nagsimulang makipag-ugnayan ang National Capital Region Police Office (NCRPO) sa Manila Police District (MPD) mula noong Disyembre para epektibong mamantine ang kapayaan at kaayusan sa taunang selebrasyon.</t>
         </is>
       </c>
-      <c r="C377" s="6" t="inlineStr">
+      <c r="C377" s="7" t="n">
+        <v/>
+      </c>
+      <c r="D377" s="6" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D377" s="6" t="inlineStr">
+      <c r="E377" s="6" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E377" s="6" t="inlineStr">
+      <c r="F377" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -9993,17 +11327,20 @@
           <t>NAKATSIKAHAN namin sa pocket presscon nina Alex Gonzaga atAlonzo Muhlach ang bagong business unit head ng Dreamscape Entertainment na si Mr. Rondel Lindayag na hangang-hanga sa anak ni Nino Muhlach dahil napaka-professional kahit musmos pa.</t>
         </is>
       </c>
-      <c r="C378" s="6" t="inlineStr">
+      <c r="C378" s="7" t="n">
+        <v/>
+      </c>
+      <c r="D378" s="6" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D378" s="6" t="inlineStr">
+      <c r="E378" s="6" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E378" s="6" t="inlineStr">
+      <c r="F378" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -10018,17 +11355,20 @@
           <t>Aniya, kulang na nga ang tauhan ng BOC ay mas mahirap pa para sa kanila ang tugisin ang mga smuggler na dumadaan sa karagatan. "Undermanned kami," ani Nepomuceno. "Ang sagot dyan ay ang agad na makapag-recruit at mag-deploy." Napaulat kamakailan ang talamak na smuggling sa Zamboanga at Mindanao Container Terminal, isang sub-port ng Cagayan de Oro. Iniulat na ginagamit ang Zamboanga sa pagpupuslit ng 5,000 sako ng bigas mula sa Sandakan sa Malaysia. Galing naman sa Vietnamn ang iba pang ilegal na kontrabando ng bigas.</t>
         </is>
       </c>
-      <c r="C379" s="6" t="inlineStr">
+      <c r="C379" s="7" t="n">
+        <v/>
+      </c>
+      <c r="D379" s="6" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D379" s="6" t="inlineStr">
+      <c r="E379" s="6" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E379" s="6" t="inlineStr">
+      <c r="F379" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -10043,17 +11383,20 @@
           <t>Si Matteo Guidicelli ang leading man ni Alex sa MMK at naging maganda ang working relationship nila. "Kami naman ni Matteo, eh, matagal na rin naman kaming magkaibigan. Masayang kasama siya. Dahil matagal na nga kaming magkaibigan, eh, parang ano lang, 'yun bang magkaibigan na nagtratrabaho ang naramdaman namin at wala kaming ilangan," sey pa rin ni Alex. Wala silang naging problema sa anumang ipinapagawa sa kanila ng direktor nila. "It's easy, kasi hindi ako ilang sa kanya dahil friends nga kami. Ayaw ko lang nga 'yung kissing scene. Hindi ako ilang kasi kilala ko na siya at alam naman namin na ang personal na buhay namin sa isa't isa, so walang ilangan talaga," banggit pa rin ng isa sa mga dalaga ni Mommy Pinty. Ayaw magkomento ni Alex tungkol sa proposal o engagement rumors ng ate niyang si Toni Gonzaga kay Direk Paul Soriano. "Let's just wait na lang for the right time," sey niya agad. Samantala, ipinagmamalaki ni Alex na abalang-abala rin siya ngayon bilang writer. Ang libro niyang Dear Alex, Break na Kami, Paano? ay isa sa mga best-seller ngayon sa bookstores.</t>
         </is>
       </c>
-      <c r="C380" s="6" t="inlineStr">
+      <c r="C380" s="7" t="n">
+        <v/>
+      </c>
+      <c r="D380" s="6" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D380" s="6" t="inlineStr">
+      <c r="E380" s="6" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E380" s="6" t="inlineStr">
+      <c r="F380" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -10068,17 +11411,20 @@
           <t>In good taste ang mga kuha ni Coleen na ipinost nila sa social media at puwede itong gamitin din para sa promo ng Ex With Benefits na si Sam Milby ang leading man ng TV host/actress. Ang sexy ni Coleen at ang gaganda ng swimsuit na suot niya kaya tiyak na maraming female personalities ang nagka-idea na gayahin din nila ang pictorial session na ito ng dalaga sa isang napakagandang lugar sa ibang bansa. Tiyak na nakita na ni Sam ang mga litrato ni Coleen at siguradong humanga rin siya sa kaseksihan ng girlfriend ni Billy. Mabuti na lang at hindi bantay-salakay si Sam kaya maski na magkasama sila sa pelikula ni Coleen ay walang kakaba-kaba si Billly at matinong girlfriend din naman ang dalaga. In fact, marami ang nakakapansing malaki ang ipinagbago ni Billy simula nang maging magkarelasyon sila dahil pumayat siya nang husto at higit sa lahat, hindi na rin daw madalas uminom at gumimik tulad nang dati. May nagkuwento rin sa amin na, "Takot si Billy na iwan siya ni Coleen, sobrang in love ni Billy kay Coleen. Hindi nga rin namin alam kung paano napatino ni Coleen si Billy."</t>
         </is>
       </c>
-      <c r="C381" s="6" t="inlineStr">
+      <c r="C381" s="7" t="n">
+        <v/>
+      </c>
+      <c r="D381" s="6" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D381" s="6" t="inlineStr">
+      <c r="E381" s="6" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E381" s="6" t="inlineStr">
+      <c r="F381" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -10093,17 +11439,20 @@
           <t>Kasalukuyang nag-aaral si Korina ng Master of Arts in Journalism sa Ateneo de Manila University at nag-apply din siya ng simultaneous course sa London School of Economics kaya kailangan niyang bumiyahe sa Europe. Paliwanag ni Koring, "I've talked about this with network management since middle of last year. The bosses were all for it. My advanced studies have taken the backseat for too long and if I don't do this now, I may never. Kaya nga pinagsasabay sabay ko na. It's not easy but I'm optimistic I can do this." Kinumpirma ng business manager ni Korina na si Girlie Rodis na nag-file sila ng leave of absence para sa katapusan ng taong ito pero baka mapaaga pa ito, depende sa travel plans ni Koring para sa pagbabakasyon sa Pasko. "I encouraged Korina to do this because education is important at any stage of one's life. And she's been planning this for so long. I'm happy she finally decided to take this seriously," say ni Ms. Girlie. Maging ang ABS-CBN news head na si Ging Reyes ay inaming natanggap niya ang leave of absence request ni Korina. "Yes it is a leave of absence of three months which management has granted to Korina. The company values higher education, as it is always a plus among our ranks. Many in our stable have also taken leaves of absence to pursue further studies. When they come back, there is always better output. We wish Korina the best of the experience," say naman ni Ms Jing. Habang on leave si Sanchez sa kanyang daily live newscast, ipagpapatuloy pa rin niya ang weekly magazine program na Rated K at ang kanyang occasional, award-winning interview show na Up Close and Personal sa ANC.</t>
         </is>
       </c>
-      <c r="C382" s="6" t="inlineStr">
+      <c r="C382" s="7" t="n">
+        <v/>
+      </c>
+      <c r="D382" s="6" t="inlineStr">
         <is>
           <t>economy / business</t>
         </is>
       </c>
-      <c r="D382" s="6" t="inlineStr">
+      <c r="E382" s="6" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E382" s="6" t="inlineStr">
+      <c r="F382" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -10118,17 +11467,20 @@
           <t>NIYANIG ng magnitude 5.0 lindol ang Davao Occidental kaninang umaga. Ayon sa Philippine Institute of Volcanology and Seismology naramdaman ang lindol alas-7:17 ng umaga. Ang epicenter nito ay 447 kilometro sa silangan ng Sarangani. May lalim itong 61 kilometro at sanhi ng paggalaw ng tectonic plate sa lugar. Ayon sa Phivolcs posibleng magkaroon ng aftershock ang pagyanig na ito bagamat walang inaasahang pinsala.</t>
         </is>
       </c>
-      <c r="C383" s="6" t="inlineStr">
+      <c r="C383" s="7" t="n">
+        <v/>
+      </c>
+      <c r="D383" s="6" t="inlineStr">
         <is>
           <t>disaster / environment</t>
         </is>
       </c>
-      <c r="D383" s="6" t="inlineStr">
+      <c r="E383" s="6" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E383" s="6" t="inlineStr">
+      <c r="F383" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -10143,17 +11495,20 @@
           <t>Ayon kay Police Senior Inspector Fidl Gentalian, bagong hepe ng Boracay PNP, nakikipag-ugnayan na sila sa Korean community para mapabilis ang imbestigasyon sa nasabing insidente.</t>
         </is>
       </c>
-      <c r="C384" s="6" t="inlineStr">
+      <c r="C384" s="7" t="n">
+        <v/>
+      </c>
+      <c r="D384" s="6" t="inlineStr">
         <is>
           <t>international news</t>
         </is>
       </c>
-      <c r="D384" s="6" t="inlineStr">
+      <c r="E384" s="6" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E384" s="6" t="inlineStr">
+      <c r="F384" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -10168,17 +11523,20 @@
           <t>Ayon sa ulat, umabot na sa 13 munisipalidad ang naapektuhan simula nang ilunsad ang opensiba laban sa BIFF na nagresulta sa paglikas sa mga government evacuation center ng 19,075 pamilya o 93,402 indibidwal. Naapektuhan din ng kaguluhan ang klase sa 42 paaralan, na roon nagaaral ang 16,000 elementary at high school student. Tinaguriang "Tabang Sibilyan, Isulong ang Kapayapaan," sinabi ni ARMM Governor Mujiv Hataman na target ng relief and peace advocacy campaign ang makapagbigay ng pagkain at tulong medikal sa mga naapektuhang residente. Kada linggo, gumagastos ang pamahalaan ng ARMM ng P12 milyon para sa food pack ng mga evacuee, bukod pa ang gastusin sa iba pang uri ng ayuda at kagamitan para sa relief operations. Sinabi ni Hataman na posibleng magtagal ang kampanya laban sa mga bandidong BIFF sa Maguindanao hanggang Hunyo o higit pa.</t>
         </is>
       </c>
-      <c r="C385" s="6" t="inlineStr">
+      <c r="C385" s="7" t="n">
+        <v/>
+      </c>
+      <c r="D385" s="6" t="inlineStr">
         <is>
           <t>lifestyle / human interest</t>
         </is>
       </c>
-      <c r="D385" s="6" t="inlineStr">
+      <c r="E385" s="6" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E385" s="6" t="inlineStr">
+      <c r="F385" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -10193,17 +11551,20 @@
           <t>Kamakailan din nakipag-agapayan ang SP Philippines sa SM Prime Holdings Inc. para sa instalasyon ng solar panels sa SM City North EDSA. Makikipag-ugnayan din ang SP sa iba pang entity para sa proyekto sa layuning ipalaganap ito sa buong bansa. Napapanahon ang pagkilos na itong SP sapagkat naririto na ang summer at mas malamang na matindi pa ang sikat ng araw sa mga darating na araw. Mainam itong paghahanda para sa napipintong mga brownout tulad na inanunsiyo na ng mga kinauukulan. Ang solar energy ang pinakamainam na pagkukuhanan ng enerhiya sapagkat ito ay banayad sa kalikasan. Isa itong lunas sa problema ng climate change. Malinis na enerhiya mula sa sikat ng araw. Malinis din na hangarin.</t>
         </is>
       </c>
-      <c r="C386" s="6" t="inlineStr">
+      <c r="C386" s="7" t="n">
+        <v/>
+      </c>
+      <c r="D386" s="6" t="inlineStr">
         <is>
           <t>religion</t>
         </is>
       </c>
-      <c r="D386" s="6" t="inlineStr">
+      <c r="E386" s="6" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="E386" s="6" t="inlineStr">
+      <c r="F386" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -10218,17 +11579,20 @@
           <t>Kinumpirma ni Justice Sec. Menardo Guevarra na hinuli at nakakulong na ngayon sa tanggapan ng National Bureau of Investigation (NBI) si Rodel Jayme na siyang nag-upload ng "Bikoy: Ang Totoong Narcolist" propaganda video. Ang nasabing propaganda video ay nagdadawit sa ilang miyembro ng pamilya Duterte sa iligal na droga kasama ang menor-de-edad na anak ng Pangulo na si Kitty. Sa isang press conference, sinabi ni Guevarra na si Jayme rin ang registered administrator ng website ng [LINK] na nagpapakilala bilang isang online news portal. Ang nasabing domain rin ang naka-rehistro na nag-upload ng Bikoy video sa YouTube. Natukoy si Jayme sa pamamagitan ng Google Adsence ID na isang unique protocol para sa mga online user na gumagamit ng serbisyo ng nasabing internet site. Mababatid na ibinunyag din ng isang pro-Duterte blogger na si Sass Rogando Sasot ang pagkatao ni Jayme noong Abril 25. "Metrobalita.net's AdSense ID is 9287075011637877. Some of my readers were able to trace all the websites bearing that ID, which eventually led us to the identity of the person behind metrobalita.net. Out of fear for their lives, they asked me not to disclose the identities revealed," saad ni Sasot. "Google AdSense ID 9287075011637877 can also be seen in another online version of Metro Balita, when it was still a dot com instead of a dot net website. The domain registrant of the old dot com version is Rodel Jayme. This information is publicly accessible via WHOXY, an online tool that reveals the domain registration records of websites," dagdag niya. Si Jayme ay sinasabing operator rin ng ilang grupo na konektado sa ilang personalidad sa hanay ng oposisyon. Kabilang sa kanyang mga naging trabaho ay administrator ng ilang anti-government online account na sinasabing pinonondohan ng ilang kritiko ng gobyerno. Ipinaliwanag ni Guevarra na inaresto si Jayme noong madaling-araw ng Abril 30 ng mga tauhan ng NBI sa hindi sinabing lugar. Siya ay inaresto sa bisa ng arrest warrant na inisyu ni Makati City Regional Trial Court Branch 148 Judge Andres Soriano. Samantala, sinabi naman ng NBI na hawak na nila ang computer at cellphone ni Jayme at kasalukuyang isinasailalim sa cyber forensic examinination para makuha ang detalye sa ilang mga personalidad na posibleng kasangkot niya sa kanyang ginawang pag-upload ng Bikoy video. Bukod sa paglabag sa Anti-Cybercrime Law ay posibleng maharap pa sa mas maraming kaso si Jayme lalo't may menor-de-edad na isinangkot sa nasabing video.</t>
         </is>
       </c>
-      <c r="C387" s="6" t="inlineStr">
+      <c r="C387" s="7" t="n">
+        <v/>
+      </c>
+      <c r="D387" s="6" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D387" s="6" t="inlineStr">
+      <c r="E387" s="6" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E387" s="6" t="inlineStr">
+      <c r="F387" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -10243,17 +11607,20 @@
           <t>Naglabas ng sama ng loob sa kanyang social media account si Attorney Larry Gadon dahil sa naging resulta ng halalan. Ayon sa sikat na abogado, biktima daw siya ng pandaraya at naniniwala siya na ang mga boto niya ay binawasan para ilipat sa mga mahihinang kandidato ng administrasyon. "Ang nakaraan ne eleksiyon ay naparumi at madaya. Ako ay naniniwala na nabiktima ako ng dagdag bawas. Na-shave ang aking mga boto para idagdag sa mga admin candidates... Ang boto ko ay idinagdag sa mga admin (candidates) na mahina," banat ni Gadon. Isa sa mga ginamit na pruweba ni Gadon ay ang mainit na pagtangkilik sa kanya ng mga tao. Mula sa online polls hanggang sa mga pag-iikot niya sa iba't-ibang lugar. "Mula pa noon, sa social media, at sa mga mock elections sa mga malalaking universidad, palagi akong nagta-top 1 or top 5. At sa mga social media surveys sa mga OFW palagi ako na nasa top 5, pinaka-malas ko na ang 7... Sa pag-ikot ko sa mga syudad at mga probinsiya ay pinagkakaguluhan ako. Even in those far places na hindi ako nagkaroon ng kahit isang posters," sabi ni Gadon. Pinagtataka rin ni Gadon na noong 2016 ay hindi siya nangampanya pero umabot ng 2 milyon ang boto. Samantalang ngayon na todo ang exposure niya sa mainstream media ay 1 milyon lang ang naidagdag sa kanyang boto. "Noong tumakbo ako ng 2016 ay nakakuha ako ng 2 milyon na boto, kahit hindi ako nangampanya at kahit hindi pa ako sikat noon. Itong 2019 elections, grabe ang naging exposure ko sa TV, sa news, sa mga interviews, sa radyo, dahil sa Sereno impeachment, at dahil sa effective social media campaign, kaya imposible na 1 million lang ang nadagdag sa akin," pahayag ni Gadon. Naniniwala ba kayo sa mga paratang ni Attorney Gadon. Sino kayang administration candidate ang tinutukoy niya?</t>
         </is>
       </c>
-      <c r="C388" s="6" t="inlineStr">
+      <c r="C388" s="7" t="n">
+        <v/>
+      </c>
+      <c r="D388" s="6" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D388" s="6" t="inlineStr">
+      <c r="E388" s="6" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E388" s="6" t="inlineStr">
+      <c r="F388" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -10268,17 +11635,20 @@
           <t>Masama umano ang loob ng lalaking gumawa ng website kung saan niya ina-upload ang video ni alyas Bikoy, na nagdadawit sa ilang pamilya Duterte sa droga. Matapos madakip, sinabi ng lalaki na handa siyang makipagtulungan sa isinasagawang imbestigasyon ng mga awtoridad kung sino ang nasa likod nito. Kinilala ang nadakip na si Rodel Jayme, ang sinasabing nasa likod ng website na metrobalita.com. Naaresto si Jayme sa isang bahay sa Paranaque ng mga tauhan ng National Bureau of Investigation (NBI), matapos umano ang mahigit isang buwang pag-iimbestiga at online surveillance. Pero iginiit ni Jayme na hindi siya si Bikoy at hindi rin siya ang nag-upload ng video sa website dahil ipinagawa lang daw ang website na gagamitin umano sa kampanya. "Nag-chat lang sa akin kung puwedeng makipagkita then nung nagkita kami sa Las Pinas, doon sinabi na kailangang gumawa ng website na gagamitin for posting article for campaign," kuwento ni Jayme. Nakilala raw niya ang kaniyang kontak noong 2015 para sa kampanya noong 2016. Naganap daw ang kanilang pagkikita nitong nakaraang Marso 31. Ayon pa kay Jayme, ang sinabi sa kaniya na gagamitin lang website para sa kandidato ng Otso Diretso. "Binigyan ko po ng access doon sa nagpagawa then April 2, no idea po ako, wala ako sa bahay nasa church po ako, biglang na-upload 'yung video. Ang plano na sinasabi sa amin ay magtago daw po ng within one month dahil ang lumalabas ngayon lang mainit yan hanggang eleksyon. Dahil parang lalabas daw po yata si Bikoy bago mag-eleksyon," saad ni Jayme. "Nilaglag ako sa bagay na wala akong alam, na parang tinraydor ako. Kasi kung tutuusin in-upload nila 'yung video na hindi man lang sinabi sa akin. Alam nilang nandyan ang pangalan ko dahil siyempre ang alam ko lang ay malinis ang intensyon ng pagpapagawa," hinanakit niya. Handa raw si Jayme na makipagtulungan sa NBI para ituro ang nasa likod ng website na ginamit ni Bikoy at naka-record daw sa kaniyang Facebook ang pag-uusap nila ng nagpagawa sa kaniya ng website. "Isa sa bilin ay mag-delete ng conversation, pero hindi ko po gawain na mag-delete ng conversation. Alam kong puwedeng ebidensiya 'yon kung may mangyari," saad niya. Susuriin naman ng NBI ang computer at laptop na ginamit ni Jayme para sa iba pang ebidensya. Nahaharap ngayon sa reklamon cyberlibel si Jayme dahil sa mapanira ang mga video ni Bikoy na nag-ugnay sa mga kaibigan at kaanak ng Pangulo sa droga, na nauna na nilang itinanggi.</t>
         </is>
       </c>
-      <c r="C389" s="6" t="inlineStr">
+      <c r="C389" s="7" t="n">
+        <v/>
+      </c>
+      <c r="D389" s="6" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D389" s="6" t="inlineStr">
+      <c r="E389" s="6" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E389" s="6" t="inlineStr">
+      <c r="F389" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -10293,17 +11663,20 @@
           <t>Lumantad ngayong araw sa media si Peter Joemel Advincula para aminin sa madla na siya umano si alyas 'Bikoy', ang misteryosong lalaking nagsasalita sa video series na "Ang Totoong Narco List". Ang naturang video series ay naninira sa mga kapamilya ni Pangulong Rodrigo Duterte at isanasangkot ang mga ito sa kalakaran ng droga. Ayon kay Advincula, humarap daw siya sa publiko dahil may banta sa kanyang buhay at sa tawag ng konsensiya. Pinanindiganan din ni Advincula ang mga paninira sa nasabing video series. Sa paglantad ni Advincula, naungkat ng ilang netizens ang artikulo na nagsasabing estapador si Advincula at naging most wanted din sa Naga City. "Advincula admitted that aside from his theft case in Sorsogon, he is also facing charges of illegal recruitment and large scale estafa in Naga City and Albay," sabi sa ulat ng ABS-CBN tungkol kay Advincula. May mga kababayan din tayo sa social media na nagsasabi na nabiktima sila ni Advincula. Diskumpiyado naman ang mga pro-government supporters at mga bloggers sa katauhan ni Advincula. Naungkat ng ilang supporters ang artikulo na nagsasabing estapador si Advincula at naging most wanted din sa Naga City. Panoorin ang naging komento ni Thinking Pinoy sa paglantad ni Advincula.</t>
         </is>
       </c>
-      <c r="C390" s="6" t="inlineStr">
+      <c r="C390" s="7" t="n">
+        <v/>
+      </c>
+      <c r="D390" s="6" t="inlineStr">
         <is>
           <t>politics</t>
         </is>
       </c>
-      <c r="D390" s="6" t="inlineStr">
+      <c r="E390" s="6" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E390" s="6" t="inlineStr">
+      <c r="F390" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -10318,17 +11691,20 @@
           <t>Sa Facebook page ng Department of Transportation (DOTr), ipinaalam ng ahensiya sa publiko ang modus ng ilang kawatan na nagnanakaw ng ng materayales at bakal sa riles ng Philippine National Railways (PNR). Huli sa akto ng PNR Civil Security Office ang 11 salarin habang binabaklas ang ang mga track materials ng PNR. Base sa impormasyon na binahagi ng DOTr, nangyari ang insidente ng pagnenenok noong Enero 10, 2019 sa PNR Carmona SPur Line. Ayon sa PNR, hahabulin nila ang sinumang grupo o mga indibiduwal na mapapatunayang nagnanakaw ng gamit ng PNR. Inanyayahan din ng PNR ang mga kababayan natin na isumbong ang mga katulad na gawain sa pinakamalapit na himpilan ng kapulisan o ng PNR. Basahin ang reaksyon ng ilang kababayan natin sa ginawa ng mga kawatan. "good job po. putulan ng kamay ang mga magnanakaw na yan," - S. Nards "Sana po maipasa na frustrated murder ang kaso ng mga illegal na nagbabaklas ng riles ng tren. Higit sa abala, delikado ang derailment accidents at nakamamatay," R. Sui "Mga loko din hindi nila naisip pag gumanda na byahe ng tren dadami turista , bibili ng lupa sa lugar at magiging komersyal at trabaho," - E. Mendoza "tsk tsk... tindi nyo men... buwis ng mga manggagawang Pilipino yan tapos gaganyanin nyo. Mahiya kayo!," - J. LRSC "Good job sa paghuli ng mga yan! Mga anay ng lipunan.. inde magwork ng tama. Inaayos na nga riles pr mapaunlad ang bayan at mabigyan serbisyo nakakarami. Haaay naku...," -M. Lawas</t>
         </is>
       </c>
-      <c r="C391" s="6" t="inlineStr">
+      <c r="C391" s="7" t="n">
+        <v/>
+      </c>
+      <c r="D391" s="6" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D391" s="6" t="inlineStr">
+      <c r="E391" s="6" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E391" s="6" t="inlineStr">
+      <c r="F391" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -10343,17 +11719,20 @@
           <t>PARA SA MGA NAG HAHANAP NG TRABAHO SA MANILA. MAG INGAT NG HUSTO Coutesy : MBC / DZRH Sa FB post na ito ng DZRH, binigyan ng babala ang mga nag aaply ng trabaho sa maynila matapos mabiktima ang ilang mga aplicante na umanoy tutulongan makahanap ng trabaho, sila ay kadalasan naka pwesto sa mga Lrt station sa manila. i -Share ang post na ito para malaman ng iba. kung meron naman kayo nalalaman sa mga ganitong modus, paki comment sa baba para maisumbong natin sa mga autoridad.</t>
         </is>
       </c>
-      <c r="C392" s="6" t="inlineStr">
+      <c r="C392" s="7" t="n">
+        <v/>
+      </c>
+      <c r="D392" s="6" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D392" s="6" t="inlineStr">
+      <c r="E392" s="6" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E392" s="6" t="inlineStr">
+      <c r="F392" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -10368,17 +11747,20 @@
           <t>Sa isang Facebook post, nanawagan ang abogada at kapatid ni former Senator Miriam Defensor-Santiago na si Paula Defensor Knack kay Pangulong Rodrigo Duterte na makialam na sa kaso ng pagpaslang sa bodyguard/aide ni Attorney Glen Chong na si Richard Santillan. Ayon kay Knack, nagtamo umano ng 64 na sugat si Santillan dahil sa torture na ginawa ng mga pulis. Nananahimik din daw ang liderato ng Philippine National Police (dahil) magkaka-mistah ang mga ito. "How can we continue supporting a drug war if the police tortures a civilian bodyguard of a lawyer exposing electoral fraud against the supposed Vice-President ? Drug courier raw sya, pero tahimik ang PNP officials kung anong solid evidence nila na sya o ang amo nyang abogado ay sangkot sa droga maliban sa ginawa nilang encounter set-up!," sabi ni Knack Basahin ang komento ng mga kababayan natinsa naging panawagan ni Knack kay Pangulong Duterte kaugnay sa kaso ng pagpatay kay Santillan.</t>
         </is>
       </c>
-      <c r="C393" s="6" t="inlineStr">
+      <c r="C393" s="7" t="n">
+        <v/>
+      </c>
+      <c r="D393" s="6" t="inlineStr">
         <is>
           <t>crime</t>
         </is>
       </c>
-      <c r="D393" s="6" t="inlineStr">
+      <c r="E393" s="6" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E393" s="6" t="inlineStr">
+      <c r="F393" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -10393,17 +11775,20 @@
           <t>Usap-usapan ngayon sa social media ang umano'y panggagaya ng kinatawan ng Thailand na si Ingchanok Prasart sa ginanap na Miss Intercontinental pageant 2018 sa trademark ni Miss Universe 2018 Catriona Gray na "lava walk." Isang netizen sa Twitter na nagngangalang Marnie Raro ang nakapansin sa paraan ng paglalakad at pag-project ni Miss Thailand na parang kinokopya ang "lava walk" ni Catriona. Bukod kay Miss Thailand, napansin din ng mga netizens ang pagkopya umano sa "Mayon Volcano gown" ni Miss Vietnam. Aminado naman ang dalawa na labis nilang hinahangaan at inspirasyon nila si Miss Universe 2018 Catriona Gray. Halo-halo naman ang naging reaksyon ng mga netizens hinggil dito. "So now everyone looks like Catriona Gray. From hair to stance to gowns. The influence. Only legends do that." "Catriona Gray's walk can never be perfect without her walking it." "I think so? Even the hand gesture of Miss Thailand seems copied too. Catriona Gray is indeed a queen." "Yet they can't copy the original. Because there will be only one Lava Walk and Catriona Gray." "Kayo na 'yung may mga originality... hala gawa kayo sarili niyong pageant, ano ba naman yung hayaan niyo na lang sila hays....daming toxic." Isang patunay lamang ito na maraming mga aspiring beauty pageant candidates, hindi lamang sa Pilipinas kundi maging sa buong mundo, ang tumitingala at humahanga kay Catriona. Aminado naman dito ang marami sa mga kandidata ng naturang katatapos na pageant. Ang 47th edition ng Miss Intercontinental 2018 ay ginanap noong Enero 26, 2019, sa SM Mall of Asia Arena sa Pasay, Metro Manila, Philippines. Kinoronahan ni Miss Intercontinental 2017 Veronica Salas Vallejo ng Mexico ang kandidata ng Pilipinas na si Karen Juanita Gallman. Ito ang kauna-unahang pagkakataong naging host ang Pilipinas sa pageant na ito. Pinili ng Japan organizers ang Pilipinas na maging venue ng pageant dahil abala ang bansang Japan sa mga paghahanda para sa 2020 Summer Olympics. Narito ang buong Twitter post ng netizen:</t>
         </is>
       </c>
-      <c r="C394" s="6" t="inlineStr">
+      <c r="C394" s="7" t="n">
+        <v/>
+      </c>
+      <c r="D394" s="6" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D394" s="6" t="inlineStr">
+      <c r="E394" s="6" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E394" s="6" t="inlineStr">
+      <c r="F394" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -10418,17 +11803,20 @@
           <t>Sa pamamagitan ng isang mahabang post sa kanyang Facebook account ay ibinulalas ng batikang movie director na si Erik Matti ang kanyang sentimyento ukol sa kalagayan ng lokal na industriya ng pelikula. Nagpahayag si direk Matti ng pagkaalarma dahil sa sunud-sunod na pagsemplang ng mga Tagalog movies sa takilya. Aniya, mayroon dapat na gumawa ng mga hakbang hinggil sa nakababalisang sitwasyon ng local film industry. Dapat daw na manghimasok na ang pamahalaan. Ibinunyag niya na ang nakaraang tatlong taon ang pinaka-abalang panahon ng local film industry. Napakarami raw ng nagawang pelikula ngunit halos wala naman daw nakapanood ng mga iyon, kabilang na ang isa niyang pelikula na ginawa sa ilalim ng sarili niyang movie outfit na Reality Entertainment. Maging ang mga malalaking local movie studios ay hindi na kumikita. Ano raw ba ang nangyayari sa mga manonood? Nito lamang daw nakaraang tatlong linggo, ay ilang pelikulang Tagalog ang ipinalabas, kabilang na ang kanyang pelikula, ngunit sa kabila magandang istorya at mga publisidad sa media ay hindi kumita ang mga iyon. Maging ang pinakahuling Metro Manila Film Festival na ipanangangalandakan ng iba na isang malaking tagumpay ay hindi gaanong kumita kumpara sa mga nagdaang taon. Sa halip daw na harapin ang problema ng industriya sa lumiliit na bilang ng mga manonood ay pilit na itinatanggi pa. Tanong ni Matti, alin kaya ang dahilan ng paghina ng local film industry ... Ang mga online platforms ba, Hollywood, pangit na istorya, kakulangan ng suporta mula sa mga sinehan, trapik, libreng download ng pelikula, o kahirapan? Hindi niya raw alam. Subalit ang tangi raw niyang nalalaman ay hindi dapat sila magpatuloy na gumasta ng milyones sa paggawa ng mga pelikula na wala namang manonood. "This is alarming. Someone somewhere somehow should do something about this," ani Matti sa bahagi ng kanyang post.</t>
         </is>
       </c>
-      <c r="C395" s="6" t="inlineStr">
+      <c r="C395" s="7" t="n">
+        <v/>
+      </c>
+      <c r="D395" s="6" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D395" s="6" t="inlineStr">
+      <c r="E395" s="6" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E395" s="6" t="inlineStr">
+      <c r="F395" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -10443,17 +11831,20 @@
           <t>"May nakita ako doon na mga love team sa mga artista," Isiniwalat ni Philippine Drug Enforcement Agency (PDEA) Chief Aaron Aquino na may love team na kasama sa listahan ng mga artista na konektado sa kalakaran ng bawal na gamot. Nagbanta na rin si PDEA Chief sa mga artista na magsitino na. "Marami na rin kaming nahuling mga artista. And 'wag n'yo nang hintayin mahuli namin kayo. 'Wag n'yong sabihin nasa hotel kayo, nasa condominium, nasa exclusive subdivision, bibirahin at bibirahin namin kayo," banat ni Aquino. Inudyukan din ni PDEA Chief Aquino ang mga tv networks na magsagawa ng suprise at mandatory drug testing sa mga kani-kanilang mga artista. Dapat din daw na mayroong mga PDEA personnel na su-surpervise sa testings. "I just hope that na kung mangyari man, lahat sana ng celebrity present just to be, just to show to the public that they are clean," sabi ni Aquino. Magugunitang sinabi ni Aquino na may listahan sila ng mga artistang sangkot sa droga at karamihan sa mga ito ay sikat. Dismayado din siya na wholsome ang mga ginagampanang mga roles ng ilan sa mga artista sa kanilang listahan. "Nakalagay po dito, merong user ng ecstasy, cocaine, shabu, party drugs. Karamihan party drugs. Mga sikat itong mga 31 na ito, wala akong nakikitang mga laos dito," pagsisiwalat ni PDEA Chief. Ayon kay Aquino, tatapusin lang daw muna nila ang narco-politician at ilalabas na rin nila ang mga pangalan ng mga hukom, celebrities at mga taga-media na sangkot sa droga.</t>
         </is>
       </c>
-      <c r="C396" s="6" t="inlineStr">
+      <c r="C396" s="7" t="n">
+        <v/>
+      </c>
+      <c r="D396" s="6" t="inlineStr">
         <is>
           <t>celebrity / entertainment</t>
         </is>
       </c>
-      <c r="D396" s="6" t="inlineStr">
+      <c r="E396" s="6" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E396" s="6" t="inlineStr">
+      <c r="F396" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -10468,17 +11859,20 @@
           <t>Mula sa tatlong oras na biyahe sa bus o jeepney, magiging 40 minutes na lang ang commute mula Antipolo, Rizal patungong Recto, Maynila oras na matapos ang rail line extension. Hudyat ng pagsisimula ng final phase ng proyekto ang ceremonial track laying at installation ng electromechanical system (EMS), na isinagawa sa LRT Line 2 Emerald Station sa Marikina ngayong araw, ika-16 ng Abril 2019. Ang EMS ay binubuo ng signaling system, overhead catenary system, telecommunications system, power supply at distribution system, na gagamitin sa dalawang bagong istasyon ng LRT Line 2 - ang Emerald Station sa Marikina at Masinag Station sa Antipolo. Kasalukuyan nang nasa 60% completion rate ang kabuuan ng proyekto at inaasahang matatapos sa huling bahagi ng taong 2020 upang makapagbigay ng maayos at mas mabilis na biyahe sa mga commuter ng eastern Metro Manila. To give the Filipinos a comfortable life as President Rodrigo Duterte directed, we at the DOTr are working on ways to efficiently and effectively ferry our commuters. The LRT2 East Extension project ranks among such projects, for this shall ease the travel of our kababayans coming from Rizal to Manila. Once this is completed, travel time from Recto to Masinag will be reduced to 40 minutes compared to up to three hours travel via bus or jeepney," pahayag ni Transportation Secretary Arthur Tugade.</t>
         </is>
       </c>
-      <c r="C397" s="6" t="inlineStr">
+      <c r="C397" s="7" t="n">
+        <v/>
+      </c>
+      <c r="D397" s="6" t="inlineStr">
         <is>
           <t>economy / business</t>
         </is>
       </c>
-      <c r="D397" s="6" t="inlineStr">
+      <c r="E397" s="6" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E397" s="6" t="inlineStr">
+      <c r="F397" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -10493,17 +11887,20 @@
           <t>MAYNILA - Sumiklab ang isang sunog sa Pacific Coast Plaza, isang condominium sa lungsod ng Paranaque nitong Lunes. Itinaas na ng Bureau of Fire Protection sa general alarm ang sunog alas-12:37 ng tanghali. Pinakamataas na babala ang general alarm, ibig sabihin, lahat ng bombero mula sa ibang distrito ay kailangan rumesponde.</t>
         </is>
       </c>
-      <c r="C398" s="6" t="inlineStr">
+      <c r="C398" s="7" t="n">
+        <v/>
+      </c>
+      <c r="D398" s="6" t="inlineStr">
         <is>
           <t>disaster / environment</t>
         </is>
       </c>
-      <c r="D398" s="6" t="inlineStr">
+      <c r="E398" s="6" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E398" s="6" t="inlineStr">
+      <c r="F398" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -10518,17 +11915,20 @@
           <t>Tuluyan nang inalis ni Pangulong Rodrigo Duterte ang deployment ban sa mga manggagawang Pinoy sa Kuwait nitong Mayo 16. Ayon sa ulat ng GMA, inatasan ng Pangulo si Department of Labor and Employment (DOLE) Secretary Silvestre Bello III na alisin na ang ban sa lahat ng Pinoy workers sa Kuwait. Ang kautusan ay inilabas ni Duterte ilang araw makaraang lagdaan ng Pilipinas at Kuwait ang kasunduan na magbibigay ng dagdag na proteksyon sa mga OFW na nagtatrabaho sa naturang na bansa sa Gitnang Silangan. "Upon recommendation of Special Envoy to Kuwait Abdullah Mama-o, President Rodrigo Roa Duterte tonight instructed [Labor] Secretary Silvestre Bello to totally lift the ban on deployment of Filipino workers to Kuwait," ayon kay presidential spokesperson Harry Roque. Bago nito, Mayo 15 nang unang alisin ang deployment ban sa mga semi-skilled at skilled workers na patungong Kuwait. Ngunit dahil sa naturang direktiba ng Pangulo, maaari nang magpadala ng mga household service worker o domestic helpers sa Kuwait. Magugunitang ipinatupad ang deployment ban sa Kuwait kasunod ng pagkakadiskubre sa labi ng OFW na si Joanna Demafelis sa loob ng freezer. Tinatayang nasa 260,000 mga Pinoy ang naninirahan at nagtatrabaho sa Kuwait at karamiha'y mga household service workers.</t>
         </is>
       </c>
-      <c r="C399" s="6" t="inlineStr">
+      <c r="C399" s="7" t="n">
+        <v/>
+      </c>
+      <c r="D399" s="6" t="inlineStr">
         <is>
           <t>international news</t>
         </is>
       </c>
-      <c r="D399" s="6" t="inlineStr">
+      <c r="E399" s="6" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E399" s="6" t="inlineStr">
+      <c r="F399" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -10543,17 +11943,20 @@
           <t>Humanga ang netizens sa katapatan na ipinakita ng dalawang pulis na nagsauli ng malaking halaga ng pera na kanilang natagpuan sa gilid ng kalsada. Ayon kay Avon Docog, asawa ni Police Corporal Brian A. Docog, masaya siya sa pagiging tapat ng kanyang asawa at kasamahan nito na si Police Auxiliary Eulalio Bucod Jr., pawang naka-assign sa Sta. Ana PNP matapos makapulot ng isang bag na naglalaman ng dokumento, at pera na nagkakahalaga ng higit P100,000. i can't contain my happiness seeing my husband so eager to give these back to the owner... on his way to our house with his police auxiliary, it just so happened nga naa silay nakita nga bag kilid sa kalsada along Marfori,. iyahang gipunit &amp; pag tan-aw niya kay money ang sulod..pag abot iyaha gi estorya sa akoa ang nahitabo,&amp; akoa gi tan-aw tanan sulod ofcors pra mahibal-an kinsay tag iya &amp; nakakita kog resibo sa palawan nga naay contact # niya, &amp; wla mi gikuha bisag piso ha... so mao to, akng gipatawagan sa akng bana &amp; nag kontakay na cla, the owner cried for joy... nahulog rjd daw iyang sling bag sa ilang car... it's a very huge amount &amp; i know dili lalim mangitag kwarta &amp; dili lalim mawalaan, i've been there, nawalaan pd kog mas labaw pas kwarta(akng phone with 20K photos) wala jd na uli, all the memoirs was there, pero wala koi gi blame bisag kinsa, i just leave it to our big God all in all, i'm just super proud of u PCpl Nairb Docz of PS1 (Sta.Ana, Davao City) i'm beyond happy, a big salute to u my honest policeman! Hindi naman napigilan ng may-ari ng bag na maiyak at magpasalamat nang maibalik sa kanyang ang pera at mga dokumentong nawawala. Dahil dito, maraming netizens ang namangha sa kabutihang pinamalas ng dalawang pulis dahil hindi umano sila nagpasilaw sa malaking halaga ng pera.</t>
         </is>
       </c>
-      <c r="C400" s="6" t="inlineStr">
+      <c r="C400" s="7" t="n">
+        <v/>
+      </c>
+      <c r="D400" s="6" t="inlineStr">
         <is>
           <t>lifestyle / human interest</t>
         </is>
       </c>
-      <c r="D400" s="6" t="inlineStr">
+      <c r="E400" s="6" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E400" s="6" t="inlineStr">
+      <c r="F400" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
@@ -10568,17 +11971,20 @@
           <t>Sa isang screenshot na ibinahagi ni Davao City information officer Jefry Tupas sa kanyang Facebook account, mababasa ang panlalait ni Jboy Gonzales SJ kay Presidential daughter at Davao City Mayor Sara Duterte. Ito ay kaugnay sa isyu tungkol sa pagiging tapat ng mga naninilbihan sa gobyerno. Ayon kay Tupas, ang naturang pari daw ay taga-Ateneo de Davao Highschool. "Father JBoy Gonzales is with Ateneo de Davao Highschool. Here, he badmouths the Mayor of Davao City over the issue of honesty while saying 'hirap magturo ng values kasi...'," resbak ni Tupas. Binanatan din ni Tupas sa sarkastikong pamamaraan si Father Gonzales. "Ang linis ni father. Hindi sya hypocrite. Naiintindihan din nya ang context ng sinasabi ni Mayor Sara tungkol sa honesty -- ang talino. Kung ako may anak, kampante ako na magiging matuwid siya kung tuturuan siya ni Father Jboy. Magsimba tayo. Magdasal. Tularan natin si Father.," buwelta pa ni Tupas. Hinapyawan din ni Tupas ang pagiging tapat ni Father Gonzales sa kasarian nito. "Basta ako, bakla ako. I don't know lang ha, dahil honest na honest naman si Father Jboy, kung siya ba isang Jboy o isang Jgherl," dagdag pa ni Tupas. Ano ang masasabi niyo sa bunganga ni Father?</t>
         </is>
       </c>
-      <c r="C401" s="6" t="inlineStr">
+      <c r="C401" s="7" t="n">
+        <v/>
+      </c>
+      <c r="D401" s="6" t="inlineStr">
         <is>
           <t>religion</t>
         </is>
       </c>
-      <c r="D401" s="6" t="inlineStr">
+      <c r="E401" s="6" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E401" s="6" t="inlineStr">
+      <c r="F401" s="6" t="inlineStr">
         <is>
           <t>test</t>
         </is>
